--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Website Signals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Website Signals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$341</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J229"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,7 +848,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>600</v>
       </c>
@@ -1357,7 +1356,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>1090</v>
       </c>
@@ -2059,7 +2057,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>225</v>
       </c>
@@ -2103,7 +2100,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>575</v>
       </c>
@@ -2153,7 +2149,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>600</v>
       </c>
@@ -2491,7 +2486,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
         <v>2585</v>
       </c>
@@ -2904,7 +2898,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
         <v>1560</v>
       </c>
@@ -3519,7 +3512,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>33715</v>
       </c>
@@ -3560,7 +3552,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>33705</v>
       </c>
@@ -3601,7 +3592,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
         <v>33700</v>
       </c>
@@ -3642,7 +3632,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>24000</v>
       </c>
@@ -3683,7 +3672,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
         <v>33725</v>
       </c>
@@ -3724,7 +3712,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
         <v>2150</v>
       </c>
@@ -5003,7 +4990,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
         <v>204</v>
       </c>
@@ -5381,7 +5367,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
         <v>204</v>
       </c>
@@ -5703,7 +5688,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
         <v>470</v>
       </c>
@@ -5793,7 +5777,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
         <v>204</v>
       </c>
@@ -5839,7 +5822,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
         <v>220</v>
       </c>
@@ -5934,7 +5916,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
         <v>402</v>
       </c>
@@ -6205,7 +6186,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
         <v>475</v>
       </c>
@@ -6381,7 +6361,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
         <v>204</v>
       </c>
@@ -6560,7 +6539,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
         <v>445</v>
       </c>
@@ -6701,7 +6679,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
         <v>5200</v>
       </c>
@@ -6742,7 +6719,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
         <v>5200</v>
       </c>
@@ -6880,7 +6856,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
         <v>220</v>
       </c>
@@ -6929,7 +6904,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
         <v>220</v>
       </c>
@@ -7029,7 +7003,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
         <v>220</v>
       </c>
@@ -7078,7 +7051,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
         <v>235</v>
       </c>
@@ -11006,8 +10978,4794 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:52:00</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E230" t="n">
+        <v>60</v>
+      </c>
+      <c r="F230" t="n">
+        <v>37</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय Sagility Ltd BUY PRICE 45.34 TARGET 60 STOP LOSS 37 विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:52:00</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>SAGILITY</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E231" t="n">
+        <v>60</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय Sagility Ltd PRICE 45.34 TARGET 60 विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:50:00</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>RKFORGE</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>732.15</v>
+      </c>
+      <c r="E232" t="n">
+        <v>765</v>
+      </c>
+      <c r="F232" t="n">
+        <v>715</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब RAMKRISHNA FORG @ 731 खरीदें STOP LOSS 715 TARGET 765 Ramkrishna Forging 735.00 2.56% विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:50:00</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>RKFORGE</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>731.85</v>
+      </c>
+      <c r="E233" t="n">
+        <v>765</v>
+      </c>
+      <c r="F233" t="n">
+        <v>715</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब RAMKRISHNA FORG @ 731 खरीदें STOP LOSS 715 TARGET 765 Ramkrishna Forging 732.50 ▲ 15.85 विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:50:00</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>RKFORGE</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>731.95</v>
+      </c>
+      <c r="E234" t="n">
+        <v>765</v>
+      </c>
+      <c r="F234" t="n">
+        <v>715</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>RAMKRISHNA FORG @ 731 खरीदें STOP LOSS 715 TARGET 765 Ramkrishna Forg 733.00 ▲ 2.28%</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:50:00</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>RKFORGE</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>731.95</v>
+      </c>
+      <c r="E235" t="n">
+        <v>765</v>
+      </c>
+      <c r="F235" t="n">
+        <v>715</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब RAMKRISHNA FORG @ 731 खरीदें STOP LOSS 715 TARGET 765 Ramkrishna Forg 734.00 2.42% विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:50:00</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>RKFORGE</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>731.95</v>
+      </c>
+      <c r="E236" t="n">
+        <v>765</v>
+      </c>
+      <c r="F236" t="n">
+        <v>715</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब RAMKRISHNA FORG @ 731 खरीदें STOP LOSS 715 TARGET 765 विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:48:00</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>3398.3</v>
+      </c>
+      <c r="E237" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय BSE Ltd. Fut खरीदें PRICE 3400.90 TARGET 3460/3480 STOP LOSS 3330</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:47:20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="n">
+        <v>3314.6</v>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>BSE Ltd. 3372.60 VALUE PICK 58.00 14/11/2020 RECO PRICE ADJ &amp; BONUS SHARE + ₹67 DIV RETURN TILL NOW 3314.60 5714.83%</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:48:00</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>3398.3</v>
+      </c>
+      <c r="E239" t="n">
+        <v>3460</v>
+      </c>
+      <c r="F239" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>BTST CALL BSE Ltd. Fut खरीदें PRICE 3398.70 TARGET 3460/3480 STOP LOSS 3330</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:48:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>3398.3</v>
+      </c>
+      <c r="E240" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F240" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>BTST CALL BSE Ltd. Fut खरीदें PRICE 3398.70 TARGET 3460/3480 STOP LOSS 3330</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:48:00</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>3398.3</v>
+      </c>
+      <c r="E241" t="n">
+        <v>3460</v>
+      </c>
+      <c r="F241" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>BTST CALL
+BSE Ltd. Fut
+खरीदें
+PRICE ▶ 3397.00
+TARGET ▶ 3460/3480
+STOP LOSS ▶ 3330</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:48:00</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>3398.3</v>
+      </c>
+      <c r="E242" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F242" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>BTST CALL
+BSE Ltd. Fut
+खरीदें
+PRICE ▶ 3397.00
+TARGET ▶ 3460/3480
+STOP LOSS ▶ 3330</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E243" t="n">
+        <v>12110</v>
+      </c>
+      <c r="F243" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उस्तेकर की राय
+Bajaj Auto Fut
+खरीदें
+PRICE → 11969.00
+TARGET → 12110/12300
+STOP LOSS → 11890</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E244" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F244" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उस्तेकर की राय
+Bajaj Auto Fut
+खरीदें
+PRICE → 11969.00
+TARGET → 12110/12300
+STOP LOSS → 11890</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E245" t="n">
+        <v>12110</v>
+      </c>
+      <c r="F245" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>BTST CALL Bajaj Auto Fut खरीदें PRICE 11976.00 TARGET 12110/12300 STOP LOSS 11890</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E246" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F246" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>BTST CALL Bajaj Auto Fut खरीदें PRICE 11976.00 TARGET 12110/12300 STOP LOSS 11890</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E247" t="n">
+        <v>12110</v>
+      </c>
+      <c r="F247" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>चेतावनी सेबी की रिपोर्ट के अनुसार इक्विटी वायदा कारोबार के सौदे करने वाले 10 में से 9 ट्रेडर्स को पाटा होता है. इक्विटी F&amp;O के सौदे भारी जोखिम वाले होते हैं, रिस्क समझकर ही सौदे करें | Bajaj Auto Fut खरीदें PRICE 11980.00 TARGET 12110/12300 STOP LOSS 11890</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:46:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>11986</v>
+      </c>
+      <c r="E248" t="n">
+        <v>12300</v>
+      </c>
+      <c r="F248" t="n">
+        <v>11890</v>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>सांचितनंद उत्तकर की राय Bajaj Auto Fut खरीदें PRICE 11980.00 TARGET 12110/12300 STOP LOSS 11890</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:41:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>9220</v>
+      </c>
+      <c r="E249" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F249" t="n">
+        <v>9160</v>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>BTST CALL Divi's Lab Fut खरीदें PRICE 9224.50 TARGET 9350/9400 STOP LOSS 9160</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:41:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>9220</v>
+      </c>
+      <c r="E250" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F250" t="n">
+        <v>9160</v>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>BTST CALL Divi's Lab Fut खरीदें PRICE 9224.50 TARGET 9350/9400 STOP LOSS 9160</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:41:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>9220</v>
+      </c>
+      <c r="E251" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F251" t="n">
+        <v>9160</v>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय
+Divi's Lab Fut
+खरीदें
+PRICE → 9226.00
+TARGET → 9350/9400
+STOP LOSS → 9160</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:41:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>9220</v>
+      </c>
+      <c r="E252" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F252" t="n">
+        <v>9160</v>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय
+Divi's Lab Fut
+खरीदें
+PRICE → 9226.00
+TARGET → 9350/9400
+STOP LOSS → 9160</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:40:00</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>1365.2</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1352</v>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शोयर
+Info Edge
+खरीदें
+PRICE ▶ 1368.80
+TARGET ▶ 1395/1410
+STOP LOSS ▶ 1352</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:40:00</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>1365.2</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1352</v>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Info Edge
+खरीदें
+PRICE → 1368.20
+TARGET → 1395/1410
+STOP LOSS → 1352</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:39:00</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>1968.4</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Coforge Ltd खरीदें PRICE 1969.00 TARGET 1995/2000 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:39:00</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>1968.4</v>
+      </c>
+      <c r="E256" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>BTST CALL Coforge Ltd खरीदें PRICE 1965.00 TARGET 1995/2000 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:39:00</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1968.4</v>
+      </c>
+      <c r="E257" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>BTST CALL Coforge Ltd खरीदें PRICE 1964.90 TARGET 1995/2000 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:39:00</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1968.4</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1995</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>BTST CALL Coforge Ltd खरीदें PRICE 1963.50 TARGET 1995/2000 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:39:00</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>1968.4</v>
+      </c>
+      <c r="E259" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Coforge Ltd खरीदें PRICE 1963.50 TARGET 1995/2000 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:38:00</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TCS29SEP26</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>2345.4</v>
+      </c>
+      <c r="E260" t="n">
+        <v>2466</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>BTST CALL TCS Fut खरीदें PRICE 2346.40 TARGET 2400/2466 STOP LOSS 2310</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:38:00</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TCS29SEP26</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>2345.4</v>
+      </c>
+      <c r="E261" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F261" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>BTST CALL
+TCS Fut
+खरीदें
+PRICE 2346.00
+TARGET 2400/2466
+STOP LOSS 2310</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:38:00</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TCS29SEP26</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>2345.4</v>
+      </c>
+      <c r="E262" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F262" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय
+TCS Fut
+खरीदें
+PRICE ▶ 2345.20
+TARGET ▶ 2400/2466
+STOP LOSS ▶ 2310</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:38:00</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TCS29SEP26</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>2345.4</v>
+      </c>
+      <c r="E263" t="n">
+        <v>2466</v>
+      </c>
+      <c r="F263" t="n">
+        <v>2310</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय
+TCS Fut
+खरीदें
+PRICE ▶ 2345.20
+TARGET ▶ 2400/2466
+STOP LOSS ▶ 2310</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:36:00</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>KIMS</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>781.2</v>
+      </c>
+      <c r="E264" t="n">
+        <v>800</v>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>SUPER SID KIMS खरीदें PRICE 780.20 TARGET 800/850 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:36:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>KIMS</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>781.2</v>
+      </c>
+      <c r="E265" t="n">
+        <v>850</v>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>KIMS खरीदें PRICE 780.20 TARGET 800/850 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:35:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>FRACTAL</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>847.7</v>
+      </c>
+      <c r="E266" t="n">
+        <v>950</v>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+FRACTAL ANALYTICS @ 838
+खरीदें
+STOP LOSS --
+TARGET 950/990/1150
+Fractal Analytics 847.90 ▲ 0.91%</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:35:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>FRACTAL</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>847.7</v>
+      </c>
+      <c r="E267" t="n">
+        <v>990</v>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+FRACTAL ANALYTICS @ 838
+खरीदें
+STOP LOSS --
+TARGET 950/990/1150
+Fractal Analytics 847.90 ▲ 0.91%</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:35:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>FRACTAL</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>847.7</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+FRACTAL ANALYTICS @ 838
+खरीदें
+STOP LOSS --
+TARGET 950/990/1150
+Fractal Analytics 847.90 ▲ 0.91%</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:28:02</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="n">
+        <v>705</v>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Sterlite Tech 705.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 442.00 168.06%</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:54</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="n">
+        <v>710</v>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Sterlite Tech 710.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 447.00 169.96%</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:46</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="n">
+        <v>709</v>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Sterlite Tech 709.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 446.00 169.58%</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>HYUNDAI29SEP26</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="E272" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F272" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>BTST CALL Hyundai Motor Fut खरीदें PRICE 2245.00 TARGET 2320/2340 STOP LOSS 2235</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>HYUNDAI29SEP26</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="E273" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F273" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>BTST CALL Hyundai Motor Fut खरीदें PRICE 2245.00 TARGET 2320/2340 STOP LOSS 2235</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HYUNDAI29SEP26</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="E274" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F274" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Hyundai Motor Fut खरीदें PRICE 2242.50 TARGET 2320/2340 STOP LOSS 2235</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HYUNDAI29SEP26</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>2251.7</v>
+      </c>
+      <c r="E275" t="n">
+        <v>2340</v>
+      </c>
+      <c r="F275" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Hyundai Motor Fut खरीदें PRICE 2242.50 TARGET 2320/2340 STOP LOSS 2235</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:26:00</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>KPITTECH29SEP26</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>602.5</v>
+      </c>
+      <c r="E276" t="n">
+        <v>622</v>
+      </c>
+      <c r="F276" t="n">
+        <v>592</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>सचितानंद उतेकर की राय KPIT Tech Fut खरीदें PRICE 601.20 TARGET 622/640 STOP LOSS 592</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:26:00</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>KPITTECH29SEP26</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>602.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>640</v>
+      </c>
+      <c r="F277" t="n">
+        <v>592</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>सचितानंद उतेकर की राय KPIT Tech Fut खरीदें PRICE 601.20 TARGET 622/640 STOP LOSS 592</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:25:00</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>PREMIERENE29SEP26</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>973</v>
+      </c>
+      <c r="E278" t="n">
+        <v>960</v>
+      </c>
+      <c r="F278" t="n">
+        <v>995</v>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 976.80 TARGET 960/950 STOP LOSS 995</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:59</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>PREMIER29SEP26</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="n">
+        <v>960</v>
+      </c>
+      <c r="F279" t="n">
+        <v>995</v>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Premier Energies Fut
+बेचें
+PRICE ▸ 977.00
+TARGET ▸ 960/950
+STOP LOSS ▸ 995</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:59</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PREMIER29SEP26</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="n">
+        <v>950</v>
+      </c>
+      <c r="F280" t="n">
+        <v>995</v>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Premier Energies Fut
+बेचें
+PRICE ▸ 977.00
+TARGET ▸ 960/950
+STOP LOSS ▸ 995</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:24:00</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>PREMIERENE29SEP26</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>973.7</v>
+      </c>
+      <c r="E281" t="n">
+        <v>960</v>
+      </c>
+      <c r="F281" t="n">
+        <v>995</v>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 977.00 TARGET 960/950 STOP LOSS 995</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:24:00</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>PREMIERENE29SEP26</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>973.7</v>
+      </c>
+      <c r="E282" t="n">
+        <v>950</v>
+      </c>
+      <c r="F282" t="n">
+        <v>995</v>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 977.00 TARGET 960/950 STOP LOSS 995</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:55</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PREMIERENE29SEP26</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="n">
+        <v>960</v>
+      </c>
+      <c r="F283" t="n">
+        <v>950</v>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>चेतावनी सेबी की रिपोर्ट के अनुसार इक्विटी वायदा कारोबार के सौदे करने वाले 10 में से 9 ट्रेडर्स को घाटा होता है. इक्विटी F&amp;O के सौदे भारी जोखिम वाले होते हैं, रिस्क समझकर ही सौदे करें Premier Energies F'ut PRICE 977.7C TARGET 960/950</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E284" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5787.00 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E285" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5782.50 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E286" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5784.00 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E287" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5784.00 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E288" t="n">
+        <v>5850</v>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5783.50 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:23:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>5789</v>
+      </c>
+      <c r="E289" t="n">
+        <v>6900</v>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>SUPER SID Persistent Sys खरीदें PRICE 5783.50 TARGET 5850/6900 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1656</v>
+      </c>
+      <c r="E290" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+PIDILITE IND
+1640.00 -0.97%
+HOLD
+लक्ष्य ₹1730</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1324.9</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>GE Shipping ₹1530/Sh के भाव पर ₹900 Cr के बायबैक को मंजूरी GE Shipping 1329.00 ▲ 11.80</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>633</v>
+      </c>
+      <c r="E292" t="n">
+        <v>655</v>
+      </c>
+      <c r="F292" t="n">
+        <v>622</v>
+      </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>MY CHOICE KALYAN JEWELLERS B 655 622</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>7750.5</v>
+      </c>
+      <c r="E293" t="n">
+        <v>8037</v>
+      </c>
+      <c r="F293" t="n">
+        <v>7547</v>
+      </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>MY CHOICE AMBER ENTERPRISES B 8037 7547</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>822.75</v>
+      </c>
+      <c r="E294" t="n">
+        <v>840</v>
+      </c>
+      <c r="F294" t="n">
+        <v>803</v>
+      </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>MY CHOICE SONA BLW PRECISION B 840 803</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1156.1</v>
+      </c>
+      <c r="E295" t="n">
+        <v>1252</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1096</v>
+      </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>INVESTMENT GODREJ INDUSTRIES B 1252 1096</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>2553.3</v>
+      </c>
+      <c r="E296" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F296" t="n">
+        <v>2524</v>
+      </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>CASH CAPLIN POINT B 2600 2524</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>20728</v>
+      </c>
+      <c r="E297" t="n">
+        <v>21240</v>
+      </c>
+      <c r="F297" t="n">
+        <v>20330</v>
+      </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>FUTURE SOLAR IND FUT B 21240 20330</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>2048.1</v>
+      </c>
+      <c r="E298" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1978</v>
+      </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>FUNDA BHARAT FORGE B 2180 1978</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="E299" t="n">
+        <v>93</v>
+      </c>
+      <c r="F299" t="n">
+        <v>86</v>
+      </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>MY CHOICE NBCC B 93 86</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>5155</v>
+      </c>
+      <c r="E300" t="n">
+        <v>5190</v>
+      </c>
+      <c r="F300" t="n">
+        <v>5092</v>
+      </c>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAN B 5190 5092</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1190</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1215</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1166</v>
+      </c>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>MY CHOICE ZYDUS LIFE B 1215 1166</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="E302" t="n">
+        <v>375</v>
+      </c>
+      <c r="F302" t="n">
+        <v>250</v>
+      </c>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>INVESTMENT SCI B 375 250</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F303" t="n">
+        <v>12</v>
+      </c>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>MY CHOICE ZYDUS LIFE B 12</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>5155</v>
+      </c>
+      <c r="E304" t="n">
+        <v>5190</v>
+      </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAN B 5190</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F305" t="n">
+        <v>1233</v>
+      </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT LODHA DEVELOPERS B 1280 1233</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="E306" t="n">
+        <v>93</v>
+      </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>MY CHOICE NBCC B 93</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>LORDSMARK</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E307" t="n">
+        <v>495</v>
+      </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>RK B 535 495</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>NYKAA29SEP26</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>341</v>
+      </c>
+      <c r="E308" t="n">
+        <v>347</v>
+      </c>
+      <c r="F308" t="n">
+        <v>335</v>
+      </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>FUTURE NYKAA FUT B 347 335</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>424.6</v>
+      </c>
+      <c r="E309" t="n">
+        <v>429</v>
+      </c>
+      <c r="F309" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>FUNDA KOTAK BANK B 429 420.5</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>9099.5</v>
+      </c>
+      <c r="E310" t="n">
+        <v>9150</v>
+      </c>
+      <c r="F310" t="n">
+        <v>9001</v>
+      </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>TECHNO DIVI'S LAB B 9150 9001</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="E311" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT HSBC BUY TARGET ₹1000</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1046</v>
+      </c>
+      <c r="E312" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>FII INVEST1 ENT F 20... जेफरीज SBI 1042.90 9.10 TARGET ₹1320</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>633</v>
+      </c>
+      <c r="E313" t="n">
+        <v>700</v>
+      </c>
+      <c r="F313" t="n">
+        <v>595</v>
+      </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Kalyan Jewellers BUY PRICE 629.30 TARGET 700/720 STOP LOSS 595</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>633</v>
+      </c>
+      <c r="E314" t="n">
+        <v>720</v>
+      </c>
+      <c r="F314" t="n">
+        <v>595</v>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Kalyan Jewellers BUY PRICE 629.30 TARGET 700/720 STOP LOSS 595</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>7750.5</v>
+      </c>
+      <c r="E315" t="n">
+        <v>7900</v>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेठानी की राय Amber Ent BUY PRICE 7701.00 TARGET 7900/8450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>7750.5</v>
+      </c>
+      <c r="E316" t="n">
+        <v>8450</v>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेठानी की राय
+Amber Ent
+PRICE ▶ 7701.00
+TARGET ▶ 7900/8450</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>710.85</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+HDFC BANK
+711.00
+OUTPERFORM
+लक्ष्य ₹1150</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E318" t="n">
+        <v>718</v>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS SBI FUNDS MGMT 562.55 -0.90 BUY लक्ष्य ₹718</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>605.25</v>
+      </c>
+      <c r="E319" t="n">
+        <v>840</v>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय Anant Raj Ltd PRICE 605.25 TARGET 840 STOP LOSS BROKERAGE CALLS BUY लक्ष्य ₹710</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ANANTRAJ</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>605.25</v>
+      </c>
+      <c r="E320" t="n">
+        <v>840</v>
+      </c>
+      <c r="F320" t="n">
+        <v>544</v>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय
+Anant Raj Ltd
+BUY
+PRICE 605.25
+TARGET 840
+STOP LOSS 544</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>1656</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Pidilite Ind 1656.00 HOLD लक्ष्य ₹1730</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>822.75</v>
+      </c>
+      <c r="E322" t="n">
+        <v>855</v>
+      </c>
+      <c r="F322" t="n">
+        <v>794</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Sona BLW Precision BUY PRICE 819.00 TARGET 850/855 STOP LOSS 794</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>822.75</v>
+      </c>
+      <c r="E323" t="n">
+        <v>855</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Sona BLW Precision PRICE 819.00 TARGET 850/855</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E324" t="n">
+        <v>710</v>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS SBI FUNDS MGMT 562.55 -0.90 BUY लक्ष्य ₹710</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SONACOMS29SEP26</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="E325" t="n">
+        <v>830</v>
+      </c>
+      <c r="F325" t="n">
+        <v>804</v>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SONACOMS29SEP26</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="E326" t="n">
+        <v>838</v>
+      </c>
+      <c r="F326" t="n">
+        <v>804</v>
+      </c>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SONACOMS29SEP26</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>822.9</v>
+      </c>
+      <c r="E327" t="n">
+        <v>845</v>
+      </c>
+      <c r="F327" t="n">
+        <v>804</v>
+      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>ASHOKLEY29SEP26</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="E328" t="n">
+        <v>180</v>
+      </c>
+      <c r="F328" t="n">
+        <v>175</v>
+      </c>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>ASHOKLEY29SEP26</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="E329" t="n">
+        <v>182</v>
+      </c>
+      <c r="F329" t="n">
+        <v>175</v>
+      </c>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ASHOKLEY29SEP26</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="E330" t="n">
+        <v>184</v>
+      </c>
+      <c r="F330" t="n">
+        <v>175</v>
+      </c>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>11870</v>
+      </c>
+      <c r="E331" t="n">
+        <v>11900</v>
+      </c>
+      <c r="F331" t="n">
+        <v>11650</v>
+      </c>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>11870</v>
+      </c>
+      <c r="E332" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F332" t="n">
+        <v>11650</v>
+      </c>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>11870</v>
+      </c>
+      <c r="E333" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>11650</v>
+      </c>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>DELHIVERY29SEP26</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="E334" t="n">
+        <v>457</v>
+      </c>
+      <c r="F334" t="n">
+        <v>472</v>
+      </c>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>TECHNO PICK
+Delhivery Ltd Fut
+बेचें
+PRICE → 466.90
+TARGET → 457
+STOP LOSS → 472</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>TATAPOWER35029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="E335" t="n">
+        <v>14</v>
+      </c>
+      <c r="F335" t="n">
+        <v>6</v>
+      </c>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>BEST ऑप्शन Tata power 350 की कॉल @ 9 खरीदें STOP LOSS 6 TARGET 14 Tata Power 352.00</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>NYKAA29SEP26</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>341</v>
+      </c>
+      <c r="E336" t="n">
+        <v>347</v>
+      </c>
+      <c r="F336" t="n">
+        <v>335</v>
+      </c>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+Nykaa Fut
+खरीदें
+PRICE ▶ 340.70
+TARGET ▶ 347
+STOP LOSS ▶ 335</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>20728</v>
+      </c>
+      <c r="E337" t="n">
+        <v>21240</v>
+      </c>
+      <c r="F337" t="n">
+        <v>20330</v>
+      </c>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Solar Ind Fut
+खरीदें
+PRICE → 20608.00
+TARGET → 21240
+STOP LOSS → 20330</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>2553.3</v>
+      </c>
+      <c r="E338" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F338" t="n">
+        <v>2524</v>
+      </c>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+Caplin Point
+खरीदें
+PRICE → 2540.70
+TARGET → 2600
+STOP LOSS → 2524</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>178</v>
+      </c>
+      <c r="E339" t="n">
+        <v>185</v>
+      </c>
+      <c r="F339" t="n">
+        <v>173</v>
+      </c>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Ashok Leyland खरीदें PRICE 177.4 TARGET 185 STOP LOSS 173 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="E340" t="n">
+        <v>395</v>
+      </c>
+      <c r="F340" t="n">
+        <v>380</v>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>RBL Bank खरीदें PRICE 385.4 TARGET 395/400 STOP LOSS 380 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:15:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="E341" t="n">
+        <v>400</v>
+      </c>
+      <c r="F341" t="n">
+        <v>380</v>
+      </c>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>RBL Bank खरीदें PRICE 385.4 TARGET 395/400 STOP LOSS 380 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J229"/>
+  <autoFilter ref="A1:J341"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11960,7 +16718,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>600</v>
       </c>
@@ -12655,7 +17412,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>445</v>
       </c>
@@ -12699,7 +17455,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>235</v>
       </c>
@@ -12886,7 +17641,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>33725</v>
       </c>
@@ -13426,7 +18180,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
         <v>475</v>
       </c>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$530</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J341"/>
+  <dimension ref="A1:J530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -11322,7 +11322,6 @@
       <c r="F237" t="n">
         <v>3330</v>
       </c>
-      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय BSE Ltd. Fut खरीदें PRICE 3400.90 TARGET 3460/3480 STOP LOSS 3330</t>
@@ -11355,11 +11354,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
       <c r="E238" t="n">
         <v>3314.6</v>
       </c>
-      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
           <t>BSE Ltd. 3372.60 VALUE PICK 58.00 14/11/2020 RECO PRICE ADJ &amp; BONUS SHARE + ₹67 DIV RETURN TILL NOW 3314.60 5714.83%</t>
@@ -11401,7 +11398,6 @@
       <c r="F239" t="n">
         <v>3330</v>
       </c>
-      <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
           <t>BTST CALL BSE Ltd. Fut खरीदें PRICE 3398.70 TARGET 3460/3480 STOP LOSS 3330</t>
@@ -11443,7 +11439,6 @@
       <c r="F240" t="n">
         <v>3330</v>
       </c>
-      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
           <t>BTST CALL BSE Ltd. Fut खरीदें PRICE 3398.70 TARGET 3460/3480 STOP LOSS 3330</t>
@@ -11485,7 +11480,6 @@
       <c r="F241" t="n">
         <v>3330</v>
       </c>
-      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
           <t>BTST CALL
@@ -11532,7 +11526,6 @@
       <c r="F242" t="n">
         <v>3330</v>
       </c>
-      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
           <t>BTST CALL
@@ -11579,7 +11572,6 @@
       <c r="F243" t="n">
         <v>11890</v>
       </c>
-      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
           <t>सच्चिदानंद उस्तेकर की राय
@@ -11626,7 +11618,6 @@
       <c r="F244" t="n">
         <v>11890</v>
       </c>
-      <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
           <t>सच्चिदानंद उस्तेकर की राय
@@ -11673,7 +11664,6 @@
       <c r="F245" t="n">
         <v>11890</v>
       </c>
-      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
           <t>BTST CALL Bajaj Auto Fut खरीदें PRICE 11976.00 TARGET 12110/12300 STOP LOSS 11890</t>
@@ -11715,7 +11705,6 @@
       <c r="F246" t="n">
         <v>11890</v>
       </c>
-      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
           <t>BTST CALL Bajaj Auto Fut खरीदें PRICE 11976.00 TARGET 12110/12300 STOP LOSS 11890</t>
@@ -11803,7 +11792,6 @@
       <c r="F248" t="n">
         <v>11890</v>
       </c>
-      <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
           <t>सांचितनंद उत्तकर की राय Bajaj Auto Fut खरीदें PRICE 11980.00 TARGET 12110/12300 STOP LOSS 11890</t>
@@ -11845,7 +11833,6 @@
       <c r="F249" t="n">
         <v>9160</v>
       </c>
-      <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
           <t>BTST CALL Divi's Lab Fut खरीदें PRICE 9224.50 TARGET 9350/9400 STOP LOSS 9160</t>
@@ -11887,7 +11874,6 @@
       <c r="F250" t="n">
         <v>9160</v>
       </c>
-      <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
           <t>BTST CALL Divi's Lab Fut खरीदें PRICE 9224.50 TARGET 9350/9400 STOP LOSS 9160</t>
@@ -11929,7 +11915,6 @@
       <c r="F251" t="n">
         <v>9160</v>
       </c>
-      <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय
@@ -11976,7 +11961,6 @@
       <c r="F252" t="n">
         <v>9160</v>
       </c>
-      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय
@@ -12023,7 +12007,6 @@
       <c r="F253" t="n">
         <v>1352</v>
       </c>
-      <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शोयर
@@ -12070,7 +12053,6 @@
       <c r="F254" t="n">
         <v>1352</v>
       </c>
-      <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -12163,7 +12145,6 @@
       <c r="F256" t="n">
         <v>1930</v>
       </c>
-      <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr">
         <is>
           <t>BTST CALL Coforge Ltd खरीदें PRICE 1965.00 TARGET 1995/2000 STOP LOSS 1930</t>
@@ -12205,7 +12186,6 @@
       <c r="F257" t="n">
         <v>1930</v>
       </c>
-      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr">
         <is>
           <t>BTST CALL Coforge Ltd खरीदें PRICE 1964.90 TARGET 1995/2000 STOP LOSS 1930</t>
@@ -12247,7 +12227,6 @@
       <c r="F258" t="n">
         <v>1930</v>
       </c>
-      <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr">
         <is>
           <t>BTST CALL Coforge Ltd खरीदें PRICE 1963.50 TARGET 1995/2000 STOP LOSS 1930</t>
@@ -12335,7 +12314,6 @@
       <c r="F260" t="n">
         <v>2310</v>
       </c>
-      <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
           <t>BTST CALL TCS Fut खरीदें PRICE 2346.40 TARGET 2400/2466 STOP LOSS 2310</t>
@@ -12377,7 +12355,6 @@
       <c r="F261" t="n">
         <v>2310</v>
       </c>
-      <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
           <t>BTST CALL
@@ -12523,7 +12500,6 @@
       <c r="E264" t="n">
         <v>800</v>
       </c>
-      <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr">
         <is>
           <t>SUPER SID KIMS खरीदें PRICE 780.20 TARGET 800/850 STOP LOSS --</t>
@@ -12562,7 +12538,6 @@
       <c r="E265" t="n">
         <v>850</v>
       </c>
-      <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr">
         <is>
           <t>KIMS खरीदें PRICE 780.20 TARGET 800/850 STOP LOSS --</t>
@@ -12601,7 +12576,6 @@
       <c r="E266" t="n">
         <v>950</v>
       </c>
-      <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -12645,7 +12619,6 @@
       <c r="E267" t="n">
         <v>990</v>
       </c>
-      <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -12689,7 +12662,6 @@
       <c r="E268" t="n">
         <v>1150</v>
       </c>
-      <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -12727,11 +12699,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
       <c r="E269" t="n">
         <v>705</v>
       </c>
-      <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr">
         <is>
           <t>Sterlite Tech 705.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 442.00 168.06%</t>
@@ -12764,11 +12734,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
       <c r="E270" t="n">
         <v>710</v>
       </c>
-      <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr">
         <is>
           <t>Sterlite Tech 710.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 447.00 169.96%</t>
@@ -12801,11 +12769,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
       <c r="E271" t="n">
         <v>709</v>
       </c>
-      <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr">
         <is>
           <t>Sterlite Tech 709.00 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 446.00 169.58%</t>
@@ -12847,7 +12813,6 @@
       <c r="F272" t="n">
         <v>2235</v>
       </c>
-      <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
           <t>BTST CALL Hyundai Motor Fut खरीदें PRICE 2245.00 TARGET 2320/2340 STOP LOSS 2235</t>
@@ -12889,7 +12854,6 @@
       <c r="F273" t="n">
         <v>2235</v>
       </c>
-      <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
           <t>BTST CALL Hyundai Motor Fut खरीदें PRICE 2245.00 TARGET 2320/2340 STOP LOSS 2235</t>
@@ -12931,7 +12895,6 @@
       <c r="F274" t="n">
         <v>2235</v>
       </c>
-      <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
           <t>Hyundai Motor Fut खरीदें PRICE 2242.50 TARGET 2320/2340 STOP LOSS 2235</t>
@@ -12973,7 +12936,6 @@
       <c r="F275" t="n">
         <v>2235</v>
       </c>
-      <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
           <t>Hyundai Motor Fut खरीदें PRICE 2242.50 TARGET 2320/2340 STOP LOSS 2235</t>
@@ -13107,7 +13069,6 @@
       <c r="F278" t="n">
         <v>995</v>
       </c>
-      <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 976.80 TARGET 960/950 STOP LOSS 995</t>
@@ -13140,14 +13101,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="n">
         <v>960</v>
       </c>
       <c r="F279" t="n">
         <v>995</v>
       </c>
-      <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -13185,14 +13144,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="n">
         <v>950</v>
       </c>
       <c r="F280" t="n">
         <v>995</v>
       </c>
-      <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -13239,7 +13196,6 @@
       <c r="F281" t="n">
         <v>995</v>
       </c>
-      <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 977.00 TARGET 960/950 STOP LOSS 995</t>
@@ -13281,7 +13237,6 @@
       <c r="F282" t="n">
         <v>995</v>
       </c>
-      <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Premier Energies Fut बेचें PRICE 977.00 TARGET 960/950 STOP LOSS 995</t>
@@ -13314,14 +13269,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
       <c r="E283" t="n">
         <v>960</v>
       </c>
       <c r="F283" t="n">
         <v>950</v>
       </c>
-      <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>चेतावनी सेबी की रिपोर्ट के अनुसार इक्विटी वायदा कारोबार के सौदे करने वाले 10 में से 9 ट्रेडर्स को घाटा होता है. इक्विटी F&amp;O के सौदे भारी जोखिम वाले होते हैं, रिस्क समझकर ही सौदे करें Premier Energies F'ut PRICE 977.7C TARGET 960/950</t>
@@ -13360,7 +13313,6 @@
       <c r="E284" t="n">
         <v>5850</v>
       </c>
-      <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5787.00 TARGET 5850/6900 STOP LOSS --</t>
@@ -13399,7 +13351,6 @@
       <c r="E285" t="n">
         <v>5850</v>
       </c>
-      <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5782.50 TARGET 5850/6900 STOP LOSS --</t>
@@ -13438,7 +13389,6 @@
       <c r="E286" t="n">
         <v>5850</v>
       </c>
-      <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5784.00 TARGET 5850/6900 STOP LOSS --</t>
@@ -13477,7 +13427,6 @@
       <c r="E287" t="n">
         <v>6900</v>
       </c>
-      <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5784.00 TARGET 5850/6900 STOP LOSS --</t>
@@ -13516,7 +13465,6 @@
       <c r="E288" t="n">
         <v>5850</v>
       </c>
-      <c r="G288" t="inlineStr"/>
       <c r="H288" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5783.50 TARGET 5850/6900 STOP LOSS --</t>
@@ -13555,7 +13503,6 @@
       <c r="E289" t="n">
         <v>6900</v>
       </c>
-      <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr">
         <is>
           <t>SUPER SID Persistent Sys खरीदें PRICE 5783.50 TARGET 5850/6900 STOP LOSS --</t>
@@ -13594,7 +13541,6 @@
       <c r="E290" t="n">
         <v>1730</v>
       </c>
-      <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -13637,7 +13583,6 @@
       <c r="E291" t="n">
         <v>1530</v>
       </c>
-      <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
           <t>GE Shipping ₹1530/Sh के भाव पर ₹900 Cr के बायबैक को मंजूरी GE Shipping 1329.00 ▲ 11.80</t>
@@ -13679,7 +13624,6 @@
       <c r="F292" t="n">
         <v>622</v>
       </c>
-      <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr">
         <is>
           <t>MY CHOICE KALYAN JEWELLERS B 655 622</t>
@@ -13721,7 +13665,6 @@
       <c r="F293" t="n">
         <v>7547</v>
       </c>
-      <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr">
         <is>
           <t>MY CHOICE AMBER ENTERPRISES B 8037 7547</t>
@@ -13763,7 +13706,6 @@
       <c r="F294" t="n">
         <v>803</v>
       </c>
-      <c r="G294" t="inlineStr"/>
       <c r="H294" t="inlineStr">
         <is>
           <t>MY CHOICE SONA BLW PRECISION B 840 803</t>
@@ -13805,7 +13747,6 @@
       <c r="F295" t="n">
         <v>1096</v>
       </c>
-      <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr">
         <is>
           <t>INVESTMENT GODREJ INDUSTRIES B 1252 1096</t>
@@ -13847,7 +13788,6 @@
       <c r="F296" t="n">
         <v>2524</v>
       </c>
-      <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
           <t>CASH CAPLIN POINT B 2600 2524</t>
@@ -13889,7 +13829,6 @@
       <c r="F297" t="n">
         <v>20330</v>
       </c>
-      <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
           <t>FUTURE SOLAR IND FUT B 21240 20330</t>
@@ -13931,7 +13870,6 @@
       <c r="F298" t="n">
         <v>1978</v>
       </c>
-      <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>FUNDA BHARAT FORGE B 2180 1978</t>
@@ -13973,7 +13911,6 @@
       <c r="F299" t="n">
         <v>86</v>
       </c>
-      <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
           <t>MY CHOICE NBCC B 93 86</t>
@@ -14015,7 +13952,6 @@
       <c r="F300" t="n">
         <v>5092</v>
       </c>
-      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr">
         <is>
           <t>MY CHOICE TITAN B 5190 5092</t>
@@ -14057,7 +13993,6 @@
       <c r="F301" t="n">
         <v>1166</v>
       </c>
-      <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr">
         <is>
           <t>MY CHOICE ZYDUS LIFE B 1215 1166</t>
@@ -14099,7 +14034,6 @@
       <c r="F302" t="n">
         <v>250</v>
       </c>
-      <c r="G302" t="inlineStr"/>
       <c r="H302" t="inlineStr">
         <is>
           <t>INVESTMENT SCI B 375 250</t>
@@ -14138,7 +14072,6 @@
       <c r="F303" t="n">
         <v>12</v>
       </c>
-      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
           <t>MY CHOICE ZYDUS LIFE B 12</t>
@@ -14177,7 +14110,6 @@
       <c r="E304" t="n">
         <v>5190</v>
       </c>
-      <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr">
         <is>
           <t>MY CHOICE TITAN B 5190</t>
@@ -14219,7 +14151,6 @@
       <c r="F305" t="n">
         <v>1233</v>
       </c>
-      <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr">
         <is>
           <t>NEWS IMPACT LODHA DEVELOPERS B 1280 1233</t>
@@ -14258,7 +14189,6 @@
       <c r="E306" t="n">
         <v>93</v>
       </c>
-      <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr">
         <is>
           <t>MY CHOICE NBCC B 93</t>
@@ -14297,7 +14227,6 @@
       <c r="E307" t="n">
         <v>495</v>
       </c>
-      <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr">
         <is>
           <t>RK B 535 495</t>
@@ -14339,7 +14268,6 @@
       <c r="F308" t="n">
         <v>335</v>
       </c>
-      <c r="G308" t="inlineStr"/>
       <c r="H308" t="inlineStr">
         <is>
           <t>FUTURE NYKAA FUT B 347 335</t>
@@ -14381,7 +14309,6 @@
       <c r="F309" t="n">
         <v>420.5</v>
       </c>
-      <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
           <t>FUNDA KOTAK BANK B 429 420.5</t>
@@ -14423,7 +14350,6 @@
       <c r="F310" t="n">
         <v>9001</v>
       </c>
-      <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr">
         <is>
           <t>TECHNO DIVI'S LAB B 9150 9001</t>
@@ -14551,7 +14477,6 @@
       <c r="F313" t="n">
         <v>595</v>
       </c>
-      <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Kalyan Jewellers BUY PRICE 629.30 TARGET 700/720 STOP LOSS 595</t>
@@ -14593,7 +14518,6 @@
       <c r="F314" t="n">
         <v>595</v>
       </c>
-      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Kalyan Jewellers BUY PRICE 629.30 TARGET 700/720 STOP LOSS 595</t>
@@ -14632,7 +14556,6 @@
       <c r="E315" t="n">
         <v>7900</v>
       </c>
-      <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेठानी की राय Amber Ent BUY PRICE 7701.00 TARGET 7900/8450 STOP LOSS --</t>
@@ -14671,7 +14594,6 @@
       <c r="E316" t="n">
         <v>8450</v>
       </c>
-      <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेठानी की राय
@@ -14713,7 +14635,6 @@
       <c r="E317" t="n">
         <v>1150</v>
       </c>
-      <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -14756,7 +14677,6 @@
       <c r="E318" t="n">
         <v>718</v>
       </c>
-      <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS SBI FUNDS MGMT 562.55 -0.90 BUY लक्ष्य ₹718</t>
@@ -14795,7 +14715,6 @@
       <c r="E319" t="n">
         <v>840</v>
       </c>
-      <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय Anant Raj Ltd PRICE 605.25 TARGET 840 STOP LOSS BROKERAGE CALLS BUY लक्ष्य ₹710</t>
@@ -14837,7 +14756,6 @@
       <c r="F320" t="n">
         <v>544</v>
       </c>
-      <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय
@@ -15013,7 +14931,6 @@
       <c r="E324" t="n">
         <v>710</v>
       </c>
-      <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS SBI FUNDS MGMT 562.55 -0.90 BUY लक्ष्य ₹710</t>
@@ -15055,7 +14972,6 @@
       <c r="F325" t="n">
         <v>804</v>
       </c>
-      <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
@@ -15097,7 +15013,6 @@
       <c r="F326" t="n">
         <v>804</v>
       </c>
-      <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
@@ -15139,7 +15054,6 @@
       <c r="F327" t="n">
         <v>804</v>
       </c>
-      <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Sona BLW Futures UY PRICE 819 TARGET 830, 838, 845 STOP LOSS 804</t>
@@ -15181,7 +15095,6 @@
       <c r="F328" t="n">
         <v>175</v>
       </c>
-      <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
@@ -15223,7 +15136,6 @@
       <c r="F329" t="n">
         <v>175</v>
       </c>
-      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
@@ -15265,7 +15177,6 @@
       <c r="F330" t="n">
         <v>175</v>
       </c>
-      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Ashok Leyland Fut BUY PRICE 177 TARGET 180, 182, 184 STOP LOSS 175</t>
@@ -15307,7 +15218,6 @@
       <c r="F331" t="n">
         <v>11650</v>
       </c>
-      <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
@@ -15349,7 +15259,6 @@
       <c r="F332" t="n">
         <v>11650</v>
       </c>
-      <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
@@ -15391,7 +15300,6 @@
       <c r="F333" t="n">
         <v>11650</v>
       </c>
-      <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Bajaj Auto Futures BUY PRICE 11791 TARGET 11900, 12000, 12200 STOP LOSS 11650</t>
@@ -15433,7 +15341,6 @@
       <c r="F334" t="n">
         <v>472</v>
       </c>
-      <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>TECHNO PICK
@@ -15480,7 +15387,6 @@
       <c r="F335" t="n">
         <v>6</v>
       </c>
-      <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr">
         <is>
           <t>BEST ऑप्शन Tata power 350 की कॉल @ 9 खरीदें STOP LOSS 6 TARGET 14 Tata Power 352.00</t>
@@ -15522,7 +15428,6 @@
       <c r="F336" t="n">
         <v>335</v>
       </c>
-      <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -15569,7 +15474,6 @@
       <c r="F337" t="n">
         <v>20330</v>
       </c>
-      <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -15616,7 +15520,6 @@
       <c r="F338" t="n">
         <v>2524</v>
       </c>
-      <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -15663,7 +15566,6 @@
       <c r="F339" t="n">
         <v>173</v>
       </c>
-      <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr">
         <is>
           <t>Ashok Leyland खरीदें PRICE 177.4 TARGET 185 STOP LOSS 173 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -15705,7 +15607,6 @@
       <c r="F340" t="n">
         <v>380</v>
       </c>
-      <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr">
         <is>
           <t>RBL Bank खरीदें PRICE 385.4 TARGET 395/400 STOP LOSS 380 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -15747,7 +15648,6 @@
       <c r="F341" t="n">
         <v>380</v>
       </c>
-      <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr">
         <is>
           <t>RBL Bank खरीदें PRICE 385.4 TARGET 395/400 STOP LOSS 380 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -15764,8 +15664,8082 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:01:41</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="n">
+        <v>888</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Lenskart पर नोमुरा BUY की रेटिंग, लक्ष्य ₹888 Lenskart 662.40 ▲ 26.25</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:01:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>HARSHA</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>455.9</v>
+      </c>
+      <c r="E343" t="n">
+        <v>470</v>
+      </c>
+      <c r="F343" t="n">
+        <v>425</v>
+      </c>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी साब
+Harsha Engineers
+455.70 3.84%
+BUY
+TGT 470
+SL 425</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:01:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>9189.5</v>
+      </c>
+      <c r="E344" t="n">
+        <v>9350</v>
+      </c>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>SUPER SID Polycab India 9185.50 97.50 BUY TGT 9350 SL --</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:00:22</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="n">
+        <v>265</v>
+      </c>
+      <c r="F345" t="n">
+        <v>246</v>
+      </c>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>EIL 261.61 7.89 BUY TGT 265 SL 246</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:01:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>597.95</v>
+      </c>
+      <c r="E346" t="n">
+        <v>630</v>
+      </c>
+      <c r="F346" t="n">
+        <v>575</v>
+      </c>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hindustan Zinc
+598.25 23.75
+BUY
+TGT 630
+SL 575</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:59:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="E347" t="n">
+        <v>440</v>
+      </c>
+      <c r="F347" t="n">
+        <v>407</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय
+BEL Fut
+खरीदें
+PRICE ▶ 415.45
+TARGET ▶ 430/440
+STOP LOSS ▶ 407</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:59:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="E348" t="n">
+        <v>430</v>
+      </c>
+      <c r="F348" t="n">
+        <v>407</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय BEL Fut खरीदें PRICE 415.45 TARGET 430/440 STOP LOSS 407</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:57:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="E349" t="n">
+        <v>364</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Karnataka Bank खरीदें PRICE 334.95 TARGET 346/364 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:57:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="E350" t="n">
+        <v>346</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Karnataka Bank खरीदें PRICE 334.95 TARGET 346/364 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:55:06</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>JP मॉर्गन OVERWEIGHT 1570 1850</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:52:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>1444.2</v>
+      </c>
+      <c r="E352" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F352" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+ICICI Bank
+1444.00 1.49%
+BUY
+TGT 1475
+SL 1425</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:51:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>COCHINSHIP29SEP26</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>1517.4</v>
+      </c>
+      <c r="E353" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1480</v>
+      </c>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>EXPIRY TRADE Cochin Shipyard Fut BUY PRICE 1517.20 TARGET 1600 STOP LOSS 1480</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:51:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>1894.7</v>
+      </c>
+      <c r="E354" t="n">
+        <v>1940</v>
+      </c>
+      <c r="F354" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Fut BUY PRICE 1894.00 TARGET 1940 STOP LOSS 1750</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:49:15</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>NIFTY2415001SEP26CE</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="n">
+        <v>175</v>
+      </c>
+      <c r="F355" t="n">
+        <v>75</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Sahaj Aggarwal</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>सहज अग्रवाल की राय Nifty 24150 की कॉल खरीदें @ ₹110 (1 SEP) B STOP LOSS 75 TARGET 175</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:44:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>725.2</v>
+      </c>
+      <c r="E356" t="n">
+        <v>825</v>
+      </c>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>शुगर सेक्टर पर DAM कैपिटल की राय Balrampur Chini खरीदें, टार्गेट ₹825 Balrampur Chini 724.60 ▲ 10.65%</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:44:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>488.65</v>
+      </c>
+      <c r="E357" t="n">
+        <v>710</v>
+      </c>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>शुगर सेक्टर पर DAM कैपिटल की राय
+Dalmia Bharat Sugar खरीदें,
+टार्गेट ₹710
+Dalmia Bharat Sugar 488.80 ▲ 2.27%</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>TRIVENI</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>293.7</v>
+      </c>
+      <c r="E358" t="n">
+        <v>415</v>
+      </c>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>Triveni Engineering खरीदने की राय, टार्गेट ₹415</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>HARSHA</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>444.75</v>
+      </c>
+      <c r="E359" t="n">
+        <v>470</v>
+      </c>
+      <c r="F359" t="n">
+        <v>425</v>
+      </c>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब Harsha Engineers 445.60 6.75 BUY TGT 470 SL 425</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>9178</v>
+      </c>
+      <c r="E360" t="n">
+        <v>9350</v>
+      </c>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Polycab India
+9173.50 85.50
+BUY
+TGT 9350
+SL --</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F361" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शोयर
+ICICI Bank
+1449.70 26.90
+BUY
+TGT 1475
+SL 1425</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1475</v>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>ICICI Bank 1449.70 26.90 BUY TGT 1475</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:43:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>426.7</v>
+      </c>
+      <c r="E363" t="n">
+        <v>438</v>
+      </c>
+      <c r="F363" t="n">
+        <v>413</v>
+      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Kotak Bank Fut ▲
+426.65 0.21%
+BUY
+TGT 438
+SL 413</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:42:03</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="n">
+        <v>265</v>
+      </c>
+      <c r="F364" t="n">
+        <v>246</v>
+      </c>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट EIL 258.20 4.48 BUY TGT 265 SL 246</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:42:00</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>597.95</v>
+      </c>
+      <c r="E365" t="n">
+        <v>630</v>
+      </c>
+      <c r="F365" t="n">
+        <v>575</v>
+      </c>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hindustan Zinc
+597.85 24.15
+BUY
+TGT 630
+SL 575</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:42:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>597.95</v>
+      </c>
+      <c r="E366" t="n">
+        <v>630</v>
+      </c>
+      <c r="F366" t="n">
+        <v>525</v>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>Mehul
+Hindustan Zinc
+597.85 24.15
+BUY
+TGT 630
+SL 525</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:42:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>FORCEMOT29SEP26</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>17568</v>
+      </c>
+      <c r="E367" t="n">
+        <v>17840</v>
+      </c>
+      <c r="F367" t="n">
+        <v>17360</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय
+Force Motors Fut
+खरीदें
+PRICE → 17560.00
+TARGET → 17840/18100
+STOP LOSS → 17360</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:42:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>FORCEMOT29SEP26</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>17568</v>
+      </c>
+      <c r="E368" t="n">
+        <v>18100</v>
+      </c>
+      <c r="F368" t="n">
+        <v>17360</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय
+Force Motors Fut
+खरीदें
+PRICE → 17560.00
+TARGET → 17840/18100
+STOP LOSS → 17360</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:41:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>INDHOTEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>717.85</v>
+      </c>
+      <c r="E369" t="n">
+        <v>695</v>
+      </c>
+      <c r="F369" t="n">
+        <v>730</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Indian Hotels Fut बेचें PRICE 717.20 TARGET 695/685 STOP LOSS 730</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:41:00</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>INDHOTEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>717.85</v>
+      </c>
+      <c r="E370" t="n">
+        <v>685</v>
+      </c>
+      <c r="F370" t="n">
+        <v>730</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Indian Hotels Fut बेचें PRICE 717.20 TARGET 695/685 STOP LOSS 730</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:39:00</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>635.9</v>
+      </c>
+      <c r="E371" t="n">
+        <v>665</v>
+      </c>
+      <c r="F371" t="n">
+        <v>615</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>NITIN SPINNERS @ 632 खरीदें STOP LOSS 615 TARGET 665 Nitin Spinners 638.00 ▲ 1.85% विकास सेठी सेठी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:39:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>NITINSPIN</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>635.9</v>
+      </c>
+      <c r="E372" t="n">
+        <v>665</v>
+      </c>
+      <c r="F372" t="n">
+        <v>615</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय NITIN SPINNERS @ 632 खरीदें STOP LOSS 615 TARGET 665 Nitin Spinners 640.40 2.24%</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:37:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>779.45</v>
+      </c>
+      <c r="E373" t="n">
+        <v>800</v>
+      </c>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>SUPER SID CAMS खरीदें PRICE 780.25 TARGET 800/940 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:37:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>779.45</v>
+      </c>
+      <c r="E374" t="n">
+        <v>940</v>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>SUPER SID CAMS खरीदें PRICE 780.25 TARGET 800/940 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:33:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>HARSHA</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>445.65</v>
+      </c>
+      <c r="E375" t="n">
+        <v>470</v>
+      </c>
+      <c r="F375" t="n">
+        <v>425</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय HARSHA ENGINEERS @ 442 खरीदें STOP LOSS 425 TARGET 470</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:25:45</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ADANIENT29SEP26</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1558</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उत्तेकर की राय
+Adani Energy Fut
+बेचें
+PRICE → 1528.90
+TARGET → 1490/1430
+STOP LOSS → 1558</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:25:45</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ADANIENT29SEP26</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F377" t="n">
+        <v>1558</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उत्तेकर की राय
+Adani Energy Fut
+बेचें
+PRICE → 1528.90
+TARGET → 1490/1430
+STOP LOSS → 1558</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:24:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>9160</v>
+      </c>
+      <c r="E378" t="n">
+        <v>9350</v>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>SUPER SID Polycab India खरीदें PRICE 9160.50 TARGET 9350/10600 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:24:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>9160</v>
+      </c>
+      <c r="E379" t="n">
+        <v>10600</v>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>SUPER SID Polycab India खरीदें PRICE 9160.50 TARGET 9350/10600 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:23:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>1441.5</v>
+      </c>
+      <c r="E380" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F380" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय ICICI Bank खरीदें PRICE 1441.60 TARGET 1475/1490 STOP LOSS 1425</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:23:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>1441.5</v>
+      </c>
+      <c r="E381" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F381" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय ICICI Bank खरीदें PRICE 1441.60 TARGET 1475/1490 STOP LOSS 1425</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="n">
+        <v>57450</v>
+      </c>
+      <c r="F382" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="n">
+        <v>57500</v>
+      </c>
+      <c r="F383" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="n">
+        <v>57600</v>
+      </c>
+      <c r="F384" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="n">
+        <v>57675</v>
+      </c>
+      <c r="F385" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="n">
+        <v>57750</v>
+      </c>
+      <c r="F386" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="n">
+        <v>57875</v>
+      </c>
+      <c r="F387" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-31 14:07:12</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="n">
+        <v>57975</v>
+      </c>
+      <c r="F388" t="n">
+        <v>56900</v>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
+STRICT STOPLOSS 56900
+TARGET
+57450 57500 57600 57675
+57750 57875 57975</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:50:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>607.35</v>
+      </c>
+      <c r="E389" t="n">
+        <v>650</v>
+      </c>
+      <c r="F389" t="n">
+        <v>595</v>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>Indegene खरीदें PRICE 607.30 TARGET 650 STOP LOSS 595</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:37:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>720.9</v>
+      </c>
+      <c r="E390" t="n">
+        <v>825</v>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>शुगर सेक्टर पर DAM कैपिटल की राय Balrampur Chini खरीदें, टार्गेट ₹825 Balrampur Chini 721.75 ▲ 66.90</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:37:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>DALMIASUG</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>491.3</v>
+      </c>
+      <c r="E391" t="n">
+        <v>710</v>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>शुगर सेक्टर पर DAM कैपिटल की राय Dalmia Bharat Sugar खरीदें, टार्गेट ₹710 Dalmia Bharat Sugar 491.90 ▲ 13.95</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:36:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>TRIVENI</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>294.38</v>
+      </c>
+      <c r="E392" t="n">
+        <v>415</v>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Triveni Engineering खरीदने की राय, टार्गेट ₹415</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:21:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>8847</v>
+      </c>
+      <c r="E393" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F393" t="n">
+        <v>8740</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की पसंद Apollo Hosp खरीदें PRICE 8850.00 TARGET 9100 STOP LOSS 8740</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:21:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="E394" t="n">
+        <v>1720</v>
+      </c>
+      <c r="F394" t="n">
+        <v>1575</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की पसंद Tech Mahindra खरीदें PRICE 1619.20 TARGET 1720 STOP LOSS 1575</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:13:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>1669.9</v>
+      </c>
+      <c r="E395" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F395" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय
+Ather Energy
+1669.40 ▲ 3.29%
+HOLD
+TARGET 1900
+STOP LOSS 1490/1370</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-31 13:13:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>1669.9</v>
+      </c>
+      <c r="E396" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F396" t="n">
+        <v>1370</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय
+Ather Energy
+1669.40 ▲ 3.29%
+HOLD
+TARGET 1900
+STOP LOSS 1490/1370</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:50:46</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>POLYCAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="n">
+        <v>9350</v>
+      </c>
+      <c r="F397" t="n">
+        <v>9225</v>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd Fut खरीदें PRICE 9244.00 TARGET 9300/9350 STOP LOSS 9225</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:50:46</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>POLYCAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="n">
+        <v>9300</v>
+      </c>
+      <c r="F398" t="n">
+        <v>9225</v>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd Fut खरीदें PRICE 9244.00 TARGET 9300/9350 STOP LOSS 9225</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:51:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>UNOMINDA29SEP26</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>1294.5</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F399" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>UNO Minda Fut खरीदें PRICE 1293.30 TARGET 1320/1335 STOP LOSS 1275</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:50:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>UNOMINDA29SEP26</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>1293.9</v>
+      </c>
+      <c r="E400" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F400" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>TRADING CALL
+UNO Minda Fut
+खरीदें
+PRICE ▶ 1293.30
+TARGET ▶ 1335
+STOP LOSS ▶ 1275</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:48:47</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>NIFTY2430001SEP26CE</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="n">
+        <v>135</v>
+      </c>
+      <c r="F401" t="n">
+        <v>65</v>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>निफ्टी 24300 की कॉल @ 85-90 खरीदें STOP LOSS 65 TARGET 120/135</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-31 12:48:47</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>NIFTY2430001SEP26CE</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="n">
+        <v>120</v>
+      </c>
+      <c r="F402" t="n">
+        <v>65</v>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>निफ्टी 24300 की कॉल @ 85-90 खरीदें STOP LOSS 65 TARGET 120/135</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:54:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="E403" t="n">
+        <v>225</v>
+      </c>
+      <c r="F403" t="n">
+        <v>175</v>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय
+New India Assurance
+खरीदें
+STOP LOSS 175
+TARGET 225/230
+DURATION --
+New India Assurance 197.89 ▲ 6.20%</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:54:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="E404" t="n">
+        <v>230</v>
+      </c>
+      <c r="F404" t="n">
+        <v>175</v>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>राजेश पालविया को राय
+New India Assurance
+खरीदें
+STOP LOSS 175 | TARGET 225/230 | DURATION --
+New India Assurance 197.89 ▲ 11.55</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:54:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>526.15</v>
+      </c>
+      <c r="E405" t="n">
+        <v>600</v>
+      </c>
+      <c r="F405" t="n">
+        <v>495</v>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 Shanthi Gears 529.90 2.35%</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:54:00</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>526.15</v>
+      </c>
+      <c r="E406" t="n">
+        <v>620</v>
+      </c>
+      <c r="F406" t="n">
+        <v>495</v>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 DURATION -- Shanthi Gears 529.90 12.15 ऑटो शेयर</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:53:00</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MAMATA</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>404.95</v>
+      </c>
+      <c r="E407" t="n">
+        <v>430</v>
+      </c>
+      <c r="F407" t="n">
+        <v>385</v>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>SHORT MIDCAP STOCKS Mamata Machinery खरीदें STOP LOSS 385 TARGET 430 DURATION -- Mamata Machinery 404.90 ▲ 1.21%</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:53:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="E408" t="n">
+        <v>435</v>
+      </c>
+      <c r="F408" t="n">
+        <v>360</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय
+Apollo Micro Systems
+खरीदें
+STOP LOSS 360 | TARGET 435 | DURATION --
+Apollo Micro Systems 386.95</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:19:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>APOLLO</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="E409" t="n">
+        <v>435</v>
+      </c>
+      <c r="F409" t="n">
+        <v>360</v>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>POSITIONAL MEDICAL STOCK Apollo Micro Systems खरीदें STOP LOSS 360 TARGET 435 DURATION</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:19:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>531.05</v>
+      </c>
+      <c r="E410" t="n">
+        <v>620</v>
+      </c>
+      <c r="F410" t="n">
+        <v>495</v>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 DURATION -- Shanthi Gears 530.50 12.75</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:18:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ECLERX</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>2008.6</v>
+      </c>
+      <c r="E411" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F411" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय
+eClerx Services
+खरीदें
+STOP LOSS 1940
+TARGET 2350/2400
+DURATION --
+eClerx Services 2003.40 ▲ 2.45%</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:18:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>ECLERX</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय
+eClerx Services
+खरीदें
+STOP LOSS 1940
+TARGET 2350/2400
+DURATION --
+eClerx Services 2003.40 ▲ 2.45%</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:17:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>ECLERX</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E413" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F413" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>eClerx Services PRICE 2001.00 TARGET 2100/2150 STOP LOSS 1940</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:16:06</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="n">
+        <v>265</v>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>EIL 254.84 1.12 BUY TGT 265</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:17:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>595.35</v>
+      </c>
+      <c r="E415" t="n">
+        <v>630</v>
+      </c>
+      <c r="F415" t="n">
+        <v>575</v>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hindustan Zinc
+594.80 27.20
+BUY
+TGT 630
+SL 575</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:15:56</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="n">
+        <v>275</v>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>संदीप जैन Northern Arc Capital 311.90 9.09% BUY TARGET HIT 275</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:15:55</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="n">
+        <v>310</v>
+      </c>
+      <c r="F417" t="n">
+        <v>275</v>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>संदीप जैन Northern Arc Capital 311.90 9.09% BUY TGT 310 SL 275</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:15:37</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ARENTERP</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F418" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>आस्था जन की राय CARE Ltd खरीदें PRICE 1740.00 TARGET 1850/1880 STOP LOSS 1610</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:15:36</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ARENTERP</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F419" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>CARE Ltd खरीदें PRICE 1740.00 TARGET 1850/1880 STOP LOSS 1610</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:16:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>CARERATING</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>1739.7</v>
+      </c>
+      <c r="E420" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>CARE Ltd खरीदें PRICE 1741.60 TARGET 1850/1880 STOP LOSS 1610</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:16:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>CARERATING</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>1739.7</v>
+      </c>
+      <c r="E421" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F421" t="n">
+        <v>1610</v>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>CARE Ltd खरीदें PRICE 1741.60 TARGET 1850/1880 STOP LOSS 1610</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:13:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>425.7</v>
+      </c>
+      <c r="E422" t="n">
+        <v>438</v>
+      </c>
+      <c r="F422" t="n">
+        <v>413</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Kotak Bank Fut खरीदें PRICE 425.85 TARGET 438/445 STOP LOSS 413</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:13:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>425.7</v>
+      </c>
+      <c r="E423" t="n">
+        <v>445</v>
+      </c>
+      <c r="F423" t="n">
+        <v>413</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Kotak Bank Fut खरीदें PRICE 425.85 TARGET 438/445 STOP LOSS 413</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:08:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="E424" t="n">
+        <v>700</v>
+      </c>
+      <c r="F424" t="n">
+        <v>520</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय Indegene खरीदें STOP LOSS 520 TARGET 700 DURATION -- 586.40 ▲ 1.29%</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:07:00</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>263.35</v>
+      </c>
+      <c r="E425" t="n">
+        <v>340</v>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Euro Pratik Sales ▲
+262.85 2.10%
+BUY
+TGT 340
+SL --</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:07:00</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ECLERX</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="E426" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F426" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Rajesh Palviya</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>RAJESH PALVIYA AXIS SECURITIES SEBI REG NO: INH000000297 eClerx Services खरीदें STOP LOSS 1940 TARGET 2350/2400 DURATION -- 2005.50 ▲ 50.00</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:07:00</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ECLERX</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="E427" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F427" t="n">
+        <v>1940</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Rajesh Palviya</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>RAJESH PALVIYA AXIS SECURITIES SEBI REG NO: INH000000297 eClerx Services खरीदें STOP LOSS 1940 TARGET 2350/2400 DURATION -- 2005.50 ▲ 50.00</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:05:56</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SWARAJ</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Swaraj खरीदें PRICE 3586.00 TARGET 4500 DURATION 6</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-31 10:06:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SWARAJENG</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>3613.7</v>
+      </c>
+      <c r="E429" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Swaraj Engine खरीदें PRICE 3582.00 TARGET 4500 STOP LOSS —</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:56:03</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="n">
+        <v>275</v>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Northern Arc Capital 309.25 23.35 BUY TARGET HIT 275</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:56:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="E431" t="n">
+        <v>310</v>
+      </c>
+      <c r="F431" t="n">
+        <v>275</v>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>संदीप जैन Northern Arc Capital 309.25 23.35 BUY TGT 310 SL 275</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:56:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>JUSTDIAL</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>710.9</v>
+      </c>
+      <c r="E432" t="n">
+        <v>840</v>
+      </c>
+      <c r="F432" t="n">
+        <v>630</v>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+Just Dial
+खरीदें
+PRICE → 706.20
+TARGET → 840
+STOP LOSS → 630</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:47:10</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>CAMS77029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="n">
+        <v>32</v>
+      </c>
+      <c r="F433" t="n">
+        <v>12</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय CAMS 770 की कॉल @ ₹19-20 खरीदें STOP LOSS 12 TARGET 32/38</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:47:10</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>CAMS77029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="n">
+        <v>38</v>
+      </c>
+      <c r="F434" t="n">
+        <v>12</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय CAMS 770 की कॉल @ ₹19-20 खरीदें STOP LOSS 12 TARGET 32/38</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:46:53</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>AUGMONT</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="F435" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:47:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>764.65</v>
+      </c>
+      <c r="E436" t="n">
+        <v>788</v>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:47:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>262.85</v>
+      </c>
+      <c r="E437" t="n">
+        <v>340</v>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Euro Pratik Sales 263.25 5.80 BUY TGT 340 SL --</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:45:55</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="n">
+        <v>265</v>
+      </c>
+      <c r="F438" t="n">
+        <v>246</v>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>EIL 254.35 0.63 BUY TGT 265 SL 246</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:46:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>597</v>
+      </c>
+      <c r="E439" t="n">
+        <v>638</v>
+      </c>
+      <c r="F439" t="n">
+        <v>575</v>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hindustan Zinc
+595.85 4.20%
+BUY
+TGT 638
+SL 575</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:45:46</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="n">
+        <v>275</v>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Northern Arc Capital 310.25 BUY TARGET HIT 275</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:45:43</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="n">
+        <v>310</v>
+      </c>
+      <c r="F441" t="n">
+        <v>275</v>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Northern Arc Capital 310.25 24.35 BUY TGT 310 SL 275</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:45:41</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>NORTHARC</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="n">
+        <v>310</v>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Northern Arc Capital 310.25 24.35 BUY TGT 310</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:37:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>MCX29SEP26</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>3366.5</v>
+      </c>
+      <c r="F443" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:32:49</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>AUGMONT</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>AUGMONT
+लिस्टिंग पर राय
+इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:33:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>263.9</v>
+      </c>
+      <c r="E445" t="n">
+        <v>350</v>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Euro Pratik Sales खरीदें PRICE 265.45 TARGET 340/350 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:33:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>263.9</v>
+      </c>
+      <c r="E446" t="n">
+        <v>340</v>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>संतीप जैन की राय Euro Pratik Sales खरीदें PRICE 265.45 TARGET 340/350 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:32:09</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>EUROPRATIK</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="F447" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Euro Pratik Sales 264.90 ▲ 2.89% TODAY 267 HIGH 267.20 LOW 254.40 Vol: 65.97 k AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:32:02</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>AUGMONT</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+      <c r="E448" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F448" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:32:01</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>AUGMONT</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F449" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:29:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>ATHERENERG29SEP26</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1720.7</v>
+      </c>
+      <c r="F450" t="n">
+        <v>1644</v>
+      </c>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>OPENING का HERO Ather Energy Fut 1672.30 ▲ 48.40 TODAY 1683 HIGH 1683.00 LOW 1644.10 Vol: 704.25 k 1644 09:15 AM 09:27 AM</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:28:23</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ATHERENERG29SEP26</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>OPENING का HERO Ather Energy Fut 1672.30 ▲ 48.40 TODAY 1683 HIGH 1683.00 LOW 1644.10 Vol: 704.25 k</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:27</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="n">
+        <v>265</v>
+      </c>
+      <c r="F452" t="n">
+        <v>246</v>
+      </c>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+EIL
+खरीदें
+PRICE ▶ 257.16
+TARGET ▶ 265/275
+STOP LOSS ▶ 246</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:27</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+      <c r="E453" t="n">
+        <v>275</v>
+      </c>
+      <c r="F453" t="n">
+        <v>246</v>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+EIL
+खरीदें
+PRICE ▶ 257.16
+TARGET ▶ 265/275
+STOP LOSS ▶ 246</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:26</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+      <c r="E454" t="n">
+        <v>265</v>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय EIL PRICE 257.15 TARGET 265/275</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:26</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+      <c r="E455" t="n">
+        <v>275</v>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय EIL PRICE 257.15 TARGET 265/275</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:27:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>595.75</v>
+      </c>
+      <c r="E456" t="n">
+        <v>630</v>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Hindustan Zinc 595.25 26.75 BUY TGT 630</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:23:52</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>NIFTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+      <c r="F457" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Nifty 50 Fut Prem 24210.80, 134.20 इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं Mon 31 Aug'26</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>660334995662a7f64ae8911e</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:24:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ASTEC</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>578.55</v>
+      </c>
+      <c r="F458" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>इन्वेस्टेस्ट ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:23:04</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+      <c r="F459" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Eternal (Zomato) 332.20 4.20 1.28% Vol: 3.08 m AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:23:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="E460" t="n">
+        <v>630</v>
+      </c>
+      <c r="F460" t="n">
+        <v>575</v>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hindustan Zinc
+खरीदें
+PRICE ▶ 596.00
+TARGET ▶ 630
+STOP LOSS ▶ 575</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:23:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="E461" t="n">
+        <v>630</v>
+      </c>
+      <c r="F461" t="n">
+        <v>575</v>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>मेहुल कोठारी की राय
+Hindustan Zinc
+खरीदें
+PRICE → 595.95
+TARGET → 630
+STOP LOSS → 575</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>729.75</v>
+      </c>
+      <c r="E462" t="n">
+        <v>745</v>
+      </c>
+      <c r="F462" t="n">
+        <v>710</v>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+HDFC Bank Fut
+BUY
+PRICE ▶ 728.00
+TARGET ▶ 730, 738, 745
+STOP LOSS ▶ 710</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>1796.4</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली PB Fintech 1791.30 -1.12% UNDERWEIGHT लक्ष्य ₹1215 से बढ़ाकर ₹1390</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>1796.4</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली
+PB Fintech
+1790.00 -21.50
+UNDERWEIGHT
+लक्ष्य ₹1215 से बढ़ाकर ₹1390</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E465" t="n">
+        <v>570</v>
+      </c>
+      <c r="F465" t="n">
+        <v>553</v>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की राय
+SBI Funds Mgmt
+B I
+PRICE ▶ 563.80
+TARGET ▶ 570, 576, 582
+STOP LOSS ▶ 553</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E466" t="n">
+        <v>576</v>
+      </c>
+      <c r="F466" t="n">
+        <v>553</v>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की राय
+SBI Funds Mgmt
+B I
+PRICE ▶ 563.80
+TARGET ▶ 570, 576, 582
+STOP LOSS ▶ 553</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E467" t="n">
+        <v>582</v>
+      </c>
+      <c r="F467" t="n">
+        <v>553</v>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की राय
+SBI Funds Mgmt
+B I
+PRICE ▶ 563.80
+TARGET ▶ 570, 576, 582
+STOP LOSS ▶ 553</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>422.6</v>
+      </c>
+      <c r="E468" t="n">
+        <v>535</v>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली Kotak Bank 422.30 -1.40 OVERWEIGHT लक्ष्य ₹500 से बढ़ाकर ₹535</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली
+ICICI Bank
+1423.60 +0.80
+OVERWEIGHT
+लक्ष्य ₹1705 से बढ़ाकर ₹1820</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>12196</v>
+      </c>
+      <c r="E470" t="n">
+        <v>13200</v>
+      </c>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>INVESTMENT ORACLE B 13200 1</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1446</v>
+      </c>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT ICICI BANK B 1446</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="E472" t="n">
+        <v>465</v>
+      </c>
+      <c r="F472" t="n">
+        <v>434</v>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>CASH EXIDE IND B 465 434</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>5151</v>
+      </c>
+      <c r="E473" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F473" t="n">
+        <v>5150</v>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>MY CHOICE INTERGLOBE AVIATION FUT B 5300 5150</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>WINDLAS</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>994.55</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F474" t="n">
+        <v>930</v>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Windlas Biotech BUY PRICE 998.55 TARGET 1190 STOP LOSS 930</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>MAHSCOOTER</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>13764</v>
+      </c>
+      <c r="E475" t="n">
+        <v>14950</v>
+      </c>
+      <c r="F475" t="n">
+        <v>13150</v>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Maha Scooters BUY PRICE 1366.00 TARGET 14950 STOP LOSS 13150</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>1413.7</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>PICK OF THE WEEK Cipla BUY PRICE 1423.50 TARGET 1460 STOP LOSS 1390</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>SBIFUNDS</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>564.55</v>
+      </c>
+      <c r="E477" t="n">
+        <v>685</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT
+BofA
+BUY
+SBI Funds Mgmt
+563.80 ▲ 1.25
+TARGET ₹685</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली OVERWEIGHT 1025 --</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>1614.6</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1680</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Pidilite Ind BUY PRICE 1629.50 TARGET 1680/1700 STOP LOSS 1590</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>1614.6</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F480" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Pidilite Ind BUY PRICE 1629.50 TARGET 1680/1700 STOP LOSS 1590</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>632</v>
+      </c>
+      <c r="E481" t="n">
+        <v>665</v>
+      </c>
+      <c r="F481" t="n">
+        <v>609</v>
+      </c>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Elgi Equipments BUY PRICE 628.85 TARGET 665/680 STOP LOSS 609</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>632</v>
+      </c>
+      <c r="E482" t="n">
+        <v>680</v>
+      </c>
+      <c r="F482" t="n">
+        <v>609</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Elgi Equipments BUY PRICE 628.85 TARGET 665/680 STOP LOSS 609</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>1985</v>
+      </c>
+      <c r="E483" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F483" t="n">
+        <v>1895</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Mehul Kothari</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>मेहुल कोठारी की राय BEML BUY PRICE 1984.90 TARGET 2130 STOP LOSS 1895</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>1278.7</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>RIL 1300 के बड़े सपोर्ट के नीचे
+RIL की 2 दिन की गिरावट पर ब्रेक, ₹5 चढ़कर 1287 पर बंद</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="E485" t="n">
+        <v>730</v>
+      </c>
+      <c r="F485" t="n">
+        <v>710</v>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+HDFC Bank Fut
+BUY
+PRICE ▶ 724.15
+TARGET ▶ 730, 738, 745
+STOP LOSS ▶ 710</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>738</v>
+      </c>
+      <c r="F486" t="n">
+        <v>710</v>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+HDFC Bank Fut
+BUY
+PRICE ▶ 724.15
+TARGET ▶ 730, 738, 745
+STOP LOSS ▶ 710</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="E487" t="n">
+        <v>745</v>
+      </c>
+      <c r="F487" t="n">
+        <v>710</v>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+HDFC Bank Fut
+BUY
+PRICE ▶ 724.15
+TARGET ▶ 730, 738, 745
+STOP LOSS ▶ 710</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E488" t="n">
+        <v>888</v>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>CALLS HDFC Bank OVERWEIGHT लक्ष्य ₹888</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E489" t="n">
+        <v>990</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>JP Morgan</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>JP मॉर्गन
+HDFC Bank
+720.30 +1.31%
+OVERWEIGHT
+लक्ष्य ₹990</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>1422.8</v>
+      </c>
+      <c r="E490" t="n">
+        <v>1446</v>
+      </c>
+      <c r="F490" t="n">
+        <v>1413</v>
+      </c>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT ICICI BANK B 1446 1413</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E491" t="n">
+        <v>773</v>
+      </c>
+      <c r="F491" t="n">
+        <v>694</v>
+      </c>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>FUNDA HDFC BANK B 773 694</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="E492" t="n">
+        <v>636</v>
+      </c>
+      <c r="F492" t="n">
+        <v>597</v>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>TECHNO KPIT TECH B 636 597</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>TATAELXSI29SEP26</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>3710</v>
+      </c>
+      <c r="E493" t="n">
+        <v>3645</v>
+      </c>
+      <c r="F493" t="n">
+        <v>3756</v>
+      </c>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>FUTURE TATA ELXSI FUT S 3645 3756</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ONGC29SEP26</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>233.81</v>
+      </c>
+      <c r="E494" t="n">
+        <v>237</v>
+      </c>
+      <c r="F494" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>FUTURE ONGC FUT B 237 231.5</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>421</v>
+      </c>
+      <c r="E495" t="n">
+        <v>455</v>
+      </c>
+      <c r="F495" t="n">
+        <v>408</v>
+      </c>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>FUNDA KOTAK BANK B 455 408</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>632</v>
+      </c>
+      <c r="E496" t="n">
+        <v>644</v>
+      </c>
+      <c r="F496" t="n">
+        <v>621</v>
+      </c>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>TECHNO ELGI EQUIPMENT B 644 621</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>2341</v>
+      </c>
+      <c r="E497" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F497" t="n">
+        <v>2313</v>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+TCS
+खरीदें
+PRICE 2342.00
+TARGET 2400
+STOP LOSS 2313</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>MANAPPURAM29SEP26</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>346.45</v>
+      </c>
+      <c r="E498" t="n">
+        <v>970</v>
+      </c>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+BUY
+लक्ष्य ₹970</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>1655</v>
+      </c>
+      <c r="E499" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS OVERWEIGHT लक्ष्य ₹1705 से बढ़ाकर ₹1820</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>142.88</v>
+      </c>
+      <c r="E500" t="n">
+        <v>118</v>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Bank of India 144.00 UNDERWEIGHT लक्ष्य ₹115 से बढ़ाकर ₹118</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>1426.5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1446</v>
+      </c>
+      <c r="F501" t="n">
+        <v>1413</v>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>अंश के शेयर ICICI Bank खरीदें PRICE 1422.80 TARGET 1446 STOP LOSS 1413</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>12196</v>
+      </c>
+      <c r="E502" t="n">
+        <v>13200</v>
+      </c>
+      <c r="F502" t="n">
+        <v>11700</v>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+Oracle Fin
+खरीदें
+PRICE ▶ 12190.00
+TARGET ▶ 13200
+STOP LOSS ▶ 11700</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E503" t="n">
+        <v>773</v>
+      </c>
+      <c r="F503" t="n">
+        <v>694</v>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>FUNDA PICK HDFC Bank खरीदें PRICE 720.30 TARGET 773 STOP LOSS 694</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>421</v>
+      </c>
+      <c r="E504" t="n">
+        <v>455</v>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>FUNDA PICK Kotak Bank खरीदें PRICE 423.70 TARGET 455 DURATION 408</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E505" t="n">
+        <v>970</v>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS HDFC Bank BUY लक्ष्य ₹970</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>632</v>
+      </c>
+      <c r="E506" t="n">
+        <v>644</v>
+      </c>
+      <c r="F506" t="n">
+        <v>621</v>
+      </c>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>TECHNO PICK
+Elgi Equipments
+खरीदें
+PRICE ▶ 628.85
+TARGET ▶ 644
+STOP LOSS ▶ 621</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="E507" t="n">
+        <v>636</v>
+      </c>
+      <c r="F507" t="n">
+        <v>597</v>
+      </c>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>TECHNO PICK KPIT Tech खरीदें PRICE 609.40 TARGET 636 STOP LOSS 597</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E508" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>PB Fintech 1811.50 -26.40, UNDERWEIGHT, लक्ष्य ₹1215 से बढ़ाकर ₹1390</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>ASHOKLEY17529SEP26CE</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="E509" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F509" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>BEST ऑप्शन Ashok Leyland 175 की कॉल @ 6 खरीदें STOP LOSS 4.5 TARGET 9.5 Ashok Leyland 175.77</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>ONGC29SEP26</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>234.26</v>
+      </c>
+      <c r="E510" t="n">
+        <v>237</v>
+      </c>
+      <c r="F510" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर ONGC Fut खरीदें PRICE 233.39 TARGET 237 STOP LOSS 231.5</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>725.55</v>
+      </c>
+      <c r="E511" t="n">
+        <v>970</v>
+      </c>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>सिटी HDFC Bank 720.30 +1.31% BUY लक्ष्य ₹970</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>TATAELXSI29SEP26</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>3710</v>
+      </c>
+      <c r="E512" t="n">
+        <v>3645</v>
+      </c>
+      <c r="F512" t="n">
+        <v>3756</v>
+      </c>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>आज का FUTURE Tata Elxsi Fut बेचें PRICE 3718.80 TARGET 3645 STOP LOSS 3756</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="E513" t="n">
+        <v>465</v>
+      </c>
+      <c r="F513" t="n">
+        <v>434</v>
+      </c>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+Exide Ind
+खरीदें
+PRICE ▶ 444.60
+TARGET ▶ 465
+STOP LOSS ▶ 434</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>1041.2</v>
+      </c>
+      <c r="E514" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>SBI CALL EQUAL WEIGHT OLD TGT 1070 NEW TGT 1120</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>723.05</v>
+      </c>
+      <c r="E515" t="n">
+        <v>880</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>HDFC Bank पर ब्रोकरेज जेफरीज BUY 1050 880</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>781</v>
+      </c>
+      <c r="E516" t="n">
+        <v>810</v>
+      </c>
+      <c r="F516" t="n">
+        <v>758</v>
+      </c>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>AGI Greenpac Ltd खरीदें PRICE 774.80 TARGET 810/830 STOP LOSS 758</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>781</v>
+      </c>
+      <c r="E517" t="n">
+        <v>830</v>
+      </c>
+      <c r="F517" t="n">
+        <v>758</v>
+      </c>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय AGI Greenpac Ltd खरीदें PRICE 774.80 TARGET 810/830 STOP LOSS 758</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="E518" t="n">
+        <v>1045</v>
+      </c>
+      <c r="F518" t="n">
+        <v>999</v>
+      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>Premier Energies खरीदें PRICE 1013.90 TARGET 1035/1045 STOP LOSS 999</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F519" t="n">
+        <v>999</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला Ltd Premier Energies 5.03% खरीदें PRICE 1013.90 TARGET 1035/1045 STOP LOSS 999 BROKERAGE CALLS सिद्धार्थ राय मंगला Sidinvesting Financial Services</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>1422.8</v>
+      </c>
+      <c r="E520" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली
+ICICI Bank
+1422.80 -20.20
+OVERWEIGHT
+लक्ष्य ₹1705 से बढ़ाकर ₹1820
+सिद्धार्थ राय मंगला
+Sidinvesting Financial Services</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>421</v>
+      </c>
+      <c r="E521" t="n">
+        <v>535</v>
+      </c>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली Kotak Bank 423.70 -0.12% OVERWEIGHT लक्ष्य ₹500 से बढ़ाकर ₹535</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>1811</v>
+      </c>
+      <c r="E522" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>मॉर्गन स्टैनली
+PB Fintech
+1811.50 -1.44%
+UNDERWEIGHT
+लक्ष्य ₹1215 से बढ़ाकर ₹1390</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>1041.2</v>
+      </c>
+      <c r="E523" t="n">
+        <v>119</v>
+      </c>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+UNDERWEIGHT
+लक्ष्य ₹115 से बढ़ाकर ₹119</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>LINCOLN</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="E524" t="n">
+        <v>640</v>
+      </c>
+      <c r="F524" t="n">
+        <v>601</v>
+      </c>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>संदीप जैन की पसंद Lincoln Ph BUY TARGET 640-650 STOP LOSS 601 Lincoln Ph 614.95 ↑ 0.95</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>LINCOLN</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="E525" t="n">
+        <v>650</v>
+      </c>
+      <c r="F525" t="n">
+        <v>601</v>
+      </c>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>संदीप जैन की पसंद Lincoln Ph BUY TARGET 640-650 STOP LOSS 601 Lincoln Ph 614.95 ↑ 0.95</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F526" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>APL Apollo 2265.60 BUY STOP LOSS 77.6</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>299</v>
+      </c>
+      <c r="E527" t="n">
+        <v>350</v>
+      </c>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>संदीप जैन की पसंद SCI BUY TARGET 350-360 DURATION 6-12 महीने SCI 299.05 6.50</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>299</v>
+      </c>
+      <c r="E528" t="n">
+        <v>360</v>
+      </c>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>संदीप जैन की पसंद SCI BUY TARGET 350-360 DURATION 6-12 महीने SCI 299.05 6.50</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:15:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>KIRLFER</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>450.3</v>
+      </c>
+      <c r="E529" t="n">
+        <v>510</v>
+      </c>
+      <c r="F529" t="n">
+        <v>430</v>
+      </c>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>सदाप जन का पसंद Kirloskar Ferrous BUY TARGET 510 STOP LOSS 430 Kirloskar Ferrous 449.85 ▲ 0.50%</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-31 09:16:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>KIRLFER</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>450.2</v>
+      </c>
+      <c r="F530" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>Kirloskar Ferrous 449.35 BUY STOP LOSS 2.2</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J341"/>
+  <autoFilter ref="A1:J530"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$530</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$652</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J530"/>
+  <dimension ref="A1:J652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -15680,7 +15680,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
       <c r="E342" t="n">
         <v>888</v>
       </c>
@@ -15730,7 +15729,6 @@
       <c r="F343" t="n">
         <v>425</v>
       </c>
-      <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr">
         <is>
           <t>सदाबहार सेठी साब
@@ -15774,7 +15772,6 @@
       <c r="E344" t="n">
         <v>9350</v>
       </c>
-      <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr">
         <is>
           <t>SUPER SID Polycab India 9185.50 97.50 BUY TGT 9350 SL --</t>
@@ -15807,14 +15804,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="n">
         <v>265</v>
       </c>
       <c r="F345" t="n">
         <v>246</v>
       </c>
-      <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>EIL 261.61 7.89 BUY TGT 265 SL 246</t>
@@ -15856,7 +15851,6 @@
       <c r="F346" t="n">
         <v>575</v>
       </c>
-      <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -16077,11 +16071,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
       <c r="E351" t="n">
         <v>1850</v>
       </c>
-      <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr">
         <is>
           <t>JP मॉर्गन OVERWEIGHT 1570 1850</t>
@@ -16123,7 +16115,6 @@
       <c r="F352" t="n">
         <v>1425</v>
       </c>
-      <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -16170,7 +16161,6 @@
       <c r="F353" t="n">
         <v>1480</v>
       </c>
-      <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr">
         <is>
           <t>EXPIRY TRADE Cochin Shipyard Fut BUY PRICE 1517.20 TARGET 1600 STOP LOSS 1480</t>
@@ -16212,7 +16202,6 @@
       <c r="F354" t="n">
         <v>1750</v>
       </c>
-      <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr">
         <is>
           <t>Bharti Airtel Fut BUY PRICE 1894.00 TARGET 1940 STOP LOSS 1750</t>
@@ -16245,7 +16234,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
       <c r="E355" t="n">
         <v>175</v>
       </c>
@@ -16295,7 +16283,6 @@
       <c r="E356" t="n">
         <v>825</v>
       </c>
-      <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr">
         <is>
           <t>शुगर सेक्टर पर DAM कैपिटल की राय Balrampur Chini खरीदें, टार्गेट ₹825 Balrampur Chini 724.60 ▲ 10.65%</t>
@@ -16334,7 +16321,6 @@
       <c r="E357" t="n">
         <v>710</v>
       </c>
-      <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr">
         <is>
           <t>शुगर सेक्टर पर DAM कैपिटल की राय
@@ -16376,7 +16362,6 @@
       <c r="E358" t="n">
         <v>415</v>
       </c>
-      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr">
         <is>
           <t>Triveni Engineering खरीदने की राय, टार्गेट ₹415</t>
@@ -16418,7 +16403,6 @@
       <c r="F359" t="n">
         <v>425</v>
       </c>
-      <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr">
         <is>
           <t>सदाबहार सेठी सा'ब Harsha Engineers 445.60 6.75 BUY TGT 470 SL 425</t>
@@ -16457,7 +16441,6 @@
       <c r="E360" t="n">
         <v>9350</v>
       </c>
-      <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -16504,7 +16487,6 @@
       <c r="F361" t="n">
         <v>1425</v>
       </c>
-      <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शोयर
@@ -16548,7 +16530,6 @@
       <c r="E362" t="n">
         <v>1475</v>
       </c>
-      <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
           <t>ICICI Bank 1449.70 26.90 BUY TGT 1475</t>
@@ -16590,7 +16571,6 @@
       <c r="F363" t="n">
         <v>413</v>
       </c>
-      <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -16628,14 +16608,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
       <c r="E364" t="n">
         <v>265</v>
       </c>
       <c r="F364" t="n">
         <v>246</v>
       </c>
-      <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट EIL 258.20 4.48 BUY TGT 265 SL 246</t>
@@ -16677,7 +16655,6 @@
       <c r="F365" t="n">
         <v>575</v>
       </c>
-      <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -16724,7 +16701,6 @@
       <c r="F366" t="n">
         <v>525</v>
       </c>
-      <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
           <t>Mehul
@@ -17054,7 +17030,6 @@
       <c r="E373" t="n">
         <v>800</v>
       </c>
-      <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr">
         <is>
           <t>SUPER SID CAMS खरीदें PRICE 780.25 TARGET 800/940 STOP LOSS --</t>
@@ -17093,7 +17068,6 @@
       <c r="E374" t="n">
         <v>940</v>
       </c>
-      <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr">
         <is>
           <t>SUPER SID CAMS खरीदें PRICE 780.25 TARGET 800/940 STOP LOSS --</t>
@@ -17172,7 +17146,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
       <c r="E376" t="n">
         <v>1490</v>
       </c>
@@ -17221,7 +17194,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
       <c r="E377" t="n">
         <v>1430</v>
       </c>
@@ -17276,7 +17248,6 @@
       <c r="E378" t="n">
         <v>9350</v>
       </c>
-      <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr">
         <is>
           <t>SUPER SID Polycab India खरीदें PRICE 9160.50 TARGET 9350/10600 STOP LOSS --</t>
@@ -17315,7 +17286,6 @@
       <c r="E379" t="n">
         <v>10600</v>
       </c>
-      <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr">
         <is>
           <t>SUPER SID Polycab India खरीदें PRICE 9160.50 TARGET 9350/10600 STOP LOSS --</t>
@@ -17440,14 +17410,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
       <c r="E382" t="n">
         <v>57450</v>
       </c>
       <c r="F382" t="n">
         <v>56900</v>
       </c>
-      <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17484,14 +17452,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
       <c r="E383" t="n">
         <v>57500</v>
       </c>
       <c r="F383" t="n">
         <v>56900</v>
       </c>
-      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17528,14 +17494,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
       <c r="E384" t="n">
         <v>57600</v>
       </c>
       <c r="F384" t="n">
         <v>56900</v>
       </c>
-      <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17572,14 +17536,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
       <c r="E385" t="n">
         <v>57675</v>
       </c>
       <c r="F385" t="n">
         <v>56900</v>
       </c>
-      <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17616,14 +17578,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
       <c r="E386" t="n">
         <v>57750</v>
       </c>
       <c r="F386" t="n">
         <v>56900</v>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17660,14 +17620,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
       <c r="E387" t="n">
         <v>57875</v>
       </c>
       <c r="F387" t="n">
         <v>56900</v>
       </c>
-      <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17704,14 +17662,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
       <c r="E388" t="n">
         <v>57975</v>
       </c>
       <c r="F388" t="n">
         <v>56900</v>
       </c>
-      <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr">
         <is>
           <t>एग्रेसिव ट्रेडर्स 57050-57275 रेंज में खरीदें
@@ -17757,7 +17713,6 @@
       <c r="F389" t="n">
         <v>595</v>
       </c>
-      <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr">
         <is>
           <t>Indegene खरीदें PRICE 607.30 TARGET 650 STOP LOSS 595</t>
@@ -17796,7 +17751,6 @@
       <c r="E390" t="n">
         <v>825</v>
       </c>
-      <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr">
         <is>
           <t>शुगर सेक्टर पर DAM कैपिटल की राय Balrampur Chini खरीदें, टार्गेट ₹825 Balrampur Chini 721.75 ▲ 66.90</t>
@@ -17835,7 +17789,6 @@
       <c r="E391" t="n">
         <v>710</v>
       </c>
-      <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr">
         <is>
           <t>शुगर सेक्टर पर DAM कैपिटल की राय Dalmia Bharat Sugar खरीदें, टार्गेट ₹710 Dalmia Bharat Sugar 491.90 ▲ 13.95</t>
@@ -17874,7 +17827,6 @@
       <c r="E392" t="n">
         <v>415</v>
       </c>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr">
         <is>
           <t>Triveni Engineering खरीदने की राय, टार्गेट ₹415</t>
@@ -18101,14 +18053,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
       <c r="E397" t="n">
         <v>9350</v>
       </c>
       <c r="F397" t="n">
         <v>9225</v>
       </c>
-      <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr">
         <is>
           <t>Polycab India Ltd Fut खरीदें PRICE 9244.00 TARGET 9300/9350 STOP LOSS 9225</t>
@@ -18141,14 +18091,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
       <c r="E398" t="n">
         <v>9300</v>
       </c>
       <c r="F398" t="n">
         <v>9225</v>
       </c>
-      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr">
         <is>
           <t>Polycab India Ltd Fut खरीदें PRICE 9244.00 TARGET 9300/9350 STOP LOSS 9225</t>
@@ -18190,7 +18138,6 @@
       <c r="F399" t="n">
         <v>1275</v>
       </c>
-      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr">
         <is>
           <t>UNO Minda Fut खरीदें PRICE 1293.30 TARGET 1320/1335 STOP LOSS 1275</t>
@@ -18232,7 +18179,6 @@
       <c r="F400" t="n">
         <v>1275</v>
       </c>
-      <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr">
         <is>
           <t>TRADING CALL
@@ -18270,14 +18216,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
       <c r="E401" t="n">
         <v>135</v>
       </c>
       <c r="F401" t="n">
         <v>65</v>
       </c>
-      <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr">
         <is>
           <t>निफ्टी 24300 की कॉल @ 85-90 खरीदें STOP LOSS 65 TARGET 120/135</t>
@@ -18310,14 +18254,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
       <c r="E402" t="n">
         <v>120</v>
       </c>
       <c r="F402" t="n">
         <v>65</v>
       </c>
-      <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr">
         <is>
           <t>निफ्टी 24300 की कॉल @ 85-90 खरीदें STOP LOSS 65 TARGET 120/135</t>
@@ -18359,7 +18301,6 @@
       <c r="F403" t="n">
         <v>175</v>
       </c>
-      <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय
@@ -18407,7 +18348,6 @@
       <c r="F404" t="n">
         <v>175</v>
       </c>
-      <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr">
         <is>
           <t>राजेश पालविया को राय
@@ -18453,7 +18393,6 @@
       <c r="F405" t="n">
         <v>495</v>
       </c>
-      <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr">
         <is>
           <t>Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 Shanthi Gears 529.90 2.35%</t>
@@ -18495,7 +18434,6 @@
       <c r="F406" t="n">
         <v>495</v>
       </c>
-      <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr">
         <is>
           <t>Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 DURATION -- Shanthi Gears 529.90 12.15 ऑटो शेयर</t>
@@ -18537,7 +18475,6 @@
       <c r="F407" t="n">
         <v>385</v>
       </c>
-      <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr">
         <is>
           <t>SHORT MIDCAP STOCKS Mamata Machinery खरीदें STOP LOSS 385 TARGET 430 DURATION -- Mamata Machinery 404.90 ▲ 1.21%</t>
@@ -18629,7 +18566,6 @@
       <c r="F409" t="n">
         <v>360</v>
       </c>
-      <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr">
         <is>
           <t>POSITIONAL MEDICAL STOCK Apollo Micro Systems खरीदें STOP LOSS 360 TARGET 435 DURATION</t>
@@ -18671,7 +18607,6 @@
       <c r="F410" t="n">
         <v>495</v>
       </c>
-      <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Shanthi Gears खरीदें STOP LOSS 495 TARGET 600/620 DURATION -- Shanthi Gears 530.50 12.75</t>
@@ -18713,7 +18648,6 @@
       <c r="F411" t="n">
         <v>1940</v>
       </c>
-      <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय
@@ -18761,7 +18695,6 @@
       <c r="F412" t="n">
         <v>1940</v>
       </c>
-      <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय
@@ -18809,7 +18742,6 @@
       <c r="F413" t="n">
         <v>1940</v>
       </c>
-      <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr">
         <is>
           <t>eClerx Services PRICE 2001.00 TARGET 2100/2150 STOP LOSS 1940</t>
@@ -18842,11 +18774,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
       <c r="E414" t="n">
         <v>265</v>
       </c>
-      <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr">
         <is>
           <t>EIL 254.84 1.12 BUY TGT 265</t>
@@ -18888,7 +18818,6 @@
       <c r="F415" t="n">
         <v>575</v>
       </c>
-      <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -18926,11 +18855,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
       <c r="E416" t="n">
         <v>275</v>
       </c>
-      <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr">
         <is>
           <t>संदीप जैन Northern Arc Capital 311.90 9.09% BUY TARGET HIT 275</t>
@@ -18963,14 +18890,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="n">
         <v>310</v>
       </c>
       <c r="F417" t="n">
         <v>275</v>
       </c>
-      <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr">
         <is>
           <t>संदीप जैन Northern Arc Capital 311.90 9.09% BUY TGT 310 SL 275</t>
@@ -19003,14 +18928,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
       <c r="E418" t="n">
         <v>1850</v>
       </c>
       <c r="F418" t="n">
         <v>1610</v>
       </c>
-      <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr">
         <is>
           <t>आस्था जन की राय CARE Ltd खरीदें PRICE 1740.00 TARGET 1850/1880 STOP LOSS 1610</t>
@@ -19043,14 +18966,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="n">
         <v>1880</v>
       </c>
       <c r="F419" t="n">
         <v>1610</v>
       </c>
-      <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr">
         <is>
           <t>CARE Ltd खरीदें PRICE 1740.00 TARGET 1850/1880 STOP LOSS 1610</t>
@@ -19092,7 +19013,6 @@
       <c r="F420" t="n">
         <v>1610</v>
       </c>
-      <c r="G420" t="inlineStr"/>
       <c r="H420" t="inlineStr">
         <is>
           <t>CARE Ltd खरीदें PRICE 1741.60 TARGET 1850/1880 STOP LOSS 1610</t>
@@ -19134,7 +19054,6 @@
       <c r="F421" t="n">
         <v>1610</v>
       </c>
-      <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr">
         <is>
           <t>CARE Ltd खरीदें PRICE 1741.60 TARGET 1850/1880 STOP LOSS 1610</t>
@@ -19311,7 +19230,6 @@
       <c r="E425" t="n">
         <v>340</v>
       </c>
-      <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -19441,11 +19359,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
       <c r="E428" t="n">
         <v>4500</v>
       </c>
-      <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr">
         <is>
           <t>Swaraj खरीदें PRICE 3586.00 TARGET 4500 DURATION 6</t>
@@ -19484,7 +19400,6 @@
       <c r="E429" t="n">
         <v>4500</v>
       </c>
-      <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr">
         <is>
           <t>Swaraj Engine खरीदें PRICE 3582.00 TARGET 4500 STOP LOSS —</t>
@@ -19517,11 +19432,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
       <c r="E430" t="n">
         <v>275</v>
       </c>
-      <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Northern Arc Capital 309.25 23.35 BUY TARGET HIT 275</t>
@@ -19563,7 +19476,6 @@
       <c r="F431" t="n">
         <v>275</v>
       </c>
-      <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr">
         <is>
           <t>संदीप जैन Northern Arc Capital 309.25 23.35 BUY TGT 310 SL 275</t>
@@ -19605,7 +19517,6 @@
       <c r="F432" t="n">
         <v>630</v>
       </c>
-      <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -19643,7 +19554,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
       <c r="E433" t="n">
         <v>32</v>
       </c>
@@ -19687,7 +19597,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
       <c r="E434" t="n">
         <v>38</v>
       </c>
@@ -19731,11 +19640,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
       <c r="F435" t="n">
         <v>1025</v>
       </c>
-      <c r="G435" t="inlineStr"/>
       <c r="H435" t="inlineStr">
         <is>
           <t>AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
@@ -19774,7 +19681,6 @@
       <c r="E436" t="n">
         <v>788</v>
       </c>
-      <c r="G436" t="inlineStr"/>
       <c r="H436" t="inlineStr">
         <is>
           <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
@@ -19813,7 +19719,6 @@
       <c r="E437" t="n">
         <v>340</v>
       </c>
-      <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr">
         <is>
           <t>Euro Pratik Sales 263.25 5.80 BUY TGT 340 SL --</t>
@@ -19846,14 +19751,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
       <c r="E438" t="n">
         <v>265</v>
       </c>
       <c r="F438" t="n">
         <v>246</v>
       </c>
-      <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr">
         <is>
           <t>EIL 254.35 0.63 BUY TGT 265 SL 246</t>
@@ -19895,7 +19798,6 @@
       <c r="F439" t="n">
         <v>575</v>
       </c>
-      <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -19933,11 +19835,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
       <c r="E440" t="n">
         <v>275</v>
       </c>
-      <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Northern Arc Capital 310.25 BUY TARGET HIT 275</t>
@@ -19970,14 +19870,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
       <c r="E441" t="n">
         <v>310</v>
       </c>
       <c r="F441" t="n">
         <v>275</v>
       </c>
-      <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr">
         <is>
           <t>Northern Arc Capital 310.25 24.35 BUY TGT 310 SL 275</t>
@@ -20010,11 +19908,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
       <c r="E442" t="n">
         <v>310</v>
       </c>
-      <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Northern Arc Capital 310.25 24.35 BUY TGT 310</t>
@@ -20053,7 +19949,6 @@
       <c r="F443" t="n">
         <v>1025</v>
       </c>
-      <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr">
         <is>
           <t>AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
@@ -20086,11 +19981,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
       <c r="E444" t="n">
         <v>1025</v>
       </c>
-      <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr">
         <is>
           <t>AUGMONT
@@ -20131,7 +20024,6 @@
       <c r="E445" t="n">
         <v>350</v>
       </c>
-      <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Euro Pratik Sales खरीदें PRICE 265.45 TARGET 340/350 STOP LOSS --</t>
@@ -20170,7 +20062,6 @@
       <c r="E446" t="n">
         <v>340</v>
       </c>
-      <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr">
         <is>
           <t>संतीप जैन की राय Euro Pratik Sales खरीदें PRICE 265.45 TARGET 340/350 STOP LOSS --</t>
@@ -20203,11 +20094,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
       <c r="F447" t="n">
         <v>1025</v>
       </c>
-      <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr">
         <is>
           <t>Euro Pratik Sales 264.90 ▲ 2.89% TODAY 267 HIGH 267.20 LOW 254.40 Vol: 65.97 k AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
@@ -20240,14 +20129,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
       <c r="E448" t="n">
         <v>1050</v>
       </c>
       <c r="F448" t="n">
         <v>1075</v>
       </c>
-      <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr">
         <is>
           <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
@@ -20280,14 +20167,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
       <c r="E449" t="n">
         <v>1075</v>
       </c>
       <c r="F449" t="n">
         <v>1050</v>
       </c>
-      <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr">
         <is>
           <t>AUGMONT लिस्टिंग पर राय ₹1050-1075 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹788</t>
@@ -20329,7 +20214,6 @@
       <c r="F450" t="n">
         <v>1644</v>
       </c>
-      <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr">
         <is>
           <t>OPENING का HERO Ather Energy Fut 1672.30 ▲ 48.40 TODAY 1683 HIGH 1683.00 LOW 1644.10 Vol: 704.25 k 1644 09:15 AM 09:27 AM</t>
@@ -20362,11 +20246,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
       <c r="E451" t="n">
         <v>48.4</v>
       </c>
-      <c r="G451" t="inlineStr"/>
       <c r="H451" t="inlineStr">
         <is>
           <t>OPENING का HERO Ather Energy Fut 1672.30 ▲ 48.40 TODAY 1683 HIGH 1683.00 LOW 1644.10 Vol: 704.25 k</t>
@@ -20399,14 +20281,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
       <c r="E452" t="n">
         <v>265</v>
       </c>
       <c r="F452" t="n">
         <v>246</v>
       </c>
-      <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -20444,14 +20324,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="n">
         <v>275</v>
       </c>
       <c r="F453" t="n">
         <v>246</v>
       </c>
-      <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -20489,11 +20367,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
       <c r="E454" t="n">
         <v>265</v>
       </c>
-      <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय EIL PRICE 257.15 TARGET 265/275</t>
@@ -20526,11 +20402,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
       <c r="E455" t="n">
         <v>275</v>
       </c>
-      <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय EIL PRICE 257.15 TARGET 265/275</t>
@@ -20569,7 +20443,6 @@
       <c r="E456" t="n">
         <v>630</v>
       </c>
-      <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr">
         <is>
           <t>Hindustan Zinc 595.25 26.75 BUY TGT 630</t>
@@ -20602,11 +20475,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
       <c r="F457" t="n">
         <v>1025</v>
       </c>
-      <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr">
         <is>
           <t>Nifty 50 Fut Prem 24210.80, 134.20 इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं Mon 31 Aug'26</t>
@@ -20645,7 +20516,6 @@
       <c r="F458" t="n">
         <v>1025</v>
       </c>
-      <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr">
         <is>
           <t>इन्वेस्टेस्ट ₹1025 के नीचे का SL लगाएं</t>
@@ -20678,11 +20548,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
       <c r="F459" t="n">
         <v>1025</v>
       </c>
-      <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr">
         <is>
           <t>Eternal (Zomato) 332.20 4.20 1.28% Vol: 3.08 m AUGMONT लिस्टिंग पर राय इन्वेस्टर्स ₹1025 के नीचे का SL लगाएं</t>
@@ -20724,7 +20592,6 @@
       <c r="F460" t="n">
         <v>575</v>
       </c>
-      <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -20771,7 +20638,6 @@
       <c r="F461" t="n">
         <v>575</v>
       </c>
-      <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr">
         <is>
           <t>मेहुल कोठारी की राय
@@ -20818,7 +20684,6 @@
       <c r="F462" t="n">
         <v>710</v>
       </c>
-      <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -20955,7 +20820,6 @@
       <c r="F465" t="n">
         <v>553</v>
       </c>
-      <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की राय
@@ -21002,7 +20866,6 @@
       <c r="F466" t="n">
         <v>553</v>
       </c>
-      <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की राय
@@ -21049,7 +20912,6 @@
       <c r="F467" t="n">
         <v>553</v>
       </c>
-      <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की राय
@@ -21093,7 +20955,6 @@
       <c r="E468" t="n">
         <v>535</v>
       </c>
-      <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr">
         <is>
           <t>मॉर्गन स्टैनली Kotak Bank 422.30 -1.40 OVERWEIGHT लक्ष्य ₹500 से बढ़ाकर ₹535</t>
@@ -21179,7 +21040,6 @@
       <c r="E470" t="n">
         <v>13200</v>
       </c>
-      <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr">
         <is>
           <t>INVESTMENT ORACLE B 13200 1</t>
@@ -21218,7 +21078,6 @@
       <c r="E471" t="n">
         <v>1446</v>
       </c>
-      <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr">
         <is>
           <t>NEWS IMPACT ICICI BANK B 1446</t>
@@ -21260,7 +21119,6 @@
       <c r="F472" t="n">
         <v>434</v>
       </c>
-      <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr">
         <is>
           <t>CASH EXIDE IND B 465 434</t>
@@ -21302,7 +21160,6 @@
       <c r="F473" t="n">
         <v>5150</v>
       </c>
-      <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr">
         <is>
           <t>MY CHOICE INTERGLOBE AVIATION FUT B 5300 5150</t>
@@ -21344,7 +21201,6 @@
       <c r="F474" t="n">
         <v>930</v>
       </c>
-      <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Windlas Biotech BUY PRICE 998.55 TARGET 1190 STOP LOSS 930</t>
@@ -21386,7 +21242,6 @@
       <c r="F475" t="n">
         <v>13150</v>
       </c>
-      <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Maha Scooters BUY PRICE 1366.00 TARGET 14950 STOP LOSS 13150</t>
@@ -21428,7 +21283,6 @@
       <c r="F476" t="n">
         <v>1390</v>
       </c>
-      <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr">
         <is>
           <t>PICK OF THE WEEK Cipla BUY PRICE 1423.50 TARGET 1460 STOP LOSS 1390</t>
@@ -21515,7 +21369,6 @@
       <c r="E478" t="n">
         <v>1025</v>
       </c>
-      <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr">
         <is>
           <t>मॉर्गन स्टैनली OVERWEIGHT 1025 --</t>
@@ -21557,7 +21410,6 @@
       <c r="F479" t="n">
         <v>1590</v>
       </c>
-      <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Pidilite Ind BUY PRICE 1629.50 TARGET 1680/1700 STOP LOSS 1590</t>
@@ -21599,7 +21451,6 @@
       <c r="F480" t="n">
         <v>1590</v>
       </c>
-      <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Pidilite Ind BUY PRICE 1629.50 TARGET 1680/1700 STOP LOSS 1590</t>
@@ -21641,7 +21492,6 @@
       <c r="F481" t="n">
         <v>609</v>
       </c>
-      <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr">
         <is>
           <t>Elgi Equipments BUY PRICE 628.85 TARGET 665/680 STOP LOSS 609</t>
@@ -21772,7 +21622,6 @@
       <c r="E484" t="n">
         <v>1300</v>
       </c>
-      <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr">
         <is>
           <t>RIL 1300 के बड़े सपोर्ट के नीचे
@@ -21815,7 +21664,6 @@
       <c r="F485" t="n">
         <v>710</v>
       </c>
-      <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -21862,7 +21710,6 @@
       <c r="F486" t="n">
         <v>710</v>
       </c>
-      <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -21909,7 +21756,6 @@
       <c r="F487" t="n">
         <v>710</v>
       </c>
-      <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -21953,7 +21799,6 @@
       <c r="E488" t="n">
         <v>888</v>
       </c>
-      <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr">
         <is>
           <t>CALLS HDFC Bank OVERWEIGHT लक्ष्य ₹888</t>
@@ -22042,7 +21887,6 @@
       <c r="F490" t="n">
         <v>1413</v>
       </c>
-      <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr">
         <is>
           <t>NEWS IMPACT ICICI BANK B 1446 1413</t>
@@ -22084,7 +21928,6 @@
       <c r="F491" t="n">
         <v>694</v>
       </c>
-      <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr">
         <is>
           <t>FUNDA HDFC BANK B 773 694</t>
@@ -22126,7 +21969,6 @@
       <c r="F492" t="n">
         <v>597</v>
       </c>
-      <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr">
         <is>
           <t>TECHNO KPIT TECH B 636 597</t>
@@ -22168,7 +22010,6 @@
       <c r="F493" t="n">
         <v>3756</v>
       </c>
-      <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr">
         <is>
           <t>FUTURE TATA ELXSI FUT S 3645 3756</t>
@@ -22210,7 +22051,6 @@
       <c r="F494" t="n">
         <v>231.5</v>
       </c>
-      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr">
         <is>
           <t>FUTURE ONGC FUT B 237 231.5</t>
@@ -22252,7 +22092,6 @@
       <c r="F495" t="n">
         <v>408</v>
       </c>
-      <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr">
         <is>
           <t>FUNDA KOTAK BANK B 455 408</t>
@@ -22294,7 +22133,6 @@
       <c r="F496" t="n">
         <v>621</v>
       </c>
-      <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr">
         <is>
           <t>TECHNO ELGI EQUIPMENT B 644 621</t>
@@ -22336,7 +22174,6 @@
       <c r="F497" t="n">
         <v>2313</v>
       </c>
-      <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -22380,7 +22217,6 @@
       <c r="E498" t="n">
         <v>970</v>
       </c>
-      <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -22421,7 +22257,6 @@
       <c r="E499" t="n">
         <v>1820</v>
       </c>
-      <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS OVERWEIGHT लक्ष्य ₹1705 से बढ़ाकर ₹1820</t>
@@ -22460,7 +22295,6 @@
       <c r="E500" t="n">
         <v>118</v>
       </c>
-      <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Bank of India 144.00 UNDERWEIGHT लक्ष्य ₹115 से बढ़ाकर ₹118</t>
@@ -22502,7 +22336,6 @@
       <c r="F501" t="n">
         <v>1413</v>
       </c>
-      <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr">
         <is>
           <t>अंश के शेयर ICICI Bank खरीदें PRICE 1422.80 TARGET 1446 STOP LOSS 1413</t>
@@ -22544,7 +22377,6 @@
       <c r="F502" t="n">
         <v>11700</v>
       </c>
-      <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -22591,7 +22423,6 @@
       <c r="F503" t="n">
         <v>694</v>
       </c>
-      <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr">
         <is>
           <t>FUNDA PICK HDFC Bank खरीदें PRICE 720.30 TARGET 773 STOP LOSS 694</t>
@@ -22630,7 +22461,6 @@
       <c r="E504" t="n">
         <v>455</v>
       </c>
-      <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr">
         <is>
           <t>FUNDA PICK Kotak Bank खरीदें PRICE 423.70 TARGET 455 DURATION 408</t>
@@ -22669,7 +22499,6 @@
       <c r="E505" t="n">
         <v>970</v>
       </c>
-      <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS HDFC Bank BUY लक्ष्य ₹970</t>
@@ -22711,7 +22540,6 @@
       <c r="F506" t="n">
         <v>621</v>
       </c>
-      <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr">
         <is>
           <t>TECHNO PICK
@@ -22758,7 +22586,6 @@
       <c r="F507" t="n">
         <v>597</v>
       </c>
-      <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr">
         <is>
           <t>TECHNO PICK KPIT Tech खरीदें PRICE 609.40 TARGET 636 STOP LOSS 597</t>
@@ -22797,7 +22624,6 @@
       <c r="E508" t="n">
         <v>1390</v>
       </c>
-      <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr">
         <is>
           <t>PB Fintech 1811.50 -26.40, UNDERWEIGHT, लक्ष्य ₹1215 से बढ़ाकर ₹1390</t>
@@ -22839,7 +22665,6 @@
       <c r="F509" t="n">
         <v>4.5</v>
       </c>
-      <c r="G509" t="inlineStr"/>
       <c r="H509" t="inlineStr">
         <is>
           <t>BEST ऑप्शन Ashok Leyland 175 की कॉल @ 6 खरीदें STOP LOSS 4.5 TARGET 9.5 Ashok Leyland 175.77</t>
@@ -22881,7 +22706,6 @@
       <c r="F510" t="n">
         <v>231.5</v>
       </c>
-      <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr">
         <is>
           <t>नेहा के शेयर ONGC Fut खरीदें PRICE 233.39 TARGET 237 STOP LOSS 231.5</t>
@@ -22920,7 +22744,6 @@
       <c r="E511" t="n">
         <v>970</v>
       </c>
-      <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr">
         <is>
           <t>सिटी HDFC Bank 720.30 +1.31% BUY लक्ष्य ₹970</t>
@@ -22962,7 +22785,6 @@
       <c r="F512" t="n">
         <v>3756</v>
       </c>
-      <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr">
         <is>
           <t>आज का FUTURE Tata Elxsi Fut बेचें PRICE 3718.80 TARGET 3645 STOP LOSS 3756</t>
@@ -23004,7 +22826,6 @@
       <c r="F513" t="n">
         <v>434</v>
       </c>
-      <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -23048,7 +22869,6 @@
       <c r="E514" t="n">
         <v>1120</v>
       </c>
-      <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr">
         <is>
           <t>SBI CALL EQUAL WEIGHT OLD TGT 1070 NEW TGT 1120</t>
@@ -23133,7 +22953,6 @@
       <c r="F516" t="n">
         <v>758</v>
       </c>
-      <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr">
         <is>
           <t>AGI Greenpac Ltd खरीदें PRICE 774.80 TARGET 810/830 STOP LOSS 758</t>
@@ -23175,7 +22994,6 @@
       <c r="F517" t="n">
         <v>758</v>
       </c>
-      <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr">
         <is>
           <t>सिद्धार्थ राय मंगला की राय AGI Greenpac Ltd खरीदें PRICE 774.80 TARGET 810/830 STOP LOSS 758</t>
@@ -23217,7 +23035,6 @@
       <c r="F518" t="n">
         <v>999</v>
       </c>
-      <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr">
         <is>
           <t>Premier Energies खरीदें PRICE 1013.90 TARGET 1035/1045 STOP LOSS 999</t>
@@ -23351,7 +23168,6 @@
       <c r="E521" t="n">
         <v>535</v>
       </c>
-      <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr">
         <is>
           <t>मॉर्गन स्टैनली Kotak Bank 423.70 -0.12% OVERWEIGHT लक्ष्य ₹500 से बढ़ाकर ₹535</t>
@@ -23437,7 +23253,6 @@
       <c r="E523" t="n">
         <v>119</v>
       </c>
-      <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -23481,7 +23296,6 @@
       <c r="F524" t="n">
         <v>601</v>
       </c>
-      <c r="G524" t="inlineStr"/>
       <c r="H524" t="inlineStr">
         <is>
           <t>संदीप जैन की पसंद Lincoln Ph BUY TARGET 640-650 STOP LOSS 601 Lincoln Ph 614.95 ↑ 0.95</t>
@@ -23523,7 +23337,6 @@
       <c r="F525" t="n">
         <v>601</v>
       </c>
-      <c r="G525" t="inlineStr"/>
       <c r="H525" t="inlineStr">
         <is>
           <t>संदीप जैन की पसंद Lincoln Ph BUY TARGET 640-650 STOP LOSS 601 Lincoln Ph 614.95 ↑ 0.95</t>
@@ -23562,7 +23375,6 @@
       <c r="F526" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr">
         <is>
           <t>APL Apollo 2265.60 BUY STOP LOSS 77.6</t>
@@ -23601,7 +23413,6 @@
       <c r="E527" t="n">
         <v>350</v>
       </c>
-      <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr">
         <is>
           <t>संदीप जैन की पसंद SCI BUY TARGET 350-360 DURATION 6-12 महीने SCI 299.05 6.50</t>
@@ -23640,7 +23451,6 @@
       <c r="E528" t="n">
         <v>360</v>
       </c>
-      <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr">
         <is>
           <t>संदीप जैन की पसंद SCI BUY TARGET 350-360 DURATION 6-12 महीने SCI 299.05 6.50</t>
@@ -23682,7 +23492,6 @@
       <c r="F529" t="n">
         <v>430</v>
       </c>
-      <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr">
         <is>
           <t>सदाप जन का पसंद Kirloskar Ferrous BUY TARGET 510 STOP LOSS 430 Kirloskar Ferrous 449.85 ▲ 0.50%</t>
@@ -23721,7 +23530,6 @@
       <c r="F530" t="n">
         <v>2.2</v>
       </c>
-      <c r="G530" t="inlineStr"/>
       <c r="H530" t="inlineStr">
         <is>
           <t>Kirloskar Ferrous 449.35 BUY STOP LOSS 2.2</t>
@@ -23738,8 +23546,5153 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:55:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>NAUKRI29SEP26</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>1368.5</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F531" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>Info Edge Fut खरीदें PRICE 1367.00 TARGET 1400/1430 STOP LOSS 1325</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:55:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>NAUKRI29SEP26</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>1368.5</v>
+      </c>
+      <c r="E532" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F532" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>Info Edge Fut खरीदें PRICE 1367.00 TARGET 1400/1430 STOP LOSS 1325</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:55:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>2641.8</v>
+      </c>
+      <c r="E533" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F533" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Caplin Point खरीदें STOP LOSS 2580 TARGET 2750/2780 DURATION -- Caplin Point 2642.70 ▲ 125.30</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:55:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>2641.8</v>
+      </c>
+      <c r="E534" t="n">
+        <v>2780</v>
+      </c>
+      <c r="F534" t="n">
+        <v>2580</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Caplin Point खरीदें STOP LOSS 2580 TARGET 2750/2780 DURATION -- Caplin Point 2642.70 ▲ 125.30</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:54:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>GUFICBIO</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="E535" t="n">
+        <v>470</v>
+      </c>
+      <c r="F535" t="n">
+        <v>401</v>
+      </c>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>SHORT MIDCAP STOCKS Gufic Bio खरीदें STOP LOSS 401 TARGET 460/470 DURATION -- Gufic Bio 421.00 5.95</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:54:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>GUFICBIO</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>419.5</v>
+      </c>
+      <c r="E536" t="n">
+        <v>460</v>
+      </c>
+      <c r="F536" t="n">
+        <v>401</v>
+      </c>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Gufic Bio खरीदें STOP LOSS 401 TARGET 460/470 DURATION -- Gufic Bio 421.00</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:53:29</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>GUJPETR</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+      <c r="E537" t="n">
+        <v>470</v>
+      </c>
+      <c r="F537" t="n">
+        <v>401</v>
+      </c>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>Gujarat Bio खरीदें STOP LOSS 401 TARGET 460/470</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:53:09</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="n">
+        <v>1630</v>
+      </c>
+      <c r="F538" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 4.90</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:53:09</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+      <c r="E539" t="n">
+        <v>1570</v>
+      </c>
+      <c r="F539" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 4.90</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:51:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>1435.5</v>
+      </c>
+      <c r="E540" t="n">
+        <v>1570</v>
+      </c>
+      <c r="F540" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 0.34%</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:51:00</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>1435.5</v>
+      </c>
+      <c r="E541" t="n">
+        <v>1630</v>
+      </c>
+      <c r="F541" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 0.34%</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:39:00</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>1248.9</v>
+      </c>
+      <c r="E542" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F542" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय
+Kajaria Ceramics
+खरीदें
+STOP LOSS 1200
+TARGET 1335/1350
+DURATION --
+Kajaria Ceramics 1248.00 ▲ 0.26%</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:39:00</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>1248.9</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F543" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Kajaria Ceramics खरीदें STOP LOSS 1200 TARGET 1335/1350 DURATION -- Kajaria Ceramics 1248.00 ▲ 3.20</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:38:00</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>657.2</v>
+      </c>
+      <c r="E544" t="n">
+        <v>730</v>
+      </c>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS --- TARGET 730/750 DURATION 6-12 महीने Vimta Labs 658.00 ▲ 2.26%</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:38:00</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>1441.9</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1570</v>
+      </c>
+      <c r="F545" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1437.40 ▼ 4.30</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:38:00</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>1441.9</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1630</v>
+      </c>
+      <c r="F546" t="n">
+        <v>1390</v>
+      </c>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1437.40 ▼ 4.30</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:38:00</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>657.2</v>
+      </c>
+      <c r="E547" t="n">
+        <v>750</v>
+      </c>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Vimta Labs खरीदें STOP LOSS --- TARGET 730/750 DURATION 6-12 महीने Vimta Labs 658.00 2.26%</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:36:18</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="n">
+        <v>730</v>
+      </c>
+      <c r="F548" t="n">
+        <v>750</v>
+      </c>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>सदापि जन का राय Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 2.04%</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:37:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>658.45</v>
+      </c>
+      <c r="E549" t="n">
+        <v>750</v>
+      </c>
+      <c r="F549" t="n">
+        <v>612</v>
+      </c>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:37:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>658.45</v>
+      </c>
+      <c r="E550" t="n">
+        <v>750</v>
+      </c>
+      <c r="F550" t="n">
+        <v>600</v>
+      </c>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 ▲ 13.10</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:37:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>VIMTALABS</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>658.45</v>
+      </c>
+      <c r="E551" t="n">
+        <v>750</v>
+      </c>
+      <c r="F551" t="n">
+        <v>6</v>
+      </c>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 2.04%</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:31:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>833.5</v>
+      </c>
+      <c r="E552" t="n">
+        <v>848</v>
+      </c>
+      <c r="F552" t="n">
+        <v>820</v>
+      </c>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Marico 834.10 14.10 BUY TGT 848 SL 820 Tue 01 Sep'26</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:22:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>629</v>
+      </c>
+      <c r="E553" t="n">
+        <v>665</v>
+      </c>
+      <c r="F553" t="n">
+        <v>600</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Elgi Equipments खरीदें STOP LOSS 600 TARGET 665/690 DURATION -- Elgi Equipments 630.10 0.44%</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:22:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>629</v>
+      </c>
+      <c r="E554" t="n">
+        <v>690</v>
+      </c>
+      <c r="F554" t="n">
+        <v>600</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Elgi Equipments खरीदें STOP LOSS 600 TARGET 665/690 DURATION -- Elgi Equipments 630.10 0.44%</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>1757.6</v>
+      </c>
+      <c r="E555" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS Nuvama Wealth 1759.10 5.50 BUY TGT 2030 SL --</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>TVSMOTOR29SEP26</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E556" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F556" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>TVS Motor Fut खरीदें PRICE 4415.90 TARGET 4500/4560 STOP LOSS 4360</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>TVSMOTOR29SEP26</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E557" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F557" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>TVS Motor Fut खरीदें PRICE 4415.90 TARGET 4500/4560 STOP LOSS 4360</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>403.45</v>
+      </c>
+      <c r="E558" t="n">
+        <v>415</v>
+      </c>
+      <c r="F558" t="n">
+        <v>395</v>
+      </c>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Coal India 403.55 1.80 BUY TGT 415 SL 395</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>TVSMOTOR29SEP26</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E559" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F559" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय TVS Motor Fut खरीदें PRICE 4417.50 TARGET 4500/4560 STOP LOSS 4360</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>TVSMOTOR29SEP26</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E560" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F560" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>TVS Motor Fut खरीदें PRICE 4414.60 TARGET 4500/4560 STOP LOSS 4360</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:07:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>TVSMOTOR29SEP26</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>4418</v>
+      </c>
+      <c r="E561" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F561" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>TVS Motor Fut खरीदें PRICE 4414.60 TARGET 4500/4560 STOP LOSS 4360</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-01 10:06:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>HEG</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>745.4</v>
+      </c>
+      <c r="E562" t="n">
+        <v>780</v>
+      </c>
+      <c r="F562" t="n">
+        <v>700</v>
+      </c>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>HEG Ltd खरीदें PRICE 746.10 TARGET 780/790 STOP LOSS 700</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:58:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="E563" t="n">
+        <v>640</v>
+      </c>
+      <c r="F563" t="n">
+        <v>520</v>
+      </c>
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>GMDC खरीदें PRICE 569.90 TARGET 640/720 STOP LOSS 520</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:58:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="E564" t="n">
+        <v>720</v>
+      </c>
+      <c r="F564" t="n">
+        <v>520</v>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>GMDC खरीदें PRICE 569.90 TARGET 640/720 STOP LOSS 520</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:58:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="E565" t="n">
+        <v>640</v>
+      </c>
+      <c r="F565" t="n">
+        <v>520</v>
+      </c>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+GMDC
+खरीदें
+PRICE → 570.20
+TARGET → 640/720
+STOP LOSS → 520</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:58:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>570.15</v>
+      </c>
+      <c r="E566" t="n">
+        <v>720</v>
+      </c>
+      <c r="F566" t="n">
+        <v>520</v>
+      </c>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+GMDC
+खरीदें
+PRICE → 570.20
+TARGET → 640/720
+STOP LOSS → 520</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:57:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="E567" t="n">
+        <v>240</v>
+      </c>
+      <c r="F567" t="n">
+        <v>180</v>
+      </c>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Rain Ind खरीदें PRICE 203.78 TARGET 240/260 STOP LOSS 180</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:57:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>RAIN</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="E568" t="n">
+        <v>260</v>
+      </c>
+      <c r="F568" t="n">
+        <v>180</v>
+      </c>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Rain Ind खरीदें PRICE 203.78 TARGET 240/260 STOP LOSS 180</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:52:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>1758.5</v>
+      </c>
+      <c r="E569" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Nuvama Wealth
+1758.80 0.30%
+BUY
+TGT 2030
+SL --</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:51:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>404.1</v>
+      </c>
+      <c r="E570" t="n">
+        <v>415</v>
+      </c>
+      <c r="F570" t="n">
+        <v>395</v>
+      </c>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Coal India 404.10 2.35 BUY TGT 415 SL 395</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:51:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>9096.5</v>
+      </c>
+      <c r="E571" t="n">
+        <v>9250</v>
+      </c>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान
+Polycab India
+9102.00 3.63%
+BUY
+TARGET HIT
+9250</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:50:34</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
+      <c r="E572" t="n">
+        <v>9600.969999999999</v>
+      </c>
+      <c r="F572" t="n">
+        <v>9250</v>
+      </c>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Polycab India 9105.00 340.00 BUY TGT 9600/97 SL 9250</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:50:32</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr"/>
+      <c r="E573" t="n">
+        <v>9600</v>
+      </c>
+      <c r="F573" t="n">
+        <v>9250</v>
+      </c>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Polycab India
+9105.00 340.00
+BUY
+TGT 9600/97
+SL 9250</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:49:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="E574" t="n">
+        <v>48</v>
+      </c>
+      <c r="F574" t="n">
+        <v>24</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय AUROBINDO PH 1720 की कॉल @ 33-34 खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1687.00</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:36</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="n">
+        <v>48</v>
+      </c>
+      <c r="F575" t="n">
+        <v>24</v>
+      </c>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>कैश का ऑप्शन Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1687.50 0.15%</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:23</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="n">
+        <v>48</v>
+      </c>
+      <c r="F576" t="n">
+        <v>24</v>
+      </c>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 3.80</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:23</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="n">
+        <v>58</v>
+      </c>
+      <c r="F577" t="n">
+        <v>24</v>
+      </c>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 3.80</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:20</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="n">
+        <v>58</v>
+      </c>
+      <c r="F578" t="n">
+        <v>24</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय AUROBINDO PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 0.22%</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:20</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="n">
+        <v>48</v>
+      </c>
+      <c r="F579" t="n">
+        <v>24</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय AUROBINDO PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 0.22%</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:14</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" t="n">
+        <v>48</v>
+      </c>
+      <c r="F580" t="n">
+        <v>24</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>कैश का ऑप्शन Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1689.40</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:14</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr"/>
+      <c r="E581" t="n">
+        <v>58</v>
+      </c>
+      <c r="F581" t="n">
+        <v>24</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>कैश का ऑप्शन Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1689.40</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:09</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr"/>
+      <c r="E582" t="n">
+        <v>48</v>
+      </c>
+      <c r="F582" t="n">
+        <v>24</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1689.40</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:09</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr"/>
+      <c r="E583" t="n">
+        <v>58</v>
+      </c>
+      <c r="F583" t="n">
+        <v>24</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1689.40</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:05</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr"/>
+      <c r="E584" t="n">
+        <v>48</v>
+      </c>
+      <c r="F584" t="n">
+        <v>24</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय AUROBINDO PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1689.40 0.04%</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:04</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr"/>
+      <c r="E585" t="n">
+        <v>48</v>
+      </c>
+      <c r="F585" t="n">
+        <v>24</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय AUROBINDO PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:46:04</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>AUROPHARMA172029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr"/>
+      <c r="E586" t="n">
+        <v>58</v>
+      </c>
+      <c r="F586" t="n">
+        <v>24</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय AUROBINDO PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:40:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>1045.5</v>
+      </c>
+      <c r="F587" t="n">
+        <v>150</v>
+      </c>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:36:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>1763</v>
+      </c>
+      <c r="E588" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+Nuvama Wealth
+खरीदें
+PRICE → 1762.50
+TARGET → 2030/2070
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:36:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>1763</v>
+      </c>
+      <c r="E589" t="n">
+        <v>2030</v>
+      </c>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Nuvama Wealth
+खरीदें
+PRICE → 1763.00
+TARGET → 2030/2070
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:36:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>1763</v>
+      </c>
+      <c r="E590" t="n">
+        <v>2070</v>
+      </c>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Nuvama Wealth खरीदें PRICE 1763.00 TARGET 2030/2070 STOP LOSS</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:36:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>1763</v>
+      </c>
+      <c r="F591" t="n">
+        <v>150</v>
+      </c>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:32:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="F592" t="n">
+        <v>150</v>
+      </c>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:31:46</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr"/>
+      <c r="E593" t="n">
+        <v>165</v>
+      </c>
+      <c r="F593" t="n">
+        <v>155</v>
+      </c>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>लिस्टिंग पर राय ₹155-165 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹138</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:27:07</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>HTEL-BE</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+      <c r="F594" t="n">
+        <v>75</v>
+      </c>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>HY-TECH ENGINEERS LTD. लिस्टिंग पर राय इन्वेस्टर्स ₹75 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:27:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>405.6</v>
+      </c>
+      <c r="E595" t="n">
+        <v>415</v>
+      </c>
+      <c r="F595" t="n">
+        <v>395</v>
+      </c>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Coal India खरीदें PRICE 405.70 TARGET 415/425 STOP LOSS 395</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:27:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>406.15</v>
+      </c>
+      <c r="E596" t="n">
+        <v>425</v>
+      </c>
+      <c r="F596" t="n">
+        <v>395</v>
+      </c>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Coal India खरीदें PRICE 405.70 TARGET 415/425 STOP LOSS 395</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:26:49</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
+      <c r="F597" t="n">
+        <v>150</v>
+      </c>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>SLE SKYWAYS GROUP लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:27:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>831.45</v>
+      </c>
+      <c r="E598" t="n">
+        <v>860</v>
+      </c>
+      <c r="F598" t="n">
+        <v>820</v>
+      </c>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Marico
+खरीदें
+PRICE → 830.30
+TARGET → 848/860
+STOP LOSS → 820</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:26:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>830.85</v>
+      </c>
+      <c r="E599" t="n">
+        <v>848</v>
+      </c>
+      <c r="F599" t="n">
+        <v>820</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Marico खरीदें PRICE 830.80 TARGET 848/860 STOP LOSS 820</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:16:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>2999.5</v>
+      </c>
+      <c r="E600" t="n">
+        <v>3705</v>
+      </c>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Muthoot Finance
+3014.00 +35.90
+OVERWEIGHT
+लक्ष्य ₹3705</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:16:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>706.5</v>
+      </c>
+      <c r="E601" t="n">
+        <v>739</v>
+      </c>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>HDFC Bank इंट्राडे में 739 का High बनाकर लगभग ₹35 फिसला</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1420.9</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1488</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1373</v>
+      </c>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT CIPLA B 1488 1373</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E603" t="n">
+        <v>1413</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1348</v>
+      </c>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>MY CHOICE CHENNAI PETRO B 1413 1348</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1413</v>
+      </c>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>MY CHOICE CHENNAI PETRO B 1413</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>1420.9</v>
+      </c>
+      <c r="E605" t="n">
+        <v>1488</v>
+      </c>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT CIPLA B 1488</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>483.35</v>
+      </c>
+      <c r="E606" t="n">
+        <v>503</v>
+      </c>
+      <c r="F606" t="n">
+        <v>471</v>
+      </c>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>CASH HONASA B 503 471</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>CGPOWER29SEP26</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>900</v>
+      </c>
+      <c r="E607" t="n">
+        <v>910</v>
+      </c>
+      <c r="F607" t="n">
+        <v>882</v>
+      </c>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>FUTURE CG POWER FUT B 910 882</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>HAPPSTMNDS</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>404</v>
+      </c>
+      <c r="E608" t="n">
+        <v>448</v>
+      </c>
+      <c r="F608" t="n">
+        <v>387</v>
+      </c>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>FUNDA HAPPIEST MINDS B 448 387</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>TIMETECHNO</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>190.05</v>
+      </c>
+      <c r="E609" t="n">
+        <v>192</v>
+      </c>
+      <c r="F609" t="n">
+        <v>185</v>
+      </c>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>MY CHOICE TIME TECHNOPLAST B 192 185</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>233.8</v>
+      </c>
+      <c r="E610" t="n">
+        <v>236</v>
+      </c>
+      <c r="F610" t="n">
+        <v>227</v>
+      </c>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>MY CHOICE ONGC B 236 227</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>1083.8</v>
+      </c>
+      <c r="E611" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>INVESTMENT AU SMALL FIN B 1200 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="E612" t="n">
+        <v>156</v>
+      </c>
+      <c r="F612" t="n">
+        <v>146</v>
+      </c>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT NCC B 156 146</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>659.9</v>
+      </c>
+      <c r="E613" t="n">
+        <v>668</v>
+      </c>
+      <c r="F613" t="n">
+        <v>648</v>
+      </c>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>TECHNO BRIGADE ENT B 668 648</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="E614" t="n">
+        <v>650</v>
+      </c>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>FUNDA ALLIED BLENDERS B 650 3 MONTH</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>386</v>
+      </c>
+      <c r="E615" t="n">
+        <v>400</v>
+      </c>
+      <c r="F615" t="n">
+        <v>378</v>
+      </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Indus Towers BUY PRICE 388.80 TARGET 400/410 STOP LOSS 378</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>386</v>
+      </c>
+      <c r="E616" t="n">
+        <v>410</v>
+      </c>
+      <c r="F616" t="n">
+        <v>378</v>
+      </c>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Indus Towers BUY PRICE 388.80 TARGET 400/410 STOP LOSS 378</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>JNPR</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>264.15</v>
+      </c>
+      <c r="E617" t="n">
+        <v>282</v>
+      </c>
+      <c r="F617" t="n">
+        <v>245</v>
+      </c>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Juniper Green BUY PRICE 264.73 TARGET 282 STOP LOSS 245</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>VGUARD</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>349.3</v>
+      </c>
+      <c r="E618" t="n">
+        <v>380</v>
+      </c>
+      <c r="F618" t="n">
+        <v>335</v>
+      </c>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>विक्रम जय झुंझुनवाला की राय V-Guard BU PRICE 346.35 TARGET 360/380 STOP LOSS 335</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>4055.1</v>
+      </c>
+      <c r="E619" t="n">
+        <v>4160</v>
+      </c>
+      <c r="F619" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Sansera Engg BUY PRICE 4018.00 TARGET 4120/4160 STOP LOSS 3960</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>VGUARD</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>349.3</v>
+      </c>
+      <c r="E620" t="n">
+        <v>360</v>
+      </c>
+      <c r="F620" t="n">
+        <v>335</v>
+      </c>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY V-Guard BUY PRICE 346.35 TARGET 360/380 STOP LOSS 335</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>4055.1</v>
+      </c>
+      <c r="E621" t="n">
+        <v>4120</v>
+      </c>
+      <c r="F621" t="n">
+        <v>3960</v>
+      </c>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ रॉय मगला की राय Sansera Engg BUY PRICE 4018.00 TARGET 4120/4160 STOP LOSS 3960</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>4055.1</v>
+      </c>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Sansera Engg BU PRICE 4018.00 TARGET 4120/4160 STOP LOSS 3960</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>KPITTECH29SEP26</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>590</v>
+      </c>
+      <c r="E623" t="n">
+        <v>570</v>
+      </c>
+      <c r="F623" t="n">
+        <v>603</v>
+      </c>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY KPIT Tech Fut SELL PRICE 588.10 TARGET 570/550 STOP LOSS 603</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>KPITTECH29SEP26</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>590</v>
+      </c>
+      <c r="E624" t="n">
+        <v>550</v>
+      </c>
+      <c r="F624" t="n">
+        <v>603</v>
+      </c>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY KPIT Tech Fut SELL PRICE 588.10 TARGET 570/550 STOP LOSS 603</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>1770.2</v>
+      </c>
+      <c r="E625" t="n">
+        <v>1805</v>
+      </c>
+      <c r="F625" t="n">
+        <v>1735</v>
+      </c>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Nuvama Wealth B I PRICE 1754 TARGET 1770, 1785, 1805 STOP LOSS 1735</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E626" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1123</v>
+      </c>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>INVESTMENT KPR MILL B 1300 1123</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>CGPOWER29SEP26</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>903.05</v>
+      </c>
+      <c r="E627" t="n">
+        <v>910</v>
+      </c>
+      <c r="F627" t="n">
+        <v>882</v>
+      </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>FUTURE CG POWER FUT B 910 882</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>149.52</v>
+      </c>
+      <c r="E628" t="n">
+        <v>156</v>
+      </c>
+      <c r="F628" t="n">
+        <v>146</v>
+      </c>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT NCC B 156 146</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>LEAPIND</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="E629" t="n">
+        <v>175</v>
+      </c>
+      <c r="F629" t="n">
+        <v>163</v>
+      </c>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>CASH LEAP INDIA B 175 163</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>622</v>
+      </c>
+      <c r="E630" t="n">
+        <v>650</v>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>FUNDA ALLIED BLENDERS B 650 3 MONTH</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>THELEELA</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>570.95</v>
+      </c>
+      <c r="E631" t="n">
+        <v>592</v>
+      </c>
+      <c r="F631" t="n">
+        <v>562</v>
+      </c>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>MY CHOICE Leela Palaces खरीदें PRICE 570.40 TARGET 592 STOP LOSS 562</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E632" t="n">
+        <v>1413</v>
+      </c>
+      <c r="F632" t="n">
+        <v>1348</v>
+      </c>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>MY CHOICE Chennai Petro खरीदें PRICE 1367.40 TARGET 1413 STOP LOSS 1348</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="E633" t="n">
+        <v>236</v>
+      </c>
+      <c r="F633" t="n">
+        <v>227</v>
+      </c>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>ONGC खरीदें PRICE 231.80 TARGET 236 STOP LOSS 227</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>1420.9</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1488</v>
+      </c>
+      <c r="F634" t="n">
+        <v>1373</v>
+      </c>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Cipla
+खरीदें
+PRICE → 1409.20
+TARGET → 1488
+STOP LOSS → 1373</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>622</v>
+      </c>
+      <c r="E635" t="n">
+        <v>788</v>
+      </c>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>CALLS Allied Blenders 618.4 BUY लक्ष्य ₹788</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>1083.8</v>
+      </c>
+      <c r="E636" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK AU Small Fin खरीदें PRICE 1086.20 TARGET 1200 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E637" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F637" t="n">
+        <v>1123</v>
+      </c>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+KPR Mill
+खरीदें
+PRICE → 1177.60
+TARGET → 1300
+STOP LOSS → 1123</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>KPRMILL</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E638" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK KPR Mill PRICE 177.60 TARGET 1300</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>HAPPSTMNDS</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>404</v>
+      </c>
+      <c r="E639" t="n">
+        <v>448</v>
+      </c>
+      <c r="F639" t="n">
+        <v>387</v>
+      </c>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Happiest Minds खरीदें PRICE 406.95 TARGET 448 STOP LOSS 387</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>622</v>
+      </c>
+      <c r="E640" t="n">
+        <v>650</v>
+      </c>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>FUNDA PICK Allied Blenders खरीदें PRICE 618.40 TARGET 650 DURATION 3 महीने</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>659.9</v>
+      </c>
+      <c r="E641" t="n">
+        <v>668</v>
+      </c>
+      <c r="F641" t="n">
+        <v>648</v>
+      </c>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>TECHNO PICK Brigade Ent खरीदें PRICE 655.85 TARGET 668 STOP LOSS 648</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN300029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="E642" t="n">
+        <v>180</v>
+      </c>
+      <c r="F642" t="n">
+        <v>50</v>
+      </c>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>BEST ऑप्शन Muthoot Finance 3000 की कॉल @101 खरीदें STOP LOSS 50 TARGET 180 Muthoot Finance 2978.10 3.65%</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>CGPOWER29SEP26</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>895</v>
+      </c>
+      <c r="E643" t="n">
+        <v>910</v>
+      </c>
+      <c r="F643" t="n">
+        <v>882</v>
+      </c>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+CG Power Fut
+खरीदें
+PRICE → 891.25
+TARGET → 910
+STOP LOSS → 882</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>CGPOWER29SEP26</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>895</v>
+      </c>
+      <c r="E644" t="n">
+        <v>910</v>
+      </c>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+CG Power Fut
+PRICE → 891.25
+TARGET → 910</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>HONASA</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>483.35</v>
+      </c>
+      <c r="E645" t="n">
+        <v>503</v>
+      </c>
+      <c r="F645" t="n">
+        <v>471</v>
+      </c>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>CASH का शेयर HONASA (Mamaearth) खरीदें PRICE 480.90 TARGET 503 STOP LOSS 471</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>LEAPIND</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="E646" t="n">
+        <v>175</v>
+      </c>
+      <c r="F646" t="n">
+        <v>163</v>
+      </c>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर LEAP India खरीदें PRICE 167.70 TARGET 175 STOP LOSS 163</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E647" t="n">
+        <v>3705</v>
+      </c>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>BROO CZX
+Muthoot Finance
+2978.10 -112.90
+OVERWEIGHT
+लक्ष्य ₹3705</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="E648" t="n">
+        <v>390</v>
+      </c>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>ITC 255.50 ▼ 10.50 पहले चरण में 11% हिस्सेदारी ₹390/Sh में खरीदें</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>ABDL</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>622</v>
+      </c>
+      <c r="E649" t="n">
+        <v>780</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>जेफरीज Allied Blenders 618.40 +8.40 BUY लक्ष्य ₹780</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:15:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>402</v>
+      </c>
+      <c r="E650" t="n">
+        <v>450</v>
+      </c>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Syngene Intl
+400.75 -2.65
+BUY
+लक्ष्य ₹450</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:16:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>1485.1</v>
+      </c>
+      <c r="E651" t="n">
+        <v>1545</v>
+      </c>
+      <c r="F651" t="n">
+        <v>1462</v>
+      </c>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>United Spirits BUY TARGET 1545 STOP LOSS 1462 United Spirits 1490.00 1.32%</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-09-01 09:16:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>1279.3</v>
+      </c>
+      <c r="E652" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F652" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>POSITIONAL CALL UNO Minda Ltd BUY TARGET 1400 STOP LOSS 1214 UNO Minda Ltd 1276.00 Unch</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J530"/>
+  <autoFilter ref="A1:J652"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$652</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$782</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J652"/>
+  <dimension ref="A1:J782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -23571,7 +23571,6 @@
       <c r="F531" t="n">
         <v>1325</v>
       </c>
-      <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr">
         <is>
           <t>Info Edge Fut खरीदें PRICE 1367.00 TARGET 1400/1430 STOP LOSS 1325</t>
@@ -23613,7 +23612,6 @@
       <c r="F532" t="n">
         <v>1325</v>
       </c>
-      <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr">
         <is>
           <t>Info Edge Fut खरीदें PRICE 1367.00 TARGET 1400/1430 STOP LOSS 1325</t>
@@ -23747,7 +23745,6 @@
       <c r="F535" t="n">
         <v>401</v>
       </c>
-      <c r="G535" t="inlineStr"/>
       <c r="H535" t="inlineStr">
         <is>
           <t>SHORT MIDCAP STOCKS Gufic Bio खरीदें STOP LOSS 401 TARGET 460/470 DURATION -- Gufic Bio 421.00 5.95</t>
@@ -23789,7 +23786,6 @@
       <c r="F536" t="n">
         <v>401</v>
       </c>
-      <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Gufic Bio खरीदें STOP LOSS 401 TARGET 460/470 DURATION -- Gufic Bio 421.00</t>
@@ -23822,14 +23818,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
       <c r="E537" t="n">
         <v>470</v>
       </c>
       <c r="F537" t="n">
         <v>401</v>
       </c>
-      <c r="G537" t="inlineStr"/>
       <c r="H537" t="inlineStr">
         <is>
           <t>Gujarat Bio खरीदें STOP LOSS 401 TARGET 460/470</t>
@@ -23862,14 +23856,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
       <c r="E538" t="n">
         <v>1630</v>
       </c>
       <c r="F538" t="n">
         <v>1390</v>
       </c>
-      <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 4.90</t>
@@ -23902,14 +23894,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
       <c r="E539" t="n">
         <v>1570</v>
       </c>
       <c r="F539" t="n">
         <v>1390</v>
       </c>
-      <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 4.90</t>
@@ -23951,7 +23941,6 @@
       <c r="F540" t="n">
         <v>1390</v>
       </c>
-      <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 0.34%</t>
@@ -23993,7 +23982,6 @@
       <c r="F541" t="n">
         <v>1390</v>
       </c>
-      <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1433.00 0.34%</t>
@@ -24130,7 +24118,6 @@
       <c r="E544" t="n">
         <v>730</v>
       </c>
-      <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS --- TARGET 730/750 DURATION 6-12 महीने Vimta Labs 658.00 ▲ 2.26%</t>
@@ -24172,7 +24159,6 @@
       <c r="F545" t="n">
         <v>1390</v>
       </c>
-      <c r="G545" t="inlineStr"/>
       <c r="H545" t="inlineStr">
         <is>
           <t>Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1437.40 ▼ 4.30</t>
@@ -24214,7 +24200,6 @@
       <c r="F546" t="n">
         <v>1390</v>
       </c>
-      <c r="G546" t="inlineStr"/>
       <c r="H546" t="inlineStr">
         <is>
           <t>Gabriel India खरीदें STOP LOSS 1390 TARGET 1570/1630 DURATION -- Gabriel India 1437.40 ▼ 4.30</t>
@@ -24253,7 +24238,6 @@
       <c r="E547" t="n">
         <v>750</v>
       </c>
-      <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Vimta Labs खरीदें STOP LOSS --- TARGET 730/750 DURATION 6-12 महीने Vimta Labs 658.00 2.26%</t>
@@ -24286,14 +24270,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
       <c r="E548" t="n">
         <v>730</v>
       </c>
       <c r="F548" t="n">
         <v>750</v>
       </c>
-      <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr">
         <is>
           <t>सदापि जन का राय Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 2.04%</t>
@@ -24335,7 +24317,6 @@
       <c r="F549" t="n">
         <v>612</v>
       </c>
-      <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55</t>
@@ -24377,7 +24358,6 @@
       <c r="F550" t="n">
         <v>600</v>
       </c>
-      <c r="G550" t="inlineStr"/>
       <c r="H550" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 ▲ 13.10</t>
@@ -24419,7 +24399,6 @@
       <c r="F551" t="n">
         <v>6</v>
       </c>
-      <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Vimta Labs खरीदें STOP LOSS 6-12 महीने TARGET 730/750 DURATION --- Vimta Labs 656.55 2.04%</t>
@@ -24461,7 +24440,6 @@
       <c r="F552" t="n">
         <v>820</v>
       </c>
-      <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr">
         <is>
           <t>Marico 834.10 14.10 BUY TGT 848 SL 820 Tue 01 Sep'26</t>
@@ -24592,7 +24570,6 @@
       <c r="E555" t="n">
         <v>2030</v>
       </c>
-      <c r="G555" t="inlineStr"/>
       <c r="H555" t="inlineStr">
         <is>
           <t>जैन साब के GEMS Nuvama Wealth 1759.10 5.50 BUY TGT 2030 SL --</t>
@@ -24634,7 +24611,6 @@
       <c r="F556" t="n">
         <v>4360</v>
       </c>
-      <c r="G556" t="inlineStr"/>
       <c r="H556" t="inlineStr">
         <is>
           <t>TVS Motor Fut खरीदें PRICE 4415.90 TARGET 4500/4560 STOP LOSS 4360</t>
@@ -24676,7 +24652,6 @@
       <c r="F557" t="n">
         <v>4360</v>
       </c>
-      <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr">
         <is>
           <t>TVS Motor Fut खरीदें PRICE 4415.90 TARGET 4500/4560 STOP LOSS 4360</t>
@@ -24718,7 +24693,6 @@
       <c r="F558" t="n">
         <v>395</v>
       </c>
-      <c r="G558" t="inlineStr"/>
       <c r="H558" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Coal India 403.55 1.80 BUY TGT 415 SL 395</t>
@@ -24806,7 +24780,6 @@
       <c r="F560" t="n">
         <v>4360</v>
       </c>
-      <c r="G560" t="inlineStr"/>
       <c r="H560" t="inlineStr">
         <is>
           <t>TVS Motor Fut खरीदें PRICE 4414.60 TARGET 4500/4560 STOP LOSS 4360</t>
@@ -24848,7 +24821,6 @@
       <c r="F561" t="n">
         <v>4360</v>
       </c>
-      <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr">
         <is>
           <t>TVS Motor Fut खरीदें PRICE 4414.60 TARGET 4500/4560 STOP LOSS 4360</t>
@@ -24890,7 +24862,6 @@
       <c r="F562" t="n">
         <v>700</v>
       </c>
-      <c r="G562" t="inlineStr"/>
       <c r="H562" t="inlineStr">
         <is>
           <t>HEG Ltd खरीदें PRICE 746.10 TARGET 780/790 STOP LOSS 700</t>
@@ -24932,7 +24903,6 @@
       <c r="F563" t="n">
         <v>520</v>
       </c>
-      <c r="G563" t="inlineStr"/>
       <c r="H563" t="inlineStr">
         <is>
           <t>GMDC खरीदें PRICE 569.90 TARGET 640/720 STOP LOSS 520</t>
@@ -24974,7 +24944,6 @@
       <c r="F564" t="n">
         <v>520</v>
       </c>
-      <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr">
         <is>
           <t>GMDC खरीदें PRICE 569.90 TARGET 640/720 STOP LOSS 520</t>
@@ -25016,7 +24985,6 @@
       <c r="F565" t="n">
         <v>520</v>
       </c>
-      <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -25063,7 +25031,6 @@
       <c r="F566" t="n">
         <v>520</v>
       </c>
-      <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -25110,7 +25077,6 @@
       <c r="F567" t="n">
         <v>180</v>
       </c>
-      <c r="G567" t="inlineStr"/>
       <c r="H567" t="inlineStr">
         <is>
           <t>Rain Ind खरीदें PRICE 203.78 TARGET 240/260 STOP LOSS 180</t>
@@ -25152,7 +25118,6 @@
       <c r="F568" t="n">
         <v>180</v>
       </c>
-      <c r="G568" t="inlineStr"/>
       <c r="H568" t="inlineStr">
         <is>
           <t>Rain Ind खरीदें PRICE 203.78 TARGET 240/260 STOP LOSS 180</t>
@@ -25191,7 +25156,6 @@
       <c r="E569" t="n">
         <v>2030</v>
       </c>
-      <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -25238,7 +25202,6 @@
       <c r="F570" t="n">
         <v>395</v>
       </c>
-      <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr">
         <is>
           <t>Coal India 404.10 2.35 BUY TGT 415 SL 395</t>
@@ -25277,7 +25240,6 @@
       <c r="E571" t="n">
         <v>9250</v>
       </c>
-      <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr">
         <is>
           <t>विश्वेश चौहान
@@ -25315,14 +25277,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
       <c r="E572" t="n">
         <v>9600.969999999999</v>
       </c>
       <c r="F572" t="n">
         <v>9250</v>
       </c>
-      <c r="G572" t="inlineStr"/>
       <c r="H572" t="inlineStr">
         <is>
           <t>Polycab India 9105.00 340.00 BUY TGT 9600/97 SL 9250</t>
@@ -25355,14 +25315,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
       <c r="E573" t="n">
         <v>9600</v>
       </c>
       <c r="F573" t="n">
         <v>9250</v>
       </c>
-      <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -25446,14 +25404,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
       <c r="E575" t="n">
         <v>48</v>
       </c>
       <c r="F575" t="n">
         <v>24</v>
       </c>
-      <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr">
         <is>
           <t>कैश का ऑप्शन Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1687.50 0.15%</t>
@@ -25486,14 +25442,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
       <c r="E576" t="n">
         <v>48</v>
       </c>
       <c r="F576" t="n">
         <v>24</v>
       </c>
-      <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr">
         <is>
           <t>Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 3.80</t>
@@ -25526,14 +25480,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr"/>
       <c r="E577" t="n">
         <v>58</v>
       </c>
       <c r="F577" t="n">
         <v>24</v>
       </c>
-      <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr">
         <is>
           <t>Aurobindo PH 1720 की कॉल खरीदें STOP LOSS 24 TARGET 48/58 Aurobindo Ph 1686.20 3.80</t>
@@ -25566,7 +25518,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
       <c r="E578" t="n">
         <v>58</v>
       </c>
@@ -25610,7 +25561,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr"/>
       <c r="E579" t="n">
         <v>48</v>
       </c>
@@ -25654,7 +25604,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr"/>
       <c r="E580" t="n">
         <v>48</v>
       </c>
@@ -25698,7 +25647,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
       <c r="E581" t="n">
         <v>58</v>
       </c>
@@ -25742,7 +25690,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr"/>
       <c r="E582" t="n">
         <v>48</v>
       </c>
@@ -25786,7 +25733,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
       <c r="E583" t="n">
         <v>58</v>
       </c>
@@ -25830,7 +25776,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
       <c r="E584" t="n">
         <v>48</v>
       </c>
@@ -25874,7 +25819,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
       <c r="E585" t="n">
         <v>48</v>
       </c>
@@ -25918,7 +25862,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
       <c r="E586" t="n">
         <v>58</v>
       </c>
@@ -25968,7 +25911,6 @@
       <c r="F587" t="n">
         <v>150</v>
       </c>
-      <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr">
         <is>
           <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
@@ -26007,7 +25949,6 @@
       <c r="E588" t="n">
         <v>2030</v>
       </c>
-      <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -26051,7 +25992,6 @@
       <c r="E589" t="n">
         <v>2030</v>
       </c>
-      <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -26095,7 +26035,6 @@
       <c r="E590" t="n">
         <v>2070</v>
       </c>
-      <c r="G590" t="inlineStr"/>
       <c r="H590" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Nuvama Wealth खरीदें PRICE 1763.00 TARGET 2030/2070 STOP LOSS</t>
@@ -26134,7 +26073,6 @@
       <c r="F591" t="n">
         <v>150</v>
       </c>
-      <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr">
         <is>
           <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
@@ -26173,7 +26111,6 @@
       <c r="F592" t="n">
         <v>150</v>
       </c>
-      <c r="G592" t="inlineStr"/>
       <c r="H592" t="inlineStr">
         <is>
           <t>लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
@@ -26206,14 +26143,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
       <c r="E593" t="n">
         <v>165</v>
       </c>
       <c r="F593" t="n">
         <v>155</v>
       </c>
-      <c r="G593" t="inlineStr"/>
       <c r="H593" t="inlineStr">
         <is>
           <t>लिस्टिंग पर राय ₹155-165 की रेंज में लिस्टिंग का अनुमान, इश्यू प्राइस ₹138</t>
@@ -26246,11 +26181,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
       <c r="F594" t="n">
         <v>75</v>
       </c>
-      <c r="G594" t="inlineStr"/>
       <c r="H594" t="inlineStr">
         <is>
           <t>HY-TECH ENGINEERS LTD. लिस्टिंग पर राय इन्वेस्टर्स ₹75 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
@@ -26292,7 +26225,6 @@
       <c r="F595" t="n">
         <v>395</v>
       </c>
-      <c r="G595" t="inlineStr"/>
       <c r="H595" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Coal India खरीदें PRICE 405.70 TARGET 415/425 STOP LOSS 395</t>
@@ -26334,7 +26266,6 @@
       <c r="F596" t="n">
         <v>395</v>
       </c>
-      <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Coal India खरीदें PRICE 405.70 TARGET 415/425 STOP LOSS 395</t>
@@ -26367,11 +26298,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
       <c r="F597" t="n">
         <v>150</v>
       </c>
-      <c r="G597" t="inlineStr"/>
       <c r="H597" t="inlineStr">
         <is>
           <t>SLE SKYWAYS GROUP लिस्टिंग पर राय इन्वेस्टर्स ₹150 के नीचे का SL जरूर लगाएं और ट्रेल करते रहें</t>
@@ -26413,7 +26342,6 @@
       <c r="F598" t="n">
         <v>820</v>
       </c>
-      <c r="G598" t="inlineStr"/>
       <c r="H598" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -26503,7 +26431,6 @@
       <c r="E600" t="n">
         <v>3705</v>
       </c>
-      <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -26546,7 +26473,6 @@
       <c r="E601" t="n">
         <v>739</v>
       </c>
-      <c r="G601" t="inlineStr"/>
       <c r="H601" t="inlineStr">
         <is>
           <t>HDFC Bank इंट्राडे में 739 का High बनाकर लगभग ₹35 फिसला</t>
@@ -26588,7 +26514,6 @@
       <c r="F602" t="n">
         <v>1373</v>
       </c>
-      <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr">
         <is>
           <t>NEWS IMPACT CIPLA B 1488 1373</t>
@@ -26630,7 +26555,6 @@
       <c r="F603" t="n">
         <v>1348</v>
       </c>
-      <c r="G603" t="inlineStr"/>
       <c r="H603" t="inlineStr">
         <is>
           <t>MY CHOICE CHENNAI PETRO B 1413 1348</t>
@@ -26669,7 +26593,6 @@
       <c r="E604" t="n">
         <v>1413</v>
       </c>
-      <c r="G604" t="inlineStr"/>
       <c r="H604" t="inlineStr">
         <is>
           <t>MY CHOICE CHENNAI PETRO B 1413</t>
@@ -26708,7 +26631,6 @@
       <c r="E605" t="n">
         <v>1488</v>
       </c>
-      <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr">
         <is>
           <t>NEWS IMPACT CIPLA B 1488</t>
@@ -26750,7 +26672,6 @@
       <c r="F606" t="n">
         <v>471</v>
       </c>
-      <c r="G606" t="inlineStr"/>
       <c r="H606" t="inlineStr">
         <is>
           <t>CASH HONASA B 503 471</t>
@@ -26792,7 +26713,6 @@
       <c r="F607" t="n">
         <v>882</v>
       </c>
-      <c r="G607" t="inlineStr"/>
       <c r="H607" t="inlineStr">
         <is>
           <t>FUTURE CG POWER FUT B 910 882</t>
@@ -26834,7 +26754,6 @@
       <c r="F608" t="n">
         <v>387</v>
       </c>
-      <c r="G608" t="inlineStr"/>
       <c r="H608" t="inlineStr">
         <is>
           <t>FUNDA HAPPIEST MINDS B 448 387</t>
@@ -26876,7 +26795,6 @@
       <c r="F609" t="n">
         <v>185</v>
       </c>
-      <c r="G609" t="inlineStr"/>
       <c r="H609" t="inlineStr">
         <is>
           <t>MY CHOICE TIME TECHNOPLAST B 192 185</t>
@@ -26918,7 +26836,6 @@
       <c r="F610" t="n">
         <v>227</v>
       </c>
-      <c r="G610" t="inlineStr"/>
       <c r="H610" t="inlineStr">
         <is>
           <t>MY CHOICE ONGC B 236 227</t>
@@ -26957,7 +26874,6 @@
       <c r="E611" t="n">
         <v>1200</v>
       </c>
-      <c r="G611" t="inlineStr"/>
       <c r="H611" t="inlineStr">
         <is>
           <t>INVESTMENT AU SMALL FIN B 1200 12 MONTH</t>
@@ -26999,7 +26915,6 @@
       <c r="F612" t="n">
         <v>146</v>
       </c>
-      <c r="G612" t="inlineStr"/>
       <c r="H612" t="inlineStr">
         <is>
           <t>NEWS IMPACT NCC B 156 146</t>
@@ -27041,7 +26956,6 @@
       <c r="F613" t="n">
         <v>648</v>
       </c>
-      <c r="G613" t="inlineStr"/>
       <c r="H613" t="inlineStr">
         <is>
           <t>TECHNO BRIGADE ENT B 668 648</t>
@@ -27080,7 +26994,6 @@
       <c r="E614" t="n">
         <v>650</v>
       </c>
-      <c r="G614" t="inlineStr"/>
       <c r="H614" t="inlineStr">
         <is>
           <t>FUNDA ALLIED BLENDERS B 650 3 MONTH</t>
@@ -27122,7 +27035,6 @@
       <c r="F615" t="n">
         <v>378</v>
       </c>
-      <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Indus Towers BUY PRICE 388.80 TARGET 400/410 STOP LOSS 378</t>
@@ -27164,7 +27076,6 @@
       <c r="F616" t="n">
         <v>378</v>
       </c>
-      <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Indus Towers BUY PRICE 388.80 TARGET 400/410 STOP LOSS 378</t>
@@ -27206,7 +27117,6 @@
       <c r="F617" t="n">
         <v>245</v>
       </c>
-      <c r="G617" t="inlineStr"/>
       <c r="H617" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Juniper Green BUY PRICE 264.73 TARGET 282 STOP LOSS 245</t>
@@ -27248,7 +27158,6 @@
       <c r="F618" t="n">
         <v>335</v>
       </c>
-      <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr">
         <is>
           <t>विक्रम जय झुंझुनवाला की राय V-Guard BU PRICE 346.35 TARGET 360/380 STOP LOSS 335</t>
@@ -27336,7 +27245,6 @@
       <c r="F620" t="n">
         <v>335</v>
       </c>
-      <c r="G620" t="inlineStr"/>
       <c r="H620" t="inlineStr">
         <is>
           <t>PICK OF THE DAY V-Guard BUY PRICE 346.35 TARGET 360/380 STOP LOSS 335</t>
@@ -27378,7 +27286,6 @@
       <c r="F621" t="n">
         <v>3960</v>
       </c>
-      <c r="G621" t="inlineStr"/>
       <c r="H621" t="inlineStr">
         <is>
           <t>सिद्धार्थ रॉय मगला की राय Sansera Engg BUY PRICE 4018.00 TARGET 4120/4160 STOP LOSS 3960</t>
@@ -27414,7 +27321,6 @@
       <c r="D622" t="n">
         <v>4055.1</v>
       </c>
-      <c r="G622" t="inlineStr"/>
       <c r="H622" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Sansera Engg BU PRICE 4018.00 TARGET 4120/4160 STOP LOSS 3960</t>
@@ -27456,7 +27362,6 @@
       <c r="F623" t="n">
         <v>603</v>
       </c>
-      <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr">
         <is>
           <t>PICK OF THE DAY KPIT Tech Fut SELL PRICE 588.10 TARGET 570/550 STOP LOSS 603</t>
@@ -27498,7 +27403,6 @@
       <c r="F624" t="n">
         <v>603</v>
       </c>
-      <c r="G624" t="inlineStr"/>
       <c r="H624" t="inlineStr">
         <is>
           <t>PICK OF THE DAY KPIT Tech Fut SELL PRICE 588.10 TARGET 570/550 STOP LOSS 603</t>
@@ -27540,7 +27444,6 @@
       <c r="F625" t="n">
         <v>1735</v>
       </c>
-      <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Nuvama Wealth B I PRICE 1754 TARGET 1770, 1785, 1805 STOP LOSS 1735</t>
@@ -27582,7 +27485,6 @@
       <c r="F626" t="n">
         <v>1123</v>
       </c>
-      <c r="G626" t="inlineStr"/>
       <c r="H626" t="inlineStr">
         <is>
           <t>INVESTMENT KPR MILL B 1300 1123</t>
@@ -27624,7 +27526,6 @@
       <c r="F627" t="n">
         <v>882</v>
       </c>
-      <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr">
         <is>
           <t>FUTURE CG POWER FUT B 910 882</t>
@@ -27666,7 +27567,6 @@
       <c r="F628" t="n">
         <v>146</v>
       </c>
-      <c r="G628" t="inlineStr"/>
       <c r="H628" t="inlineStr">
         <is>
           <t>NEWS IMPACT NCC B 156 146</t>
@@ -27708,7 +27608,6 @@
       <c r="F629" t="n">
         <v>163</v>
       </c>
-      <c r="G629" t="inlineStr"/>
       <c r="H629" t="inlineStr">
         <is>
           <t>CASH LEAP INDIA B 175 163</t>
@@ -27747,7 +27646,6 @@
       <c r="E630" t="n">
         <v>650</v>
       </c>
-      <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr">
         <is>
           <t>FUNDA ALLIED BLENDERS B 650 3 MONTH</t>
@@ -27789,7 +27687,6 @@
       <c r="F631" t="n">
         <v>562</v>
       </c>
-      <c r="G631" t="inlineStr"/>
       <c r="H631" t="inlineStr">
         <is>
           <t>MY CHOICE Leela Palaces खरीदें PRICE 570.40 TARGET 592 STOP LOSS 562</t>
@@ -27831,7 +27728,6 @@
       <c r="F632" t="n">
         <v>1348</v>
       </c>
-      <c r="G632" t="inlineStr"/>
       <c r="H632" t="inlineStr">
         <is>
           <t>MY CHOICE Chennai Petro खरीदें PRICE 1367.40 TARGET 1413 STOP LOSS 1348</t>
@@ -27873,7 +27769,6 @@
       <c r="F633" t="n">
         <v>227</v>
       </c>
-      <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr">
         <is>
           <t>ONGC खरीदें PRICE 231.80 TARGET 236 STOP LOSS 227</t>
@@ -27915,7 +27810,6 @@
       <c r="F634" t="n">
         <v>1373</v>
       </c>
-      <c r="G634" t="inlineStr"/>
       <c r="H634" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -27959,7 +27853,6 @@
       <c r="E635" t="n">
         <v>788</v>
       </c>
-      <c r="G635" t="inlineStr"/>
       <c r="H635" t="inlineStr">
         <is>
           <t>CALLS Allied Blenders 618.4 BUY लक्ष्य ₹788</t>
@@ -27998,7 +27891,6 @@
       <c r="E636" t="n">
         <v>1200</v>
       </c>
-      <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK AU Small Fin खरीदें PRICE 1086.20 TARGET 1200 DURATION 12 महीने</t>
@@ -28040,7 +27932,6 @@
       <c r="F637" t="n">
         <v>1123</v>
       </c>
-      <c r="G637" t="inlineStr"/>
       <c r="H637" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -28084,7 +27975,6 @@
       <c r="E638" t="n">
         <v>1300</v>
       </c>
-      <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK KPR Mill PRICE 177.60 TARGET 1300</t>
@@ -28126,7 +28016,6 @@
       <c r="F639" t="n">
         <v>387</v>
       </c>
-      <c r="G639" t="inlineStr"/>
       <c r="H639" t="inlineStr">
         <is>
           <t>Happiest Minds खरीदें PRICE 406.95 TARGET 448 STOP LOSS 387</t>
@@ -28165,7 +28054,6 @@
       <c r="E640" t="n">
         <v>650</v>
       </c>
-      <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr">
         <is>
           <t>FUNDA PICK Allied Blenders खरीदें PRICE 618.40 TARGET 650 DURATION 3 महीने</t>
@@ -28207,7 +28095,6 @@
       <c r="F641" t="n">
         <v>648</v>
       </c>
-      <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr">
         <is>
           <t>TECHNO PICK Brigade Ent खरीदें PRICE 655.85 TARGET 668 STOP LOSS 648</t>
@@ -28249,7 +28136,6 @@
       <c r="F642" t="n">
         <v>50</v>
       </c>
-      <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr">
         <is>
           <t>BEST ऑप्शन Muthoot Finance 3000 की कॉल @101 खरीदें STOP LOSS 50 TARGET 180 Muthoot Finance 2978.10 3.65%</t>
@@ -28291,7 +28177,6 @@
       <c r="F643" t="n">
         <v>882</v>
       </c>
-      <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -28335,7 +28220,6 @@
       <c r="E644" t="n">
         <v>910</v>
       </c>
-      <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -28380,7 +28264,6 @@
       <c r="F645" t="n">
         <v>471</v>
       </c>
-      <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr">
         <is>
           <t>CASH का शेयर HONASA (Mamaearth) खरीदें PRICE 480.90 TARGET 503 STOP LOSS 471</t>
@@ -28422,7 +28305,6 @@
       <c r="F646" t="n">
         <v>163</v>
       </c>
-      <c r="G646" t="inlineStr"/>
       <c r="H646" t="inlineStr">
         <is>
           <t>पूजा के शेयर LEAP India खरीदें PRICE 167.70 TARGET 175 STOP LOSS 163</t>
@@ -28461,7 +28343,6 @@
       <c r="E647" t="n">
         <v>3705</v>
       </c>
-      <c r="G647" t="inlineStr"/>
       <c r="H647" t="inlineStr">
         <is>
           <t>BROO CZX
@@ -28504,7 +28385,6 @@
       <c r="E648" t="n">
         <v>390</v>
       </c>
-      <c r="G648" t="inlineStr"/>
       <c r="H648" t="inlineStr">
         <is>
           <t>ITC 255.50 ▼ 10.50 पहले चरण में 11% हिस्सेदारी ₹390/Sh में खरीदें</t>
@@ -28586,7 +28466,6 @@
       <c r="E650" t="n">
         <v>450</v>
       </c>
-      <c r="G650" t="inlineStr"/>
       <c r="H650" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -28632,7 +28511,6 @@
       <c r="F651" t="n">
         <v>1462</v>
       </c>
-      <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr">
         <is>
           <t>United Spirits BUY TARGET 1545 STOP LOSS 1462 United Spirits 1490.00 1.32%</t>
@@ -28674,7 +28552,6 @@
       <c r="F652" t="n">
         <v>1214</v>
       </c>
-      <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr">
         <is>
           <t>POSITIONAL CALL UNO Minda Ltd BUY TARGET 1400 STOP LOSS 1214 UNO Minda Ltd 1276.00 Unch</t>
@@ -28691,8 +28568,5548 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:57:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>ITC29SEP26</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="E653" t="n">
+        <v>277</v>
+      </c>
+      <c r="F653" t="n">
+        <v>262</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय
+ITC Fut
+खरीदें
+PRICE ▶ 268.30
+TARGET ▶ 277/283
+STOP LOSS ▶ 262</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:57:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>ITC29SEP26</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="E654" t="n">
+        <v>283</v>
+      </c>
+      <c r="F654" t="n">
+        <v>262</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय
+ITC Fut
+खरीदें
+PRICE ▶ 268.30
+TARGET ▶ 277/283
+STOP LOSS ▶ 262</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:57:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>ITC29SEP26</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="E655" t="n">
+        <v>277</v>
+      </c>
+      <c r="F655" t="n">
+        <v>203</v>
+      </c>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>ITC Fut PRICE 268.3 TARGET 277/203</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:56:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>GNA</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>538</v>
+      </c>
+      <c r="E656" t="n">
+        <v>560</v>
+      </c>
+      <c r="F656" t="n">
+        <v>520</v>
+      </c>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>GNA Axles @ 536 खरीदें STOP LOSS 520 TARGET 560 DURATION -- GNA Axles 540.50 8.05</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:55:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>POLYMED</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>1830.8</v>
+      </c>
+      <c r="E657" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1770</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय Poly Medicine खरीदें STOP LOSS 1770 TARGET 2000 DURATION -- Poly Medicine 1835.50 4.50%</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:55:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>MANGLMCEM</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>1108.5</v>
+      </c>
+      <c r="E658" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F658" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Mangalam Cem खरीदें PRICE 1109.40 TARGET 1200/1250 STOP LOSS 1000 नवनीत मुनोत MD &amp; CEO HDFC AMC COMING UP</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:55:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>MANGLMCEM</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>1108.5</v>
+      </c>
+      <c r="E659" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F659" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>10 की कमाई Mangalam Cem खरीदें PRICE 1110.00 TARGET 1200/1250 STOP LOSS 1000</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="E660" t="n">
+        <v>432</v>
+      </c>
+      <c r="F660" t="n">
+        <v>422</v>
+      </c>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>विशेष के विशेष
+Kotak Bank Fut
+423.95  2.80
+BUY
+TGT 432
+SL 422</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="E661" t="n">
+        <v>432</v>
+      </c>
+      <c r="F661" t="n">
+        <v>422</v>
+      </c>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>विशेष के विशेष
+Kotak Bank Fut
+424.00 2.75
+BUY
+TGT 432
+SL 422</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>883</v>
+      </c>
+      <c r="E662" t="n">
+        <v>930</v>
+      </c>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+875.05  82.40
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>883</v>
+      </c>
+      <c r="E663" t="n">
+        <v>930</v>
+      </c>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+876.00 83.35
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>1853</v>
+      </c>
+      <c r="E664" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F664" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT Oberoi Realty Fut 1854.30 31.30 BUY TGT 1930 SL 1840</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:38:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>ALKYLAMINE</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>2029.1</v>
+      </c>
+      <c r="E665" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F665" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+Alkyl Amines
+खरीदें
+PRICE ▶ 2028.40
+TARGET ▶ 2100/2150
+STOP LOSS ▶ 1960</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:38:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>ALKYLAMINE</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>2029.1</v>
+      </c>
+      <c r="E666" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F666" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>10 की कमाई Alkyl Amines खरीदें PRICE 2028.40 TARGET 2100/2150 STOP LOSS 1960 MARKET MENTORS नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:30:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>TEJASNET</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>547.65</v>
+      </c>
+      <c r="E667" t="n">
+        <v>730</v>
+      </c>
+      <c r="F667" t="n">
+        <v>485</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय Tejas Networks खरीदें STOP LOSS 485 TARGET 730 DURATION -- Tejas Networks 547.70 ▲ 1.07%</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:29:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="E668" t="n">
+        <v>850</v>
+      </c>
+      <c r="F668" t="n">
+        <v>500</v>
+      </c>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+Indegene
+खरीदें
+STOP LOSS 500 | TARGET 850 | DURATION --
+Indegene 603.85 ▼ 0.26%
+MARKET MENTORS
+नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:29:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Innogene खरीदें STOP LOSS 500 TARGET ₹50</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:23:03</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="n">
+        <v>340</v>
+      </c>
+      <c r="F670" t="n">
+        <v>270</v>
+      </c>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK SCI खरीदें STOP LOSS 270 TARGET 340 DURATION</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:23:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>448.65</v>
+      </c>
+      <c r="E671" t="n">
+        <v>550</v>
+      </c>
+      <c r="F671" t="n">
+        <v>380</v>
+      </c>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 448.80 ▲ 2.91%</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:17:33</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>NIFTY2380029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="n">
+        <v>240</v>
+      </c>
+      <c r="F672" t="n">
+        <v>152</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY 23800 की कॉल @ ₹190 खरीदें STOP LOSS 152 TARGET 240/270</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:17:33</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>NIFTY2380029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr"/>
+      <c r="E673" t="n">
+        <v>270</v>
+      </c>
+      <c r="F673" t="n">
+        <v>152</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY 23800 की कॉल @ ₹190 खरीदें STOP LOSS 152 TARGET 240/270</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:18:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>NIFTY2380008SEP26CE</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>191.65</v>
+      </c>
+      <c r="E674" t="n">
+        <v>240</v>
+      </c>
+      <c r="F674" t="n">
+        <v>152</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY 23800 की कॉल @ ₹190 खरीदें STOP LOSS 152 TARGET 240/270</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:06:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>606.15</v>
+      </c>
+      <c r="E675" t="n">
+        <v>850</v>
+      </c>
+      <c r="F675" t="n">
+        <v>500</v>
+      </c>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>सौमिल मेहता की राय Indegene खरीदें STOP LOSS 500 TARGET 850 DURATION -- Indegene 606.25 0.14%</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:59:03</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="n">
+        <v>550</v>
+      </c>
+      <c r="F676" t="n">
+        <v>380</v>
+      </c>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 436.00</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:58:59</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="n">
+        <v>550</v>
+      </c>
+      <c r="F677" t="n">
+        <v>380</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 436.00</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:58:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="E678" t="n">
+        <v>432</v>
+      </c>
+      <c r="F678" t="n">
+        <v>422</v>
+      </c>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Kotak Bank Fut 425.25 1.50 BUY TGT 432 SL 422</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:56:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>UFLEX</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>669</v>
+      </c>
+      <c r="E679" t="n">
+        <v>720</v>
+      </c>
+      <c r="F679" t="n">
+        <v>606</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय UFLEX @ 656-660 खरीदें STOP LOSS 606 TARGET 720/750 Uflex 667.25 ↑ 21.70</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:56:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>UFLEX</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>669</v>
+      </c>
+      <c r="E680" t="n">
+        <v>750</v>
+      </c>
+      <c r="F680" t="n">
+        <v>606</v>
+      </c>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>10 की कमाई UFLEX @ 656-660 खरीदें STOP LOSS 606 TARGET 720/750 Uflex 667.25 ▲ 3.36%</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:54:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="E681" t="n">
+        <v>400</v>
+      </c>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Eternal TARGET 400 ALLOCATION 25%</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:53:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>MAPMYINDIA</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>986.8</v>
+      </c>
+      <c r="E682" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>SID की SIP MapmyIndia CMP 985.20 TARGET 1500 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:53:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>1533.9</v>
+      </c>
+      <c r="E683" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G683" t="inlineStr"/>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>SID की SIP, Affle 3i, CMP 1534.00, TARGET 2000, 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>1533</v>
+      </c>
+      <c r="E684" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>SID की SIP
+Affle 3i
+CMP 1533.40
+TARGET 2000
+25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>MEESHO</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="E685" t="n">
+        <v>230</v>
+      </c>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>SID की SIP Meesho CMP 206.54 TARGET 230 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:51:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="E686" t="n">
+        <v>400</v>
+      </c>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>SID को SIP
+Eternal (Zomato)
+CMP 323.50
+TARGET 400
+25% ALLOCATION
+MARKET UPDATE</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:49:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>823</v>
+      </c>
+      <c r="E687" t="n">
+        <v>930</v>
+      </c>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+823.50 30.85
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:49:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>1842.7</v>
+      </c>
+      <c r="E688" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F688" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Fut 1839.80 45.80 BUY TGT 1930 SL 1840</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:41:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>427.45</v>
+      </c>
+      <c r="E689" t="n">
+        <v>432</v>
+      </c>
+      <c r="F689" t="n">
+        <v>422</v>
+      </c>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:41:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>427.45</v>
+      </c>
+      <c r="E690" t="n">
+        <v>436</v>
+      </c>
+      <c r="F690" t="n">
+        <v>422</v>
+      </c>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:40:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Interglobe Aviation Fut
+4949.50 -96.50
+SELL
+TARGET HIT
+5125</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:39:58</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
+      <c r="E692" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F692" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4949.50 -1.91%
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:39:48</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="n">
+        <v>12358</v>
+      </c>
+      <c r="F693" t="n">
+        <v>12238</v>
+      </c>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Fut 12163.00 BUY T 12238 S 12358 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E694" t="n">
+        <v>930</v>
+      </c>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E695" t="n">
+        <v>950</v>
+      </c>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E696" t="n">
+        <v>930</v>
+      </c>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+ANTELOPUS SELAN ENRGY LTD
+PRICE ▶ 833.70
+TARGET ▶ 930/950</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E697" t="n">
+        <v>950</v>
+      </c>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+ANTELOPUS SELAN ENRGY LTD
+PRICE ▶ 833.70
+TARGET ▶ 930/950</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:35:16</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr"/>
+      <c r="E698" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>OF THE DAY InterGlobe Aviation Fut 4947 SELL TGT 5000 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:36:00</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>4946</v>
+      </c>
+      <c r="E699" t="n">
+        <v>3125</v>
+      </c>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation Fut 4947.40 -99.00 SELL TARGET HIT 3125</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:35:09</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
+      <c r="E700" t="n">
+        <v>371</v>
+      </c>
+      <c r="F700" t="n">
+        <v>335</v>
+      </c>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>EMS Ltd 406.8 BUY TGT 371 SL 335 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:36:00</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>405.05</v>
+      </c>
+      <c r="E701" t="n">
+        <v>565</v>
+      </c>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 406.00 34.05 BUY TARGET HIT 565</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:34:55</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
+      <c r="E702" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F702" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Centum Elec 3505 BUY TGT 3500 SL 3300 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:34:46</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5408.50 -2.61% SELL TARGET HIT 5600</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:26</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F704" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4955.00 -91.00
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:31:00</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="E705" t="n">
+        <v>565</v>
+      </c>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TARGET HIT 565</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:18</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="n">
+        <v>371</v>
+      </c>
+      <c r="F706" t="n">
+        <v>365</v>
+      </c>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TGT 371 SL 365</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:16</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr"/>
+      <c r="E707" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Fut 12235.00 -1.17% SELL TARGET HIT 12550</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:12</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr"/>
+      <c r="E708" t="n">
+        <v>12250</v>
+      </c>
+      <c r="F708" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Bajaj Auto Fut
+12238.00 -142.00
+SELL
+TGT 12250
+SL 12550</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:07</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
+      <c r="E709" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+Centum Elec
+3512.70 2.63%
+BUY
+TARGET HIT
+3360</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:06</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F710" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+Centum Elec
+3512.70 2.63%
+BUY
+TGT 3500
+SL 3360</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:29:58</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="n">
+        <v>5520</v>
+      </c>
+      <c r="F711" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Hero Motocorp Fut
+5429.00 -124.50
+SELL
+TGT 5520
+SL 5600</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:35</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
+      <c r="E712" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Inter globe Aviation Fut
+4953.50 -1.83%
+SELL
+TARGET HIT
+5125</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>4964</v>
+      </c>
+      <c r="E713" t="n">
+        <v>3125</v>
+      </c>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Inter globe Aviation Fut
+4953.50 -92.50
+SELL
+TARGET HIT
+3125</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:32</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr"/>
+      <c r="E714" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F714" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Inter globe Aviation Fut
+4953.50 -1.83%
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:31</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr"/>
+      <c r="E715" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F715" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4953.50 -92.50
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>403.05</v>
+      </c>
+      <c r="E716" t="n">
+        <v>565</v>
+      </c>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>अरुण शर्मा जैन
+EMS Ltd
+400.00 7.54%
+BUY
+TARGET HIT
+565</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:26</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr"/>
+      <c r="E717" t="n">
+        <v>365</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+EMS Ltd
+400.00 7.54%
+BUY
+TARGET HIT
+365</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:11</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -125.50 SELL TARGET HIT 5600</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>5436.5</v>
+      </c>
+      <c r="E719" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -2.26% SELL TARGET HIT 3600</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:08</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr"/>
+      <c r="E720" t="n">
+        <v>5520</v>
+      </c>
+      <c r="F720" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Hero Motocorp Fut
+5427.00 -2.28%
+SELL
+TGT 5520
+SL 5600</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>1924.6</v>
+      </c>
+      <c r="E721" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Bernstein</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>बर्नस्टीन Sun Pharma 1911.70 -17.30 OUTPERFORM लक्ष्य ₹2235</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E722" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Bernstein</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>बर्नस्टीन Sun Pharma 1910.00 -19.00 OUTPERFORM लक्ष्य ₹2235</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>7860</v>
+      </c>
+      <c r="E723" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Eicher Motors
+7821.00 -149.00
+BUY
+लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E724" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>SBI Life 1728.30 11.00 0.63% Vol: 639 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E725" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS BUY लक्ष्य ₹2235</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E726" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>HSBC Sun Pharma 1913.30 -0.81% BUY लक्ष्य ₹2120</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E727" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>HSBC
+Sun Pharma
+1914.00 -15.00
+BUY
+लक्ष्य ₹2120</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="E728" t="n">
+        <v>440</v>
+      </c>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>Coal India 406.00 +4.40 HOLD लक्ष्य ₹440</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>162.74</v>
+      </c>
+      <c r="E729" t="n">
+        <v>440</v>
+      </c>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson 164.00 1.60 0.97% Vol: 19.98 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹440</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="E730" t="n">
+        <v>550</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>UBS Coal India 406.00 +4.40 BUY लक्ष्य ₹550</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E731" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F731" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E732" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F732" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E733" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F733" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>274</v>
+      </c>
+      <c r="E734" t="n">
+        <v>281</v>
+      </c>
+      <c r="F734" t="n">
+        <v>271</v>
+      </c>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>MY CHOICE NLC INDIA B 281 271</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>495</v>
+      </c>
+      <c r="E735" t="n">
+        <v>510</v>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI PRU LIFE B 510</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E736" t="n">
+        <v>867</v>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAGARH B 867</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>361</v>
+      </c>
+      <c r="E737" t="n">
+        <v>350</v>
+      </c>
+      <c r="F737" t="n">
+        <v>368</v>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>MY CHOICE HPCL FUT S 350 368</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E738" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT गोल्डमैन सैक्स SBI Life 1739.30 1.20 TARGET ₹2235</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>1270</v>
+      </c>
+      <c r="E739" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F739" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY UNO Minda Ltd BUY PRICE 1274.40 TARGET 1320/1340 STOP LOSS 1240</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>MARUTI29SEP26</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>12882</v>
+      </c>
+      <c r="E740" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F740" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Maruti Suzuki Fut
+SELL
+PRICE ▶ 12956.00
+TARGET ▶ 12200
+STOP LOSS ▶ 13500</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>238.25</v>
+      </c>
+      <c r="E741" t="n">
+        <v>240</v>
+      </c>
+      <c r="F741" t="n">
+        <v>231</v>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC BUY PRICE 236.45 TARGET 240 STOP LOSS 231</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>3449</v>
+      </c>
+      <c r="E742" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F742" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Centum Elec BUY PRICE 3422.65 TARGET 3500 STOP LOSS 3360</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E743" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Bernstein</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>बर्नस्टीन Sun Pharma 1929.00 -55.80 OUTPERFORM लक्ष्य ₹2235</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E744" t="n">
+        <v>12250</v>
+      </c>
+      <c r="F744" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E745" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F745" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E746" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F746" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E747" t="n">
+        <v>5450</v>
+      </c>
+      <c r="F747" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Hero Moto Futures
+SELL
+PRICE ▶ 5553
+TARGET ▶ 5520, 5450, 5405
+STOP LOSS ▶ 5600</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>7893</v>
+      </c>
+      <c r="E748" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Eicher Motors
+7970.00 +16.50
+BUY
+लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>LEMONTREE</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="E749" t="n">
+        <v>183</v>
+      </c>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Lemon Tree Hotels 106.15 ACCUMULATE लक्ष्य ₹175 से बढ़ाकर ₹183</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>CONCORDBIO</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>1484</v>
+      </c>
+      <c r="E750" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F750" t="n">
+        <v>1424</v>
+      </c>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>INVESTMENT CONCORD BIO B 1610 1424</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E751" t="n">
+        <v>867</v>
+      </c>
+      <c r="F751" t="n">
+        <v>817</v>
+      </c>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAGARH B 867 817</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>495</v>
+      </c>
+      <c r="E752" t="n">
+        <v>510</v>
+      </c>
+      <c r="F752" t="n">
+        <v>488</v>
+      </c>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI PRU LIFE B 510 488</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>MARICO29SEP26</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>836.6</v>
+      </c>
+      <c r="E753" t="n">
+        <v>852</v>
+      </c>
+      <c r="F753" t="n">
+        <v>831</v>
+      </c>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>FUTURE MARICO FUT B 852 831</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E754" t="n">
+        <v>92</v>
+      </c>
+      <c r="F754" t="n">
+        <v>83</v>
+      </c>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>FUNDA NMDC B 92 83</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>252</v>
+      </c>
+      <c r="E755" t="n">
+        <v>262</v>
+      </c>
+      <c r="F755" t="n">
+        <v>248</v>
+      </c>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>CASH APTUS VALUE B 262 248</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>460</v>
+      </c>
+      <c r="E756" t="n">
+        <v>520</v>
+      </c>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>INVESTMENT TATA MOTORS CV B 520 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E757" t="n">
+        <v>186</v>
+      </c>
+      <c r="F757" t="n">
+        <v>170</v>
+      </c>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 186 170</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E758" t="n">
+        <v>310</v>
+      </c>
+      <c r="F758" t="n">
+        <v>322</v>
+      </c>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>MY CHOICE BPCL FUT S 310 322</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E759" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 1086 170</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="F760" t="n">
+        <v>3350</v>
+      </c>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>MY CHOICE HDFC BANK S 3350</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E761" t="n">
+        <v>5446</v>
+      </c>
+      <c r="F761" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>FUTURE HERO MOTO FUT S 5446 5610</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>12211</v>
+      </c>
+      <c r="E762" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>FUNDA BAJAJ AUTO B 12800 3 MONTH</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>274</v>
+      </c>
+      <c r="E763" t="n">
+        <v>281</v>
+      </c>
+      <c r="F763" t="n">
+        <v>271</v>
+      </c>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+NLC India
+खरीदें
+PRICE ▶ 274.30
+TARGET ▶ 281
+STOP LOSS ▶ 271</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>495</v>
+      </c>
+      <c r="E764" t="n">
+        <v>510</v>
+      </c>
+      <c r="F764" t="n">
+        <v>488</v>
+      </c>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>ICICI Pru खरीदें PRICE 495.45 TARGET 510 STOP LOSS 488</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E765" t="n">
+        <v>867</v>
+      </c>
+      <c r="F765" t="n">
+        <v>817</v>
+      </c>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Titagarh Rail खरीदें PRICE 833.95 TARGET 867 STOP LOSS 817</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E766" t="n">
+        <v>310</v>
+      </c>
+      <c r="F766" t="n">
+        <v>322</v>
+      </c>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+BPCL Fut
+बेचें
+PRICE ▶ 318.00
+TARGET ▶ 310
+STOP LOSS ▶ 322</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E767" t="n">
+        <v>310</v>
+      </c>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+BPCL Fut
+PRICE 318.00
+TARGET 310</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="E768" t="n">
+        <v>350</v>
+      </c>
+      <c r="F768" t="n">
+        <v>368</v>
+      </c>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>MY CHOICE HPCL Fut बेचें PRICE 362.85 TARGET 350 STOP LOSS 368</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E769" t="n">
+        <v>186</v>
+      </c>
+      <c r="F769" t="n">
+        <v>170</v>
+      </c>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sri Lotus
+खरीदें
+PRICE ▶ 179.18
+TARGET ▶ 186
+STOP LOSS ▶ 170</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E770" t="n">
+        <v>186</v>
+      </c>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sri Lotus
+PRICE → 179.18
+TARGET → 186</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E771" t="n">
+        <v>92</v>
+      </c>
+      <c r="F771" t="n">
+        <v>83</v>
+      </c>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>FUNDA PICK NMDC खरीदें PRICE 85.69 TARGET 92 STOP LOSS 83</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>12275</v>
+      </c>
+      <c r="E772" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+Bajaj Auto
+खरीदें
+PRICE → 12361.00
+TARGET → 12800
+DURATION → 3-6 महीने</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E773" t="n">
+        <v>5446</v>
+      </c>
+      <c r="F773" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Hero Motocorp Fut
+बेचें
+PRICE → 5553.50
+TARGET → 5446
+STOP LOSS → 5610</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>MARICO29SEP26</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>836.6</v>
+      </c>
+      <c r="E774" t="n">
+        <v>852</v>
+      </c>
+      <c r="F774" t="n">
+        <v>831</v>
+      </c>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Marico Fut
+खरीदें
+PRICE → 838.35
+TARGET → 852
+STOP LOSS → 831</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>252</v>
+      </c>
+      <c r="E775" t="n">
+        <v>262</v>
+      </c>
+      <c r="F775" t="n">
+        <v>248</v>
+      </c>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Aptus Value खरीदें PRICE 253.36 TARGET 262 STOP LOSS 248</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E776" t="n">
+        <v>2935</v>
+      </c>
+      <c r="F776" t="n">
+        <v>2846</v>
+      </c>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+Gland Pharma
+खरीदें
+PRICE → 2875.00
+TARGET → 2935
+STOP LOSS → 2846</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>LEMONTREE</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="E777" t="n">
+        <v>163</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>CLSA</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT CLSA ACCUMULATE Lemon Tree Hotels 106.15 0.09% लक्ष्य ₹175 से घटाकर ₹163</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="E778" t="n">
+        <v>350</v>
+      </c>
+      <c r="F778" t="n">
+        <v>322</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Eternal (Zomato) खरीदें PRICE 327.75 TARGET 340/350 STOP LOSS 322</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="E779" t="n">
+        <v>340</v>
+      </c>
+      <c r="F779" t="n">
+        <v>322</v>
+      </c>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Eternal (Zomato) खरीदें PRICE 327.75 TARGET 340/350 STOP LOSS 322</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>3966</v>
+      </c>
+      <c r="E780" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>सिटी
+L&amp;T
+3980.10 -1.60%
+BUY
+लक्ष्य ₹4650</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E781" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G781" t="inlineStr"/>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>Sun Pharma 1929 BUY लक्ष्य ₹2120</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E782" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>HSBC
+Sun Pharma
+1929.00 -55.80
+BUY
+लक्ष्य ₹2120</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J652"/>
+  <autoFilter ref="A1:J782"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$782</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$938</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J782"/>
+  <dimension ref="A1:J938"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -28695,7 +28695,6 @@
       <c r="F655" t="n">
         <v>203</v>
       </c>
-      <c r="G655" t="inlineStr"/>
       <c r="H655" t="inlineStr">
         <is>
           <t>ITC Fut PRICE 268.3 TARGET 277/203</t>
@@ -28737,7 +28736,6 @@
       <c r="F656" t="n">
         <v>520</v>
       </c>
-      <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr">
         <is>
           <t>GNA Axles @ 536 खरीदें STOP LOSS 520 TARGET 560 DURATION -- GNA Axles 540.50 8.05</t>
@@ -28825,7 +28823,6 @@
       <c r="F658" t="n">
         <v>1000</v>
       </c>
-      <c r="G658" t="inlineStr"/>
       <c r="H658" t="inlineStr">
         <is>
           <t>Mangalam Cem खरीदें PRICE 1109.40 TARGET 1200/1250 STOP LOSS 1000 नवनीत मुनोत MD &amp; CEO HDFC AMC COMING UP</t>
@@ -28867,7 +28864,6 @@
       <c r="F659" t="n">
         <v>1000</v>
       </c>
-      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr">
         <is>
           <t>10 की कमाई Mangalam Cem खरीदें PRICE 1110.00 TARGET 1200/1250 STOP LOSS 1000</t>
@@ -28909,7 +28905,6 @@
       <c r="F660" t="n">
         <v>422</v>
       </c>
-      <c r="G660" t="inlineStr"/>
       <c r="H660" t="inlineStr">
         <is>
           <t>विशेष के विशेष
@@ -28956,7 +28951,6 @@
       <c r="F661" t="n">
         <v>422</v>
       </c>
-      <c r="G661" t="inlineStr"/>
       <c r="H661" t="inlineStr">
         <is>
           <t>विशेष के विशेष
@@ -29000,7 +28994,6 @@
       <c r="E662" t="n">
         <v>930</v>
       </c>
-      <c r="G662" t="inlineStr"/>
       <c r="H662" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -29044,7 +29037,6 @@
       <c r="E663" t="n">
         <v>930</v>
       </c>
-      <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -29091,7 +29083,6 @@
       <c r="F664" t="n">
         <v>1840</v>
       </c>
-      <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr">
         <is>
           <t>जय का JACKPOT Oberoi Realty Fut 1854.30 31.30 BUY TGT 1930 SL 1840</t>
@@ -29133,7 +29124,6 @@
       <c r="F665" t="n">
         <v>1960</v>
       </c>
-      <c r="G665" t="inlineStr"/>
       <c r="H665" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -29180,7 +29170,6 @@
       <c r="F666" t="n">
         <v>1960</v>
       </c>
-      <c r="G666" t="inlineStr"/>
       <c r="H666" t="inlineStr">
         <is>
           <t>10 की कमाई Alkyl Amines खरीदें PRICE 2028.40 TARGET 2100/2150 STOP LOSS 1960 MARKET MENTORS नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
@@ -29268,7 +29257,6 @@
       <c r="F668" t="n">
         <v>500</v>
       </c>
-      <c r="G668" t="inlineStr"/>
       <c r="H668" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -29310,7 +29298,6 @@
       <c r="D669" t="n">
         <v>603.5</v>
       </c>
-      <c r="G669" t="inlineStr"/>
       <c r="H669" t="inlineStr">
         <is>
           <t>Innogene खरीदें STOP LOSS 500 TARGET ₹50</t>
@@ -29343,14 +29330,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
       <c r="E670" t="n">
         <v>340</v>
       </c>
       <c r="F670" t="n">
         <v>270</v>
       </c>
-      <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK SCI खरीदें STOP LOSS 270 TARGET 340 DURATION</t>
@@ -29392,7 +29377,6 @@
       <c r="F671" t="n">
         <v>380</v>
       </c>
-      <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -29429,7 +29413,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
       <c r="E672" t="n">
         <v>240</v>
       </c>
@@ -29473,7 +29456,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
       <c r="E673" t="n">
         <v>270</v>
       </c>
@@ -29572,7 +29554,6 @@
       <c r="F675" t="n">
         <v>500</v>
       </c>
-      <c r="G675" t="inlineStr"/>
       <c r="H675" t="inlineStr">
         <is>
           <t>सौमिल मेहता की राय Indegene खरीदें STOP LOSS 500 TARGET 850 DURATION -- Indegene 606.25 0.14%</t>
@@ -29605,14 +29586,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
       <c r="E676" t="n">
         <v>550</v>
       </c>
       <c r="F676" t="n">
         <v>380</v>
       </c>
-      <c r="G676" t="inlineStr"/>
       <c r="H676" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -29649,7 +29628,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr"/>
       <c r="E677" t="n">
         <v>550</v>
       </c>
@@ -29706,7 +29684,6 @@
       <c r="F678" t="n">
         <v>422</v>
       </c>
-      <c r="G678" t="inlineStr"/>
       <c r="H678" t="inlineStr">
         <is>
           <t>Kotak Bank Fut 425.25 1.50 BUY TGT 432 SL 422</t>
@@ -29794,7 +29771,6 @@
       <c r="F680" t="n">
         <v>606</v>
       </c>
-      <c r="G680" t="inlineStr"/>
       <c r="H680" t="inlineStr">
         <is>
           <t>10 की कमाई UFLEX @ 656-660 खरीदें STOP LOSS 606 TARGET 720/750 Uflex 667.25 ▲ 3.36%</t>
@@ -29833,7 +29809,6 @@
       <c r="E681" t="n">
         <v>400</v>
       </c>
-      <c r="G681" t="inlineStr"/>
       <c r="H681" t="inlineStr">
         <is>
           <t>Eternal TARGET 400 ALLOCATION 25%</t>
@@ -29872,7 +29847,6 @@
       <c r="E682" t="n">
         <v>1500</v>
       </c>
-      <c r="G682" t="inlineStr"/>
       <c r="H682" t="inlineStr">
         <is>
           <t>SID की SIP MapmyIndia CMP 985.20 TARGET 1500 25% ALLOCATION</t>
@@ -29911,7 +29885,6 @@
       <c r="E683" t="n">
         <v>2000</v>
       </c>
-      <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr">
         <is>
           <t>SID की SIP, Affle 3i, CMP 1534.00, TARGET 2000, 25% ALLOCATION</t>
@@ -29950,7 +29923,6 @@
       <c r="E684" t="n">
         <v>2000</v>
       </c>
-      <c r="G684" t="inlineStr"/>
       <c r="H684" t="inlineStr">
         <is>
           <t>SID की SIP
@@ -29993,7 +29965,6 @@
       <c r="E685" t="n">
         <v>230</v>
       </c>
-      <c r="G685" t="inlineStr"/>
       <c r="H685" t="inlineStr">
         <is>
           <t>SID की SIP Meesho CMP 206.54 TARGET 230 25% ALLOCATION</t>
@@ -30032,7 +30003,6 @@
       <c r="E686" t="n">
         <v>400</v>
       </c>
-      <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr">
         <is>
           <t>SID को SIP
@@ -30076,7 +30046,6 @@
       <c r="E687" t="n">
         <v>930</v>
       </c>
-      <c r="G687" t="inlineStr"/>
       <c r="H687" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -30123,7 +30092,6 @@
       <c r="F688" t="n">
         <v>1840</v>
       </c>
-      <c r="G688" t="inlineStr"/>
       <c r="H688" t="inlineStr">
         <is>
           <t>Oberoi Realty Fut 1839.80 45.80 BUY TGT 1930 SL 1840</t>
@@ -30165,7 +30133,6 @@
       <c r="F689" t="n">
         <v>422</v>
       </c>
-      <c r="G689" t="inlineStr"/>
       <c r="H689" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
@@ -30207,7 +30174,6 @@
       <c r="F690" t="n">
         <v>422</v>
       </c>
-      <c r="G690" t="inlineStr"/>
       <c r="H690" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
@@ -30240,11 +30206,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr"/>
       <c r="E691" t="n">
         <v>5125</v>
       </c>
-      <c r="G691" t="inlineStr"/>
       <c r="H691" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -30282,14 +30246,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
       <c r="E692" t="n">
         <v>5000</v>
       </c>
       <c r="F692" t="n">
         <v>5125</v>
       </c>
-      <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -30327,14 +30289,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
       <c r="E693" t="n">
         <v>12358</v>
       </c>
       <c r="F693" t="n">
         <v>12238</v>
       </c>
-      <c r="G693" t="inlineStr"/>
       <c r="H693" t="inlineStr">
         <is>
           <t>Bajaj Auto Fut 12163.00 BUY T 12238 S 12358 TARGET HIT</t>
@@ -30373,7 +30333,6 @@
       <c r="E694" t="n">
         <v>930</v>
       </c>
-      <c r="G694" t="inlineStr"/>
       <c r="H694" t="inlineStr">
         <is>
           <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
@@ -30412,7 +30371,6 @@
       <c r="E695" t="n">
         <v>950</v>
       </c>
-      <c r="G695" t="inlineStr"/>
       <c r="H695" t="inlineStr">
         <is>
           <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
@@ -30451,7 +30409,6 @@
       <c r="E696" t="n">
         <v>930</v>
       </c>
-      <c r="G696" t="inlineStr"/>
       <c r="H696" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -30493,7 +30450,6 @@
       <c r="E697" t="n">
         <v>950</v>
       </c>
-      <c r="G697" t="inlineStr"/>
       <c r="H697" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -30529,11 +30485,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
       <c r="E698" t="n">
         <v>5000</v>
       </c>
-      <c r="G698" t="inlineStr"/>
       <c r="H698" t="inlineStr">
         <is>
           <t>OF THE DAY InterGlobe Aviation Fut 4947 SELL TGT 5000 TARGET HIT</t>
@@ -30572,7 +30526,6 @@
       <c r="E699" t="n">
         <v>3125</v>
       </c>
-      <c r="G699" t="inlineStr"/>
       <c r="H699" t="inlineStr">
         <is>
           <t>Interglobe Aviation Fut 4947.40 -99.00 SELL TARGET HIT 3125</t>
@@ -30605,14 +30558,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
       <c r="E700" t="n">
         <v>371</v>
       </c>
       <c r="F700" t="n">
         <v>335</v>
       </c>
-      <c r="G700" t="inlineStr"/>
       <c r="H700" t="inlineStr">
         <is>
           <t>EMS Ltd 406.8 BUY TGT 371 SL 335 TARGET HIT</t>
@@ -30651,7 +30602,6 @@
       <c r="E701" t="n">
         <v>565</v>
       </c>
-      <c r="G701" t="inlineStr"/>
       <c r="H701" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 406.00 34.05 BUY TARGET HIT 565</t>
@@ -30684,14 +30634,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
       <c r="E702" t="n">
         <v>3500</v>
       </c>
       <c r="F702" t="n">
         <v>3300</v>
       </c>
-      <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr">
         <is>
           <t>Centum Elec 3505 BUY TGT 3500 SL 3300 TARGET HIT</t>
@@ -30724,11 +30672,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
       <c r="E703" t="n">
         <v>5600</v>
       </c>
-      <c r="G703" t="inlineStr"/>
       <c r="H703" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5408.50 -2.61% SELL TARGET HIT 5600</t>
@@ -30761,14 +30707,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
       <c r="E704" t="n">
         <v>5000</v>
       </c>
       <c r="F704" t="n">
         <v>5125</v>
       </c>
-      <c r="G704" t="inlineStr"/>
       <c r="H704" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -30812,7 +30756,6 @@
       <c r="E705" t="n">
         <v>565</v>
       </c>
-      <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TARGET HIT 565</t>
@@ -30845,14 +30788,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
       <c r="E706" t="n">
         <v>371</v>
       </c>
       <c r="F706" t="n">
         <v>365</v>
       </c>
-      <c r="G706" t="inlineStr"/>
       <c r="H706" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TGT 371 SL 365</t>
@@ -30885,11 +30826,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
       <c r="E707" t="n">
         <v>12550</v>
       </c>
-      <c r="G707" t="inlineStr"/>
       <c r="H707" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Fut 12235.00 -1.17% SELL TARGET HIT 12550</t>
@@ -30922,14 +30861,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
       <c r="E708" t="n">
         <v>12250</v>
       </c>
       <c r="F708" t="n">
         <v>12550</v>
       </c>
-      <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -30967,11 +30904,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
       <c r="E709" t="n">
         <v>3360</v>
       </c>
-      <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr">
         <is>
           <t>आस्था जैन
@@ -31009,7 +30944,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D710" t="inlineStr"/>
       <c r="E710" t="n">
         <v>3500</v>
       </c>
@@ -31058,14 +30992,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr"/>
       <c r="E711" t="n">
         <v>5520</v>
       </c>
       <c r="F711" t="n">
         <v>5600</v>
       </c>
-      <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -31103,11 +31035,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
       <c r="E712" t="n">
         <v>5125</v>
       </c>
-      <c r="G712" t="inlineStr"/>
       <c r="H712" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -31151,7 +31081,6 @@
       <c r="E713" t="n">
         <v>3125</v>
       </c>
-      <c r="G713" t="inlineStr"/>
       <c r="H713" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -31189,14 +31118,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D714" t="inlineStr"/>
       <c r="E714" t="n">
         <v>5000</v>
       </c>
       <c r="F714" t="n">
         <v>5125</v>
       </c>
-      <c r="G714" t="inlineStr"/>
       <c r="H714" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -31234,14 +31161,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
       <c r="E715" t="n">
         <v>5000</v>
       </c>
       <c r="F715" t="n">
         <v>5125</v>
       </c>
-      <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -31285,7 +31210,6 @@
       <c r="E716" t="n">
         <v>565</v>
       </c>
-      <c r="G716" t="inlineStr"/>
       <c r="H716" t="inlineStr">
         <is>
           <t>अरुण शर्मा जैन
@@ -31323,7 +31247,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr"/>
       <c r="E717" t="n">
         <v>365</v>
       </c>
@@ -31369,11 +31292,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D718" t="inlineStr"/>
       <c r="E718" t="n">
         <v>5600</v>
       </c>
-      <c r="G718" t="inlineStr"/>
       <c r="H718" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -125.50 SELL TARGET HIT 5600</t>
@@ -31412,7 +31333,6 @@
       <c r="E719" t="n">
         <v>3600</v>
       </c>
-      <c r="G719" t="inlineStr"/>
       <c r="H719" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -2.26% SELL TARGET HIT 3600</t>
@@ -31445,14 +31365,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D720" t="inlineStr"/>
       <c r="E720" t="n">
         <v>5520</v>
       </c>
       <c r="F720" t="n">
         <v>5600</v>
       </c>
-      <c r="G720" t="inlineStr"/>
       <c r="H720" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -31582,7 +31500,6 @@
       <c r="E723" t="n">
         <v>9400</v>
       </c>
-      <c r="G723" t="inlineStr"/>
       <c r="H723" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -31625,7 +31542,6 @@
       <c r="E724" t="n">
         <v>9400</v>
       </c>
-      <c r="G724" t="inlineStr"/>
       <c r="H724" t="inlineStr">
         <is>
           <t>SBI Life 1728.30 11.00 0.63% Vol: 639 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹9400</t>
@@ -31664,7 +31580,6 @@
       <c r="E725" t="n">
         <v>2235</v>
       </c>
-      <c r="G725" t="inlineStr"/>
       <c r="H725" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS BUY लक्ष्य ₹2235</t>
@@ -31793,7 +31708,6 @@
       <c r="E728" t="n">
         <v>440</v>
       </c>
-      <c r="G728" t="inlineStr"/>
       <c r="H728" t="inlineStr">
         <is>
           <t>Coal India 406.00 +4.40 HOLD लक्ष्य ₹440</t>
@@ -31832,7 +31746,6 @@
       <c r="E729" t="n">
         <v>440</v>
       </c>
-      <c r="G729" t="inlineStr"/>
       <c r="H729" t="inlineStr">
         <is>
           <t>Samvardhana Motherson 164.00 1.60 0.97% Vol: 19.98 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹440</t>
@@ -31917,7 +31830,6 @@
       <c r="F731" t="n">
         <v>12650</v>
       </c>
-      <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -31959,7 +31871,6 @@
       <c r="F732" t="n">
         <v>12650</v>
       </c>
-      <c r="G732" t="inlineStr"/>
       <c r="H732" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -32001,7 +31912,6 @@
       <c r="F733" t="n">
         <v>12650</v>
       </c>
-      <c r="G733" t="inlineStr"/>
       <c r="H733" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -32043,7 +31953,6 @@
       <c r="F734" t="n">
         <v>271</v>
       </c>
-      <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr">
         <is>
           <t>MY CHOICE NLC INDIA B 281 271</t>
@@ -32082,7 +31991,6 @@
       <c r="E735" t="n">
         <v>510</v>
       </c>
-      <c r="G735" t="inlineStr"/>
       <c r="H735" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI PRU LIFE B 510</t>
@@ -32121,7 +32029,6 @@
       <c r="E736" t="n">
         <v>867</v>
       </c>
-      <c r="G736" t="inlineStr"/>
       <c r="H736" t="inlineStr">
         <is>
           <t>MY CHOICE TITAGARH B 867</t>
@@ -32163,7 +32070,6 @@
       <c r="F737" t="n">
         <v>368</v>
       </c>
-      <c r="G737" t="inlineStr"/>
       <c r="H737" t="inlineStr">
         <is>
           <t>MY CHOICE HPCL FUT S 350 368</t>
@@ -32248,7 +32154,6 @@
       <c r="F739" t="n">
         <v>1240</v>
       </c>
-      <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr">
         <is>
           <t>PICK OF THE DAY UNO Minda Ltd BUY PRICE 1274.40 TARGET 1320/1340 STOP LOSS 1240</t>
@@ -32290,7 +32195,6 @@
       <c r="F740" t="n">
         <v>13500</v>
       </c>
-      <c r="G740" t="inlineStr"/>
       <c r="H740" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -32337,7 +32241,6 @@
       <c r="F741" t="n">
         <v>231</v>
       </c>
-      <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC BUY PRICE 236.45 TARGET 240 STOP LOSS 231</t>
@@ -32379,7 +32282,6 @@
       <c r="F742" t="n">
         <v>3360</v>
       </c>
-      <c r="G742" t="inlineStr"/>
       <c r="H742" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Centum Elec BUY PRICE 3422.65 TARGET 3500 STOP LOSS 3360</t>
@@ -32464,7 +32366,6 @@
       <c r="F744" t="n">
         <v>12550</v>
       </c>
-      <c r="G744" t="inlineStr"/>
       <c r="H744" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -32506,7 +32407,6 @@
       <c r="F745" t="n">
         <v>12550</v>
       </c>
-      <c r="G745" t="inlineStr"/>
       <c r="H745" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -32548,7 +32448,6 @@
       <c r="F746" t="n">
         <v>12550</v>
       </c>
-      <c r="G746" t="inlineStr"/>
       <c r="H746" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -32590,7 +32489,6 @@
       <c r="F747" t="n">
         <v>5600</v>
       </c>
-      <c r="G747" t="inlineStr"/>
       <c r="H747" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -32634,7 +32532,6 @@
       <c r="E748" t="n">
         <v>9400</v>
       </c>
-      <c r="G748" t="inlineStr"/>
       <c r="H748" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -32677,7 +32574,6 @@
       <c r="E749" t="n">
         <v>183</v>
       </c>
-      <c r="G749" t="inlineStr"/>
       <c r="H749" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Lemon Tree Hotels 106.15 ACCUMULATE लक्ष्य ₹175 से बढ़ाकर ₹183</t>
@@ -32719,7 +32615,6 @@
       <c r="F750" t="n">
         <v>1424</v>
       </c>
-      <c r="G750" t="inlineStr"/>
       <c r="H750" t="inlineStr">
         <is>
           <t>INVESTMENT CONCORD BIO B 1610 1424</t>
@@ -32761,7 +32656,6 @@
       <c r="F751" t="n">
         <v>817</v>
       </c>
-      <c r="G751" t="inlineStr"/>
       <c r="H751" t="inlineStr">
         <is>
           <t>MY CHOICE TITAGARH B 867 817</t>
@@ -32803,7 +32697,6 @@
       <c r="F752" t="n">
         <v>488</v>
       </c>
-      <c r="G752" t="inlineStr"/>
       <c r="H752" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI PRU LIFE B 510 488</t>
@@ -32845,7 +32738,6 @@
       <c r="F753" t="n">
         <v>831</v>
       </c>
-      <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr">
         <is>
           <t>FUTURE MARICO FUT B 852 831</t>
@@ -32887,7 +32779,6 @@
       <c r="F754" t="n">
         <v>83</v>
       </c>
-      <c r="G754" t="inlineStr"/>
       <c r="H754" t="inlineStr">
         <is>
           <t>FUNDA NMDC B 92 83</t>
@@ -32929,7 +32820,6 @@
       <c r="F755" t="n">
         <v>248</v>
       </c>
-      <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr">
         <is>
           <t>CASH APTUS VALUE B 262 248</t>
@@ -32968,7 +32858,6 @@
       <c r="E756" t="n">
         <v>520</v>
       </c>
-      <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr">
         <is>
           <t>INVESTMENT TATA MOTORS CV B 520 12 MONTH</t>
@@ -33010,7 +32899,6 @@
       <c r="F757" t="n">
         <v>170</v>
       </c>
-      <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr">
         <is>
           <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 186 170</t>
@@ -33052,7 +32940,6 @@
       <c r="F758" t="n">
         <v>322</v>
       </c>
-      <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr">
         <is>
           <t>MY CHOICE BPCL FUT S 310 322</t>
@@ -33091,7 +32978,6 @@
       <c r="E759" t="n">
         <v>1086</v>
       </c>
-      <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr">
         <is>
           <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 1086 170</t>
@@ -33130,7 +33016,6 @@
       <c r="F760" t="n">
         <v>3350</v>
       </c>
-      <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr">
         <is>
           <t>MY CHOICE HDFC BANK S 3350</t>
@@ -33172,7 +33057,6 @@
       <c r="F761" t="n">
         <v>5610</v>
       </c>
-      <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr">
         <is>
           <t>FUTURE HERO MOTO FUT S 5446 5610</t>
@@ -33211,7 +33095,6 @@
       <c r="E762" t="n">
         <v>12800</v>
       </c>
-      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
           <t>FUNDA BAJAJ AUTO B 12800 3 MONTH</t>
@@ -33253,7 +33136,6 @@
       <c r="F763" t="n">
         <v>271</v>
       </c>
-      <c r="G763" t="inlineStr"/>
       <c r="H763" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -33300,7 +33182,6 @@
       <c r="F764" t="n">
         <v>488</v>
       </c>
-      <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr">
         <is>
           <t>ICICI Pru खरीदें PRICE 495.45 TARGET 510 STOP LOSS 488</t>
@@ -33342,7 +33223,6 @@
       <c r="F765" t="n">
         <v>817</v>
       </c>
-      <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr">
         <is>
           <t>अंश के शेयर Titagarh Rail खरीदें PRICE 833.95 TARGET 867 STOP LOSS 817</t>
@@ -33384,7 +33264,6 @@
       <c r="F766" t="n">
         <v>322</v>
       </c>
-      <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -33428,7 +33307,6 @@
       <c r="E767" t="n">
         <v>310</v>
       </c>
-      <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -33473,7 +33351,6 @@
       <c r="F768" t="n">
         <v>368</v>
       </c>
-      <c r="G768" t="inlineStr"/>
       <c r="H768" t="inlineStr">
         <is>
           <t>MY CHOICE HPCL Fut बेचें PRICE 362.85 TARGET 350 STOP LOSS 368</t>
@@ -33515,7 +33392,6 @@
       <c r="F769" t="n">
         <v>170</v>
       </c>
-      <c r="G769" t="inlineStr"/>
       <c r="H769" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -33559,7 +33435,6 @@
       <c r="E770" t="n">
         <v>186</v>
       </c>
-      <c r="G770" t="inlineStr"/>
       <c r="H770" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -33604,7 +33479,6 @@
       <c r="F771" t="n">
         <v>83</v>
       </c>
-      <c r="G771" t="inlineStr"/>
       <c r="H771" t="inlineStr">
         <is>
           <t>FUNDA PICK NMDC खरीदें PRICE 85.69 TARGET 92 STOP LOSS 83</t>
@@ -33643,7 +33517,6 @@
       <c r="E772" t="n">
         <v>12800</v>
       </c>
-      <c r="G772" t="inlineStr"/>
       <c r="H772" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -33690,7 +33563,6 @@
       <c r="F773" t="n">
         <v>5610</v>
       </c>
-      <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -33737,7 +33609,6 @@
       <c r="F774" t="n">
         <v>831</v>
       </c>
-      <c r="G774" t="inlineStr"/>
       <c r="H774" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -33784,7 +33655,6 @@
       <c r="F775" t="n">
         <v>248</v>
       </c>
-      <c r="G775" t="inlineStr"/>
       <c r="H775" t="inlineStr">
         <is>
           <t>CASH का शेयर Aptus Value खरीदें PRICE 253.36 TARGET 262 STOP LOSS 248</t>
@@ -33826,7 +33696,6 @@
       <c r="F776" t="n">
         <v>2846</v>
       </c>
-      <c r="G776" t="inlineStr"/>
       <c r="H776" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -33962,7 +33831,6 @@
       <c r="F779" t="n">
         <v>322</v>
       </c>
-      <c r="G779" t="inlineStr"/>
       <c r="H779" t="inlineStr">
         <is>
           <t>सिद्धार्थ राय मंगला की राय Eternal (Zomato) खरीदें PRICE 327.75 TARGET 340/350 STOP LOSS 322</t>
@@ -34001,7 +33869,6 @@
       <c r="E780" t="n">
         <v>4650</v>
       </c>
-      <c r="G780" t="inlineStr"/>
       <c r="H780" t="inlineStr">
         <is>
           <t>सिटी
@@ -34044,7 +33911,6 @@
       <c r="E781" t="n">
         <v>2120</v>
       </c>
-      <c r="G781" t="inlineStr"/>
       <c r="H781" t="inlineStr">
         <is>
           <t>Sun Pharma 1929 BUY लक्ष्य ₹2120</t>
@@ -34108,8 +33974,6715 @@
         </is>
       </c>
     </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="E783" t="n">
+        <v>405</v>
+      </c>
+      <c r="F783" t="n">
+        <v>360</v>
+      </c>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 387.65 15.50 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="E784" t="n">
+        <v>370</v>
+      </c>
+      <c r="F784" t="n">
+        <v>335</v>
+      </c>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Sunflag Iron 346.55 6.90 BUY TGT 370 SL 335</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>520.2</v>
+      </c>
+      <c r="E785" t="n">
+        <v>600</v>
+      </c>
+      <c r="F785" t="n">
+        <v>480</v>
+      </c>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL Hind Copper 520.25 1.22% BUY TGT 600 SL 480</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>2033</v>
+      </c>
+      <c r="E786" t="n">
+        <v>2078</v>
+      </c>
+      <c r="F786" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>BEML 2033.30 BUY TGT 2078 SL 2005</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>2033</v>
+      </c>
+      <c r="E787" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F787" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर BEML 2032.20 62.00 BUY TGT 2070 SL 2005</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:19:00</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>ITC29SEP26</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="E788" t="n">
+        <v>277</v>
+      </c>
+      <c r="F788" t="n">
+        <v>262</v>
+      </c>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>ITC Fut 267.90 0.80 BUY TGT 277 SL 262</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:17:55</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr"/>
+      <c r="E789" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+951.15 158.50
+BUY
+TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:17:50</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr"/>
+      <c r="E790" t="n">
+        <v>930</v>
+      </c>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+951.15  158.50
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:09:00</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>20700</v>
+      </c>
+      <c r="E791" t="n">
+        <v>21300</v>
+      </c>
+      <c r="F791" t="n">
+        <v>20200</v>
+      </c>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Solar Ind Fut
+खरीदें
+PRICE ▶ 20700.00
+TARGET ▶ 21300/21600
+STOP LOSS ▶ 20200</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:08:00</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>20690</v>
+      </c>
+      <c r="E792" t="n">
+        <v>21300</v>
+      </c>
+      <c r="F792" t="n">
+        <v>20200</v>
+      </c>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Solar Ind Fut
+खरीदें
+PRICE → 20695.00
+TARGET → 21300/21600
+STOP LOSS → 20200</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:08:00</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>20690</v>
+      </c>
+      <c r="E793" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F793" t="n">
+        <v>20200</v>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Solar Ind Fut
+खरीदें
+PRICE → 20695.00
+TARGET → 21300/21600
+STOP LOSS → 20200</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:08:00</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>20690</v>
+      </c>
+      <c r="E794" t="n">
+        <v>21300</v>
+      </c>
+      <c r="F794" t="n">
+        <v>20200</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय
+Solar Ind Fut
+खरीदें
+PRICE → 20650.00
+TARGET → 21300/21600
+STOP LOSS → 20200</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:08:00</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>SOLARINDS29SEP26</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>20690</v>
+      </c>
+      <c r="E795" t="n">
+        <v>21600</v>
+      </c>
+      <c r="F795" t="n">
+        <v>20200</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय
+Solar Ind Fut
+खरीदें
+PRICE → 20650.00
+TARGET → 21300/21600
+STOP LOSS → 20200</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:07:00</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="E796" t="n">
+        <v>475</v>
+      </c>
+      <c r="F796" t="n">
+        <v>425</v>
+      </c>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>Super Kool Mehul
+LT Foods
+खरीदें
+PRICE → 441.50
+TARGET → 475/485
+STOP LOSS → 425</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:07:00</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="E797" t="n">
+        <v>485</v>
+      </c>
+      <c r="F797" t="n">
+        <v>425</v>
+      </c>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>Super Kool Mehul
+LT Foods
+खरीदें
+PRICE → 441.50
+TARGET → 475/485
+STOP LOSS → 425</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:07:00</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="E798" t="n">
+        <v>485</v>
+      </c>
+      <c r="F798" t="n">
+        <v>425</v>
+      </c>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>मेहुल कोटारी की राय
+LT Foods
+खरीदें
+PRICE → 442.10
+TARGET → 475/485
+STOP LOSS → 425</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:07:00</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>LTFOODS</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>442.65</v>
+      </c>
+      <c r="E799" t="n">
+        <v>475</v>
+      </c>
+      <c r="F799" t="n">
+        <v>425</v>
+      </c>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>मेहुल कोटारी की राय
+LT Foods
+खरीदें
+PRICE → 442.10
+TARGET → 475/485
+STOP LOSS → 425</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:01:00</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="E800" t="n">
+        <v>370</v>
+      </c>
+      <c r="F800" t="n">
+        <v>335</v>
+      </c>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब
+Sunflag Iron
+348.00 8.35
+BUY
+TGT 370
+SL 335</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:44:00</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E801" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F801" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Kajaria Ceramics खरीदें PRICE 1261.00 TARGET 1300/1330 STOP LOSS 1240</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:44:00</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E802" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F802" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Kajaria Ceramics खरीदें PRICE 1261.10 TARGET 1300/1330 STOP LOSS 1240</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:44:00</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="E803" t="n">
+        <v>405</v>
+      </c>
+      <c r="F803" t="n">
+        <v>360</v>
+      </c>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी साब Indian Hume Pipe 386.05 13.90 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:33:00</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>350.85</v>
+      </c>
+      <c r="E804" t="n">
+        <v>370</v>
+      </c>
+      <c r="F804" t="n">
+        <v>335</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय SUNFLAG IRON @ 347 खरीदें STOP LOSS 335 TARGET 370 Sunflag Iron 353.00 ▲ 3.93%</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:33:00</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="E805" t="n">
+        <v>370</v>
+      </c>
+      <c r="F805" t="n">
+        <v>335</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय SUNFLAG IRON @ 347 खरीदें STOP LOSS 335 TARGET 370 Sunflag Iron 353.00 ▲ 3.93%</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:28:00</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>523.65</v>
+      </c>
+      <c r="E806" t="n">
+        <v>600</v>
+      </c>
+      <c r="F806" t="n">
+        <v>480</v>
+      </c>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL
+Hind Copper
+खरीदें
+PRICE → 523.00
+TARGET → 600
+STOP LOSS → 480
+MARKET MENTORS
+रामदेव अग्रवाल
+कल 11 AM</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:27:00</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>523.1</v>
+      </c>
+      <c r="E807" t="n">
+        <v>600</v>
+      </c>
+      <c r="F807" t="n">
+        <v>480</v>
+      </c>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>Super Kool Mehul
+Hind Copper
+खरीदें
+PRICE → 522.80
+TARGET → 600
+STOP LOSS → 480</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:24:00</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="E808" t="n">
+        <v>362</v>
+      </c>
+      <c r="F808" t="n">
+        <v>351</v>
+      </c>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय Federal Bank Fut खरीदें PRICE 355.75 TARGET 362/370 STOP LOSS 351</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:24:00</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="E809" t="n">
+        <v>370</v>
+      </c>
+      <c r="F809" t="n">
+        <v>351</v>
+      </c>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय Federal Bank Fut खरीदें PRICE 355.75 TARGET 362/370 STOP LOSS 351</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:23:00</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>2035.4</v>
+      </c>
+      <c r="E810" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F810" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय BEML खरीदें PRICE 2033.90 TARGET 2070/2090 STOP LOSS 2005</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:23:00</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>2035.4</v>
+      </c>
+      <c r="E811" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F811" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय BEML खरीदें PRICE 2033.90 TARGET 2070/2090 STOP LOSS 2005</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:51:00</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D812" t="n">
+        <v>486.7</v>
+      </c>
+      <c r="E812" t="n">
+        <v>510</v>
+      </c>
+      <c r="F812" t="n">
+        <v>470</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय Bajaj Consumer खरीदें PRICE 486.90 TARGET 505/510 STOP LOSS 470</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:51:00</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>BAJAJCON</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D813" t="n">
+        <v>486.7</v>
+      </c>
+      <c r="E813" t="n">
+        <v>505</v>
+      </c>
+      <c r="F813" t="n">
+        <v>470</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय Bajaj Consumer खरीदें PRICE 486.90 TARGET 505/510 STOP LOSS 470</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:51:00</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D814" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="E814" t="n">
+        <v>222</v>
+      </c>
+      <c r="F814" t="n">
+        <v>212</v>
+      </c>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>TRADING CALL Piramal Pharma खरीदें PRICE 217.30 TARGET 222/225 STOP LOSS 212</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:51:00</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D815" t="n">
+        <v>217.42</v>
+      </c>
+      <c r="E815" t="n">
+        <v>225</v>
+      </c>
+      <c r="F815" t="n">
+        <v>212</v>
+      </c>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>TRADING CALL Piramal Pharma खरीदें PRICE 217.30 TARGET 222/225 STOP LOSS 212</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:22:00</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D816" t="n">
+        <v>722.8</v>
+      </c>
+      <c r="E816" t="n">
+        <v>750</v>
+      </c>
+      <c r="F816" t="n">
+        <v>710</v>
+      </c>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>शिवांगी सारदा की पसंद Indian Hotels खरीदें PRICE 724.40 TARGET 750 STOP LOSS 710</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:21:00</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D817" t="n">
+        <v>5026.5</v>
+      </c>
+      <c r="E817" t="n">
+        <v>5250</v>
+      </c>
+      <c r="F817" t="n">
+        <v>4920</v>
+      </c>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>शिवांगी सारदा की पसंद Titan खरीदें PRICE 5025.00 TARGET 5250 STOP LOSS 4920</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:15:00</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D818" t="n">
+        <v>326.15</v>
+      </c>
+      <c r="E818" t="n">
+        <v>340</v>
+      </c>
+      <c r="F818" t="n">
+        <v>320</v>
+      </c>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>शिवांगी सारदा की राय
+Eternal (Zomato)
+325.70 ▼ 0.63%
+BUY
+TARGET 340
+STOP LOSS 320</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:11:00</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D819" t="n">
+        <v>1020.9</v>
+      </c>
+      <c r="E819" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F819" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>शिवांगी सारदा की राय SBI 1020.60 ▼ 1.35% HOLD TARGET 1060 STOP LOSS 1000</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-02 13:10:00</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>INDIGOPNTS</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D820" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="E820" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F820" t="n">
+        <v>1111</v>
+      </c>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>शिवांगी सारदा की राय
+Indigo Paints
+1137.80 ▼ 2.95%
+HOLD
+TARGET 1200
+STOP LOSS 1111</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:52:00</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D821" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E821" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F821" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>अक्षय भागवत की राय
+Oberoi Realty
+खरीदें
+PRICE ▶ 1855.20
+TARGET ▶ 1930/1960
+STOP LOSS ▶ 1800</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:52:00</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D822" t="n">
+        <v>1855</v>
+      </c>
+      <c r="E822" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F822" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>अक्षय भागवत की राय
+Oberoi Realty
+खरीदें
+PRICE ▶ 1855.20
+TARGET ▶ 1930/1960
+STOP LOSS ▶ 1800</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:50:00</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>NIFTY2405008SEP26CE</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D823" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E823" t="n">
+        <v>105</v>
+      </c>
+      <c r="F823" t="n">
+        <v>55</v>
+      </c>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>छोटा ऑप्शन बड़ी कमाई
+निफ्टी 24050 की कॉल @ 75-76
+खरीदें
+STOP LOSS 55
+TARGET 105/125</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:50:00</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>NIFTY2405008SEP26CE</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D824" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E824" t="n">
+        <v>125</v>
+      </c>
+      <c r="F824" t="n">
+        <v>55</v>
+      </c>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>छोटा ऑप्शन बड़ी कमाई
+निफ्टी 24050 की कॉल @ 75-76
+खरीदें
+STOP LOSS 55
+TARGET 105/125</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:57:00</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>ITC29SEP26</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D825" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="E825" t="n">
+        <v>277</v>
+      </c>
+      <c r="F825" t="n">
+        <v>203</v>
+      </c>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>ITC Fut PRICE 268.3 TARGET 277/203</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:56:00</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>GNA</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D826" t="n">
+        <v>538</v>
+      </c>
+      <c r="E826" t="n">
+        <v>560</v>
+      </c>
+      <c r="F826" t="n">
+        <v>520</v>
+      </c>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>GNA Axles @ 536 खरीदें STOP LOSS 520 TARGET 560 DURATION -- GNA Axles 540.50 8.05</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:55:00</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>MANGLMCEM</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D827" t="n">
+        <v>1108.5</v>
+      </c>
+      <c r="E827" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F827" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>Mangalam Cem खरीदें PRICE 1109.40 TARGET 1200/1250 STOP LOSS 1000 नवनीत मुनोत MD &amp; CEO HDFC AMC COMING UP</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:55:00</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>MANGLMCEM</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D828" t="n">
+        <v>1108.5</v>
+      </c>
+      <c r="E828" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F828" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>10 की कमाई Mangalam Cem खरीदें PRICE 1110.00 TARGET 1200/1250 STOP LOSS 1000</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D829" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="E829" t="n">
+        <v>432</v>
+      </c>
+      <c r="F829" t="n">
+        <v>422</v>
+      </c>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>विशेष के विशेष
+Kotak Bank Fut
+423.95  2.80
+BUY
+TGT 432
+SL 422</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D830" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="E830" t="n">
+        <v>432</v>
+      </c>
+      <c r="F830" t="n">
+        <v>422</v>
+      </c>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>विशेष के विशेष
+Kotak Bank Fut
+424.00 2.75
+BUY
+TGT 432
+SL 422</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D831" t="n">
+        <v>883</v>
+      </c>
+      <c r="E831" t="n">
+        <v>930</v>
+      </c>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+875.05  82.40
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D832" t="n">
+        <v>883</v>
+      </c>
+      <c r="E832" t="n">
+        <v>930</v>
+      </c>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+876.00 83.35
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:45:00</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D833" t="n">
+        <v>1853</v>
+      </c>
+      <c r="E833" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F833" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT Oberoi Realty Fut 1854.30 31.30 BUY TGT 1930 SL 1840</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:38:00</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>ALKYLAMINE</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D834" t="n">
+        <v>2029.1</v>
+      </c>
+      <c r="E834" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F834" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G834" t="inlineStr"/>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+Alkyl Amines
+खरीदें
+PRICE ▶ 2028.40
+TARGET ▶ 2100/2150
+STOP LOSS ▶ 1960</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:38:00</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>ALKYLAMINE</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D835" t="n">
+        <v>2029.1</v>
+      </c>
+      <c r="E835" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F835" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G835" t="inlineStr"/>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>10 की कमाई Alkyl Amines खरीदें PRICE 2028.40 TARGET 2100/2150 STOP LOSS 1960 MARKET MENTORS नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:29:00</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D836" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="E836" t="n">
+        <v>850</v>
+      </c>
+      <c r="F836" t="n">
+        <v>500</v>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+Indegene
+खरीदें
+STOP LOSS 500 | TARGET 850 | DURATION --
+Indegene 603.85 ▼ 0.26%
+MARKET MENTORS
+नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:29:00</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D837" t="n">
+        <v>603.5</v>
+      </c>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>Innogene खरीदें STOP LOSS 500 TARGET ₹50</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:23:03</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>SCI</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr"/>
+      <c r="E838" t="n">
+        <v>340</v>
+      </c>
+      <c r="F838" t="n">
+        <v>270</v>
+      </c>
+      <c r="G838" t="inlineStr"/>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK SCI खरीदें STOP LOSS 270 TARGET 340 DURATION</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:23:00</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D839" t="n">
+        <v>448.65</v>
+      </c>
+      <c r="E839" t="n">
+        <v>550</v>
+      </c>
+      <c r="F839" t="n">
+        <v>380</v>
+      </c>
+      <c r="G839" t="inlineStr"/>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 448.80 ▲ 2.91%</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:17:33</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>NIFTY2380029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr"/>
+      <c r="E840" t="n">
+        <v>240</v>
+      </c>
+      <c r="F840" t="n">
+        <v>152</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY 23800 की कॉल @ ₹190 खरीदें STOP LOSS 152 TARGET 240/270</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:17:33</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>NIFTY2380029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr"/>
+      <c r="E841" t="n">
+        <v>270</v>
+      </c>
+      <c r="F841" t="n">
+        <v>152</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY 23800 की कॉल @ ₹190 खरीदें STOP LOSS 152 TARGET 240/270</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-09-02 10:06:00</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
+        <v>606.15</v>
+      </c>
+      <c r="E842" t="n">
+        <v>850</v>
+      </c>
+      <c r="F842" t="n">
+        <v>500</v>
+      </c>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>सौमिल मेहता की राय Indegene खरीदें STOP LOSS 500 TARGET 850 DURATION -- Indegene 606.25 0.14%</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:59:03</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr"/>
+      <c r="E843" t="n">
+        <v>550</v>
+      </c>
+      <c r="F843" t="n">
+        <v>380</v>
+      </c>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 436.00</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:58:59</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>DLINKINDIA</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="n">
+        <v>550</v>
+      </c>
+      <c r="F844" t="n">
+        <v>380</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय
+D-Link Ind @ 430
+खरीदें
+STOP LOSS 380 | TARGET 550 | DURATION --
+D-Link Ind 436.00</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:58:00</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D845" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="E845" t="n">
+        <v>432</v>
+      </c>
+      <c r="F845" t="n">
+        <v>422</v>
+      </c>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>Kotak Bank Fut 425.25 1.50 BUY TGT 432 SL 422</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:56:00</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>UFLEX</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D846" t="n">
+        <v>669</v>
+      </c>
+      <c r="E846" t="n">
+        <v>750</v>
+      </c>
+      <c r="F846" t="n">
+        <v>606</v>
+      </c>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>10 की कमाई UFLEX @ 656-660 खरीदें STOP LOSS 606 TARGET 720/750 Uflex 667.25 ▲ 3.36%</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:54:00</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D847" t="n">
+        <v>323.75</v>
+      </c>
+      <c r="E847" t="n">
+        <v>400</v>
+      </c>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>Eternal TARGET 400 ALLOCATION 25%</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:53:00</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>MAPMYINDIA</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D848" t="n">
+        <v>986.8</v>
+      </c>
+      <c r="E848" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>SID की SIP MapmyIndia CMP 985.20 TARGET 1500 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:53:00</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D849" t="n">
+        <v>1533.9</v>
+      </c>
+      <c r="E849" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>SID की SIP, Affle 3i, CMP 1534.00, TARGET 2000, 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:00</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D850" t="n">
+        <v>1533</v>
+      </c>
+      <c r="E850" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>SID की SIP
+Affle 3i
+CMP 1533.40
+TARGET 2000
+25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:52:00</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>MEESHO</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D851" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="E851" t="n">
+        <v>230</v>
+      </c>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>SID की SIP Meesho CMP 206.54 TARGET 230 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:51:00</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D852" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="E852" t="n">
+        <v>400</v>
+      </c>
+      <c r="G852" t="inlineStr"/>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>SID को SIP
+Eternal (Zomato)
+CMP 323.50
+TARGET 400
+25% ALLOCATION
+MARKET UPDATE</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:49:00</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D853" t="n">
+        <v>823</v>
+      </c>
+      <c r="E853" t="n">
+        <v>930</v>
+      </c>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+ANTELOPUS SELAN ENRGY LTD
+823.50 30.85
+BUY
+TGT 930
+SL --</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:49:00</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D854" t="n">
+        <v>1842.7</v>
+      </c>
+      <c r="E854" t="n">
+        <v>1930</v>
+      </c>
+      <c r="F854" t="n">
+        <v>1840</v>
+      </c>
+      <c r="G854" t="inlineStr"/>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Fut 1839.80 45.80 BUY TGT 1930 SL 1840</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:41:00</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D855" t="n">
+        <v>427.45</v>
+      </c>
+      <c r="E855" t="n">
+        <v>432</v>
+      </c>
+      <c r="F855" t="n">
+        <v>422</v>
+      </c>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:41:00</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>KOTAKBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D856" t="n">
+        <v>427.45</v>
+      </c>
+      <c r="E856" t="n">
+        <v>436</v>
+      </c>
+      <c r="F856" t="n">
+        <v>422</v>
+      </c>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:40:00</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Interglobe Aviation Fut
+4949.50 -96.50
+SELL
+TARGET HIT
+5125</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:39:58</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F858" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G858" t="inlineStr"/>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4949.50 -1.91%
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:39:48</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="n">
+        <v>12358</v>
+      </c>
+      <c r="F859" t="n">
+        <v>12238</v>
+      </c>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Fut 12163.00 BUY T 12238 S 12358 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E860" t="n">
+        <v>930</v>
+      </c>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E861" t="n">
+        <v>950</v>
+      </c>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E862" t="n">
+        <v>930</v>
+      </c>
+      <c r="G862" t="inlineStr"/>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+ANTELOPUS SELAN ENRGY LTD
+PRICE ▶ 833.70
+TARGET ▶ 930/950</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:38:00</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>830.4</v>
+      </c>
+      <c r="E863" t="n">
+        <v>950</v>
+      </c>
+      <c r="G863" t="inlineStr"/>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+ANTELOPUS SELAN ENRGY LTD
+PRICE ▶ 833.70
+TARGET ▶ 930/950</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:35:16</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr"/>
+      <c r="E864" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>OF THE DAY InterGlobe Aviation Fut 4947 SELL TGT 5000 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:36:00</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>4946</v>
+      </c>
+      <c r="E865" t="n">
+        <v>3125</v>
+      </c>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation Fut 4947.40 -99.00 SELL TARGET HIT 3125</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:35:09</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="n">
+        <v>371</v>
+      </c>
+      <c r="F866" t="n">
+        <v>335</v>
+      </c>
+      <c r="G866" t="inlineStr"/>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>EMS Ltd 406.8 BUY TGT 371 SL 335 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:36:00</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>405.05</v>
+      </c>
+      <c r="E867" t="n">
+        <v>565</v>
+      </c>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 406.00 34.05 BUY TARGET HIT 565</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:34:55</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F868" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G868" t="inlineStr"/>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>Centum Elec 3505 BUY TGT 3500 SL 3300 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:34:46</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G869" t="inlineStr"/>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5408.50 -2.61% SELL TARGET HIT 5600</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:26</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F870" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4955.00 -91.00
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:31:00</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
+        <v>403.9</v>
+      </c>
+      <c r="E871" t="n">
+        <v>565</v>
+      </c>
+      <c r="G871" t="inlineStr"/>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TARGET HIT 565</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:18</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="n">
+        <v>371</v>
+      </c>
+      <c r="F872" t="n">
+        <v>365</v>
+      </c>
+      <c r="G872" t="inlineStr"/>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TGT 371 SL 365</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:16</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr"/>
+      <c r="E873" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Fut 12235.00 -1.17% SELL TARGET HIT 12550</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:12</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="n">
+        <v>12250</v>
+      </c>
+      <c r="F874" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G874" t="inlineStr"/>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Bajaj Auto Fut
+12238.00 -142.00
+SELL
+TGT 12250
+SL 12550</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:07</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+Centum Elec
+3512.70 2.63%
+BUY
+TARGET HIT
+3360</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:30:06</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F876" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+Centum Elec
+3512.70 2.63%
+BUY
+TGT 3500
+SL 3360</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:29:58</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="n">
+        <v>5520</v>
+      </c>
+      <c r="F877" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G877" t="inlineStr"/>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Hero Motocorp Fut
+5429.00 -124.50
+SELL
+TGT 5520
+SL 5600</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:35</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G878" t="inlineStr"/>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Inter globe Aviation Fut
+4953.50 -1.83%
+SELL
+TARGET HIT
+5125</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D879" t="n">
+        <v>4964</v>
+      </c>
+      <c r="E879" t="n">
+        <v>3125</v>
+      </c>
+      <c r="G879" t="inlineStr"/>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Inter globe Aviation Fut
+4953.50 -92.50
+SELL
+TARGET HIT
+3125</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:32</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F880" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Inter globe Aviation Fut
+4953.50 -1.83%
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:31</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F881" t="n">
+        <v>5125</v>
+      </c>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Interglobe Aviation Fut
+4953.50 -92.50
+SELL
+TGT 5000
+SL 5125</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D882" t="n">
+        <v>403.05</v>
+      </c>
+      <c r="E882" t="n">
+        <v>565</v>
+      </c>
+      <c r="G882" t="inlineStr"/>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>अरुण शर्मा जैन
+EMS Ltd
+400.00 7.54%
+BUY
+TARGET HIT
+565</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:26</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>EMSLIMITED</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="n">
+        <v>365</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>आस्था जैन
+EMS Ltd
+400.00 7.54%
+BUY
+TARGET HIT
+365</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:11</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -125.50 SELL TARGET HIT 5600</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:26:00</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D885" t="n">
+        <v>5436.5</v>
+      </c>
+      <c r="E885" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G885" t="inlineStr"/>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -2.26% SELL TARGET HIT 3600</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:25:08</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="n">
+        <v>5520</v>
+      </c>
+      <c r="F886" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G886" t="inlineStr"/>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Hero Motocorp Fut
+5427.00 -2.28%
+SELL
+TGT 5520
+SL 5600</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D887" t="n">
+        <v>7860</v>
+      </c>
+      <c r="E887" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G887" t="inlineStr"/>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Eicher Motors
+7821.00 -149.00
+BUY
+लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D888" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E888" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G888" t="inlineStr"/>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>SBI Life 1728.30 11.00 0.63% Vol: 639 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D889" t="n">
+        <v>1730</v>
+      </c>
+      <c r="E889" t="n">
+        <v>2235</v>
+      </c>
+      <c r="G889" t="inlineStr"/>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS BUY लक्ष्य ₹2235</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D890" t="n">
+        <v>408.2</v>
+      </c>
+      <c r="E890" t="n">
+        <v>440</v>
+      </c>
+      <c r="G890" t="inlineStr"/>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>Coal India 406.00 +4.40 HOLD लक्ष्य ₹440</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D891" t="n">
+        <v>162.74</v>
+      </c>
+      <c r="E891" t="n">
+        <v>440</v>
+      </c>
+      <c r="G891" t="inlineStr"/>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>Samvardhana Motherson 164.00 1.60 0.97% Vol: 19.98 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹440</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D892" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E892" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F892" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G892" t="inlineStr"/>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D893" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E893" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F893" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D894" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E894" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F894" t="n">
+        <v>12650</v>
+      </c>
+      <c r="G894" t="inlineStr"/>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D895" t="n">
+        <v>274</v>
+      </c>
+      <c r="E895" t="n">
+        <v>281</v>
+      </c>
+      <c r="F895" t="n">
+        <v>271</v>
+      </c>
+      <c r="G895" t="inlineStr"/>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>MY CHOICE NLC INDIA B 281 271</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D896" t="n">
+        <v>495</v>
+      </c>
+      <c r="E896" t="n">
+        <v>510</v>
+      </c>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI PRU LIFE B 510</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D897" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E897" t="n">
+        <v>867</v>
+      </c>
+      <c r="G897" t="inlineStr"/>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAGARH B 867</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D898" t="n">
+        <v>361</v>
+      </c>
+      <c r="E898" t="n">
+        <v>350</v>
+      </c>
+      <c r="F898" t="n">
+        <v>368</v>
+      </c>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>MY CHOICE HPCL FUT S 350 368</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D899" t="n">
+        <v>1270</v>
+      </c>
+      <c r="E899" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F899" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY UNO Minda Ltd BUY PRICE 1274.40 TARGET 1320/1340 STOP LOSS 1240</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>MARUTI29SEP26</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D900" t="n">
+        <v>12882</v>
+      </c>
+      <c r="E900" t="n">
+        <v>12200</v>
+      </c>
+      <c r="F900" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Maruti Suzuki Fut
+SELL
+PRICE ▶ 12956.00
+TARGET ▶ 12200
+STOP LOSS ▶ 13500</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D901" t="n">
+        <v>238.25</v>
+      </c>
+      <c r="E901" t="n">
+        <v>240</v>
+      </c>
+      <c r="F901" t="n">
+        <v>231</v>
+      </c>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC BUY PRICE 236.45 TARGET 240 STOP LOSS 231</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>CENTUM</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D902" t="n">
+        <v>3449</v>
+      </c>
+      <c r="E902" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F902" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Centum Elec BUY PRICE 3422.65 TARGET 3500 STOP LOSS 3360</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D903" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E903" t="n">
+        <v>12250</v>
+      </c>
+      <c r="F903" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G903" t="inlineStr"/>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D904" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E904" t="n">
+        <v>12150</v>
+      </c>
+      <c r="F904" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO29SEP26</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D905" t="n">
+        <v>12278</v>
+      </c>
+      <c r="E905" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F905" t="n">
+        <v>12550</v>
+      </c>
+      <c r="G905" t="inlineStr"/>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E906" t="n">
+        <v>5450</v>
+      </c>
+      <c r="F906" t="n">
+        <v>5600</v>
+      </c>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Hero Moto Futures
+SELL
+PRICE ▶ 5553
+TARGET ▶ 5520, 5450, 5405
+STOP LOSS ▶ 5600</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>7893</v>
+      </c>
+      <c r="E907" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G907" t="inlineStr"/>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Eicher Motors
+7970.00 +16.50
+BUY
+लक्ष्य ₹9400</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:16:00</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>LEMONTREE</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="E908" t="n">
+        <v>183</v>
+      </c>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Lemon Tree Hotels 106.15 ACCUMULATE लक्ष्य ₹175 से बढ़ाकर ₹183</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>CONCORDBIO</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>1484</v>
+      </c>
+      <c r="E909" t="n">
+        <v>1610</v>
+      </c>
+      <c r="F909" t="n">
+        <v>1424</v>
+      </c>
+      <c r="G909" t="inlineStr"/>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>INVESTMENT CONCORD BIO B 1610 1424</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E910" t="n">
+        <v>867</v>
+      </c>
+      <c r="F910" t="n">
+        <v>817</v>
+      </c>
+      <c r="G910" t="inlineStr"/>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>MY CHOICE TITAGARH B 867 817</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>495</v>
+      </c>
+      <c r="E911" t="n">
+        <v>510</v>
+      </c>
+      <c r="F911" t="n">
+        <v>488</v>
+      </c>
+      <c r="G911" t="inlineStr"/>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI PRU LIFE B 510 488</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>252</v>
+      </c>
+      <c r="E912" t="n">
+        <v>262</v>
+      </c>
+      <c r="F912" t="n">
+        <v>248</v>
+      </c>
+      <c r="G912" t="inlineStr"/>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>CASH APTUS VALUE B 262 248</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>MARICO29SEP26</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>836.6</v>
+      </c>
+      <c r="E913" t="n">
+        <v>852</v>
+      </c>
+      <c r="F913" t="n">
+        <v>831</v>
+      </c>
+      <c r="G913" t="inlineStr"/>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>FUTURE MARICO FUT B 852 831</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E914" t="n">
+        <v>92</v>
+      </c>
+      <c r="F914" t="n">
+        <v>83</v>
+      </c>
+      <c r="G914" t="inlineStr"/>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>FUNDA NMDC B 92 83</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>TMCV</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>460</v>
+      </c>
+      <c r="E915" t="n">
+        <v>520</v>
+      </c>
+      <c r="G915" t="inlineStr"/>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>INVESTMENT TATA MOTORS CV B 520 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E916" t="n">
+        <v>186</v>
+      </c>
+      <c r="F916" t="n">
+        <v>170</v>
+      </c>
+      <c r="G916" t="inlineStr"/>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 186 170</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E917" t="n">
+        <v>310</v>
+      </c>
+      <c r="F917" t="n">
+        <v>322</v>
+      </c>
+      <c r="G917" t="inlineStr"/>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>MY CHOICE BPCL FUT S 310 322</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E918" t="n">
+        <v>1086</v>
+      </c>
+      <c r="G918" t="inlineStr"/>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 1086 170</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="F919" t="n">
+        <v>3350</v>
+      </c>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>MY CHOICE HDFC BANK S 3350</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E920" t="n">
+        <v>5446</v>
+      </c>
+      <c r="F920" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G920" t="inlineStr"/>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>FUTURE HERO MOTO FUT S 5446 5610</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>12211</v>
+      </c>
+      <c r="E921" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>FUNDA BAJAJ AUTO B 12800 3 MONTH</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>274</v>
+      </c>
+      <c r="E922" t="n">
+        <v>281</v>
+      </c>
+      <c r="F922" t="n">
+        <v>271</v>
+      </c>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+NLC India
+खरीदें
+PRICE ▶ 274.30
+TARGET ▶ 281
+STOP LOSS ▶ 271</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>495</v>
+      </c>
+      <c r="E923" t="n">
+        <v>510</v>
+      </c>
+      <c r="F923" t="n">
+        <v>488</v>
+      </c>
+      <c r="G923" t="inlineStr"/>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>ICICI Pru खरीदें PRICE 495.45 TARGET 510 STOP LOSS 488</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>839.45</v>
+      </c>
+      <c r="E924" t="n">
+        <v>867</v>
+      </c>
+      <c r="F924" t="n">
+        <v>817</v>
+      </c>
+      <c r="G924" t="inlineStr"/>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Titagarh Rail खरीदें PRICE 833.95 TARGET 867 STOP LOSS 817</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E925" t="n">
+        <v>310</v>
+      </c>
+      <c r="F925" t="n">
+        <v>322</v>
+      </c>
+      <c r="G925" t="inlineStr"/>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+BPCL Fut
+बेचें
+PRICE ▶ 318.00
+TARGET ▶ 310
+STOP LOSS ▶ 322</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="E926" t="n">
+        <v>310</v>
+      </c>
+      <c r="G926" t="inlineStr"/>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+BPCL Fut
+PRICE 318.00
+TARGET 310</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>358.95</v>
+      </c>
+      <c r="E927" t="n">
+        <v>350</v>
+      </c>
+      <c r="F927" t="n">
+        <v>368</v>
+      </c>
+      <c r="G927" t="inlineStr"/>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>MY CHOICE HPCL Fut बेचें PRICE 362.85 TARGET 350 STOP LOSS 368</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E928" t="n">
+        <v>186</v>
+      </c>
+      <c r="F928" t="n">
+        <v>170</v>
+      </c>
+      <c r="G928" t="inlineStr"/>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sri Lotus
+खरीदें
+PRICE ▶ 179.18
+TARGET ▶ 186
+STOP LOSS ▶ 170</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>180.29</v>
+      </c>
+      <c r="E929" t="n">
+        <v>186</v>
+      </c>
+      <c r="G929" t="inlineStr"/>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sri Lotus
+PRICE → 179.18
+TARGET → 186</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E930" t="n">
+        <v>92</v>
+      </c>
+      <c r="F930" t="n">
+        <v>83</v>
+      </c>
+      <c r="G930" t="inlineStr"/>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>FUNDA PICK NMDC खरीदें PRICE 85.69 TARGET 92 STOP LOSS 83</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>12275</v>
+      </c>
+      <c r="E931" t="n">
+        <v>12800</v>
+      </c>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+Bajaj Auto
+खरीदें
+PRICE → 12361.00
+TARGET → 12800
+DURATION → 3-6 महीने</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO29SEP26</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E932" t="n">
+        <v>5446</v>
+      </c>
+      <c r="F932" t="n">
+        <v>5610</v>
+      </c>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Hero Motocorp Fut
+बेचें
+PRICE → 5553.50
+TARGET → 5446
+STOP LOSS → 5610</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>MARICO29SEP26</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>836.6</v>
+      </c>
+      <c r="E933" t="n">
+        <v>852</v>
+      </c>
+      <c r="F933" t="n">
+        <v>831</v>
+      </c>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Marico Fut
+खरीदें
+PRICE → 838.35
+TARGET → 852
+STOP LOSS → 831</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>APTUS</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>252</v>
+      </c>
+      <c r="E934" t="n">
+        <v>262</v>
+      </c>
+      <c r="F934" t="n">
+        <v>248</v>
+      </c>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Aptus Value खरीदें PRICE 253.36 TARGET 262 STOP LOSS 248</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E935" t="n">
+        <v>2935</v>
+      </c>
+      <c r="F935" t="n">
+        <v>2846</v>
+      </c>
+      <c r="G935" t="inlineStr"/>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+Gland Pharma
+खरीदें
+PRICE → 2875.00
+TARGET → 2935
+STOP LOSS → 2846</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="E936" t="n">
+        <v>340</v>
+      </c>
+      <c r="F936" t="n">
+        <v>322</v>
+      </c>
+      <c r="G936" t="inlineStr"/>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Eternal (Zomato) खरीदें PRICE 327.75 TARGET 340/350 STOP LOSS 322</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>3966</v>
+      </c>
+      <c r="E937" t="n">
+        <v>4650</v>
+      </c>
+      <c r="G937" t="inlineStr"/>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>सिटी
+L&amp;T
+3980.10 -1.60%
+BUY
+लक्ष्य ₹4650</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-09-02 09:15:00</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E938" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G938" t="inlineStr"/>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>Sun Pharma 1929 BUY लक्ष्य ₹2120</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J782"/>
+  <autoFilter ref="A1:J938"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$938</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1002</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J938"/>
+  <dimension ref="A1:J1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -33999,7 +33999,6 @@
       <c r="F783" t="n">
         <v>360</v>
       </c>
-      <c r="G783" t="inlineStr"/>
       <c r="H783" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 387.65 15.50 BUY TGT 405 SL 360</t>
@@ -34041,7 +34040,6 @@
       <c r="F784" t="n">
         <v>335</v>
       </c>
-      <c r="G784" t="inlineStr"/>
       <c r="H784" t="inlineStr">
         <is>
           <t>Sunflag Iron 346.55 6.90 BUY TGT 370 SL 335</t>
@@ -34083,7 +34081,6 @@
       <c r="F785" t="n">
         <v>480</v>
       </c>
-      <c r="G785" t="inlineStr"/>
       <c r="H785" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL Hind Copper 520.25 1.22% BUY TGT 600 SL 480</t>
@@ -34125,7 +34122,6 @@
       <c r="F786" t="n">
         <v>2005</v>
       </c>
-      <c r="G786" t="inlineStr"/>
       <c r="H786" t="inlineStr">
         <is>
           <t>BEML 2033.30 BUY TGT 2078 SL 2005</t>
@@ -34167,7 +34163,6 @@
       <c r="F787" t="n">
         <v>2005</v>
       </c>
-      <c r="G787" t="inlineStr"/>
       <c r="H787" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर BEML 2032.20 62.00 BUY TGT 2070 SL 2005</t>
@@ -34209,7 +34204,6 @@
       <c r="F788" t="n">
         <v>262</v>
       </c>
-      <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr">
         <is>
           <t>ITC Fut 267.90 0.80 BUY TGT 277 SL 262</t>
@@ -34242,11 +34236,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D789" t="inlineStr"/>
       <c r="E789" t="n">
         <v>158.5</v>
       </c>
-      <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -34283,11 +34275,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr"/>
       <c r="E790" t="n">
         <v>930</v>
       </c>
-      <c r="G790" t="inlineStr"/>
       <c r="H790" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -34334,7 +34324,6 @@
       <c r="F791" t="n">
         <v>20200</v>
       </c>
-      <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -34381,7 +34370,6 @@
       <c r="F792" t="n">
         <v>20200</v>
       </c>
-      <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -34428,7 +34416,6 @@
       <c r="F793" t="n">
         <v>20200</v>
       </c>
-      <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -34577,7 +34564,6 @@
       <c r="F796" t="n">
         <v>425</v>
       </c>
-      <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr">
         <is>
           <t>Super Kool Mehul
@@ -34624,7 +34610,6 @@
       <c r="F797" t="n">
         <v>425</v>
       </c>
-      <c r="G797" t="inlineStr"/>
       <c r="H797" t="inlineStr">
         <is>
           <t>Super Kool Mehul
@@ -34671,7 +34656,6 @@
       <c r="F798" t="n">
         <v>425</v>
       </c>
-      <c r="G798" t="inlineStr"/>
       <c r="H798" t="inlineStr">
         <is>
           <t>मेहुल कोटारी की राय
@@ -34718,7 +34702,6 @@
       <c r="F799" t="n">
         <v>425</v>
       </c>
-      <c r="G799" t="inlineStr"/>
       <c r="H799" t="inlineStr">
         <is>
           <t>मेहुल कोटारी की राय
@@ -34765,7 +34748,6 @@
       <c r="F800" t="n">
         <v>335</v>
       </c>
-      <c r="G800" t="inlineStr"/>
       <c r="H800" t="inlineStr">
         <is>
           <t>सदाबहार सेठी सा'ब
@@ -34904,7 +34886,6 @@
       <c r="F803" t="n">
         <v>360</v>
       </c>
-      <c r="G803" t="inlineStr"/>
       <c r="H803" t="inlineStr">
         <is>
           <t>सदाबहार सेठी साब Indian Hume Pipe 386.05 13.90 BUY TGT 405 SL 360</t>
@@ -35038,7 +35019,6 @@
       <c r="F806" t="n">
         <v>480</v>
       </c>
-      <c r="G806" t="inlineStr"/>
       <c r="H806" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL
@@ -35088,7 +35068,6 @@
       <c r="F807" t="n">
         <v>480</v>
       </c>
-      <c r="G807" t="inlineStr"/>
       <c r="H807" t="inlineStr">
         <is>
           <t>Super Kool Mehul
@@ -35135,7 +35114,6 @@
       <c r="F808" t="n">
         <v>351</v>
       </c>
-      <c r="G808" t="inlineStr"/>
       <c r="H808" t="inlineStr">
         <is>
           <t>सच्चितानंद उस्तेकर की राय Federal Bank Fut खरीदें PRICE 355.75 TARGET 362/370 STOP LOSS 351</t>
@@ -35177,7 +35155,6 @@
       <c r="F809" t="n">
         <v>351</v>
       </c>
-      <c r="G809" t="inlineStr"/>
       <c r="H809" t="inlineStr">
         <is>
           <t>सच्चितानंद उस्तेकर की राय Federal Bank Fut खरीदें PRICE 355.75 TARGET 362/370 STOP LOSS 351</t>
@@ -35403,7 +35380,6 @@
       <c r="F814" t="n">
         <v>212</v>
       </c>
-      <c r="G814" t="inlineStr"/>
       <c r="H814" t="inlineStr">
         <is>
           <t>TRADING CALL Piramal Pharma खरीदें PRICE 217.30 TARGET 222/225 STOP LOSS 212</t>
@@ -35445,7 +35421,6 @@
       <c r="F815" t="n">
         <v>212</v>
       </c>
-      <c r="G815" t="inlineStr"/>
       <c r="H815" t="inlineStr">
         <is>
           <t>TRADING CALL Piramal Pharma खरीदें PRICE 217.30 TARGET 222/225 STOP LOSS 212</t>
@@ -35487,7 +35462,6 @@
       <c r="F816" t="n">
         <v>710</v>
       </c>
-      <c r="G816" t="inlineStr"/>
       <c r="H816" t="inlineStr">
         <is>
           <t>शिवांगी सारदा की पसंद Indian Hotels खरीदें PRICE 724.40 TARGET 750 STOP LOSS 710</t>
@@ -35529,7 +35503,6 @@
       <c r="F817" t="n">
         <v>4920</v>
       </c>
-      <c r="G817" t="inlineStr"/>
       <c r="H817" t="inlineStr">
         <is>
           <t>शिवांगी सारदा की पसंद Titan खरीदें PRICE 5025.00 TARGET 5250 STOP LOSS 4920</t>
@@ -35571,7 +35544,6 @@
       <c r="F818" t="n">
         <v>320</v>
       </c>
-      <c r="G818" t="inlineStr"/>
       <c r="H818" t="inlineStr">
         <is>
           <t>शिवांगी सारदा की राय
@@ -35618,7 +35590,6 @@
       <c r="F819" t="n">
         <v>1000</v>
       </c>
-      <c r="G819" t="inlineStr"/>
       <c r="H819" t="inlineStr">
         <is>
           <t>शिवांगी सारदा की राय SBI 1020.60 ▼ 1.35% HOLD TARGET 1060 STOP LOSS 1000</t>
@@ -35660,7 +35631,6 @@
       <c r="F820" t="n">
         <v>1111</v>
       </c>
-      <c r="G820" t="inlineStr"/>
       <c r="H820" t="inlineStr">
         <is>
           <t>शिवांगी सारदा की राय
@@ -35707,7 +35677,6 @@
       <c r="F821" t="n">
         <v>1800</v>
       </c>
-      <c r="G821" t="inlineStr"/>
       <c r="H821" t="inlineStr">
         <is>
           <t>अक्षय भागवत की राय
@@ -35754,7 +35723,6 @@
       <c r="F822" t="n">
         <v>1800</v>
       </c>
-      <c r="G822" t="inlineStr"/>
       <c r="H822" t="inlineStr">
         <is>
           <t>अक्षय भागवत की राय
@@ -35801,7 +35769,6 @@
       <c r="F823" t="n">
         <v>55</v>
       </c>
-      <c r="G823" t="inlineStr"/>
       <c r="H823" t="inlineStr">
         <is>
           <t>छोटा ऑप्शन बड़ी कमाई
@@ -35847,7 +35814,6 @@
       <c r="F824" t="n">
         <v>55</v>
       </c>
-      <c r="G824" t="inlineStr"/>
       <c r="H824" t="inlineStr">
         <is>
           <t>छोटा ऑप्शन बड़ी कमाई
@@ -35893,7 +35859,6 @@
       <c r="F825" t="n">
         <v>203</v>
       </c>
-      <c r="G825" t="inlineStr"/>
       <c r="H825" t="inlineStr">
         <is>
           <t>ITC Fut PRICE 268.3 TARGET 277/203</t>
@@ -35935,7 +35900,6 @@
       <c r="F826" t="n">
         <v>520</v>
       </c>
-      <c r="G826" t="inlineStr"/>
       <c r="H826" t="inlineStr">
         <is>
           <t>GNA Axles @ 536 खरीदें STOP LOSS 520 TARGET 560 DURATION -- GNA Axles 540.50 8.05</t>
@@ -35977,7 +35941,6 @@
       <c r="F827" t="n">
         <v>1000</v>
       </c>
-      <c r="G827" t="inlineStr"/>
       <c r="H827" t="inlineStr">
         <is>
           <t>Mangalam Cem खरीदें PRICE 1109.40 TARGET 1200/1250 STOP LOSS 1000 नवनीत मुनोत MD &amp; CEO HDFC AMC COMING UP</t>
@@ -36019,7 +35982,6 @@
       <c r="F828" t="n">
         <v>1000</v>
       </c>
-      <c r="G828" t="inlineStr"/>
       <c r="H828" t="inlineStr">
         <is>
           <t>10 की कमाई Mangalam Cem खरीदें PRICE 1110.00 TARGET 1200/1250 STOP LOSS 1000</t>
@@ -36061,7 +36023,6 @@
       <c r="F829" t="n">
         <v>422</v>
       </c>
-      <c r="G829" t="inlineStr"/>
       <c r="H829" t="inlineStr">
         <is>
           <t>विशेष के विशेष
@@ -36108,7 +36069,6 @@
       <c r="F830" t="n">
         <v>422</v>
       </c>
-      <c r="G830" t="inlineStr"/>
       <c r="H830" t="inlineStr">
         <is>
           <t>विशेष के विशेष
@@ -36152,7 +36112,6 @@
       <c r="E831" t="n">
         <v>930</v>
       </c>
-      <c r="G831" t="inlineStr"/>
       <c r="H831" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -36196,7 +36155,6 @@
       <c r="E832" t="n">
         <v>930</v>
       </c>
-      <c r="G832" t="inlineStr"/>
       <c r="H832" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -36243,7 +36201,6 @@
       <c r="F833" t="n">
         <v>1840</v>
       </c>
-      <c r="G833" t="inlineStr"/>
       <c r="H833" t="inlineStr">
         <is>
           <t>जय का JACKPOT Oberoi Realty Fut 1854.30 31.30 BUY TGT 1930 SL 1840</t>
@@ -36285,7 +36242,6 @@
       <c r="F834" t="n">
         <v>1960</v>
       </c>
-      <c r="G834" t="inlineStr"/>
       <c r="H834" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -36332,7 +36288,6 @@
       <c r="F835" t="n">
         <v>1960</v>
       </c>
-      <c r="G835" t="inlineStr"/>
       <c r="H835" t="inlineStr">
         <is>
           <t>10 की कमाई Alkyl Amines खरीदें PRICE 2028.40 TARGET 2100/2150 STOP LOSS 1960 MARKET MENTORS नवनीत मुनोत MD &amp; CEO HDFC AMC 11 AM</t>
@@ -36374,7 +36329,6 @@
       <c r="F836" t="n">
         <v>500</v>
       </c>
-      <c r="G836" t="inlineStr"/>
       <c r="H836" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -36416,7 +36370,6 @@
       <c r="D837" t="n">
         <v>603.5</v>
       </c>
-      <c r="G837" t="inlineStr"/>
       <c r="H837" t="inlineStr">
         <is>
           <t>Innogene खरीदें STOP LOSS 500 TARGET ₹50</t>
@@ -36449,14 +36402,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D838" t="inlineStr"/>
       <c r="E838" t="n">
         <v>340</v>
       </c>
       <c r="F838" t="n">
         <v>270</v>
       </c>
-      <c r="G838" t="inlineStr"/>
       <c r="H838" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK SCI खरीदें STOP LOSS 270 TARGET 340 DURATION</t>
@@ -36498,7 +36449,6 @@
       <c r="F839" t="n">
         <v>380</v>
       </c>
-      <c r="G839" t="inlineStr"/>
       <c r="H839" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -36535,7 +36485,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D840" t="inlineStr"/>
       <c r="E840" t="n">
         <v>240</v>
       </c>
@@ -36579,7 +36528,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D841" t="inlineStr"/>
       <c r="E841" t="n">
         <v>270</v>
       </c>
@@ -36632,7 +36580,6 @@
       <c r="F842" t="n">
         <v>500</v>
       </c>
-      <c r="G842" t="inlineStr"/>
       <c r="H842" t="inlineStr">
         <is>
           <t>सौमिल मेहता की राय Indegene खरीदें STOP LOSS 500 TARGET 850 DURATION -- Indegene 606.25 0.14%</t>
@@ -36665,14 +36612,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D843" t="inlineStr"/>
       <c r="E843" t="n">
         <v>550</v>
       </c>
       <c r="F843" t="n">
         <v>380</v>
       </c>
-      <c r="G843" t="inlineStr"/>
       <c r="H843" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS
@@ -36709,7 +36654,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr"/>
       <c r="E844" t="n">
         <v>550</v>
       </c>
@@ -36766,7 +36710,6 @@
       <c r="F845" t="n">
         <v>422</v>
       </c>
-      <c r="G845" t="inlineStr"/>
       <c r="H845" t="inlineStr">
         <is>
           <t>Kotak Bank Fut 425.25 1.50 BUY TGT 432 SL 422</t>
@@ -36808,7 +36751,6 @@
       <c r="F846" t="n">
         <v>606</v>
       </c>
-      <c r="G846" t="inlineStr"/>
       <c r="H846" t="inlineStr">
         <is>
           <t>10 की कमाई UFLEX @ 656-660 खरीदें STOP LOSS 606 TARGET 720/750 Uflex 667.25 ▲ 3.36%</t>
@@ -36847,7 +36789,6 @@
       <c r="E847" t="n">
         <v>400</v>
       </c>
-      <c r="G847" t="inlineStr"/>
       <c r="H847" t="inlineStr">
         <is>
           <t>Eternal TARGET 400 ALLOCATION 25%</t>
@@ -36886,7 +36827,6 @@
       <c r="E848" t="n">
         <v>1500</v>
       </c>
-      <c r="G848" t="inlineStr"/>
       <c r="H848" t="inlineStr">
         <is>
           <t>SID की SIP MapmyIndia CMP 985.20 TARGET 1500 25% ALLOCATION</t>
@@ -36925,7 +36865,6 @@
       <c r="E849" t="n">
         <v>2000</v>
       </c>
-      <c r="G849" t="inlineStr"/>
       <c r="H849" t="inlineStr">
         <is>
           <t>SID की SIP, Affle 3i, CMP 1534.00, TARGET 2000, 25% ALLOCATION</t>
@@ -36964,7 +36903,6 @@
       <c r="E850" t="n">
         <v>2000</v>
       </c>
-      <c r="G850" t="inlineStr"/>
       <c r="H850" t="inlineStr">
         <is>
           <t>SID की SIP
@@ -37007,7 +36945,6 @@
       <c r="E851" t="n">
         <v>230</v>
       </c>
-      <c r="G851" t="inlineStr"/>
       <c r="H851" t="inlineStr">
         <is>
           <t>SID की SIP Meesho CMP 206.54 TARGET 230 25% ALLOCATION</t>
@@ -37046,7 +36983,6 @@
       <c r="E852" t="n">
         <v>400</v>
       </c>
-      <c r="G852" t="inlineStr"/>
       <c r="H852" t="inlineStr">
         <is>
           <t>SID को SIP
@@ -37090,7 +37026,6 @@
       <c r="E853" t="n">
         <v>930</v>
       </c>
-      <c r="G853" t="inlineStr"/>
       <c r="H853" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -37137,7 +37072,6 @@
       <c r="F854" t="n">
         <v>1840</v>
       </c>
-      <c r="G854" t="inlineStr"/>
       <c r="H854" t="inlineStr">
         <is>
           <t>Oberoi Realty Fut 1839.80 45.80 BUY TGT 1930 SL 1840</t>
@@ -37179,7 +37113,6 @@
       <c r="F855" t="n">
         <v>422</v>
       </c>
-      <c r="G855" t="inlineStr"/>
       <c r="H855" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
@@ -37221,7 +37154,6 @@
       <c r="F856" t="n">
         <v>422</v>
       </c>
-      <c r="G856" t="inlineStr"/>
       <c r="H856" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय Kotak Bank Fut खरीदें PRICE 426.60 TARGET 432/436 STOP LOSS 422</t>
@@ -37254,11 +37186,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
       <c r="E857" t="n">
         <v>5125</v>
       </c>
-      <c r="G857" t="inlineStr"/>
       <c r="H857" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -37296,14 +37226,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
       <c r="E858" t="n">
         <v>5000</v>
       </c>
       <c r="F858" t="n">
         <v>5125</v>
       </c>
-      <c r="G858" t="inlineStr"/>
       <c r="H858" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -37341,14 +37269,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
       <c r="E859" t="n">
         <v>12358</v>
       </c>
       <c r="F859" t="n">
         <v>12238</v>
       </c>
-      <c r="G859" t="inlineStr"/>
       <c r="H859" t="inlineStr">
         <is>
           <t>Bajaj Auto Fut 12163.00 BUY T 12238 S 12358 TARGET HIT</t>
@@ -37387,7 +37313,6 @@
       <c r="E860" t="n">
         <v>930</v>
       </c>
-      <c r="G860" t="inlineStr"/>
       <c r="H860" t="inlineStr">
         <is>
           <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
@@ -37426,7 +37351,6 @@
       <c r="E861" t="n">
         <v>950</v>
       </c>
-      <c r="G861" t="inlineStr"/>
       <c r="H861" t="inlineStr">
         <is>
           <t>ANTELOPUS SELAN ENRGY LTD खरीदें PRICE 832.40 TARGET 930/950 STOP LOSS --</t>
@@ -37465,7 +37389,6 @@
       <c r="E862" t="n">
         <v>930</v>
       </c>
-      <c r="G862" t="inlineStr"/>
       <c r="H862" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -37507,7 +37430,6 @@
       <c r="E863" t="n">
         <v>950</v>
       </c>
-      <c r="G863" t="inlineStr"/>
       <c r="H863" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -37543,11 +37465,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
       <c r="E864" t="n">
         <v>5000</v>
       </c>
-      <c r="G864" t="inlineStr"/>
       <c r="H864" t="inlineStr">
         <is>
           <t>OF THE DAY InterGlobe Aviation Fut 4947 SELL TGT 5000 TARGET HIT</t>
@@ -37586,7 +37506,6 @@
       <c r="E865" t="n">
         <v>3125</v>
       </c>
-      <c r="G865" t="inlineStr"/>
       <c r="H865" t="inlineStr">
         <is>
           <t>Interglobe Aviation Fut 4947.40 -99.00 SELL TARGET HIT 3125</t>
@@ -37619,14 +37538,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
       <c r="E866" t="n">
         <v>371</v>
       </c>
       <c r="F866" t="n">
         <v>335</v>
       </c>
-      <c r="G866" t="inlineStr"/>
       <c r="H866" t="inlineStr">
         <is>
           <t>EMS Ltd 406.8 BUY TGT 371 SL 335 TARGET HIT</t>
@@ -37665,7 +37582,6 @@
       <c r="E867" t="n">
         <v>565</v>
       </c>
-      <c r="G867" t="inlineStr"/>
       <c r="H867" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 406.00 34.05 BUY TARGET HIT 565</t>
@@ -37698,14 +37614,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr"/>
       <c r="E868" t="n">
         <v>3500</v>
       </c>
       <c r="F868" t="n">
         <v>3300</v>
       </c>
-      <c r="G868" t="inlineStr"/>
       <c r="H868" t="inlineStr">
         <is>
           <t>Centum Elec 3505 BUY TGT 3500 SL 3300 TARGET HIT</t>
@@ -37738,11 +37652,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D869" t="inlineStr"/>
       <c r="E869" t="n">
         <v>5600</v>
       </c>
-      <c r="G869" t="inlineStr"/>
       <c r="H869" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5408.50 -2.61% SELL TARGET HIT 5600</t>
@@ -37775,14 +37687,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr"/>
       <c r="E870" t="n">
         <v>5000</v>
       </c>
       <c r="F870" t="n">
         <v>5125</v>
       </c>
-      <c r="G870" t="inlineStr"/>
       <c r="H870" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -37826,7 +37736,6 @@
       <c r="E871" t="n">
         <v>565</v>
       </c>
-      <c r="G871" t="inlineStr"/>
       <c r="H871" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TARGET HIT 565</t>
@@ -37859,14 +37768,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D872" t="inlineStr"/>
       <c r="E872" t="n">
         <v>371</v>
       </c>
       <c r="F872" t="n">
         <v>365</v>
       </c>
-      <c r="G872" t="inlineStr"/>
       <c r="H872" t="inlineStr">
         <is>
           <t>PICK OF THE DAY EMS Ltd 407.55 35.60 BUY TGT 371 SL 365</t>
@@ -37899,11 +37806,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr"/>
       <c r="E873" t="n">
         <v>12550</v>
       </c>
-      <c r="G873" t="inlineStr"/>
       <c r="H873" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Fut 12235.00 -1.17% SELL TARGET HIT 12550</t>
@@ -37936,14 +37841,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
       <c r="E874" t="n">
         <v>12250</v>
       </c>
       <c r="F874" t="n">
         <v>12550</v>
       </c>
-      <c r="G874" t="inlineStr"/>
       <c r="H874" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -37981,11 +37884,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr"/>
       <c r="E875" t="n">
         <v>3360</v>
       </c>
-      <c r="G875" t="inlineStr"/>
       <c r="H875" t="inlineStr">
         <is>
           <t>आस्था जैन
@@ -38023,7 +37924,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr"/>
       <c r="E876" t="n">
         <v>3500</v>
       </c>
@@ -38072,14 +37972,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr"/>
       <c r="E877" t="n">
         <v>5520</v>
       </c>
       <c r="F877" t="n">
         <v>5600</v>
       </c>
-      <c r="G877" t="inlineStr"/>
       <c r="H877" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -38117,11 +38015,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr"/>
       <c r="E878" t="n">
         <v>5125</v>
       </c>
-      <c r="G878" t="inlineStr"/>
       <c r="H878" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -38165,7 +38061,6 @@
       <c r="E879" t="n">
         <v>3125</v>
       </c>
-      <c r="G879" t="inlineStr"/>
       <c r="H879" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -38203,14 +38098,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr"/>
       <c r="E880" t="n">
         <v>5000</v>
       </c>
       <c r="F880" t="n">
         <v>5125</v>
       </c>
-      <c r="G880" t="inlineStr"/>
       <c r="H880" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -38248,14 +38141,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr"/>
       <c r="E881" t="n">
         <v>5000</v>
       </c>
       <c r="F881" t="n">
         <v>5125</v>
       </c>
-      <c r="G881" t="inlineStr"/>
       <c r="H881" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -38299,7 +38190,6 @@
       <c r="E882" t="n">
         <v>565</v>
       </c>
-      <c r="G882" t="inlineStr"/>
       <c r="H882" t="inlineStr">
         <is>
           <t>अरुण शर्मा जैन
@@ -38337,7 +38227,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D883" t="inlineStr"/>
       <c r="E883" t="n">
         <v>365</v>
       </c>
@@ -38383,11 +38272,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D884" t="inlineStr"/>
       <c r="E884" t="n">
         <v>5600</v>
       </c>
-      <c r="G884" t="inlineStr"/>
       <c r="H884" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -125.50 SELL TARGET HIT 5600</t>
@@ -38426,7 +38313,6 @@
       <c r="E885" t="n">
         <v>3600</v>
       </c>
-      <c r="G885" t="inlineStr"/>
       <c r="H885" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Hero Motocorp Fut 5428.00 -2.26% SELL TARGET HIT 3600</t>
@@ -38459,14 +38345,12 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr"/>
       <c r="E886" t="n">
         <v>5520</v>
       </c>
       <c r="F886" t="n">
         <v>5600</v>
       </c>
-      <c r="G886" t="inlineStr"/>
       <c r="H886" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -38510,7 +38394,6 @@
       <c r="E887" t="n">
         <v>9400</v>
       </c>
-      <c r="G887" t="inlineStr"/>
       <c r="H887" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -38553,7 +38436,6 @@
       <c r="E888" t="n">
         <v>9400</v>
       </c>
-      <c r="G888" t="inlineStr"/>
       <c r="H888" t="inlineStr">
         <is>
           <t>SBI Life 1728.30 11.00 0.63% Vol: 639 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹9400</t>
@@ -38592,7 +38474,6 @@
       <c r="E889" t="n">
         <v>2235</v>
       </c>
-      <c r="G889" t="inlineStr"/>
       <c r="H889" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS BUY लक्ष्य ₹2235</t>
@@ -38631,7 +38512,6 @@
       <c r="E890" t="n">
         <v>440</v>
       </c>
-      <c r="G890" t="inlineStr"/>
       <c r="H890" t="inlineStr">
         <is>
           <t>Coal India 406.00 +4.40 HOLD लक्ष्य ₹440</t>
@@ -38670,7 +38550,6 @@
       <c r="E891" t="n">
         <v>440</v>
       </c>
-      <c r="G891" t="inlineStr"/>
       <c r="H891" t="inlineStr">
         <is>
           <t>Samvardhana Motherson 164.00 1.60 0.97% Vol: 19.98 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹440</t>
@@ -38712,7 +38591,6 @@
       <c r="F892" t="n">
         <v>12650</v>
       </c>
-      <c r="G892" t="inlineStr"/>
       <c r="H892" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -38754,7 +38632,6 @@
       <c r="F893" t="n">
         <v>12650</v>
       </c>
-      <c r="G893" t="inlineStr"/>
       <c r="H893" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -38796,7 +38673,6 @@
       <c r="F894" t="n">
         <v>12650</v>
       </c>
-      <c r="G894" t="inlineStr"/>
       <c r="H894" t="inlineStr">
         <is>
           <t>STOCK FTH D Bajaj Auto Futures SELL PRICE 12380 TARGET 2250, 12150, 1200 STOP LOSS 12650</t>
@@ -38838,7 +38714,6 @@
       <c r="F895" t="n">
         <v>271</v>
       </c>
-      <c r="G895" t="inlineStr"/>
       <c r="H895" t="inlineStr">
         <is>
           <t>MY CHOICE NLC INDIA B 281 271</t>
@@ -38877,7 +38752,6 @@
       <c r="E896" t="n">
         <v>510</v>
       </c>
-      <c r="G896" t="inlineStr"/>
       <c r="H896" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI PRU LIFE B 510</t>
@@ -38916,7 +38790,6 @@
       <c r="E897" t="n">
         <v>867</v>
       </c>
-      <c r="G897" t="inlineStr"/>
       <c r="H897" t="inlineStr">
         <is>
           <t>MY CHOICE TITAGARH B 867</t>
@@ -38958,7 +38831,6 @@
       <c r="F898" t="n">
         <v>368</v>
       </c>
-      <c r="G898" t="inlineStr"/>
       <c r="H898" t="inlineStr">
         <is>
           <t>MY CHOICE HPCL FUT S 350 368</t>
@@ -39000,7 +38872,6 @@
       <c r="F899" t="n">
         <v>1240</v>
       </c>
-      <c r="G899" t="inlineStr"/>
       <c r="H899" t="inlineStr">
         <is>
           <t>PICK OF THE DAY UNO Minda Ltd BUY PRICE 1274.40 TARGET 1320/1340 STOP LOSS 1240</t>
@@ -39042,7 +38913,6 @@
       <c r="F900" t="n">
         <v>13500</v>
       </c>
-      <c r="G900" t="inlineStr"/>
       <c r="H900" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -39089,7 +38959,6 @@
       <c r="F901" t="n">
         <v>231</v>
       </c>
-      <c r="G901" t="inlineStr"/>
       <c r="H901" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC BUY PRICE 236.45 TARGET 240 STOP LOSS 231</t>
@@ -39131,7 +39000,6 @@
       <c r="F902" t="n">
         <v>3360</v>
       </c>
-      <c r="G902" t="inlineStr"/>
       <c r="H902" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Centum Elec BUY PRICE 3422.65 TARGET 3500 STOP LOSS 3360</t>
@@ -39173,7 +39041,6 @@
       <c r="F903" t="n">
         <v>12550</v>
       </c>
-      <c r="G903" t="inlineStr"/>
       <c r="H903" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -39215,7 +39082,6 @@
       <c r="F904" t="n">
         <v>12550</v>
       </c>
-      <c r="G904" t="inlineStr"/>
       <c r="H904" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -39257,7 +39123,6 @@
       <c r="F905" t="n">
         <v>12550</v>
       </c>
-      <c r="G905" t="inlineStr"/>
       <c r="H905" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY Bajaj Auto Futures SELL PRICE 12380 TARGET 12250, 12150, 12000 STOP LOSS 12550</t>
@@ -39299,7 +39164,6 @@
       <c r="F906" t="n">
         <v>5600</v>
       </c>
-      <c r="G906" t="inlineStr"/>
       <c r="H906" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -39343,7 +39207,6 @@
       <c r="E907" t="n">
         <v>9400</v>
       </c>
-      <c r="G907" t="inlineStr"/>
       <c r="H907" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -39386,7 +39249,6 @@
       <c r="E908" t="n">
         <v>183</v>
       </c>
-      <c r="G908" t="inlineStr"/>
       <c r="H908" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Lemon Tree Hotels 106.15 ACCUMULATE लक्ष्य ₹175 से बढ़ाकर ₹183</t>
@@ -39428,7 +39290,6 @@
       <c r="F909" t="n">
         <v>1424</v>
       </c>
-      <c r="G909" t="inlineStr"/>
       <c r="H909" t="inlineStr">
         <is>
           <t>INVESTMENT CONCORD BIO B 1610 1424</t>
@@ -39470,7 +39331,6 @@
       <c r="F910" t="n">
         <v>817</v>
       </c>
-      <c r="G910" t="inlineStr"/>
       <c r="H910" t="inlineStr">
         <is>
           <t>MY CHOICE TITAGARH B 867 817</t>
@@ -39512,7 +39372,6 @@
       <c r="F911" t="n">
         <v>488</v>
       </c>
-      <c r="G911" t="inlineStr"/>
       <c r="H911" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI PRU LIFE B 510 488</t>
@@ -39554,7 +39413,6 @@
       <c r="F912" t="n">
         <v>248</v>
       </c>
-      <c r="G912" t="inlineStr"/>
       <c r="H912" t="inlineStr">
         <is>
           <t>CASH APTUS VALUE B 262 248</t>
@@ -39596,7 +39454,6 @@
       <c r="F913" t="n">
         <v>831</v>
       </c>
-      <c r="G913" t="inlineStr"/>
       <c r="H913" t="inlineStr">
         <is>
           <t>FUTURE MARICO FUT B 852 831</t>
@@ -39638,7 +39495,6 @@
       <c r="F914" t="n">
         <v>83</v>
       </c>
-      <c r="G914" t="inlineStr"/>
       <c r="H914" t="inlineStr">
         <is>
           <t>FUNDA NMDC B 92 83</t>
@@ -39677,7 +39533,6 @@
       <c r="E915" t="n">
         <v>520</v>
       </c>
-      <c r="G915" t="inlineStr"/>
       <c r="H915" t="inlineStr">
         <is>
           <t>INVESTMENT TATA MOTORS CV B 520 12 MONTH</t>
@@ -39719,7 +39574,6 @@
       <c r="F916" t="n">
         <v>170</v>
       </c>
-      <c r="G916" t="inlineStr"/>
       <c r="H916" t="inlineStr">
         <is>
           <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 186 170</t>
@@ -39761,7 +39615,6 @@
       <c r="F917" t="n">
         <v>322</v>
       </c>
-      <c r="G917" t="inlineStr"/>
       <c r="H917" t="inlineStr">
         <is>
           <t>MY CHOICE BPCL FUT S 310 322</t>
@@ -39800,7 +39653,6 @@
       <c r="E918" t="n">
         <v>1086</v>
       </c>
-      <c r="G918" t="inlineStr"/>
       <c r="H918" t="inlineStr">
         <is>
           <t>NEWS IMPACT SRI LOTUS DEVELOPERS B 1086 170</t>
@@ -39839,7 +39691,6 @@
       <c r="F919" t="n">
         <v>3350</v>
       </c>
-      <c r="G919" t="inlineStr"/>
       <c r="H919" t="inlineStr">
         <is>
           <t>MY CHOICE HDFC BANK S 3350</t>
@@ -39881,7 +39732,6 @@
       <c r="F920" t="n">
         <v>5610</v>
       </c>
-      <c r="G920" t="inlineStr"/>
       <c r="H920" t="inlineStr">
         <is>
           <t>FUTURE HERO MOTO FUT S 5446 5610</t>
@@ -39920,7 +39770,6 @@
       <c r="E921" t="n">
         <v>12800</v>
       </c>
-      <c r="G921" t="inlineStr"/>
       <c r="H921" t="inlineStr">
         <is>
           <t>FUNDA BAJAJ AUTO B 12800 3 MONTH</t>
@@ -39962,7 +39811,6 @@
       <c r="F922" t="n">
         <v>271</v>
       </c>
-      <c r="G922" t="inlineStr"/>
       <c r="H922" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -40009,7 +39857,6 @@
       <c r="F923" t="n">
         <v>488</v>
       </c>
-      <c r="G923" t="inlineStr"/>
       <c r="H923" t="inlineStr">
         <is>
           <t>ICICI Pru खरीदें PRICE 495.45 TARGET 510 STOP LOSS 488</t>
@@ -40051,7 +39898,6 @@
       <c r="F924" t="n">
         <v>817</v>
       </c>
-      <c r="G924" t="inlineStr"/>
       <c r="H924" t="inlineStr">
         <is>
           <t>अंश के शेयर Titagarh Rail खरीदें PRICE 833.95 TARGET 867 STOP LOSS 817</t>
@@ -40093,7 +39939,6 @@
       <c r="F925" t="n">
         <v>322</v>
       </c>
-      <c r="G925" t="inlineStr"/>
       <c r="H925" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -40137,7 +39982,6 @@
       <c r="E926" t="n">
         <v>310</v>
       </c>
-      <c r="G926" t="inlineStr"/>
       <c r="H926" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -40182,7 +40026,6 @@
       <c r="F927" t="n">
         <v>368</v>
       </c>
-      <c r="G927" t="inlineStr"/>
       <c r="H927" t="inlineStr">
         <is>
           <t>MY CHOICE HPCL Fut बेचें PRICE 362.85 TARGET 350 STOP LOSS 368</t>
@@ -40224,7 +40067,6 @@
       <c r="F928" t="n">
         <v>170</v>
       </c>
-      <c r="G928" t="inlineStr"/>
       <c r="H928" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -40268,7 +40110,6 @@
       <c r="E929" t="n">
         <v>186</v>
       </c>
-      <c r="G929" t="inlineStr"/>
       <c r="H929" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -40313,7 +40154,6 @@
       <c r="F930" t="n">
         <v>83</v>
       </c>
-      <c r="G930" t="inlineStr"/>
       <c r="H930" t="inlineStr">
         <is>
           <t>FUNDA PICK NMDC खरीदें PRICE 85.69 TARGET 92 STOP LOSS 83</t>
@@ -40352,7 +40192,6 @@
       <c r="E931" t="n">
         <v>12800</v>
       </c>
-      <c r="G931" t="inlineStr"/>
       <c r="H931" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -40399,7 +40238,6 @@
       <c r="F932" t="n">
         <v>5610</v>
       </c>
-      <c r="G932" t="inlineStr"/>
       <c r="H932" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -40446,7 +40284,6 @@
       <c r="F933" t="n">
         <v>831</v>
       </c>
-      <c r="G933" t="inlineStr"/>
       <c r="H933" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -40493,7 +40330,6 @@
       <c r="F934" t="n">
         <v>248</v>
       </c>
-      <c r="G934" t="inlineStr"/>
       <c r="H934" t="inlineStr">
         <is>
           <t>CASH का शेयर Aptus Value खरीदें PRICE 253.36 TARGET 262 STOP LOSS 248</t>
@@ -40535,7 +40371,6 @@
       <c r="F935" t="n">
         <v>2846</v>
       </c>
-      <c r="G935" t="inlineStr"/>
       <c r="H935" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -40582,7 +40417,6 @@
       <c r="F936" t="n">
         <v>322</v>
       </c>
-      <c r="G936" t="inlineStr"/>
       <c r="H936" t="inlineStr">
         <is>
           <t>सिद्धार्थ राय मंगला की राय Eternal (Zomato) खरीदें PRICE 327.75 TARGET 340/350 STOP LOSS 322</t>
@@ -40621,7 +40455,6 @@
       <c r="E937" t="n">
         <v>4650</v>
       </c>
-      <c r="G937" t="inlineStr"/>
       <c r="H937" t="inlineStr">
         <is>
           <t>सिटी
@@ -40664,7 +40497,6 @@
       <c r="E938" t="n">
         <v>2120</v>
       </c>
-      <c r="G938" t="inlineStr"/>
       <c r="H938" t="inlineStr">
         <is>
           <t>Sun Pharma 1929 BUY लक्ष्य ₹2120</t>
@@ -40681,8 +40513,2733 @@
         </is>
       </c>
     </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:42:42</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr"/>
+      <c r="E939" t="n">
+        <v>910</v>
+      </c>
+      <c r="F939" t="n">
+        <v>879</v>
+      </c>
+      <c r="G939" t="inlineStr"/>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Indian Bank
+खरीदें
+PRICE 893.80
+TARGET 910/925
+STOP LOSS 879</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:42:40</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="n">
+        <v>925</v>
+      </c>
+      <c r="F940" t="n">
+        <v>879</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय
+Indian Bank
+खरीदें
+PRICE ▶ 893.85
+TARGET ▶ 910/925
+STOP LOSS ▶ 879</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:37:57</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr"/>
+      <c r="E941" t="n">
+        <v>360</v>
+      </c>
+      <c r="G941" t="inlineStr"/>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 395.00 1.62% BUY TARGET HIT 360</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:37:53</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr"/>
+      <c r="E942" t="n">
+        <v>405</v>
+      </c>
+      <c r="F942" t="n">
+        <v>360</v>
+      </c>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe ▲ 396.85 8.15 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:36:25</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr"/>
+      <c r="E943" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G943" t="inlineStr"/>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+NGL Fine Chem Ltd
+खरीदें
+PRICE → 2836.00
+TARGET → 3190
+STOP LOSS → ---</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:36:24</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr"/>
+      <c r="E944" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+NGL Fine Chem Ltd
+खरीदें
+PRICE ▶ 2835.10
+TARGET ▶ 3190
+STOP LOSS ▶ ---</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:32:00</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>398</v>
+      </c>
+      <c r="E945" t="n">
+        <v>405</v>
+      </c>
+      <c r="G945" t="inlineStr"/>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 401.15 BUY TGT 405 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:32:00</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>398</v>
+      </c>
+      <c r="E946" t="n">
+        <v>405</v>
+      </c>
+      <c r="F946" t="n">
+        <v>360</v>
+      </c>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 401.15 12.45 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:28:47</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr"/>
+      <c r="E947" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="G947" t="inlineStr"/>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>Union Bank 189.04 INVESTMENT PICK 106.00 28/01/2025 RECO PRICE RETURN TILL NOW 83.04 78.34%</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:28:00</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E948" t="n">
+        <v>560</v>
+      </c>
+      <c r="G948" t="inlineStr"/>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 400.00 11.30 BUY TARGET HIT 560</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:28:00</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E949" t="n">
+        <v>405</v>
+      </c>
+      <c r="F949" t="n">
+        <v>360</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब
+Indian Hume Pipe
+400.00 11.30
+BUY
+TGT 405
+SL 360</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:27:00</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>537.5</v>
+      </c>
+      <c r="E950" t="n">
+        <v>545</v>
+      </c>
+      <c r="F950" t="n">
+        <v>530</v>
+      </c>
+      <c r="G950" t="inlineStr"/>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:27:00</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>537.5</v>
+      </c>
+      <c r="E951" t="n">
+        <v>555</v>
+      </c>
+      <c r="F951" t="n">
+        <v>530</v>
+      </c>
+      <c r="G951" t="inlineStr"/>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E952" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F952" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G952" t="inlineStr"/>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Muthoot Finance खरीदें PRICE 2969.00 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E953" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F953" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Muthoot Finance खरीदें PRICE 2969.90 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E954" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F954" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G954" t="inlineStr"/>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E955" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F955" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G955" t="inlineStr"/>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:51</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>BANKBARODA29SEP26</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr"/>
+      <c r="E956" t="n">
+        <v>90</v>
+      </c>
+      <c r="F956" t="n">
+        <v>81</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय
+Bank of Maha Fut
+खरीदें
+PRICE ▶ 85.37
+TARGET ▶ 90
+STOP LOSS ▶ 81</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:00</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>1032.6</v>
+      </c>
+      <c r="E957" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F957" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G957" t="inlineStr"/>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+SBI
+खरीदें
+PRICE → 1030.30
+TARGET → 1050/1070
+STOP LOSS → 1015</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:00</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>1032.6</v>
+      </c>
+      <c r="E958" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F958" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G958" t="inlineStr"/>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+SBI
+खरीदें
+PRICE → 1030.30
+TARGET → 1050/1070
+STOP LOSS → 1015</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>2575</v>
+      </c>
+      <c r="E959" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G959" t="inlineStr"/>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Welspun Corp
+2554.70 +31.20
+BUY
+लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>RBLBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="E960" t="n">
+        <v>405</v>
+      </c>
+      <c r="F960" t="n">
+        <v>385</v>
+      </c>
+      <c r="G960" t="inlineStr"/>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>RBLBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="E961" t="n">
+        <v>400</v>
+      </c>
+      <c r="F961" t="n">
+        <v>385</v>
+      </c>
+      <c r="G961" t="inlineStr"/>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>270.15</v>
+      </c>
+      <c r="E962" t="n">
+        <v>279</v>
+      </c>
+      <c r="F962" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="G962" t="inlineStr"/>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>MY CHOICE FIRSTSOURCE B 279 266.5</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>1438.3</v>
+      </c>
+      <c r="E963" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F963" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G963" t="inlineStr"/>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI BANK B 1454 1411</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E964" t="n">
+        <v>192</v>
+      </c>
+      <c r="F964" t="n">
+        <v>182</v>
+      </c>
+      <c r="G964" t="inlineStr"/>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E965" t="n">
+        <v>195</v>
+      </c>
+      <c r="F965" t="n">
+        <v>182</v>
+      </c>
+      <c r="G965" t="inlineStr"/>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E966" t="n">
+        <v>212</v>
+      </c>
+      <c r="F966" t="n">
+        <v>204</v>
+      </c>
+      <c r="G966" t="inlineStr"/>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Adani Power B PRICE 207.70 TARGET 212 STOP LOSS 204</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:17:00</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>268.6</v>
+      </c>
+      <c r="E967" t="n">
+        <v>272</v>
+      </c>
+      <c r="F967" t="n">
+        <v>265</v>
+      </c>
+      <c r="G967" t="inlineStr"/>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Power Grid BUY PRICE 267.50 TARGET 272 STOP LOSS 265</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="E968" t="n">
+        <v>510</v>
+      </c>
+      <c r="F968" t="n">
+        <v>494</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय ICICI Pru BUY PRICE 499.50 TARGET 510 STOP LOSS 494</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E969" t="n">
+        <v>375</v>
+      </c>
+      <c r="F969" t="n">
+        <v>346</v>
+      </c>
+      <c r="G969" t="inlineStr"/>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Federal Bank Fut
+BUY
+PRICE ▶ 354.65
+TARGET ▶ 375
+STOP LOSS ▶ 346</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>JSWENERGY29SEP26</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>544.85</v>
+      </c>
+      <c r="E970" t="n">
+        <v>557</v>
+      </c>
+      <c r="F970" t="n">
+        <v>530</v>
+      </c>
+      <c r="G970" t="inlineStr"/>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>JSWENERGY29SEP26</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>544.85</v>
+      </c>
+      <c r="E971" t="n">
+        <v>550</v>
+      </c>
+      <c r="F971" t="n">
+        <v>530</v>
+      </c>
+      <c r="G971" t="inlineStr"/>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E972" t="n">
+        <v>365</v>
+      </c>
+      <c r="F972" t="n">
+        <v>347</v>
+      </c>
+      <c r="G972" t="inlineStr"/>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Federal Bank Futures
+UY
+PRICE ▶ 354.5
+TARGET ▶ 358, 361, 365
+STOP LOSS ▶ 347</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E973" t="n">
+        <v>361</v>
+      </c>
+      <c r="F973" t="n">
+        <v>347</v>
+      </c>
+      <c r="G973" t="inlineStr"/>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Federal Bank Futures
+UY
+PRICE ▶ 354.5
+TARGET ▶ 358, 361, 365
+STOP LOSS ▶ 347</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>269.3</v>
+      </c>
+      <c r="E974" t="n">
+        <v>273</v>
+      </c>
+      <c r="F974" t="n">
+        <v>264</v>
+      </c>
+      <c r="G974" t="inlineStr"/>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT POWER GRID B 273 264</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E975" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F975" t="n">
+        <v>1926</v>
+      </c>
+      <c r="G975" t="inlineStr"/>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>INVESTMENT GODFREY PHILLIPS B 2230 1926</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>ZENSARTECH</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="E976" t="n">
+        <v>474</v>
+      </c>
+      <c r="F976" t="n">
+        <v>455</v>
+      </c>
+      <c r="G976" t="inlineStr"/>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>MY CHOICE ZENSAR TECH B 474 455</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>UPL29SEP26</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>579.9</v>
+      </c>
+      <c r="E977" t="n">
+        <v>593</v>
+      </c>
+      <c r="F977" t="n">
+        <v>573</v>
+      </c>
+      <c r="G977" t="inlineStr"/>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>FUTURE UPL FUT B 593 573</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E978" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F978" t="n">
+        <v>1857</v>
+      </c>
+      <c r="G978" t="inlineStr"/>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>TECHNO PHOENIX MILLS B 2060 1857</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>2173.8</v>
+      </c>
+      <c r="E979" t="n">
+        <v>2215</v>
+      </c>
+      <c r="F979" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G979" t="inlineStr"/>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>MY CHOICE KIRLOSKAR OIL ENGINES B 2215 2150</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>422</v>
+      </c>
+      <c r="E980" t="n">
+        <v>460</v>
+      </c>
+      <c r="G980" t="inlineStr"/>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>INVESTMENT COAL INDIA B 460 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>425</v>
+      </c>
+      <c r="E981" t="n">
+        <v>432</v>
+      </c>
+      <c r="F981" t="n">
+        <v>418</v>
+      </c>
+      <c r="G981" t="inlineStr"/>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>MY CHOICE KOTAK BANK B 432 418</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="E982" t="n">
+        <v>361</v>
+      </c>
+      <c r="F982" t="n">
+        <v>349</v>
+      </c>
+      <c r="G982" t="inlineStr"/>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>FUTURE FEDERAL BANK FUT B 361 349</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>OLAELEC</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="E983" t="n">
+        <v>41</v>
+      </c>
+      <c r="F983" t="n">
+        <v>37</v>
+      </c>
+      <c r="G983" t="inlineStr"/>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>CASH OLA ELECTRIC B 41 37</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>1818</v>
+      </c>
+      <c r="E984" t="n">
+        <v>1852</v>
+      </c>
+      <c r="F984" t="n">
+        <v>1794</v>
+      </c>
+      <c r="G984" t="inlineStr"/>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>MY CHOICE Lloyds Metals &amp; Energy Ltd खरीदें PRICE 1813.00 TARGET 1852 STOP LOSS 1794</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>270.15</v>
+      </c>
+      <c r="E985" t="n">
+        <v>279</v>
+      </c>
+      <c r="F985" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="G985" t="inlineStr"/>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Firstsource खरीदें PRICE 270.40 TARGET 279 STOP LOSS 266.5</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>2173.8</v>
+      </c>
+      <c r="E986" t="n">
+        <v>2215</v>
+      </c>
+      <c r="F986" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G986" t="inlineStr"/>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Kirloskar Oil खरीदें PRICE 2160.90 TARGET 2215 STOP LOSS 2150</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>1438.3</v>
+      </c>
+      <c r="E987" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F987" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G987" t="inlineStr"/>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI Bank खरीदें PRICE 1426.50 TARGET 1454 STOP LOSS 1411</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>425</v>
+      </c>
+      <c r="E988" t="n">
+        <v>432</v>
+      </c>
+      <c r="F988" t="n">
+        <v>418</v>
+      </c>
+      <c r="G988" t="inlineStr"/>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>Kotak Bank खरीदें PRICE 423.50 TARGET 432 STOP LOSS 418</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:17:00</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>268.6</v>
+      </c>
+      <c r="E989" t="n">
+        <v>273</v>
+      </c>
+      <c r="F989" t="n">
+        <v>264</v>
+      </c>
+      <c r="G989" t="inlineStr"/>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>Power Grid खरीदें PRICE 266.80 TARGET 273 STOP LOSS 264</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="E990" t="n">
+        <v>460</v>
+      </c>
+      <c r="G990" t="inlineStr"/>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK Coal India खरीदें PRICE 417.85 TARGET 460 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E991" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F991" t="n">
+        <v>1926</v>
+      </c>
+      <c r="G991" t="inlineStr"/>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK Godfrey Phillips खरीदें PRICE 2025.40 TARGET 2230 STOP LOSS 1926</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="E992" t="n">
+        <v>371</v>
+      </c>
+      <c r="F992" t="n">
+        <v>360</v>
+      </c>
+      <c r="G992" t="inlineStr"/>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Tata Power खरीदें PRICE 364.00 TARGET 371 STOP LOSS 360</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E993" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F993" t="n">
+        <v>1857</v>
+      </c>
+      <c r="G993" t="inlineStr"/>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>TECHNO PICK Phoenix Mills खरीदें PRICE 1920.10 TARGET 2060 STOP LOSS 1857</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>2172</v>
+      </c>
+      <c r="E994" t="n">
+        <v>2438</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>अंश के शेयर मॉर्गन स्टैनली की ओवरवेट राय, लक्ष्य ₹2131 से बढ़ाकर ₹2438 Hyundai Motor 2154.40 1.17%</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="E995" t="n">
+        <v>361</v>
+      </c>
+      <c r="F995" t="n">
+        <v>349</v>
+      </c>
+      <c r="G995" t="inlineStr"/>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+Federal Bank Fut
+खरीदें
+PRICE 354.65
+TARGET 361
+STOP LOSS 349</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="E996" t="n">
+        <v>1470</v>
+      </c>
+      <c r="G996" t="inlineStr"/>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>STOCKS IN NEWS
+ICICI Bank 1426.50 -0.80%
+ICICI Pru का 2 % हिस्सा ₹ 1470 Cr में खरीदा</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>1864.9</v>
+      </c>
+      <c r="E997" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F997" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G997" t="inlineStr"/>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>1864.9</v>
+      </c>
+      <c r="E998" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F998" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G998" t="inlineStr"/>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>1681.8</v>
+      </c>
+      <c r="E999" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G999" t="inlineStr"/>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1672.70 +25.20
+OVERWEIGHT
+लक्ष्य ₹2000</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>465</v>
+      </c>
+      <c r="G1000" t="inlineStr"/>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALL
+Coal India
+417.85 +4.05%
+BUY
+लक्ष्य ₹430 से बढ़ाकर ₹465</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>935</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G1001" t="inlineStr"/>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>LUNG-TERM CALL Shilpa Medicare BUY TARGET 1200 DURATION 12 महीने Shilpa Medicare 928.55 4.37%</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>HAPPSTMNDS</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>356</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1002" t="inlineStr"/>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>सुदीप बंदोपाध्याय की पसंद Happiest Minds BUY TARGET 550 DURATION 12 महीने Happiest Minds 354.85 7.85</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J938"/>
+  <autoFilter ref="A1:J1002"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1002</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1002"/>
+  <dimension ref="A1:J1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -40529,14 +40529,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D939" t="inlineStr"/>
       <c r="E939" t="n">
         <v>910</v>
       </c>
       <c r="F939" t="n">
         <v>879</v>
       </c>
-      <c r="G939" t="inlineStr"/>
       <c r="H939" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -40574,7 +40572,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D940" t="inlineStr"/>
       <c r="E940" t="n">
         <v>925</v>
       </c>
@@ -40623,11 +40620,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D941" t="inlineStr"/>
       <c r="E941" t="n">
         <v>360</v>
       </c>
-      <c r="G941" t="inlineStr"/>
       <c r="H941" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 395.00 1.62% BUY TARGET HIT 360</t>
@@ -40660,14 +40655,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D942" t="inlineStr"/>
       <c r="E942" t="n">
         <v>405</v>
       </c>
       <c r="F942" t="n">
         <v>360</v>
       </c>
-      <c r="G942" t="inlineStr"/>
       <c r="H942" t="inlineStr">
         <is>
           <t>Indian Hume Pipe ▲ 396.85 8.15 BUY TGT 405 SL 360</t>
@@ -40700,11 +40693,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D943" t="inlineStr"/>
       <c r="E943" t="n">
         <v>3190</v>
       </c>
-      <c r="G943" t="inlineStr"/>
       <c r="H943" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -40742,11 +40733,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D944" t="inlineStr"/>
       <c r="E944" t="n">
         <v>3190</v>
       </c>
-      <c r="G944" t="inlineStr"/>
       <c r="H944" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -40790,7 +40779,6 @@
       <c r="E945" t="n">
         <v>405</v>
       </c>
-      <c r="G945" t="inlineStr"/>
       <c r="H945" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 401.15 BUY TGT 405 TARGET HIT</t>
@@ -40832,7 +40820,6 @@
       <c r="F946" t="n">
         <v>360</v>
       </c>
-      <c r="G946" t="inlineStr"/>
       <c r="H946" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 401.15 12.45 BUY TGT 405 SL 360</t>
@@ -40865,11 +40852,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D947" t="inlineStr"/>
       <c r="E947" t="n">
         <v>189.04</v>
       </c>
-      <c r="G947" t="inlineStr"/>
       <c r="H947" t="inlineStr">
         <is>
           <t>Union Bank 189.04 INVESTMENT PICK 106.00 28/01/2025 RECO PRICE RETURN TILL NOW 83.04 78.34%</t>
@@ -40908,7 +40893,6 @@
       <c r="E948" t="n">
         <v>560</v>
       </c>
-      <c r="G948" t="inlineStr"/>
       <c r="H948" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 400.00 11.30 BUY TARGET HIT 560</t>
@@ -41001,7 +40985,6 @@
       <c r="F950" t="n">
         <v>530</v>
       </c>
-      <c r="G950" t="inlineStr"/>
       <c r="H950" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
@@ -41043,7 +41026,6 @@
       <c r="F951" t="n">
         <v>530</v>
       </c>
-      <c r="G951" t="inlineStr"/>
       <c r="H951" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
@@ -41085,7 +41067,6 @@
       <c r="F952" t="n">
         <v>2945</v>
       </c>
-      <c r="G952" t="inlineStr"/>
       <c r="H952" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Muthoot Finance खरीदें PRICE 2969.00 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -41173,7 +41154,6 @@
       <c r="F954" t="n">
         <v>2945</v>
       </c>
-      <c r="G954" t="inlineStr"/>
       <c r="H954" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -41215,7 +41195,6 @@
       <c r="F955" t="n">
         <v>2945</v>
       </c>
-      <c r="G955" t="inlineStr"/>
       <c r="H955" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -41248,7 +41227,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D956" t="inlineStr"/>
       <c r="E956" t="n">
         <v>90</v>
       </c>
@@ -41306,7 +41284,6 @@
       <c r="F957" t="n">
         <v>1015</v>
       </c>
-      <c r="G957" t="inlineStr"/>
       <c r="H957" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -41353,7 +41330,6 @@
       <c r="F958" t="n">
         <v>1015</v>
       </c>
-      <c r="G958" t="inlineStr"/>
       <c r="H958" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -41397,7 +41373,6 @@
       <c r="E959" t="n">
         <v>3250</v>
       </c>
-      <c r="G959" t="inlineStr"/>
       <c r="H959" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -41443,7 +41418,6 @@
       <c r="F960" t="n">
         <v>385</v>
       </c>
-      <c r="G960" t="inlineStr"/>
       <c r="H960" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
@@ -41485,7 +41459,6 @@
       <c r="F961" t="n">
         <v>385</v>
       </c>
-      <c r="G961" t="inlineStr"/>
       <c r="H961" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
@@ -41527,7 +41500,6 @@
       <c r="F962" t="n">
         <v>266.5</v>
       </c>
-      <c r="G962" t="inlineStr"/>
       <c r="H962" t="inlineStr">
         <is>
           <t>MY CHOICE FIRSTSOURCE B 279 266.5</t>
@@ -41569,7 +41541,6 @@
       <c r="F963" t="n">
         <v>1411</v>
       </c>
-      <c r="G963" t="inlineStr"/>
       <c r="H963" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI BANK B 1454 1411</t>
@@ -41611,7 +41582,6 @@
       <c r="F964" t="n">
         <v>182</v>
       </c>
-      <c r="G964" t="inlineStr"/>
       <c r="H964" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
@@ -41653,7 +41623,6 @@
       <c r="F965" t="n">
         <v>182</v>
       </c>
-      <c r="G965" t="inlineStr"/>
       <c r="H965" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
@@ -41695,7 +41664,6 @@
       <c r="F966" t="n">
         <v>204</v>
       </c>
-      <c r="G966" t="inlineStr"/>
       <c r="H966" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Adani Power B PRICE 207.70 TARGET 212 STOP LOSS 204</t>
@@ -41737,7 +41705,6 @@
       <c r="F967" t="n">
         <v>265</v>
       </c>
-      <c r="G967" t="inlineStr"/>
       <c r="H967" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Power Grid BUY PRICE 267.50 TARGET 272 STOP LOSS 265</t>
@@ -41825,7 +41792,6 @@
       <c r="F969" t="n">
         <v>346</v>
       </c>
-      <c r="G969" t="inlineStr"/>
       <c r="H969" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -41872,7 +41838,6 @@
       <c r="F970" t="n">
         <v>530</v>
       </c>
-      <c r="G970" t="inlineStr"/>
       <c r="H970" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
@@ -41914,7 +41879,6 @@
       <c r="F971" t="n">
         <v>530</v>
       </c>
-      <c r="G971" t="inlineStr"/>
       <c r="H971" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
@@ -41956,7 +41920,6 @@
       <c r="F972" t="n">
         <v>347</v>
       </c>
-      <c r="G972" t="inlineStr"/>
       <c r="H972" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -42003,7 +41966,6 @@
       <c r="F973" t="n">
         <v>347</v>
       </c>
-      <c r="G973" t="inlineStr"/>
       <c r="H973" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -42050,7 +42012,6 @@
       <c r="F974" t="n">
         <v>264</v>
       </c>
-      <c r="G974" t="inlineStr"/>
       <c r="H974" t="inlineStr">
         <is>
           <t>NEWS IMPACT POWER GRID B 273 264</t>
@@ -42092,7 +42053,6 @@
       <c r="F975" t="n">
         <v>1926</v>
       </c>
-      <c r="G975" t="inlineStr"/>
       <c r="H975" t="inlineStr">
         <is>
           <t>INVESTMENT GODFREY PHILLIPS B 2230 1926</t>
@@ -42134,7 +42094,6 @@
       <c r="F976" t="n">
         <v>455</v>
       </c>
-      <c r="G976" t="inlineStr"/>
       <c r="H976" t="inlineStr">
         <is>
           <t>MY CHOICE ZENSAR TECH B 474 455</t>
@@ -42176,7 +42135,6 @@
       <c r="F977" t="n">
         <v>573</v>
       </c>
-      <c r="G977" t="inlineStr"/>
       <c r="H977" t="inlineStr">
         <is>
           <t>FUTURE UPL FUT B 593 573</t>
@@ -42218,7 +42176,6 @@
       <c r="F978" t="n">
         <v>1857</v>
       </c>
-      <c r="G978" t="inlineStr"/>
       <c r="H978" t="inlineStr">
         <is>
           <t>TECHNO PHOENIX MILLS B 2060 1857</t>
@@ -42260,7 +42217,6 @@
       <c r="F979" t="n">
         <v>2150</v>
       </c>
-      <c r="G979" t="inlineStr"/>
       <c r="H979" t="inlineStr">
         <is>
           <t>MY CHOICE KIRLOSKAR OIL ENGINES B 2215 2150</t>
@@ -42299,7 +42255,6 @@
       <c r="E980" t="n">
         <v>460</v>
       </c>
-      <c r="G980" t="inlineStr"/>
       <c r="H980" t="inlineStr">
         <is>
           <t>INVESTMENT COAL INDIA B 460 12 MONTH</t>
@@ -42341,7 +42296,6 @@
       <c r="F981" t="n">
         <v>418</v>
       </c>
-      <c r="G981" t="inlineStr"/>
       <c r="H981" t="inlineStr">
         <is>
           <t>MY CHOICE KOTAK BANK B 432 418</t>
@@ -42383,7 +42337,6 @@
       <c r="F982" t="n">
         <v>349</v>
       </c>
-      <c r="G982" t="inlineStr"/>
       <c r="H982" t="inlineStr">
         <is>
           <t>FUTURE FEDERAL BANK FUT B 361 349</t>
@@ -42425,7 +42378,6 @@
       <c r="F983" t="n">
         <v>37</v>
       </c>
-      <c r="G983" t="inlineStr"/>
       <c r="H983" t="inlineStr">
         <is>
           <t>CASH OLA ELECTRIC B 41 37</t>
@@ -42467,7 +42419,6 @@
       <c r="F984" t="n">
         <v>1794</v>
       </c>
-      <c r="G984" t="inlineStr"/>
       <c r="H984" t="inlineStr">
         <is>
           <t>MY CHOICE Lloyds Metals &amp; Energy Ltd खरीदें PRICE 1813.00 TARGET 1852 STOP LOSS 1794</t>
@@ -42509,7 +42460,6 @@
       <c r="F985" t="n">
         <v>266.5</v>
       </c>
-      <c r="G985" t="inlineStr"/>
       <c r="H985" t="inlineStr">
         <is>
           <t>अंश के शेयर Firstsource खरीदें PRICE 270.40 TARGET 279 STOP LOSS 266.5</t>
@@ -42551,7 +42501,6 @@
       <c r="F986" t="n">
         <v>2150</v>
       </c>
-      <c r="G986" t="inlineStr"/>
       <c r="H986" t="inlineStr">
         <is>
           <t>पूजा के शेयर Kirloskar Oil खरीदें PRICE 2160.90 TARGET 2215 STOP LOSS 2150</t>
@@ -42593,7 +42542,6 @@
       <c r="F987" t="n">
         <v>1411</v>
       </c>
-      <c r="G987" t="inlineStr"/>
       <c r="H987" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI Bank खरीदें PRICE 1426.50 TARGET 1454 STOP LOSS 1411</t>
@@ -42635,7 +42583,6 @@
       <c r="F988" t="n">
         <v>418</v>
       </c>
-      <c r="G988" t="inlineStr"/>
       <c r="H988" t="inlineStr">
         <is>
           <t>Kotak Bank खरीदें PRICE 423.50 TARGET 432 STOP LOSS 418</t>
@@ -42677,7 +42624,6 @@
       <c r="F989" t="n">
         <v>264</v>
       </c>
-      <c r="G989" t="inlineStr"/>
       <c r="H989" t="inlineStr">
         <is>
           <t>Power Grid खरीदें PRICE 266.80 TARGET 273 STOP LOSS 264</t>
@@ -42716,7 +42662,6 @@
       <c r="E990" t="n">
         <v>460</v>
       </c>
-      <c r="G990" t="inlineStr"/>
       <c r="H990" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK Coal India खरीदें PRICE 417.85 TARGET 460 DURATION 12 महीने</t>
@@ -42758,7 +42703,6 @@
       <c r="F991" t="n">
         <v>1926</v>
       </c>
-      <c r="G991" t="inlineStr"/>
       <c r="H991" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK Godfrey Phillips खरीदें PRICE 2025.40 TARGET 2230 STOP LOSS 1926</t>
@@ -42800,7 +42744,6 @@
       <c r="F992" t="n">
         <v>360</v>
       </c>
-      <c r="G992" t="inlineStr"/>
       <c r="H992" t="inlineStr">
         <is>
           <t>पूजा के शेयर Tata Power खरीदें PRICE 364.00 TARGET 371 STOP LOSS 360</t>
@@ -42842,7 +42785,6 @@
       <c r="F993" t="n">
         <v>1857</v>
       </c>
-      <c r="G993" t="inlineStr"/>
       <c r="H993" t="inlineStr">
         <is>
           <t>TECHNO PICK Phoenix Mills खरीदें PRICE 1920.10 TARGET 2060 STOP LOSS 1857</t>
@@ -42927,7 +42869,6 @@
       <c r="F995" t="n">
         <v>349</v>
       </c>
-      <c r="G995" t="inlineStr"/>
       <c r="H995" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -42971,7 +42912,6 @@
       <c r="E996" t="n">
         <v>1470</v>
       </c>
-      <c r="G996" t="inlineStr"/>
       <c r="H996" t="inlineStr">
         <is>
           <t>STOCKS IN NEWS
@@ -43015,7 +42955,6 @@
       <c r="F997" t="n">
         <v>1835</v>
       </c>
-      <c r="G997" t="inlineStr"/>
       <c r="H997" t="inlineStr">
         <is>
           <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
@@ -43057,7 +42996,6 @@
       <c r="F998" t="n">
         <v>1835</v>
       </c>
-      <c r="G998" t="inlineStr"/>
       <c r="H998" t="inlineStr">
         <is>
           <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
@@ -43096,7 +43034,6 @@
       <c r="E999" t="n">
         <v>2000</v>
       </c>
-      <c r="G999" t="inlineStr"/>
       <c r="H999" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -43139,7 +43076,6 @@
       <c r="E1000" t="n">
         <v>465</v>
       </c>
-      <c r="G1000" t="inlineStr"/>
       <c r="H1000" t="inlineStr">
         <is>
           <t>BROKERAGE CALL
@@ -43182,7 +43118,6 @@
       <c r="E1001" t="n">
         <v>1200</v>
       </c>
-      <c r="G1001" t="inlineStr"/>
       <c r="H1001" t="inlineStr">
         <is>
           <t>LUNG-TERM CALL Shilpa Medicare BUY TARGET 1200 DURATION 12 महीने Shilpa Medicare 928.55 4.37%</t>
@@ -43221,7 +43156,6 @@
       <c r="E1002" t="n">
         <v>550</v>
       </c>
-      <c r="G1002" t="inlineStr"/>
       <c r="H1002" t="inlineStr">
         <is>
           <t>सुदीप बंदोपाध्याय की पसंद Happiest Minds BUY TARGET 550 DURATION 12 महीने Happiest Minds 354.85 7.85</t>
@@ -43238,8 +43172,5447 @@
         </is>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:09:00</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>100</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1003" t="inlineStr"/>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>अक्षय भागवत की राय
+Bank of Maha
+87.02 ▲ 5.61%
+BUY
+TARGET 97/100
+STOP LOSS 80</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-09-03 13:09:00</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>97</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>80</v>
+      </c>
+      <c r="G1004" t="inlineStr"/>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>अक्षय भागवत की राय
+Bank of Maha
+87.02 ▲ 5.61%
+BUY
+TARGET 97/100
+STOP LOSS 80</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:52:00</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>144.79</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>152</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>140</v>
+      </c>
+      <c r="G1005" t="inlineStr"/>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>TRADING CALL Bank of India खरीदें PRICE 144.78 TARGET 152 STOP LOSS 140</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:51:00</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>1256.9</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G1006" t="inlineStr"/>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>TRADING CALL Bharat Dynamics खरीदें PRICE 1255.90 TARGET 1430 STOP LOSS 1160</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:49:44</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>NIFTY2380008SEP26PE</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr"/>
+      <c r="E1007" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>Nitin Murarka</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>नितिन मुरारका की राय निफ्टी 23800 की पुट @ 40-45 खरीदें STOP LOSS 30 TARGET 65</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:49:41</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>NIFTY2380029SEP26PE</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr"/>
+      <c r="E1008" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1008" t="inlineStr"/>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>निफ्टी 23800 की पुट @ 40-45 खरीदें STOP LOSS 30 TARGET 65</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:20:00</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1009" t="n">
+        <v>2661.4</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>Welspun Corp पर जेफरीज Welspun Corp 2671.70 ▲ 5.87% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:10:00</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1010" t="n">
+        <v>2617.5</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1010" t="inlineStr"/>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>Welspun Corp 2619.00 ▲ 3.78% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-09-03 11:10:00</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1011" t="n">
+        <v>2617.5</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>Welspun Corp पर जेफरीज Welspun Corp 2617.40 ▲ कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1012" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G1012" t="inlineStr"/>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Oberoi Realty Fut खरीदें PRICE 1899.60 TARGET 1960/2000 STOP LOSS 1865</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1013" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G1013" t="inlineStr"/>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय Oberoi Realty Fut खरीदें PRICE 1899.60 TARGET 1960/2000 STOP LOSS 1865</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1014" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G1014" t="inlineStr"/>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Fut खरीदें PRICE 1900.00 TARGET 1960/2000 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1015" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1015" t="inlineStr"/>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>Oberoi Realty Fut खरीदें PRICE 1900.00 TARGET 1960/2000 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1016" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G1016" t="inlineStr"/>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Oberoi Realty Fut
+खरीदें
+PRICE ▶ 1898.40
+TARGET ▶ 1960/2000
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1017" t="n">
+        <v>1897.9</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1017" t="inlineStr"/>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Oberoi Realty Fut
+खरीदें
+PRICE ▶ 1898.40
+TARGET ▶ 1960/2000
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:00</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1018" t="n">
+        <v>1672</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G1018" t="inlineStr"/>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>SHORT MIDCAP STOCKS
+Astra Micro
+खरीदें
+STOP LOSS -- | TARGET 1760 | DURATION 1-2 महीने
+Astra Micro 1667.40 ▲ 25.60</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:00</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1019" t="n">
+        <v>733.35</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>770</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>699</v>
+      </c>
+      <c r="G1019" t="inlineStr"/>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय Graphite India खरीदें STOP LOSS 699 TARGET 770/800 DURATION -- Graphite India 733.25 0.92%</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:51:00</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1020" t="n">
+        <v>733.35</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>699</v>
+      </c>
+      <c r="G1020" t="inlineStr"/>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय Graphite India खरीदें STOP LOSS 699 TARGET 770/800 DURATION -- Graphite India 733.25 0.92%</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:50:00</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1021" t="n">
+        <v>228.7</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>262</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1021" t="inlineStr"/>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय
+Sapphire Foods
+खरीदें
+STOP LOSS 211 | TARGET 245/262 | DURATION --
+Sapphire Foods 228.69 ▲ 0.21%</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:50:00</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1022" t="n">
+        <v>228.7</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>245</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1022" t="inlineStr"/>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 228.69 0.48</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1023" t="n">
+        <v>623.1</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1023" t="inlineStr"/>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी साब
+Insecticides Ind ▲
+622.70 10.10
+BUY
+TGT 650
+SL 600</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1024" t="n">
+        <v>898</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>873</v>
+      </c>
+      <c r="G1024" t="inlineStr"/>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>Indian Bank 896.55 BUY TGT 910 SL 873</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1025" t="n">
+        <v>2871.3</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G1025" t="inlineStr"/>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+NGL Fine Chem Ltd ▲
+2871.90 183.20
+BUY
+TGT 3190
+SL ---</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1026" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1026" t="inlineStr"/>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट HDFC Life 536.35 3.35 BUY TGT 545 SL 530</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1027" t="n">
+        <v>1895</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>1861</v>
+      </c>
+      <c r="G1027" t="inlineStr"/>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>BTSTT BUY TODAY Oberoi Realty Fut 1897.20 1.16% BUY TGT 2000 SL 1861</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:45:00</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>MAHABANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1028" t="n">
+        <v>87.26000000000001</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1028" t="inlineStr"/>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>BTSTT BUY TODAY Bank of Maha Fut 87.10 4.66 BUY TGT 90 SL 81</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:44:09</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr"/>
+      <c r="E1029" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G1029" t="inlineStr"/>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर BEML 2085.30 2.60% BUY TARGET HIT 2005</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:44:06</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr"/>
+      <c r="E1030" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G1030" t="inlineStr"/>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+BEML
+2085.30 52.90
+BUY
+TGT 2070
+SL 2005</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1031" t="n">
+        <v>603.3</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>520</v>
+      </c>
+      <c r="G1031" t="inlineStr"/>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>1 की कमाई Indegene खरीदें PRICE 602.00 TARGET 800 STOP LOSS 520</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1032" t="n">
+        <v>603.3</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>520</v>
+      </c>
+      <c r="G1032" t="inlineStr"/>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>Indegene खरीदें PRICE 601.95 TARGET 800 STOP LOSS 520</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:19:00</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1033" t="n">
+        <v>230.48</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>245</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1033" t="inlineStr"/>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 229.82 ▲ 0.71%</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:19:00</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1034" t="n">
+        <v>230.48</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>262</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1034" t="inlineStr"/>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 229.82 ▲ 0.71%</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:14:00</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1035" t="n">
+        <v>2601</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>Welspun Corp पर जेफरीज Welspun Corp 2599.30 ▲ 3.00% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:14:00</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1036" t="n">
+        <v>2601</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1036" t="inlineStr"/>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>BUZZING STOCK Welspun Corp 2600.00 ▲ 3.03% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1037" t="n">
+        <v>624</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1037" t="inlineStr"/>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी सा'ब
+Insecticides Ind
+624.00 11.40
+BUY
+TGT 650
+SL 600</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1038" t="n">
+        <v>624</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>650</v>
+      </c>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>Insecticides Ind 624.00 11.40 BUY TGT 650</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1039" t="n">
+        <v>2840.1</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G1039" t="inlineStr"/>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+NGL Fine Chem Ltd
+2837.30 148.60
+BUY
+TGT 3190
+SL ---</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1040" t="n">
+        <v>538.65</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1040" t="inlineStr"/>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>HDFC Life 538.50 1.03% BUY TGT 545 SL 530</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1041" t="n">
+        <v>2974.4</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1041" t="inlineStr"/>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Muthoot Finance
+2971.00 33.30
+BUY
+TGT 3010
+SL 2945</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1042" t="n">
+        <v>2974.4</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1042" t="inlineStr"/>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>Muthoot Finance 2970.90 33.20 BUY TGT 3010 SL 2945</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1043" t="n">
+        <v>1029.6</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G1043" t="inlineStr"/>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>SBI 1029.60 8.70 BUY TGT 1050 SL 1015</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1044" t="n">
+        <v>1919.5</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>1861</v>
+      </c>
+      <c r="G1044" t="inlineStr"/>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>BTSTT BUY TODAY Oberoi Realty Fut 1917.60 42.20 BUY TGT 2000 SL 1861</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1045" t="n">
+        <v>167.39</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>149</v>
+      </c>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 167.58 ▲ 1.91% MARKET MENTORS रामदेव अग्रवाल चेयरमैन &amp; को-फाउंडर MOFSL 11 AM</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1046" t="n">
+        <v>167.39</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>149</v>
+      </c>
+      <c r="G1046" t="inlineStr"/>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 167.58 ▲ 1.91% MARKET MENTORS रामदेव अग्रवाल चेयरमैन &amp; को-फाउंडर MOFSL 11 AM</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:08:24</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>GPPL</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr"/>
+      <c r="E1047" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>149</v>
+      </c>
+      <c r="G1047" t="inlineStr"/>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 147.68</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:07:00</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>BELRISE</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1048" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>290</v>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Belrise Ind खरीदें STOP LOSS -- TARGET 290 DURATION 6-9 महीने Belrise Ind 238.38</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5850029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1049" t="n">
+        <v>454</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>580</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>334</v>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 58500 की कॉल @ 446 खरीदें STOP LOSS 334 TARGET 580/640</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5850029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1050" t="n">
+        <v>454</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>334</v>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 58500 की कॉल @ 446 खरीदें STOP LOSS 334 TARGET 580/640</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1051" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>51</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1051" t="inlineStr"/>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>South Indian Bank खरीदें PRICE 47.58 TARGET 51/53 STOP LOSS 45</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1052" t="n">
+        <v>47.43</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>53</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1052" t="inlineStr"/>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>South Indian Bank खरीदें PRICE 47.58 TARGET 51/53 STOP LOSS 45</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1053" t="n">
+        <v>894.25</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>879</v>
+      </c>
+      <c r="G1053" t="inlineStr"/>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Indian Bank 894.55 1.79% BUY TGT 910 SL 879</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1054" t="n">
+        <v>871.8</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>743</v>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>CLSA</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>CLSA BROKERAGE CALLS REDUCE लक्ष्य ₹772 से घटाकर ₹743 Godrej Cons 870.85 34.15 3.77% Vol: 2.31</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1055" t="n">
+        <v>2837.5</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G1055" t="inlineStr"/>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+NGL Fine Chem Ltd ▲
+2838.00 149.30
+BUY
+TGT 3190
+SL</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1056" t="n">
+        <v>539.4</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1056" t="inlineStr"/>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट HDFC Life 539.30 6.30 BUY TGT 545 SL 530</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1057" t="n">
+        <v>2962.4</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1057" t="inlineStr"/>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Muthoot Finance
+2965.20 27.50
+BUY
+TGT 3010
+SL 2945</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1058" t="n">
+        <v>1032.9</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G1058" t="inlineStr"/>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>SBI 1032.80 11.90 BUY TGT 1050 SL 1015</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1059" t="n">
+        <v>1032.9</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G1059" t="inlineStr"/>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>SBI 1033.00 12.10 BUY TGT 1050 SL 1015 Thu 03 Sep'26</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>MAHABANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1060" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1060" t="inlineStr"/>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>BTSTT BUY TODAY Bank of Maha Fut 86.54 4.10 BUY TGT 90 SL 81</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>ABB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1061" t="n">
+        <v>7450</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>7478</v>
+      </c>
+      <c r="G1061" t="inlineStr"/>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>BTSTT ABB Fut 7450.00 BUY TGT 7478 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>ABB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1062" t="n">
+        <v>7450</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>7540</v>
+      </c>
+      <c r="G1062" t="inlineStr"/>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर
+ABB Fut
+7450.00 0.61%
+BUY
+TARGET HIT
+7540</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>ABB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1063" t="n">
+        <v>7450</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>7470</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>7340</v>
+      </c>
+      <c r="G1063" t="inlineStr"/>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>BTSTT BUY TODAY ABB Fut 7450.00 45.50 BUY TGT 7470 SL 7340</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:52:11</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr"/>
+      <c r="E1064" t="n">
+        <v>150</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>125</v>
+      </c>
+      <c r="G1064" t="inlineStr"/>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>Godrej Cons: FY27 की गाइडेंस बरकरार अगले 3 तिमाही में ₹125-150 Cr का इन्वेंट्री करेक्शन करेगी Godrej Cons 870.20 ▼ 34.80</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:52:00</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1065" t="n">
+        <v>1919.4</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>1861</v>
+      </c>
+      <c r="G1065" t="inlineStr"/>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>BTSTT CALL Oberoi Realty Fut खरीदें PRICE 1922.00 TARGET 2000 STOP LOSS 1861</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:52:00</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1066" t="n">
+        <v>1919.4</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>1861</v>
+      </c>
+      <c r="G1066" t="inlineStr"/>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>BTSTT CALL Oberoi Realty Fut खरीदें PRICE 1920.50 TARGET 2000 STOP LOSS 1861</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1067" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>560</v>
+      </c>
+      <c r="G1067" t="inlineStr"/>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 398.05 2.41% BUY TARGET HIT 560</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1068" t="n">
+        <v>397.75</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>405</v>
+      </c>
+      <c r="G1068" t="inlineStr"/>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>INDIAN HOME PIPE 398.05 BUY TGT 405</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1069" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय INSECTICIDES IND @ 615 खरीदें STOP LOSS 600 TARGET 650 Insecticides Ind 629.85 ▲ 2.82%</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>INSECTICID</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1070" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1070" t="inlineStr"/>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>विकास सेठ की राय INSECTICIDES IND @ 615 खरीदें STOP LOSS 600 TARGET 650 Insecticides Ind 630.00 2.84%</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1071" t="n">
+        <v>894.45</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>879</v>
+      </c>
+      <c r="G1071" t="inlineStr"/>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Indian Bank
+खरीदें
+PRICE 893.80
+TARGET 910/925
+STOP LOSS 879</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1072" t="n">
+        <v>894.45</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>925</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>879</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय
+Indian Bank
+खरीदें
+PRICE ▶ 893.85
+TARGET ▶ 910/925
+STOP LOSS ▶ 879</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:37:57</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1073" t="inlineStr"/>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 395.00 1.62% BUY TARGET HIT 360</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:38:00</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1074" t="n">
+        <v>396.95</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>405</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1074" t="inlineStr"/>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe ▲ 396.85 8.15 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:37:00</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1075" t="n">
+        <v>2833.7</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G1075" t="inlineStr"/>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+NGL Fine Chem Ltd
+खरीदें
+PRICE → 2836.00
+TARGET → 3190
+STOP LOSS → ---</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:37:00</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1076" t="n">
+        <v>2833.7</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G1076" t="inlineStr"/>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय
+NGL Fine Chem Ltd
+खरीदें
+PRICE ▶ 2835.10
+TARGET ▶ 3190
+STOP LOSS ▶ ---</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:32:00</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1077" t="n">
+        <v>398</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>405</v>
+      </c>
+      <c r="G1077" t="inlineStr"/>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 401.15 BUY TGT 405 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:32:00</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1078" t="n">
+        <v>398</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>405</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1078" t="inlineStr"/>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 401.15 12.45 BUY TGT 405 SL 360</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:28:47</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr"/>
+      <c r="E1079" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="G1079" t="inlineStr"/>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>Union Bank 189.04 INVESTMENT PICK 106.00 28/01/2025 RECO PRICE RETURN TILL NOW 83.04 78.34%</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:28:00</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1080" t="n">
+        <v>401.5</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>560</v>
+      </c>
+      <c r="G1080" t="inlineStr"/>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe 400.00 11.30 BUY TARGET HIT 560</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:27:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1081" t="n">
+        <v>537.5</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>555</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1081" t="inlineStr"/>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:27:00</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1082" t="n">
+        <v>537.5</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1082" t="inlineStr"/>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1083" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1083" t="inlineStr"/>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Muthoot Finance खरीदें PRICE 2969.00 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1084" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>3010</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1084" t="inlineStr"/>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1085" t="n">
+        <v>2970.3</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>3030</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>2945</v>
+      </c>
+      <c r="G1085" t="inlineStr"/>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:51</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>BANKBARODA29SEP26</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr"/>
+      <c r="E1086" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>81</v>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>Somil Mehta</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>सोमिल मेहता की राय
+Bank of Maha Fut
+खरीदें
+PRICE ▶ 85.37
+TARGET ▶ 90
+STOP LOSS ▶ 81</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1087" t="n">
+        <v>1032.6</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G1087" t="inlineStr"/>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+SBI
+खरीदें
+PRICE → 1030.30
+TARGET → 1050/1070
+STOP LOSS → 1015</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1088" t="n">
+        <v>1032.6</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G1088" t="inlineStr"/>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+SBI
+खरीदें
+PRICE → 1030.30
+TARGET → 1050/1070
+STOP LOSS → 1015</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1089" t="n">
+        <v>2575</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G1089" t="inlineStr"/>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Welspun Corp
+2554.70 +31.20
+BUY
+लक्ष्य ₹3250</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>RBLBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1090" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>405</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>385</v>
+      </c>
+      <c r="G1090" t="inlineStr"/>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>RBLBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1091" t="n">
+        <v>399.85</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>385</v>
+      </c>
+      <c r="G1091" t="inlineStr"/>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1092" t="n">
+        <v>270.15</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>279</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="G1092" t="inlineStr"/>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>MY CHOICE FIRSTSOURCE B 279 266.5</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1093" t="n">
+        <v>1438.3</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G1093" t="inlineStr"/>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI BANK B 1454 1411</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1094" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>192</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>182</v>
+      </c>
+      <c r="G1094" t="inlineStr"/>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>195</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>182</v>
+      </c>
+      <c r="G1095" t="inlineStr"/>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>212</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>204</v>
+      </c>
+      <c r="G1096" t="inlineStr"/>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Adani Power B PRICE 207.70 TARGET 212 STOP LOSS 204</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:17:00</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>268.6</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1097" t="inlineStr"/>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Power Grid BUY PRICE 267.50 TARGET 272 STOP LOSS 265</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>375</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>346</v>
+      </c>
+      <c r="G1098" t="inlineStr"/>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Federal Bank Fut
+BUY
+PRICE ▶ 354.65
+TARGET ▶ 375
+STOP LOSS ▶ 346</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>JSWENERGY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>544.85</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>550</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1099" t="inlineStr"/>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>JSWENERGY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>544.85</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>557</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>530</v>
+      </c>
+      <c r="G1100" t="inlineStr"/>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>361</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>347</v>
+      </c>
+      <c r="G1101" t="inlineStr"/>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Federal Bank Futures
+UY
+PRICE ▶ 354.5
+TARGET ▶ 358, 361, 365
+STOP LOSS ▶ 347</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>365</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>347</v>
+      </c>
+      <c r="G1102" t="inlineStr"/>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Federal Bank Futures
+UY
+PRICE ▶ 354.5
+TARGET ▶ 358, 361, 365
+STOP LOSS ▶ 347</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>ZENSARTECH</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>474</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>455</v>
+      </c>
+      <c r="G1103" t="inlineStr"/>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>MY CHOICE ZENSAR TECH B 474 455</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>1926</v>
+      </c>
+      <c r="G1104" t="inlineStr"/>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>INVESTMENT GODFREY PHILLIPS B 2230 1926</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>269.3</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>273</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1105" t="inlineStr"/>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT POWER GRID B 273 264</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>UPL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1106" t="n">
+        <v>579.9</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>593</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>573</v>
+      </c>
+      <c r="G1106" t="inlineStr"/>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>FUTURE UPL FUT B 593 573</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1107" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>1857</v>
+      </c>
+      <c r="G1107" t="inlineStr"/>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>TECHNO PHOENIX MILLS B 2060 1857</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1108" t="n">
+        <v>422</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>460</v>
+      </c>
+      <c r="G1108" t="inlineStr"/>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>INVESTMENT COAL INDIA B 460 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1109" t="n">
+        <v>425</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>432</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>418</v>
+      </c>
+      <c r="G1109" t="inlineStr"/>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>MY CHOICE KOTAK BANK B 432 418</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1110" t="n">
+        <v>2173.8</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>2215</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G1110" t="inlineStr"/>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>MY CHOICE KIRLOSKAR OIL ENGINES B 2215 2150</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>OLAELEC</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1111" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>41</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1111" t="inlineStr"/>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>CASH OLA ELECTRIC B 41 37</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1112" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>361</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>349</v>
+      </c>
+      <c r="G1112" t="inlineStr"/>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>FUTURE FEDERAL BANK FUT B 361 349</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1113" t="n">
+        <v>1818</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>1852</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>1794</v>
+      </c>
+      <c r="G1113" t="inlineStr"/>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>MY CHOICE Lloyds Metals &amp; Energy Ltd खरीदें PRICE 1813.00 TARGET 1852 STOP LOSS 1794</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>FSL</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1114" t="n">
+        <v>270.15</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>279</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>266.5</v>
+      </c>
+      <c r="G1114" t="inlineStr"/>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Firstsource खरीदें PRICE 270.40 TARGET 279 STOP LOSS 266.5</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>KIRLOSENG</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1115" t="n">
+        <v>2173.8</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>2215</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G1115" t="inlineStr"/>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Kirloskar Oil खरीदें PRICE 2160.90 TARGET 2215 STOP LOSS 2150</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1116" t="n">
+        <v>1438.3</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G1116" t="inlineStr"/>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>MY CHOICE ICICI Bank खरीदें PRICE 1426.50 TARGET 1454 STOP LOSS 1411</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1117" t="n">
+        <v>425</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>432</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>418</v>
+      </c>
+      <c r="G1117" t="inlineStr"/>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>Kotak Bank खरीदें PRICE 423.50 TARGET 432 STOP LOSS 418</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:17:00</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1118" t="n">
+        <v>268.6</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>273</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>264</v>
+      </c>
+      <c r="G1118" t="inlineStr"/>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>Power Grid खरीदें PRICE 266.80 TARGET 273 STOP LOSS 264</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1119" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>460</v>
+      </c>
+      <c r="G1119" t="inlineStr"/>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK Coal India खरीदें PRICE 417.85 TARGET 460 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1120" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>2230</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>1926</v>
+      </c>
+      <c r="G1120" t="inlineStr"/>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK Godfrey Phillips खरीदें PRICE 2025.40 TARGET 2230 STOP LOSS 1926</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1121" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>371</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1121" t="inlineStr"/>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Tata Power खरीदें PRICE 364.00 TARGET 371 STOP LOSS 360</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1122" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>1857</v>
+      </c>
+      <c r="G1122" t="inlineStr"/>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>TECHNO PICK Phoenix Mills खरीदें PRICE 1920.10 TARGET 2060 STOP LOSS 1857</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1123" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>361</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>349</v>
+      </c>
+      <c r="G1123" t="inlineStr"/>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+Federal Bank Fut
+खरीदें
+PRICE 354.65
+TARGET 361
+STOP LOSS 349</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1124" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>1470</v>
+      </c>
+      <c r="G1124" t="inlineStr"/>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>STOCKS IN NEWS
+ICICI Bank 1426.50 -0.80%
+ICICI Pru का 2 % हिस्सा ₹ 1470 Cr में खरीदा</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1125" t="n">
+        <v>1864.9</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G1125" t="inlineStr"/>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1126" t="n">
+        <v>1864.9</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G1126" t="inlineStr"/>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1127" t="n">
+        <v>1681.8</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1127" t="inlineStr"/>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1672.70 +25.20
+OVERWEIGHT
+लक्ष्य ₹2000</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1128" t="n">
+        <v>419.1</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>465</v>
+      </c>
+      <c r="G1128" t="inlineStr"/>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALL
+Coal India
+417.85 +4.05%
+BUY
+लक्ष्य ₹430 से बढ़ाकर ₹465</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1129" t="n">
+        <v>935</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G1129" t="inlineStr"/>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>LUNG-TERM CALL Shilpa Medicare BUY TARGET 1200 DURATION 12 महीने Shilpa Medicare 928.55 4.37%</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-09-03 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>HAPPSTMNDS</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1130" t="n">
+        <v>356</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1130" t="inlineStr"/>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>सुदीप बंदोपाध्याय की पसंद Happiest Minds BUY TARGET 550 DURATION 12 महीने Happiest Minds 354.85 7.85</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1002"/>
+  <autoFilter ref="A1:J1130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1237</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1130"/>
+  <dimension ref="A1:J1237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -43197,7 +43197,6 @@
       <c r="F1003" t="n">
         <v>80</v>
       </c>
-      <c r="G1003" t="inlineStr"/>
       <c r="H1003" t="inlineStr">
         <is>
           <t>अक्षय भागवत की राय
@@ -43244,7 +43243,6 @@
       <c r="F1004" t="n">
         <v>80</v>
       </c>
-      <c r="G1004" t="inlineStr"/>
       <c r="H1004" t="inlineStr">
         <is>
           <t>अक्षय भागवत की राय
@@ -43291,7 +43289,6 @@
       <c r="F1005" t="n">
         <v>140</v>
       </c>
-      <c r="G1005" t="inlineStr"/>
       <c r="H1005" t="inlineStr">
         <is>
           <t>TRADING CALL Bank of India खरीदें PRICE 144.78 TARGET 152 STOP LOSS 140</t>
@@ -43333,7 +43330,6 @@
       <c r="F1006" t="n">
         <v>1160</v>
       </c>
-      <c r="G1006" t="inlineStr"/>
       <c r="H1006" t="inlineStr">
         <is>
           <t>TRADING CALL Bharat Dynamics खरीदें PRICE 1255.90 TARGET 1430 STOP LOSS 1160</t>
@@ -43366,7 +43362,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1007" t="inlineStr"/>
       <c r="E1007" t="n">
         <v>65</v>
       </c>
@@ -43410,14 +43405,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1008" t="inlineStr"/>
       <c r="E1008" t="n">
         <v>65</v>
       </c>
       <c r="F1008" t="n">
         <v>30</v>
       </c>
-      <c r="G1008" t="inlineStr"/>
       <c r="H1008" t="inlineStr">
         <is>
           <t>निफ्टी 23800 की पुट @ 40-45 खरीदें STOP LOSS 30 TARGET 65</t>
@@ -43499,7 +43492,6 @@
       <c r="E1010" t="n">
         <v>3250</v>
       </c>
-      <c r="G1010" t="inlineStr"/>
       <c r="H1010" t="inlineStr">
         <is>
           <t>Welspun Corp 2619.00 ▲ 3.78% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
@@ -43584,7 +43576,6 @@
       <c r="F1012" t="n">
         <v>1865</v>
       </c>
-      <c r="G1012" t="inlineStr"/>
       <c r="H1012" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय Oberoi Realty Fut खरीदें PRICE 1899.60 TARGET 1960/2000 STOP LOSS 1865</t>
@@ -43626,7 +43617,6 @@
       <c r="F1013" t="n">
         <v>1865</v>
       </c>
-      <c r="G1013" t="inlineStr"/>
       <c r="H1013" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय Oberoi Realty Fut खरीदें PRICE 1899.60 TARGET 1960/2000 STOP LOSS 1865</t>
@@ -43665,7 +43655,6 @@
       <c r="E1014" t="n">
         <v>1960</v>
       </c>
-      <c r="G1014" t="inlineStr"/>
       <c r="H1014" t="inlineStr">
         <is>
           <t>Oberoi Realty Fut खरीदें PRICE 1900.00 TARGET 1960/2000 STOP LOSS --</t>
@@ -43704,7 +43693,6 @@
       <c r="E1015" t="n">
         <v>2000</v>
       </c>
-      <c r="G1015" t="inlineStr"/>
       <c r="H1015" t="inlineStr">
         <is>
           <t>Oberoi Realty Fut खरीदें PRICE 1900.00 TARGET 1960/2000 STOP LOSS --</t>
@@ -43743,7 +43731,6 @@
       <c r="E1016" t="n">
         <v>1960</v>
       </c>
-      <c r="G1016" t="inlineStr"/>
       <c r="H1016" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -43787,7 +43774,6 @@
       <c r="E1017" t="n">
         <v>2000</v>
       </c>
-      <c r="G1017" t="inlineStr"/>
       <c r="H1017" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -43831,7 +43817,6 @@
       <c r="E1018" t="n">
         <v>1760</v>
       </c>
-      <c r="G1018" t="inlineStr"/>
       <c r="H1018" t="inlineStr">
         <is>
           <t>SHORT MIDCAP STOCKS
@@ -43877,7 +43862,6 @@
       <c r="F1019" t="n">
         <v>699</v>
       </c>
-      <c r="G1019" t="inlineStr"/>
       <c r="H1019" t="inlineStr">
         <is>
           <t>तेजस शाह की राय Graphite India खरीदें STOP LOSS 699 TARGET 770/800 DURATION -- Graphite India 733.25 0.92%</t>
@@ -43919,7 +43903,6 @@
       <c r="F1020" t="n">
         <v>699</v>
       </c>
-      <c r="G1020" t="inlineStr"/>
       <c r="H1020" t="inlineStr">
         <is>
           <t>तेजस शाह की राय Graphite India खरीदें STOP LOSS 699 TARGET 770/800 DURATION -- Graphite India 733.25 0.92%</t>
@@ -43961,7 +43944,6 @@
       <c r="F1021" t="n">
         <v>211</v>
       </c>
-      <c r="G1021" t="inlineStr"/>
       <c r="H1021" t="inlineStr">
         <is>
           <t>तेजस शाह की राय
@@ -44007,7 +43989,6 @@
       <c r="F1022" t="n">
         <v>211</v>
       </c>
-      <c r="G1022" t="inlineStr"/>
       <c r="H1022" t="inlineStr">
         <is>
           <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 228.69 0.48</t>
@@ -44049,7 +44030,6 @@
       <c r="F1023" t="n">
         <v>600</v>
       </c>
-      <c r="G1023" t="inlineStr"/>
       <c r="H1023" t="inlineStr">
         <is>
           <t>सदाबहार सेठी साब
@@ -44096,7 +44076,6 @@
       <c r="F1024" t="n">
         <v>873</v>
       </c>
-      <c r="G1024" t="inlineStr"/>
       <c r="H1024" t="inlineStr">
         <is>
           <t>Indian Bank 896.55 BUY TGT 910 SL 873</t>
@@ -44135,7 +44114,6 @@
       <c r="E1025" t="n">
         <v>3190</v>
       </c>
-      <c r="G1025" t="inlineStr"/>
       <c r="H1025" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -44182,7 +44160,6 @@
       <c r="F1026" t="n">
         <v>530</v>
       </c>
-      <c r="G1026" t="inlineStr"/>
       <c r="H1026" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट HDFC Life 536.35 3.35 BUY TGT 545 SL 530</t>
@@ -44224,7 +44201,6 @@
       <c r="F1027" t="n">
         <v>1861</v>
       </c>
-      <c r="G1027" t="inlineStr"/>
       <c r="H1027" t="inlineStr">
         <is>
           <t>BTSTT BUY TODAY Oberoi Realty Fut 1897.20 1.16% BUY TGT 2000 SL 1861</t>
@@ -44266,7 +44242,6 @@
       <c r="F1028" t="n">
         <v>81</v>
       </c>
-      <c r="G1028" t="inlineStr"/>
       <c r="H1028" t="inlineStr">
         <is>
           <t>BTSTT BUY TODAY Bank of Maha Fut 87.10 4.66 BUY TGT 90 SL 81</t>
@@ -44299,11 +44274,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1029" t="inlineStr"/>
       <c r="E1029" t="n">
         <v>2005</v>
       </c>
-      <c r="G1029" t="inlineStr"/>
       <c r="H1029" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर BEML 2085.30 2.60% BUY TARGET HIT 2005</t>
@@ -44336,14 +44309,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1030" t="inlineStr"/>
       <c r="E1030" t="n">
         <v>2070</v>
       </c>
       <c r="F1030" t="n">
         <v>2005</v>
       </c>
-      <c r="G1030" t="inlineStr"/>
       <c r="H1030" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -44390,7 +44361,6 @@
       <c r="F1031" t="n">
         <v>520</v>
       </c>
-      <c r="G1031" t="inlineStr"/>
       <c r="H1031" t="inlineStr">
         <is>
           <t>1 की कमाई Indegene खरीदें PRICE 602.00 TARGET 800 STOP LOSS 520</t>
@@ -44432,7 +44402,6 @@
       <c r="F1032" t="n">
         <v>520</v>
       </c>
-      <c r="G1032" t="inlineStr"/>
       <c r="H1032" t="inlineStr">
         <is>
           <t>Indegene खरीदें PRICE 601.95 TARGET 800 STOP LOSS 520</t>
@@ -44474,7 +44443,6 @@
       <c r="F1033" t="n">
         <v>211</v>
       </c>
-      <c r="G1033" t="inlineStr"/>
       <c r="H1033" t="inlineStr">
         <is>
           <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 229.82 ▲ 0.71%</t>
@@ -44516,7 +44484,6 @@
       <c r="F1034" t="n">
         <v>211</v>
       </c>
-      <c r="G1034" t="inlineStr"/>
       <c r="H1034" t="inlineStr">
         <is>
           <t>तेजस शाह की राय Sapphire Foods खरीदें STOP LOSS 211 TARGET 245/262 DURATION -- Sapphire Foods 229.82 ▲ 0.71%</t>
@@ -44598,7 +44565,6 @@
       <c r="E1036" t="n">
         <v>3250</v>
       </c>
-      <c r="G1036" t="inlineStr"/>
       <c r="H1036" t="inlineStr">
         <is>
           <t>BUZZING STOCK Welspun Corp 2600.00 ▲ 3.03% कवरेज की शुरुआत के साथ 'BUY' रेटिंग, लक्ष्य ₹3250</t>
@@ -44640,7 +44606,6 @@
       <c r="F1037" t="n">
         <v>600</v>
       </c>
-      <c r="G1037" t="inlineStr"/>
       <c r="H1037" t="inlineStr">
         <is>
           <t>सदाबहार सेठी सा'ब
@@ -44684,7 +44649,6 @@
       <c r="E1038" t="n">
         <v>650</v>
       </c>
-      <c r="G1038" t="inlineStr"/>
       <c r="H1038" t="inlineStr">
         <is>
           <t>Insecticides Ind 624.00 11.40 BUY TGT 650</t>
@@ -44723,7 +44687,6 @@
       <c r="E1039" t="n">
         <v>3190</v>
       </c>
-      <c r="G1039" t="inlineStr"/>
       <c r="H1039" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -44770,7 +44733,6 @@
       <c r="F1040" t="n">
         <v>530</v>
       </c>
-      <c r="G1040" t="inlineStr"/>
       <c r="H1040" t="inlineStr">
         <is>
           <t>HDFC Life 538.50 1.03% BUY TGT 545 SL 530</t>
@@ -44812,7 +44774,6 @@
       <c r="F1041" t="n">
         <v>2945</v>
       </c>
-      <c r="G1041" t="inlineStr"/>
       <c r="H1041" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -44859,7 +44820,6 @@
       <c r="F1042" t="n">
         <v>2945</v>
       </c>
-      <c r="G1042" t="inlineStr"/>
       <c r="H1042" t="inlineStr">
         <is>
           <t>Muthoot Finance 2970.90 33.20 BUY TGT 3010 SL 2945</t>
@@ -44901,7 +44861,6 @@
       <c r="F1043" t="n">
         <v>1015</v>
       </c>
-      <c r="G1043" t="inlineStr"/>
       <c r="H1043" t="inlineStr">
         <is>
           <t>SBI 1029.60 8.70 BUY TGT 1050 SL 1015</t>
@@ -44943,7 +44902,6 @@
       <c r="F1044" t="n">
         <v>1861</v>
       </c>
-      <c r="G1044" t="inlineStr"/>
       <c r="H1044" t="inlineStr">
         <is>
           <t>BTSTT BUY TODAY Oberoi Realty Fut 1917.60 42.20 BUY TGT 2000 SL 1861</t>
@@ -44985,7 +44943,6 @@
       <c r="F1045" t="n">
         <v>149</v>
       </c>
-      <c r="G1045" t="inlineStr"/>
       <c r="H1045" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 167.58 ▲ 1.91% MARKET MENTORS रामदेव अग्रवाल चेयरमैन &amp; को-फाउंडर MOFSL 11 AM</t>
@@ -45027,7 +44984,6 @@
       <c r="F1046" t="n">
         <v>149</v>
       </c>
-      <c r="G1046" t="inlineStr"/>
       <c r="H1046" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 167.58 ▲ 1.91% MARKET MENTORS रामदेव अग्रवाल चेयरमैन &amp; को-फाउंडर MOFSL 11 AM</t>
@@ -45060,14 +45016,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1047" t="inlineStr"/>
       <c r="E1047" t="n">
         <v>200</v>
       </c>
       <c r="F1047" t="n">
         <v>149</v>
       </c>
-      <c r="G1047" t="inlineStr"/>
       <c r="H1047" t="inlineStr">
         <is>
           <t>Gujarat Pipavav खरीदें STOP LOSS 149 TARGET 185/200 DURATION -- Gujarat Pipavav 147.68</t>
@@ -45244,7 +45198,6 @@
       <c r="F1051" t="n">
         <v>45</v>
       </c>
-      <c r="G1051" t="inlineStr"/>
       <c r="H1051" t="inlineStr">
         <is>
           <t>South Indian Bank खरीदें PRICE 47.58 TARGET 51/53 STOP LOSS 45</t>
@@ -45286,7 +45239,6 @@
       <c r="F1052" t="n">
         <v>45</v>
       </c>
-      <c r="G1052" t="inlineStr"/>
       <c r="H1052" t="inlineStr">
         <is>
           <t>South Indian Bank खरीदें PRICE 47.58 TARGET 51/53 STOP LOSS 45</t>
@@ -45328,7 +45280,6 @@
       <c r="F1053" t="n">
         <v>879</v>
       </c>
-      <c r="G1053" t="inlineStr"/>
       <c r="H1053" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Indian Bank 894.55 1.79% BUY TGT 910 SL 879</t>
@@ -45410,7 +45361,6 @@
       <c r="E1055" t="n">
         <v>3190</v>
       </c>
-      <c r="G1055" t="inlineStr"/>
       <c r="H1055" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -45457,7 +45407,6 @@
       <c r="F1056" t="n">
         <v>530</v>
       </c>
-      <c r="G1056" t="inlineStr"/>
       <c r="H1056" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट HDFC Life 539.30 6.30 BUY TGT 545 SL 530</t>
@@ -45499,7 +45448,6 @@
       <c r="F1057" t="n">
         <v>2945</v>
       </c>
-      <c r="G1057" t="inlineStr"/>
       <c r="H1057" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -45546,7 +45494,6 @@
       <c r="F1058" t="n">
         <v>1015</v>
       </c>
-      <c r="G1058" t="inlineStr"/>
       <c r="H1058" t="inlineStr">
         <is>
           <t>SBI 1032.80 11.90 BUY TGT 1050 SL 1015</t>
@@ -45588,7 +45535,6 @@
       <c r="F1059" t="n">
         <v>1015</v>
       </c>
-      <c r="G1059" t="inlineStr"/>
       <c r="H1059" t="inlineStr">
         <is>
           <t>SBI 1033.00 12.10 BUY TGT 1050 SL 1015 Thu 03 Sep'26</t>
@@ -45630,7 +45576,6 @@
       <c r="F1060" t="n">
         <v>81</v>
       </c>
-      <c r="G1060" t="inlineStr"/>
       <c r="H1060" t="inlineStr">
         <is>
           <t>BTSTT BUY TODAY Bank of Maha Fut 86.54 4.10 BUY TGT 90 SL 81</t>
@@ -45669,7 +45614,6 @@
       <c r="E1061" t="n">
         <v>7478</v>
       </c>
-      <c r="G1061" t="inlineStr"/>
       <c r="H1061" t="inlineStr">
         <is>
           <t>BTSTT ABB Fut 7450.00 BUY TGT 7478 TARGET HIT</t>
@@ -45708,7 +45652,6 @@
       <c r="E1062" t="n">
         <v>7540</v>
       </c>
-      <c r="G1062" t="inlineStr"/>
       <c r="H1062" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर
@@ -45755,7 +45698,6 @@
       <c r="F1063" t="n">
         <v>7340</v>
       </c>
-      <c r="G1063" t="inlineStr"/>
       <c r="H1063" t="inlineStr">
         <is>
           <t>BTSTT BUY TODAY ABB Fut 7450.00 45.50 BUY TGT 7470 SL 7340</t>
@@ -45788,14 +45730,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1064" t="inlineStr"/>
       <c r="E1064" t="n">
         <v>150</v>
       </c>
       <c r="F1064" t="n">
         <v>125</v>
       </c>
-      <c r="G1064" t="inlineStr"/>
       <c r="H1064" t="inlineStr">
         <is>
           <t>Godrej Cons: FY27 की गाइडेंस बरकरार अगले 3 तिमाही में ₹125-150 Cr का इन्वेंट्री करेक्शन करेगी Godrej Cons 870.20 ▼ 34.80</t>
@@ -45837,7 +45777,6 @@
       <c r="F1065" t="n">
         <v>1861</v>
       </c>
-      <c r="G1065" t="inlineStr"/>
       <c r="H1065" t="inlineStr">
         <is>
           <t>BTSTT CALL Oberoi Realty Fut खरीदें PRICE 1922.00 TARGET 2000 STOP LOSS 1861</t>
@@ -45879,7 +45818,6 @@
       <c r="F1066" t="n">
         <v>1861</v>
       </c>
-      <c r="G1066" t="inlineStr"/>
       <c r="H1066" t="inlineStr">
         <is>
           <t>BTSTT CALL Oberoi Realty Fut खरीदें PRICE 1920.50 TARGET 2000 STOP LOSS 1861</t>
@@ -45918,7 +45856,6 @@
       <c r="E1067" t="n">
         <v>560</v>
       </c>
-      <c r="G1067" t="inlineStr"/>
       <c r="H1067" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 398.05 2.41% BUY TARGET HIT 560</t>
@@ -45957,7 +45894,6 @@
       <c r="E1068" t="n">
         <v>405</v>
       </c>
-      <c r="G1068" t="inlineStr"/>
       <c r="H1068" t="inlineStr">
         <is>
           <t>INDIAN HOME PIPE 398.05 BUY TGT 405</t>
@@ -46045,7 +45981,6 @@
       <c r="F1070" t="n">
         <v>600</v>
       </c>
-      <c r="G1070" t="inlineStr"/>
       <c r="H1070" t="inlineStr">
         <is>
           <t>विकास सेठ की राय INSECTICIDES IND @ 615 खरीदें STOP LOSS 600 TARGET 650 Insecticides Ind 630.00 2.84%</t>
@@ -46087,7 +46022,6 @@
       <c r="F1071" t="n">
         <v>879</v>
       </c>
-      <c r="G1071" t="inlineStr"/>
       <c r="H1071" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -46176,11 +46110,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1073" t="inlineStr"/>
       <c r="E1073" t="n">
         <v>360</v>
       </c>
-      <c r="G1073" t="inlineStr"/>
       <c r="H1073" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 395.00 1.62% BUY TARGET HIT 360</t>
@@ -46222,7 +46154,6 @@
       <c r="F1074" t="n">
         <v>360</v>
       </c>
-      <c r="G1074" t="inlineStr"/>
       <c r="H1074" t="inlineStr">
         <is>
           <t>Indian Hume Pipe ▲ 396.85 8.15 BUY TGT 405 SL 360</t>
@@ -46261,7 +46192,6 @@
       <c r="E1075" t="n">
         <v>3190</v>
       </c>
-      <c r="G1075" t="inlineStr"/>
       <c r="H1075" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -46305,7 +46235,6 @@
       <c r="E1076" t="n">
         <v>3190</v>
       </c>
-      <c r="G1076" t="inlineStr"/>
       <c r="H1076" t="inlineStr">
         <is>
           <t>संदीप जैन की राय
@@ -46349,7 +46278,6 @@
       <c r="E1077" t="n">
         <v>405</v>
       </c>
-      <c r="G1077" t="inlineStr"/>
       <c r="H1077" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 401.15 BUY TGT 405 TARGET HIT</t>
@@ -46391,7 +46319,6 @@
       <c r="F1078" t="n">
         <v>360</v>
       </c>
-      <c r="G1078" t="inlineStr"/>
       <c r="H1078" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 401.15 12.45 BUY TGT 405 SL 360</t>
@@ -46424,11 +46351,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1079" t="inlineStr"/>
       <c r="E1079" t="n">
         <v>189.04</v>
       </c>
-      <c r="G1079" t="inlineStr"/>
       <c r="H1079" t="inlineStr">
         <is>
           <t>Union Bank 189.04 INVESTMENT PICK 106.00 28/01/2025 RECO PRICE RETURN TILL NOW 83.04 78.34%</t>
@@ -46467,7 +46392,6 @@
       <c r="E1080" t="n">
         <v>560</v>
       </c>
-      <c r="G1080" t="inlineStr"/>
       <c r="H1080" t="inlineStr">
         <is>
           <t>Indian Hume Pipe 400.00 11.30 BUY TARGET HIT 560</t>
@@ -46509,7 +46433,6 @@
       <c r="F1081" t="n">
         <v>530</v>
       </c>
-      <c r="G1081" t="inlineStr"/>
       <c r="H1081" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
@@ -46551,7 +46474,6 @@
       <c r="F1082" t="n">
         <v>530</v>
       </c>
-      <c r="G1082" t="inlineStr"/>
       <c r="H1082" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय HDFC Life खरीदें PRICE 537.10 TARGET 545/555 STOP LOSS 530</t>
@@ -46593,7 +46515,6 @@
       <c r="F1083" t="n">
         <v>2945</v>
       </c>
-      <c r="G1083" t="inlineStr"/>
       <c r="H1083" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Muthoot Finance खरीदें PRICE 2969.00 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -46635,7 +46556,6 @@
       <c r="F1084" t="n">
         <v>2945</v>
       </c>
-      <c r="G1084" t="inlineStr"/>
       <c r="H1084" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -46677,7 +46597,6 @@
       <c r="F1085" t="n">
         <v>2945</v>
       </c>
-      <c r="G1085" t="inlineStr"/>
       <c r="H1085" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शरीर Muthoot Finance खरीदें PRICE 2968.40 TARGET 3010/3030 STOP LOSS 2945</t>
@@ -46710,7 +46629,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1086" t="inlineStr"/>
       <c r="E1086" t="n">
         <v>90</v>
       </c>
@@ -46768,7 +46686,6 @@
       <c r="F1087" t="n">
         <v>1015</v>
       </c>
-      <c r="G1087" t="inlineStr"/>
       <c r="H1087" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -46815,7 +46732,6 @@
       <c r="F1088" t="n">
         <v>1015</v>
       </c>
-      <c r="G1088" t="inlineStr"/>
       <c r="H1088" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -46859,7 +46775,6 @@
       <c r="E1089" t="n">
         <v>3250</v>
       </c>
-      <c r="G1089" t="inlineStr"/>
       <c r="H1089" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -46905,7 +46820,6 @@
       <c r="F1090" t="n">
         <v>385</v>
       </c>
-      <c r="G1090" t="inlineStr"/>
       <c r="H1090" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
@@ -46947,7 +46861,6 @@
       <c r="F1091" t="n">
         <v>385</v>
       </c>
-      <c r="G1091" t="inlineStr"/>
       <c r="H1091" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह RBL Bank Futures BUY PRICE 392 TARGET 396, 400, 405 STOP LOSS 385</t>
@@ -46989,7 +46902,6 @@
       <c r="F1092" t="n">
         <v>266.5</v>
       </c>
-      <c r="G1092" t="inlineStr"/>
       <c r="H1092" t="inlineStr">
         <is>
           <t>MY CHOICE FIRSTSOURCE B 279 266.5</t>
@@ -47031,7 +46943,6 @@
       <c r="F1093" t="n">
         <v>1411</v>
       </c>
-      <c r="G1093" t="inlineStr"/>
       <c r="H1093" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI BANK B 1454 1411</t>
@@ -47073,7 +46984,6 @@
       <c r="F1094" t="n">
         <v>182</v>
       </c>
-      <c r="G1094" t="inlineStr"/>
       <c r="H1094" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
@@ -47115,7 +47025,6 @@
       <c r="F1095" t="n">
         <v>182</v>
       </c>
-      <c r="G1095" t="inlineStr"/>
       <c r="H1095" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Union Bank BUY PRICE 186.86 TARGET 192/195 STOP LOSS 182</t>
@@ -47157,7 +47066,6 @@
       <c r="F1096" t="n">
         <v>204</v>
       </c>
-      <c r="G1096" t="inlineStr"/>
       <c r="H1096" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Adani Power B PRICE 207.70 TARGET 212 STOP LOSS 204</t>
@@ -47199,7 +47107,6 @@
       <c r="F1097" t="n">
         <v>265</v>
       </c>
-      <c r="G1097" t="inlineStr"/>
       <c r="H1097" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Power Grid BUY PRICE 267.50 TARGET 272 STOP LOSS 265</t>
@@ -47241,7 +47148,6 @@
       <c r="F1098" t="n">
         <v>346</v>
       </c>
-      <c r="G1098" t="inlineStr"/>
       <c r="H1098" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -47288,7 +47194,6 @@
       <c r="F1099" t="n">
         <v>530</v>
       </c>
-      <c r="G1099" t="inlineStr"/>
       <c r="H1099" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
@@ -47330,7 +47235,6 @@
       <c r="F1100" t="n">
         <v>530</v>
       </c>
-      <c r="G1100" t="inlineStr"/>
       <c r="H1100" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह JSW Energy Futures BUY PRICE 541 TARGET 545, 550, 557 STOP LOSS 530</t>
@@ -47372,7 +47276,6 @@
       <c r="F1101" t="n">
         <v>347</v>
       </c>
-      <c r="G1101" t="inlineStr"/>
       <c r="H1101" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -47419,7 +47322,6 @@
       <c r="F1102" t="n">
         <v>347</v>
       </c>
-      <c r="G1102" t="inlineStr"/>
       <c r="H1102" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -47466,7 +47368,6 @@
       <c r="F1103" t="n">
         <v>455</v>
       </c>
-      <c r="G1103" t="inlineStr"/>
       <c r="H1103" t="inlineStr">
         <is>
           <t>MY CHOICE ZENSAR TECH B 474 455</t>
@@ -47508,7 +47409,6 @@
       <c r="F1104" t="n">
         <v>1926</v>
       </c>
-      <c r="G1104" t="inlineStr"/>
       <c r="H1104" t="inlineStr">
         <is>
           <t>INVESTMENT GODFREY PHILLIPS B 2230 1926</t>
@@ -47550,7 +47450,6 @@
       <c r="F1105" t="n">
         <v>264</v>
       </c>
-      <c r="G1105" t="inlineStr"/>
       <c r="H1105" t="inlineStr">
         <is>
           <t>NEWS IMPACT POWER GRID B 273 264</t>
@@ -47592,7 +47491,6 @@
       <c r="F1106" t="n">
         <v>573</v>
       </c>
-      <c r="G1106" t="inlineStr"/>
       <c r="H1106" t="inlineStr">
         <is>
           <t>FUTURE UPL FUT B 593 573</t>
@@ -47634,7 +47532,6 @@
       <c r="F1107" t="n">
         <v>1857</v>
       </c>
-      <c r="G1107" t="inlineStr"/>
       <c r="H1107" t="inlineStr">
         <is>
           <t>TECHNO PHOENIX MILLS B 2060 1857</t>
@@ -47673,7 +47570,6 @@
       <c r="E1108" t="n">
         <v>460</v>
       </c>
-      <c r="G1108" t="inlineStr"/>
       <c r="H1108" t="inlineStr">
         <is>
           <t>INVESTMENT COAL INDIA B 460 12 MONTH</t>
@@ -47715,7 +47611,6 @@
       <c r="F1109" t="n">
         <v>418</v>
       </c>
-      <c r="G1109" t="inlineStr"/>
       <c r="H1109" t="inlineStr">
         <is>
           <t>MY CHOICE KOTAK BANK B 432 418</t>
@@ -47757,7 +47652,6 @@
       <c r="F1110" t="n">
         <v>2150</v>
       </c>
-      <c r="G1110" t="inlineStr"/>
       <c r="H1110" t="inlineStr">
         <is>
           <t>MY CHOICE KIRLOSKAR OIL ENGINES B 2215 2150</t>
@@ -47799,7 +47693,6 @@
       <c r="F1111" t="n">
         <v>37</v>
       </c>
-      <c r="G1111" t="inlineStr"/>
       <c r="H1111" t="inlineStr">
         <is>
           <t>CASH OLA ELECTRIC B 41 37</t>
@@ -47841,7 +47734,6 @@
       <c r="F1112" t="n">
         <v>349</v>
       </c>
-      <c r="G1112" t="inlineStr"/>
       <c r="H1112" t="inlineStr">
         <is>
           <t>FUTURE FEDERAL BANK FUT B 361 349</t>
@@ -47883,7 +47775,6 @@
       <c r="F1113" t="n">
         <v>1794</v>
       </c>
-      <c r="G1113" t="inlineStr"/>
       <c r="H1113" t="inlineStr">
         <is>
           <t>MY CHOICE Lloyds Metals &amp; Energy Ltd खरीदें PRICE 1813.00 TARGET 1852 STOP LOSS 1794</t>
@@ -47925,7 +47816,6 @@
       <c r="F1114" t="n">
         <v>266.5</v>
       </c>
-      <c r="G1114" t="inlineStr"/>
       <c r="H1114" t="inlineStr">
         <is>
           <t>अंश के शेयर Firstsource खरीदें PRICE 270.40 TARGET 279 STOP LOSS 266.5</t>
@@ -47967,7 +47857,6 @@
       <c r="F1115" t="n">
         <v>2150</v>
       </c>
-      <c r="G1115" t="inlineStr"/>
       <c r="H1115" t="inlineStr">
         <is>
           <t>पूजा के शेयर Kirloskar Oil खरीदें PRICE 2160.90 TARGET 2215 STOP LOSS 2150</t>
@@ -48009,7 +47898,6 @@
       <c r="F1116" t="n">
         <v>1411</v>
       </c>
-      <c r="G1116" t="inlineStr"/>
       <c r="H1116" t="inlineStr">
         <is>
           <t>MY CHOICE ICICI Bank खरीदें PRICE 1426.50 TARGET 1454 STOP LOSS 1411</t>
@@ -48051,7 +47939,6 @@
       <c r="F1117" t="n">
         <v>418</v>
       </c>
-      <c r="G1117" t="inlineStr"/>
       <c r="H1117" t="inlineStr">
         <is>
           <t>Kotak Bank खरीदें PRICE 423.50 TARGET 432 STOP LOSS 418</t>
@@ -48093,7 +47980,6 @@
       <c r="F1118" t="n">
         <v>264</v>
       </c>
-      <c r="G1118" t="inlineStr"/>
       <c r="H1118" t="inlineStr">
         <is>
           <t>Power Grid खरीदें PRICE 266.80 TARGET 273 STOP LOSS 264</t>
@@ -48132,7 +48018,6 @@
       <c r="E1119" t="n">
         <v>460</v>
       </c>
-      <c r="G1119" t="inlineStr"/>
       <c r="H1119" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK Coal India खरीदें PRICE 417.85 TARGET 460 DURATION 12 महीने</t>
@@ -48174,7 +48059,6 @@
       <c r="F1120" t="n">
         <v>1926</v>
       </c>
-      <c r="G1120" t="inlineStr"/>
       <c r="H1120" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK Godfrey Phillips खरीदें PRICE 2025.40 TARGET 2230 STOP LOSS 1926</t>
@@ -48216,7 +48100,6 @@
       <c r="F1121" t="n">
         <v>360</v>
       </c>
-      <c r="G1121" t="inlineStr"/>
       <c r="H1121" t="inlineStr">
         <is>
           <t>पूजा के शेयर Tata Power खरीदें PRICE 364.00 TARGET 371 STOP LOSS 360</t>
@@ -48258,7 +48141,6 @@
       <c r="F1122" t="n">
         <v>1857</v>
       </c>
-      <c r="G1122" t="inlineStr"/>
       <c r="H1122" t="inlineStr">
         <is>
           <t>TECHNO PICK Phoenix Mills खरीदें PRICE 1920.10 TARGET 2060 STOP LOSS 1857</t>
@@ -48300,7 +48182,6 @@
       <c r="F1123" t="n">
         <v>349</v>
       </c>
-      <c r="G1123" t="inlineStr"/>
       <c r="H1123" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -48344,7 +48225,6 @@
       <c r="E1124" t="n">
         <v>1470</v>
       </c>
-      <c r="G1124" t="inlineStr"/>
       <c r="H1124" t="inlineStr">
         <is>
           <t>STOCKS IN NEWS
@@ -48388,7 +48268,6 @@
       <c r="F1125" t="n">
         <v>1835</v>
       </c>
-      <c r="G1125" t="inlineStr"/>
       <c r="H1125" t="inlineStr">
         <is>
           <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
@@ -48430,7 +48309,6 @@
       <c r="F1126" t="n">
         <v>1835</v>
       </c>
-      <c r="G1126" t="inlineStr"/>
       <c r="H1126" t="inlineStr">
         <is>
           <t>TRADING CALL Laurus Labs खरीदें PRICE 1864.00 TARGET 1890/1910 STOP LOSS 1835</t>
@@ -48469,7 +48347,6 @@
       <c r="E1127" t="n">
         <v>2000</v>
       </c>
-      <c r="G1127" t="inlineStr"/>
       <c r="H1127" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -48512,7 +48389,6 @@
       <c r="E1128" t="n">
         <v>465</v>
       </c>
-      <c r="G1128" t="inlineStr"/>
       <c r="H1128" t="inlineStr">
         <is>
           <t>BROKERAGE CALL
@@ -48555,7 +48431,6 @@
       <c r="E1129" t="n">
         <v>1200</v>
       </c>
-      <c r="G1129" t="inlineStr"/>
       <c r="H1129" t="inlineStr">
         <is>
           <t>LUNG-TERM CALL Shilpa Medicare BUY TARGET 1200 DURATION 12 महीने Shilpa Medicare 928.55 4.37%</t>
@@ -48594,7 +48469,6 @@
       <c r="E1130" t="n">
         <v>550</v>
       </c>
-      <c r="G1130" t="inlineStr"/>
       <c r="H1130" t="inlineStr">
         <is>
           <t>सुदीप बंदोपाध्याय की पसंद Happiest Minds BUY TARGET 550 DURATION 12 महीने Happiest Minds 354.85 7.85</t>
@@ -48611,8 +48485,4467 @@
         </is>
       </c>
     </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1131" t="n">
+        <v>4849.6</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1131" t="inlineStr"/>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4848.80 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1132" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय CRISIL खरीदें PRICE 4846.00 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1133" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय CRISIL खरीदें PRICE 4846.00 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1134" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1134" t="inlineStr"/>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1135" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1135" t="inlineStr"/>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1136" t="n">
+        <v>865.5</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1136" t="inlineStr"/>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Amara Raja
+खरीदें
+PRICE 866.95
+TARGET 1100/1200
+STOP LOSS 790</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1137" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1137" t="inlineStr"/>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Amara Raja
+खरीदें
+PRICE ▶ 866.00
+TARGET ▶ 1100/1200
+STOP LOSS ▶ 790</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1138" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1138" t="inlineStr"/>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>10 की कमाई Amara Raja खरीदें PRICE 865.95 TARGET 1100/1200 STOP LOSS 790</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1139" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1139" t="inlineStr"/>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1140" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1140" t="inlineStr"/>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1141" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1141" t="inlineStr"/>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1142" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1142" t="inlineStr"/>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1143" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1143" t="inlineStr"/>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1144" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>सचितानंद उत्तकर की राय Reliance Ind Fut खरीदें PRICE 1340.00 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1145" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>सचितानंद उत्तकर की राय Reliance Ind Fut खरीदें PRICE 1340.00 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1146" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1146" t="inlineStr"/>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>BTSTT CALL
+Reliance Ind Fut
+खरीदें
+PRICE ▶ 1338.00
+TARGET ▶ 1360/1386
+STOP LOSS ▶ 1318</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1147" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उस्तेकर की राय Reliance Ind Fut खरीदें PRICE 1338.50 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1148" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1148" t="inlineStr"/>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1149" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1149" t="inlineStr"/>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1150" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1150" t="inlineStr"/>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:51:00</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>NIFTY2390008SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1151" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>177</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>कैश का ऑप्शन NIFTY 23900 की कॉल @ ₹140 खरीदें STOP LOSS 109 TARGET 177/195</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:51:00</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>NIFTY2390008SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1152" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>195</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>109</v>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>कैश का ऑप्शन NIFTY 23900 की कॉल @ ₹140 खरीदें STOP LOSS 109 TARGET 177/195</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1153" t="n">
+        <v>947.3</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1153" t="inlineStr"/>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1154" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1154" t="inlineStr"/>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1155" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1155" t="inlineStr"/>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1156" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1156" t="inlineStr"/>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1157" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1157" t="inlineStr"/>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1158" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1158" t="inlineStr"/>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1159" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1159" t="inlineStr"/>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1160" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1160" t="inlineStr"/>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Innova Captab खरीदें PRICE 1165.00 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1161" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1162" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G1162" t="inlineStr"/>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1163" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G1163" t="inlineStr"/>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS Innova Captab खरीदें PRICE 1163.70 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1164" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1164" t="inlineStr"/>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1163.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1165" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1165" t="inlineStr"/>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1166" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1166" t="inlineStr"/>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1167" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1167" t="inlineStr"/>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1168" t="n">
+        <v>910.6</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1168" t="inlineStr"/>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1169" t="n">
+        <v>910.6</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1169" t="inlineStr"/>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1170" t="n">
+        <v>909.85</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1170" t="inlineStr"/>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1171" t="n">
+        <v>909.85</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1171" t="inlineStr"/>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:33:10</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr"/>
+      <c r="E1172" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1380/12500</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:32</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr"/>
+      <c r="E1173" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G1173" t="inlineStr"/>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 14000,18000</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1174" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>1284</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1174" t="inlineStr"/>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1175" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>1306</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1175" t="inlineStr"/>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1176" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>1284</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1176" t="inlineStr"/>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1177" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>1305</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1177" t="inlineStr"/>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1178" t="n">
+        <v>1976.7</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1178" t="inlineStr"/>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930 RESULT TODAY</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1179" t="n">
+        <v>1976.7</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1179" t="inlineStr"/>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>सुमित बंगडिया की राय Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1180" t="n">
+        <v>947.2</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1181" t="n">
+        <v>947.2</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1182" t="n">
+        <v>947.2</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:06</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr"/>
+      <c r="E1183" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>23900</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 0,18000,23900</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1184" t="n">
+        <v>949.05</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1184" t="inlineStr"/>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1185" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1185" t="inlineStr"/>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1186" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1186" t="inlineStr"/>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1187" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1187" t="inlineStr"/>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1188" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1188" t="inlineStr"/>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:22:09</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>ANGELONE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr"/>
+      <c r="E1189" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G1189" t="inlineStr"/>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:22:09</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>ANGELONE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr"/>
+      <c r="E1190" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G1190" t="inlineStr"/>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1191" t="n">
+        <v>11344</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>जेफरीज UltraTech 11380.00 +105.00 BUY लक्ष्य ₹14065</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1192" t="n">
+        <v>1397.7</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G1192" t="inlineStr"/>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT मॉर्गन स्टैनली UNDERWEIGHT Cipla 1394.70 TARGET ₹1218</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1193" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>14700</v>
+      </c>
+      <c r="G1193" t="inlineStr"/>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT मॉर्गन स्टैनली OVERWEIGHT UltraTech 11275.00 Unch TARGET ₹14700</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1194" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G1194" t="inlineStr"/>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1195" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>2740</v>
+      </c>
+      <c r="G1195" t="inlineStr"/>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1196" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>2840</v>
+      </c>
+      <c r="G1196" t="inlineStr"/>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1197" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1197" t="inlineStr"/>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उत्तकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 STOP LOSS 1220</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1198" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G1198" t="inlineStr"/>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 DURATION 1220</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>VINATIORGA</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1199" t="n">
+        <v>1324.1</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1199" t="inlineStr"/>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>अंबरीश बलिगा की राय Vinati Org BUY PRICE 1313.70 TARGET 1800 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1200" t="n">
+        <v>196.49</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>215</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>180</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय New India Assurance BUY PRICE 195.33 TARGET 215/218 STOP LOSS 180</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1201" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>194</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1201" t="inlineStr"/>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1202" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>196</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1202" t="inlineStr"/>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1203" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1203" t="inlineStr"/>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>INVESTMENT RVNL B 230 201</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1204" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G1204" t="inlineStr"/>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>TECHNO IDFC FIRST BANK B 91 85.5</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1205" t="n">
+        <v>510.05</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>499</v>
+      </c>
+      <c r="G1205" t="inlineStr"/>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>CASH SARDA ENERGY B 525 499</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1206" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1206" t="inlineStr"/>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT POWER GRID B 272 262</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1207" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1207" t="inlineStr"/>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>INVESTMENT GMR AIRPORTS B 110 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1208" t="n">
+        <v>1022.8</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G1208" t="inlineStr"/>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>MY CHOICE MOTILAL OSWAL B 1032 1001</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1209" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G1209" t="inlineStr"/>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>TECHNO INFOSYS B 1154 1120</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1210" t="n">
+        <v>1071.9</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1210" t="inlineStr"/>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>FUNDA AU SMALL FINANCE B 11500 33</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1211" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>11154</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>1112</v>
+      </c>
+      <c r="G1211" t="inlineStr"/>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>TECHNO INFOSYS B 11154 1112</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>BHARATFORG29SEP26</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1212" t="n">
+        <v>1997.8</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G1212" t="inlineStr"/>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>FUTURE BHARAT FORGE FUT B 2020 1961</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1213" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G1213" t="inlineStr"/>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Nuvama Wealth
+खरीदें
+PRICE 1839.20
+TARGET 1925
+STOP LOSS 1799</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1214" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>197</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1214" t="inlineStr"/>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Groww खरीदें PRICE 190.24 TARGET 197 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>POLYCAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1215" t="n">
+        <v>8455.5</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>8697</v>
+      </c>
+      <c r="G1215" t="inlineStr"/>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>MY CHOICE Polycab India Ltd Fut PRICE 8875.50 TARGET 8697</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1216" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>11445</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>11191</v>
+      </c>
+      <c r="G1216" t="inlineStr"/>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+UltraTech
+खरीदें
+PRICE 11275.00
+TARGET 11445
+STOP LOSS 11191</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1217" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1217" t="inlineStr"/>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+Power Grid
+खरीदें
+PRICE → 265.60
+TARGET → 272
+STOP LOSS → 262</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1218" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1218" t="inlineStr"/>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK GMR Airports खरीदें PRICE 96.87 TARGET 110 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1219" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1219" t="inlineStr"/>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+RVNL
+खरीदें
+PRICE → 209.30
+TARGET → 230
+STOP LOSS → 201</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1220" t="n">
+        <v>1071.9</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G1220" t="inlineStr"/>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>FUNDA PICK AU Small Fin खरीदें PRICE 1072.00 TARGET 1150 DURATION 3 महीने</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1221" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G1221" t="inlineStr"/>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>TECHNO PICK Infosys खरीदें PRICE 1130.30 TARGET 1154 STOP LOSS 1120</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1222" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G1222" t="inlineStr"/>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>TECHNO PICK IDFC First Bank खरीदें PRICE 87.50 TARGET 91 STOP LOSS 85.5</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>AXISBANK126029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1223" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1223" t="inlineStr"/>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>Axis Bank 1260 की कॉल @ 30 खरीदें STOP LOSS 15 TARGET 80 Axis Bank 1267.00</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>BHARATFORG29SEP26</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1224" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G1224" t="inlineStr"/>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>आज का FUTURE Bharat Forge Fut खरीदें PRICE 1997.80 TARGET 2020 STOP LOSS 1961</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1225" t="n">
+        <v>510.05</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>499</v>
+      </c>
+      <c r="G1225" t="inlineStr"/>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Sarda Energy खरीदें PRICE 506.55 TARGET 525 STOP LOSS 499</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1226" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G1226" t="inlineStr"/>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>UltraTech 11275.00 -118.00 BUY लक्ष्य ₹14065</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1226" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1227" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G1227" t="inlineStr"/>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>RVNL 209.30 ▲ 1.60% ईस्ट कोस्ट रेलवे जोन से जुड़ा है रेलवे का प्रोजेक्ट BROKERAGE CALLS BUY लक्ष्य ₹14065</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1227" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1228" t="n">
+        <v>790.85</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>810</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>770</v>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Aster DM Health खरीदें PRICE 787.00 TARGET 810/825 STOP LOSS 770</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1228" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1229" t="n">
+        <v>790.85</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>770</v>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Aster DM Health खरीदें PRICE 787.00 TARGET 810/825 STOP LOSS 770</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1229" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1230" t="n">
+        <v>4352</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>4450</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>4320</v>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय GE Vernova T&amp;D खरीदें PRICE 4362.00 TARGET 4450/4470 STOP LOSS 4320</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1230" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1231" t="n">
+        <v>4352</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>4470</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>4320</v>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय GE Vernova T&amp;D खरीदें PRICE 4362.00 TARGET 4450/4470 STOP LOSS 4320</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1231" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1232" t="n">
+        <v>162.09</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Samvardhana Motherson 162.00 -1.30 ACCUMULATE लक्ष्य ₹190 Sidinvesting Financial Services</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1233" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1233" t="inlineStr"/>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>खबरों वाले शेयर GE Shipping 1353.60 ▲ 3.68% बायबैक प्राइस ₹1530/शेयर</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1234" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1234" t="inlineStr"/>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>अभिनाश गोरेश्कर की पसंद Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1235" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1235" t="inlineStr"/>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>LONG-TERM CALL Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1236" t="n">
+        <v>1695.2</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G1236" t="inlineStr"/>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>POSITIONAL C Adani Ports BUY TARGET 1750 Adani Ports 1706.50</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1237" t="n">
+        <v>1695.2</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G1237" t="inlineStr"/>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>POSITIONAL CALL Adani Ports BUY TARGET 1750 STOP LOSS 1690 Adani Ports 1706.50 2.02%</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1130"/>
+  <autoFilter ref="A1:J1237"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1327</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1237"/>
+  <dimension ref="A1:J1327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -48510,7 +48510,6 @@
       <c r="F1131" t="n">
         <v>4725</v>
       </c>
-      <c r="G1131" t="inlineStr"/>
       <c r="H1131" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4848.80 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -48644,7 +48643,6 @@
       <c r="F1134" t="n">
         <v>4725</v>
       </c>
-      <c r="G1134" t="inlineStr"/>
       <c r="H1134" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -48686,7 +48684,6 @@
       <c r="F1135" t="n">
         <v>4725</v>
       </c>
-      <c r="G1135" t="inlineStr"/>
       <c r="H1135" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -48728,7 +48725,6 @@
       <c r="F1136" t="n">
         <v>790</v>
       </c>
-      <c r="G1136" t="inlineStr"/>
       <c r="H1136" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -48775,7 +48771,6 @@
       <c r="F1137" t="n">
         <v>790</v>
       </c>
-      <c r="G1137" t="inlineStr"/>
       <c r="H1137" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -48822,7 +48817,6 @@
       <c r="F1138" t="n">
         <v>790</v>
       </c>
-      <c r="G1138" t="inlineStr"/>
       <c r="H1138" t="inlineStr">
         <is>
           <t>10 की कमाई Amara Raja खरीदें PRICE 865.95 TARGET 1100/1200 STOP LOSS 790</t>
@@ -48861,7 +48855,6 @@
       <c r="E1139" t="n">
         <v>1400</v>
       </c>
-      <c r="G1139" t="inlineStr"/>
       <c r="H1139" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -48900,7 +48893,6 @@
       <c r="E1140" t="n">
         <v>1800</v>
       </c>
-      <c r="G1140" t="inlineStr"/>
       <c r="H1140" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -48939,7 +48931,6 @@
       <c r="E1141" t="n">
         <v>2500</v>
       </c>
-      <c r="G1141" t="inlineStr"/>
       <c r="H1141" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -48981,7 +48972,6 @@
       <c r="F1142" t="n">
         <v>1318</v>
       </c>
-      <c r="G1142" t="inlineStr"/>
       <c r="H1142" t="inlineStr">
         <is>
           <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
@@ -49023,7 +49013,6 @@
       <c r="F1143" t="n">
         <v>1318</v>
       </c>
-      <c r="G1143" t="inlineStr"/>
       <c r="H1143" t="inlineStr">
         <is>
           <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
@@ -49157,7 +49146,6 @@
       <c r="F1146" t="n">
         <v>1318</v>
       </c>
-      <c r="G1146" t="inlineStr"/>
       <c r="H1146" t="inlineStr">
         <is>
           <t>BTSTT CALL
@@ -49247,7 +49235,6 @@
       <c r="E1148" t="n">
         <v>2500</v>
       </c>
-      <c r="G1148" t="inlineStr"/>
       <c r="H1148" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49286,7 +49273,6 @@
       <c r="E1149" t="n">
         <v>1400</v>
       </c>
-      <c r="G1149" t="inlineStr"/>
       <c r="H1149" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49325,7 +49311,6 @@
       <c r="E1150" t="n">
         <v>1800</v>
       </c>
-      <c r="G1150" t="inlineStr"/>
       <c r="H1150" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49456,7 +49441,6 @@
       <c r="E1153" t="n">
         <v>2500</v>
       </c>
-      <c r="G1153" t="inlineStr"/>
       <c r="H1153" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49495,7 +49479,6 @@
       <c r="E1154" t="n">
         <v>1400</v>
       </c>
-      <c r="G1154" t="inlineStr"/>
       <c r="H1154" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49534,7 +49517,6 @@
       <c r="E1155" t="n">
         <v>1800</v>
       </c>
-      <c r="G1155" t="inlineStr"/>
       <c r="H1155" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49573,7 +49555,6 @@
       <c r="E1156" t="n">
         <v>2500</v>
       </c>
-      <c r="G1156" t="inlineStr"/>
       <c r="H1156" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49612,7 +49593,6 @@
       <c r="E1157" t="n">
         <v>1400</v>
       </c>
-      <c r="G1157" t="inlineStr"/>
       <c r="H1157" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49651,7 +49631,6 @@
       <c r="E1158" t="n">
         <v>1800</v>
       </c>
-      <c r="G1158" t="inlineStr"/>
       <c r="H1158" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49690,7 +49669,6 @@
       <c r="E1159" t="n">
         <v>2500</v>
       </c>
-      <c r="G1159" t="inlineStr"/>
       <c r="H1159" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -49729,7 +49707,6 @@
       <c r="E1160" t="n">
         <v>1260</v>
       </c>
-      <c r="G1160" t="inlineStr"/>
       <c r="H1160" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Innova Captab खरीदें PRICE 1165.00 TARGET 1260/1270 STOP LOSS --</t>
@@ -49768,7 +49745,6 @@
       <c r="E1161" t="n">
         <v>1260</v>
       </c>
-      <c r="G1161" t="inlineStr"/>
       <c r="H1161" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -49807,7 +49783,6 @@
       <c r="E1162" t="n">
         <v>1270</v>
       </c>
-      <c r="G1162" t="inlineStr"/>
       <c r="H1162" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -49846,7 +49821,6 @@
       <c r="E1163" t="n">
         <v>1270</v>
       </c>
-      <c r="G1163" t="inlineStr"/>
       <c r="H1163" t="inlineStr">
         <is>
           <t>जैन साब के GEMS Innova Captab खरीदें PRICE 1163.70 TARGET 1260/1270 STOP LOSS --</t>
@@ -49885,7 +49859,6 @@
       <c r="E1164" t="n">
         <v>1260</v>
       </c>
-      <c r="G1164" t="inlineStr"/>
       <c r="H1164" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1163.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -49924,7 +49897,6 @@
       <c r="E1165" t="n">
         <v>1400</v>
       </c>
-      <c r="G1165" t="inlineStr"/>
       <c r="H1165" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -49967,7 +49939,6 @@
       <c r="E1166" t="n">
         <v>1800</v>
       </c>
-      <c r="G1166" t="inlineStr"/>
       <c r="H1166" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -50010,7 +49981,6 @@
       <c r="E1167" t="n">
         <v>2500</v>
       </c>
-      <c r="G1167" t="inlineStr"/>
       <c r="H1167" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -50053,7 +50023,6 @@
       <c r="E1168" t="n">
         <v>1400</v>
       </c>
-      <c r="G1168" t="inlineStr"/>
       <c r="H1168" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50092,7 +50061,6 @@
       <c r="E1169" t="n">
         <v>1800</v>
       </c>
-      <c r="G1169" t="inlineStr"/>
       <c r="H1169" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50131,7 +50099,6 @@
       <c r="E1170" t="n">
         <v>1800</v>
       </c>
-      <c r="G1170" t="inlineStr"/>
       <c r="H1170" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50170,7 +50137,6 @@
       <c r="E1171" t="n">
         <v>2500</v>
       </c>
-      <c r="G1171" t="inlineStr"/>
       <c r="H1171" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50203,14 +50169,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1172" t="inlineStr"/>
       <c r="E1172" t="n">
         <v>1380</v>
       </c>
       <c r="F1172" t="n">
         <v>12500</v>
       </c>
-      <c r="G1172" t="inlineStr"/>
       <c r="H1172" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1380/12500</t>
@@ -50243,11 +50207,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1173" t="inlineStr"/>
       <c r="E1173" t="n">
         <v>18000</v>
       </c>
-      <c r="G1173" t="inlineStr"/>
       <c r="H1173" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 14000,18000</t>
@@ -50289,7 +50251,6 @@
       <c r="F1174" t="n">
         <v>1248</v>
       </c>
-      <c r="G1174" t="inlineStr"/>
       <c r="H1174" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
@@ -50331,7 +50292,6 @@
       <c r="F1175" t="n">
         <v>1248</v>
       </c>
-      <c r="G1175" t="inlineStr"/>
       <c r="H1175" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
@@ -50373,7 +50333,6 @@
       <c r="F1176" t="n">
         <v>1248</v>
       </c>
-      <c r="G1176" t="inlineStr"/>
       <c r="H1176" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
@@ -50415,7 +50374,6 @@
       <c r="F1177" t="n">
         <v>1248</v>
       </c>
-      <c r="G1177" t="inlineStr"/>
       <c r="H1177" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
@@ -50457,7 +50415,6 @@
       <c r="F1178" t="n">
         <v>1930</v>
       </c>
-      <c r="G1178" t="inlineStr"/>
       <c r="H1178" t="inlineStr">
         <is>
           <t>Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930 RESULT TODAY</t>
@@ -50499,7 +50456,6 @@
       <c r="F1179" t="n">
         <v>1930</v>
       </c>
-      <c r="G1179" t="inlineStr"/>
       <c r="H1179" t="inlineStr">
         <is>
           <t>सुमित बंगडिया की राय Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930</t>
@@ -50661,7 +50617,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1183" t="inlineStr"/>
       <c r="E1183" t="n">
         <v>1800</v>
       </c>
@@ -50711,7 +50666,6 @@
       <c r="E1184" t="n">
         <v>2500</v>
       </c>
-      <c r="G1184" t="inlineStr"/>
       <c r="H1184" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50750,7 +50704,6 @@
       <c r="E1185" t="n">
         <v>1400</v>
       </c>
-      <c r="G1185" t="inlineStr"/>
       <c r="H1185" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50789,7 +50742,6 @@
       <c r="E1186" t="n">
         <v>1800</v>
       </c>
-      <c r="G1186" t="inlineStr"/>
       <c r="H1186" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50828,7 +50780,6 @@
       <c r="E1187" t="n">
         <v>2500</v>
       </c>
-      <c r="G1187" t="inlineStr"/>
       <c r="H1187" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50867,7 +50818,6 @@
       <c r="E1188" t="n">
         <v>2500</v>
       </c>
-      <c r="G1188" t="inlineStr"/>
       <c r="H1188" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -50900,14 +50850,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1189" t="inlineStr"/>
       <c r="E1189" t="n">
         <v>5000</v>
       </c>
       <c r="F1189" t="n">
         <v>3000</v>
       </c>
-      <c r="G1189" t="inlineStr"/>
       <c r="H1189" t="inlineStr">
         <is>
           <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
@@ -50940,14 +50888,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1190" t="inlineStr"/>
       <c r="E1190" t="n">
         <v>5000</v>
       </c>
       <c r="F1190" t="n">
         <v>4000</v>
       </c>
-      <c r="G1190" t="inlineStr"/>
       <c r="H1190" t="inlineStr">
         <is>
           <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
@@ -51029,7 +50975,6 @@
       <c r="E1192" t="n">
         <v>1218</v>
       </c>
-      <c r="G1192" t="inlineStr"/>
       <c r="H1192" t="inlineStr">
         <is>
           <t>FII INVESTMENT REPORT मॉर्गन स्टैनली UNDERWEIGHT Cipla 1394.70 TARGET ₹1218</t>
@@ -51068,7 +51013,6 @@
       <c r="E1193" t="n">
         <v>14700</v>
       </c>
-      <c r="G1193" t="inlineStr"/>
       <c r="H1193" t="inlineStr">
         <is>
           <t>FII INVESTMENT REPORT मॉर्गन स्टैनली OVERWEIGHT UltraTech 11275.00 Unch TARGET ₹14700</t>
@@ -51107,7 +51051,6 @@
       <c r="E1194" t="n">
         <v>2640</v>
       </c>
-      <c r="G1194" t="inlineStr"/>
       <c r="H1194" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -51151,7 +51094,6 @@
       <c r="E1195" t="n">
         <v>2740</v>
       </c>
-      <c r="G1195" t="inlineStr"/>
       <c r="H1195" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -51195,7 +51137,6 @@
       <c r="E1196" t="n">
         <v>2840</v>
       </c>
-      <c r="G1196" t="inlineStr"/>
       <c r="H1196" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -51242,7 +51183,6 @@
       <c r="F1197" t="n">
         <v>1220</v>
       </c>
-      <c r="G1197" t="inlineStr"/>
       <c r="H1197" t="inlineStr">
         <is>
           <t>सच्चितानंद उत्तकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 STOP LOSS 1220</t>
@@ -51281,7 +51221,6 @@
       <c r="E1198" t="n">
         <v>1960</v>
       </c>
-      <c r="G1198" t="inlineStr"/>
       <c r="H1198" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 DURATION 1220</t>
@@ -51320,7 +51259,6 @@
       <c r="E1199" t="n">
         <v>1800</v>
       </c>
-      <c r="G1199" t="inlineStr"/>
       <c r="H1199" t="inlineStr">
         <is>
           <t>अंबरीश बलिगा की राय Vinati Org BUY PRICE 1313.70 TARGET 1800 STOP LOSS --</t>
@@ -51408,7 +51346,6 @@
       <c r="F1201" t="n">
         <v>188</v>
       </c>
-      <c r="G1201" t="inlineStr"/>
       <c r="H1201" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
@@ -51450,7 +51387,6 @@
       <c r="F1202" t="n">
         <v>188</v>
       </c>
-      <c r="G1202" t="inlineStr"/>
       <c r="H1202" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
@@ -51492,7 +51428,6 @@
       <c r="F1203" t="n">
         <v>201</v>
       </c>
-      <c r="G1203" t="inlineStr"/>
       <c r="H1203" t="inlineStr">
         <is>
           <t>INVESTMENT RVNL B 230 201</t>
@@ -51534,7 +51469,6 @@
       <c r="F1204" t="n">
         <v>85.5</v>
       </c>
-      <c r="G1204" t="inlineStr"/>
       <c r="H1204" t="inlineStr">
         <is>
           <t>TECHNO IDFC FIRST BANK B 91 85.5</t>
@@ -51576,7 +51510,6 @@
       <c r="F1205" t="n">
         <v>499</v>
       </c>
-      <c r="G1205" t="inlineStr"/>
       <c r="H1205" t="inlineStr">
         <is>
           <t>CASH SARDA ENERGY B 525 499</t>
@@ -51618,7 +51551,6 @@
       <c r="F1206" t="n">
         <v>262</v>
       </c>
-      <c r="G1206" t="inlineStr"/>
       <c r="H1206" t="inlineStr">
         <is>
           <t>NEWS IMPACT POWER GRID B 272 262</t>
@@ -51657,7 +51589,6 @@
       <c r="E1207" t="n">
         <v>110</v>
       </c>
-      <c r="G1207" t="inlineStr"/>
       <c r="H1207" t="inlineStr">
         <is>
           <t>INVESTMENT GMR AIRPORTS B 110 12 MONTH</t>
@@ -51699,7 +51630,6 @@
       <c r="F1208" t="n">
         <v>1001</v>
       </c>
-      <c r="G1208" t="inlineStr"/>
       <c r="H1208" t="inlineStr">
         <is>
           <t>MY CHOICE MOTILAL OSWAL B 1032 1001</t>
@@ -51741,7 +51671,6 @@
       <c r="F1209" t="n">
         <v>1120</v>
       </c>
-      <c r="G1209" t="inlineStr"/>
       <c r="H1209" t="inlineStr">
         <is>
           <t>TECHNO INFOSYS B 1154 1120</t>
@@ -51783,7 +51712,6 @@
       <c r="F1210" t="n">
         <v>33</v>
       </c>
-      <c r="G1210" t="inlineStr"/>
       <c r="H1210" t="inlineStr">
         <is>
           <t>FUNDA AU SMALL FINANCE B 11500 33</t>
@@ -51825,7 +51753,6 @@
       <c r="F1211" t="n">
         <v>1112</v>
       </c>
-      <c r="G1211" t="inlineStr"/>
       <c r="H1211" t="inlineStr">
         <is>
           <t>TECHNO INFOSYS B 11154 1112</t>
@@ -51867,7 +51794,6 @@
       <c r="F1212" t="n">
         <v>1961</v>
       </c>
-      <c r="G1212" t="inlineStr"/>
       <c r="H1212" t="inlineStr">
         <is>
           <t>FUTURE BHARAT FORGE FUT B 2020 1961</t>
@@ -51909,7 +51835,6 @@
       <c r="F1213" t="n">
         <v>1799</v>
       </c>
-      <c r="G1213" t="inlineStr"/>
       <c r="H1213" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -51956,7 +51881,6 @@
       <c r="F1214" t="n">
         <v>188</v>
       </c>
-      <c r="G1214" t="inlineStr"/>
       <c r="H1214" t="inlineStr">
         <is>
           <t>अंश के शेयर Groww खरीदें PRICE 190.24 TARGET 197 STOP LOSS 188</t>
@@ -51995,7 +51919,6 @@
       <c r="E1215" t="n">
         <v>8697</v>
       </c>
-      <c r="G1215" t="inlineStr"/>
       <c r="H1215" t="inlineStr">
         <is>
           <t>MY CHOICE Polycab India Ltd Fut PRICE 8875.50 TARGET 8697</t>
@@ -52037,7 +51960,6 @@
       <c r="F1216" t="n">
         <v>11191</v>
       </c>
-      <c r="G1216" t="inlineStr"/>
       <c r="H1216" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -52084,7 +52006,6 @@
       <c r="F1217" t="n">
         <v>262</v>
       </c>
-      <c r="G1217" t="inlineStr"/>
       <c r="H1217" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -52128,7 +52049,6 @@
       <c r="E1218" t="n">
         <v>110</v>
       </c>
-      <c r="G1218" t="inlineStr"/>
       <c r="H1218" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK GMR Airports खरीदें PRICE 96.87 TARGET 110 DURATION 12 महीने</t>
@@ -52170,7 +52090,6 @@
       <c r="F1219" t="n">
         <v>201</v>
       </c>
-      <c r="G1219" t="inlineStr"/>
       <c r="H1219" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -52214,7 +52133,6 @@
       <c r="E1220" t="n">
         <v>1150</v>
       </c>
-      <c r="G1220" t="inlineStr"/>
       <c r="H1220" t="inlineStr">
         <is>
           <t>FUNDA PICK AU Small Fin खरीदें PRICE 1072.00 TARGET 1150 DURATION 3 महीने</t>
@@ -52256,7 +52174,6 @@
       <c r="F1221" t="n">
         <v>1120</v>
       </c>
-      <c r="G1221" t="inlineStr"/>
       <c r="H1221" t="inlineStr">
         <is>
           <t>TECHNO PICK Infosys खरीदें PRICE 1130.30 TARGET 1154 STOP LOSS 1120</t>
@@ -52298,7 +52215,6 @@
       <c r="F1222" t="n">
         <v>85.5</v>
       </c>
-      <c r="G1222" t="inlineStr"/>
       <c r="H1222" t="inlineStr">
         <is>
           <t>TECHNO PICK IDFC First Bank खरीदें PRICE 87.50 TARGET 91 STOP LOSS 85.5</t>
@@ -52340,7 +52256,6 @@
       <c r="F1223" t="n">
         <v>15</v>
       </c>
-      <c r="G1223" t="inlineStr"/>
       <c r="H1223" t="inlineStr">
         <is>
           <t>Axis Bank 1260 की कॉल @ 30 खरीदें STOP LOSS 15 TARGET 80 Axis Bank 1267.00</t>
@@ -52382,7 +52297,6 @@
       <c r="F1224" t="n">
         <v>1961</v>
       </c>
-      <c r="G1224" t="inlineStr"/>
       <c r="H1224" t="inlineStr">
         <is>
           <t>आज का FUTURE Bharat Forge Fut खरीदें PRICE 1997.80 TARGET 2020 STOP LOSS 1961</t>
@@ -52424,7 +52338,6 @@
       <c r="F1225" t="n">
         <v>499</v>
       </c>
-      <c r="G1225" t="inlineStr"/>
       <c r="H1225" t="inlineStr">
         <is>
           <t>CASH का शेयर Sarda Energy खरीदें PRICE 506.55 TARGET 525 STOP LOSS 499</t>
@@ -52463,7 +52376,6 @@
       <c r="E1226" t="n">
         <v>14065</v>
       </c>
-      <c r="G1226" t="inlineStr"/>
       <c r="H1226" t="inlineStr">
         <is>
           <t>UltraTech 11275.00 -118.00 BUY लक्ष्य ₹14065</t>
@@ -52502,7 +52414,6 @@
       <c r="E1227" t="n">
         <v>14065</v>
       </c>
-      <c r="G1227" t="inlineStr"/>
       <c r="H1227" t="inlineStr">
         <is>
           <t>RVNL 209.30 ▲ 1.60% ईस्ट कोस्ट रेलवे जोन से जुड़ा है रेलवे का प्रोजेक्ट BROKERAGE CALLS BUY लक्ष्य ₹14065</t>
@@ -52768,7 +52679,6 @@
       <c r="E1233" t="n">
         <v>1530</v>
       </c>
-      <c r="G1233" t="inlineStr"/>
       <c r="H1233" t="inlineStr">
         <is>
           <t>खबरों वाले शेयर GE Shipping 1353.60 ▲ 3.68% बायबैक प्राइस ₹1530/शेयर</t>
@@ -52807,7 +52717,6 @@
       <c r="E1234" t="n">
         <v>105</v>
       </c>
-      <c r="G1234" t="inlineStr"/>
       <c r="H1234" t="inlineStr">
         <is>
           <t>अभिनाश गोरेश्कर की पसंद Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
@@ -52846,7 +52755,6 @@
       <c r="E1235" t="n">
         <v>106</v>
       </c>
-      <c r="G1235" t="inlineStr"/>
       <c r="H1235" t="inlineStr">
         <is>
           <t>LONG-TERM CALL Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
@@ -52885,7 +52793,6 @@
       <c r="E1236" t="n">
         <v>1750</v>
       </c>
-      <c r="G1236" t="inlineStr"/>
       <c r="H1236" t="inlineStr">
         <is>
           <t>POSITIONAL C Adani Ports BUY TARGET 1750 Adani Ports 1706.50</t>
@@ -52927,7 +52834,6 @@
       <c r="F1237" t="n">
         <v>1690</v>
       </c>
-      <c r="G1237" t="inlineStr"/>
       <c r="H1237" t="inlineStr">
         <is>
           <t>POSITIONAL CALL Adani Ports BUY TARGET 1750 STOP LOSS 1690 Adani Ports 1706.50 2.02%</t>
@@ -52944,8 +52850,3700 @@
         </is>
       </c>
     </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1238" t="n">
+        <v>4849.6</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1238" t="inlineStr"/>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4848.80 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1239" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1239" t="inlineStr"/>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1240" t="n">
+        <v>4842.5</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>4980</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>4725</v>
+      </c>
+      <c r="G1240" t="inlineStr"/>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1241" t="n">
+        <v>865.5</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Amara Raja
+खरीदें
+PRICE 866.95
+TARGET 1100/1200
+STOP LOSS 790</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1242" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Amara Raja
+खरीदें
+PRICE ▶ 866.00
+TARGET ▶ 1100/1200
+STOP LOSS ▶ 790</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:59:00</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>ARE&amp;M</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1243" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>790</v>
+      </c>
+      <c r="G1243" t="inlineStr"/>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>10 की कमाई Amara Raja खरीदें PRICE 865.95 TARGET 1100/1200 STOP LOSS 790</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1244" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1244" t="inlineStr"/>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1245" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1245" t="inlineStr"/>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1246" t="n">
+        <v>904.75</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1246" t="inlineStr"/>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1247" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1247" t="inlineStr"/>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1248" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1248" t="inlineStr"/>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>RELIANCE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1249" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>1318</v>
+      </c>
+      <c r="G1249" t="inlineStr"/>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>BTSTT CALL
+Reliance Ind Fut
+खरीदें
+PRICE ▶ 1338.00
+TARGET ▶ 1360/1386
+STOP LOSS ▶ 1318</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1250" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1250" t="inlineStr"/>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1251" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1251" t="inlineStr"/>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1252" t="n">
+        <v>946.3</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1252" t="inlineStr"/>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1253" t="n">
+        <v>947.3</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1253" t="inlineStr"/>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1254" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1254" t="inlineStr"/>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1255" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1255" t="inlineStr"/>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1256" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1256" t="inlineStr"/>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1257" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1257" t="inlineStr"/>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1258" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1258" t="inlineStr"/>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1259" t="n">
+        <v>905.95</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1259" t="inlineStr"/>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1259" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1260" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1260" t="inlineStr"/>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Innova Captab खरीदें PRICE 1165.00 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1261" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1261" t="inlineStr"/>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1262" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G1262" t="inlineStr"/>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1263" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>1270</v>
+      </c>
+      <c r="G1263" t="inlineStr"/>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS Innova Captab खरीदें PRICE 1163.70 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1264" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G1264" t="inlineStr"/>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Innova Captab खरीदें PRICE 1163.60 TARGET 1260/1270 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1265" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1265" t="inlineStr"/>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1266" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1266" t="inlineStr"/>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:39:00</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1267" t="n">
+        <v>948</v>
+      </c>
+      <c r="E1267" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1267" t="inlineStr"/>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन
+Anthem Biosciences
+BUY
+लक्ष्य 1400, 1800, 2500
+अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1268" t="n">
+        <v>910.6</v>
+      </c>
+      <c r="E1268" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1268" t="inlineStr"/>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1268" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1269" t="n">
+        <v>910.6</v>
+      </c>
+      <c r="E1269" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1269" t="inlineStr"/>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1269" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1270" t="n">
+        <v>909.85</v>
+      </c>
+      <c r="E1270" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1270" t="inlineStr"/>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1270" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1271" t="n">
+        <v>909.85</v>
+      </c>
+      <c r="E1271" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1271" t="inlineStr"/>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:33:10</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr"/>
+      <c r="E1272" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G1272" t="inlineStr"/>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1380/12500</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1272" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:32</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr"/>
+      <c r="E1273" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G1273" t="inlineStr"/>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 14000,18000</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1273" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1274" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1274" t="n">
+        <v>1284</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1274" t="inlineStr"/>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1274" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1275" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1275" t="n">
+        <v>1306</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1275" t="inlineStr"/>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1275" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1276" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1276" t="n">
+        <v>1284</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1276" t="inlineStr"/>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>BDL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1277" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E1277" t="n">
+        <v>1305</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1277" t="inlineStr"/>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1278" t="n">
+        <v>1976.7</v>
+      </c>
+      <c r="E1278" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1278" t="inlineStr"/>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930 RESULT TODAY</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1279" t="n">
+        <v>1976.7</v>
+      </c>
+      <c r="E1279" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1279" t="inlineStr"/>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>सुमित बंगडिया की राय Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:06</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr"/>
+      <c r="E1280" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>23900</v>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 0,18000,23900</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>ANTHEM</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1281" t="n">
+        <v>949.05</v>
+      </c>
+      <c r="E1281" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1281" t="inlineStr"/>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1282" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1282" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G1282" t="inlineStr"/>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1283" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1283" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1283" t="inlineStr"/>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1284" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1284" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1284" t="inlineStr"/>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1285" t="n">
+        <v>916.15</v>
+      </c>
+      <c r="E1285" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1285" t="inlineStr"/>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 400, 1800, 2500 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:22:09</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>ANGELONE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr"/>
+      <c r="E1286" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G1286" t="inlineStr"/>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:22:09</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>ANGELONE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr"/>
+      <c r="E1287" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G1287" t="inlineStr"/>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1288" t="n">
+        <v>1397.7</v>
+      </c>
+      <c r="E1288" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G1288" t="inlineStr"/>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT मॉर्गन स्टैनली UNDERWEIGHT Cipla 1394.70 TARGET ₹1218</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1289" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1289" t="n">
+        <v>14700</v>
+      </c>
+      <c r="G1289" t="inlineStr"/>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT मॉर्गन स्टैनली OVERWEIGHT UltraTech 11275.00 Unch TARGET ₹14700</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1290" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1290" t="n">
+        <v>2640</v>
+      </c>
+      <c r="G1290" t="inlineStr"/>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1291" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1291" t="n">
+        <v>2740</v>
+      </c>
+      <c r="G1291" t="inlineStr"/>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1292" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E1292" t="n">
+        <v>2840</v>
+      </c>
+      <c r="G1292" t="inlineStr"/>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय
+Asian Paints
+BUY
+PRICE ▶ 2541.60
+TARGET ▶ 2640/2740/2840
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1293" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1293" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1293" t="inlineStr"/>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उत्तकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 STOP LOSS 1220</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1294" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1294" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G1294" t="inlineStr"/>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 DURATION 1220</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>VINATIORGA</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1295" t="n">
+        <v>1324.1</v>
+      </c>
+      <c r="E1295" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G1295" t="inlineStr"/>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>अंबरीश बलिगा की राय Vinati Org BUY PRICE 1313.70 TARGET 1800 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1296" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1296" t="n">
+        <v>194</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1296" t="inlineStr"/>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1297" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1297" t="n">
+        <v>196</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1297" t="inlineStr"/>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1298" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1298" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1298" t="inlineStr"/>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>INVESTMENT RVNL B 230 201</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1299" t="n">
+        <v>87.54000000000001</v>
+      </c>
+      <c r="E1299" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G1299" t="inlineStr"/>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>TECHNO IDFC FIRST BANK B 91 85.5</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1300" t="n">
+        <v>510.05</v>
+      </c>
+      <c r="E1300" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>499</v>
+      </c>
+      <c r="G1300" t="inlineStr"/>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>CASH SARDA ENERGY B 525 499</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1301" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1301" t="inlineStr"/>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT POWER GRID B 272 262</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1302" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1302" t="inlineStr"/>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>INVESTMENT GMR AIRPORTS B 110 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1303" t="n">
+        <v>1022.8</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>1032</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G1303" t="inlineStr"/>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>MY CHOICE MOTILAL OSWAL B 1032 1001</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1304" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G1304" t="inlineStr"/>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>TECHNO INFOSYS B 1154 1120</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1305" t="n">
+        <v>1071.9</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>11500</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1305" t="inlineStr"/>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>FUNDA AU SMALL FINANCE B 11500 33</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1306" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>11154</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>1112</v>
+      </c>
+      <c r="G1306" t="inlineStr"/>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>TECHNO INFOSYS B 11154 1112</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>BHARATFORG29SEP26</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1307" t="n">
+        <v>1997.8</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G1307" t="inlineStr"/>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>FUTURE BHARAT FORGE FUT B 2020 1961</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1307" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1308" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>1925</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>1799</v>
+      </c>
+      <c r="G1308" t="inlineStr"/>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Nuvama Wealth
+खरीदें
+PRICE 1839.20
+TARGET 1925
+STOP LOSS 1799</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1308" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1309" t="n">
+        <v>193</v>
+      </c>
+      <c r="E1309" t="n">
+        <v>197</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>188</v>
+      </c>
+      <c r="G1309" t="inlineStr"/>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>अंश के शेयर Groww खरीदें PRICE 190.24 TARGET 197 STOP LOSS 188</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1309" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>POLYCAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1310" t="n">
+        <v>8455.5</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>8697</v>
+      </c>
+      <c r="G1310" t="inlineStr"/>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>MY CHOICE Polycab India Ltd Fut PRICE 8875.50 TARGET 8697</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1310" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1311" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1311" t="n">
+        <v>11445</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>11191</v>
+      </c>
+      <c r="G1311" t="inlineStr"/>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+UltraTech
+खरीदें
+PRICE 11275.00
+TARGET 11445
+STOP LOSS 11191</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1311" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1312" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="E1312" t="n">
+        <v>272</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>262</v>
+      </c>
+      <c r="G1312" t="inlineStr"/>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+Power Grid
+खरीदें
+PRICE → 265.60
+TARGET → 272
+STOP LOSS → 262</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1312" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1313" t="n">
+        <v>96.86</v>
+      </c>
+      <c r="E1313" t="n">
+        <v>110</v>
+      </c>
+      <c r="G1313" t="inlineStr"/>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK GMR Airports खरीदें PRICE 96.87 TARGET 110 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1313" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1314" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1314" t="n">
+        <v>230</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>201</v>
+      </c>
+      <c r="G1314" t="inlineStr"/>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+RVNL
+खरीदें
+PRICE → 209.30
+TARGET → 230
+STOP LOSS → 201</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1314" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1315" t="n">
+        <v>1071.9</v>
+      </c>
+      <c r="E1315" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G1315" t="inlineStr"/>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>FUNDA PICK AU Small Fin खरीदें PRICE 1072.00 TARGET 1150 DURATION 3 महीने</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1315" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1316" t="n">
+        <v>1133</v>
+      </c>
+      <c r="E1316" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G1316" t="inlineStr"/>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>TECHNO PICK Infosys खरीदें PRICE 1130.30 TARGET 1154 STOP LOSS 1120</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1316" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1317" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>91</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G1317" t="inlineStr"/>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>TECHNO PICK IDFC First Bank खरीदें PRICE 87.50 TARGET 91 STOP LOSS 85.5</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1317" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>AXISBANK126029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1318" t="n">
+        <v>29</v>
+      </c>
+      <c r="E1318" t="n">
+        <v>80</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>15</v>
+      </c>
+      <c r="G1318" t="inlineStr"/>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>Axis Bank 1260 की कॉल @ 30 खरीदें STOP LOSS 15 TARGET 80 Axis Bank 1267.00</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1318" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>BHARATFORG29SEP26</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1319" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>1961</v>
+      </c>
+      <c r="G1319" t="inlineStr"/>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>आज का FUTURE Bharat Forge Fut खरीदें PRICE 1997.80 TARGET 2020 STOP LOSS 1961</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1319" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>SARDAEN</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1320" t="n">
+        <v>510.05</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>525</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>499</v>
+      </c>
+      <c r="G1320" t="inlineStr"/>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Sarda Energy खरीदें PRICE 506.55 TARGET 525 STOP LOSS 499</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1320" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1321" t="n">
+        <v>11357</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G1321" t="inlineStr"/>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>UltraTech 11275.00 -118.00 BUY लक्ष्य ₹14065</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1321" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1322" t="n">
+        <v>211</v>
+      </c>
+      <c r="E1322" t="n">
+        <v>14065</v>
+      </c>
+      <c r="G1322" t="inlineStr"/>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>RVNL 209.30 ▲ 1.60% ईस्ट कोस्ट रेलवे जोन से जुड़ा है रेलवे का प्रोजेक्ट BROKERAGE CALLS BUY लक्ष्य ₹14065</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1322" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1323" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="E1323" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1323" t="inlineStr"/>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>खबरों वाले शेयर GE Shipping 1353.60 ▲ 3.68% बायबैक प्राइस ₹1530/शेयर</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1323" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1324" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1324" t="inlineStr"/>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>अभिनाश गोरेश्कर की पसंद Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1324" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1325" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>106</v>
+      </c>
+      <c r="G1325" t="inlineStr"/>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>LONG-TERM CALL Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1325" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1326" t="n">
+        <v>1695.2</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G1326" t="inlineStr"/>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>POSITIONAL C Adani Ports BUY TARGET 1750 Adani Ports 1706.50</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1326" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-09-04 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1327" t="n">
+        <v>1695.2</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>1750</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G1327" t="inlineStr"/>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>POSITIONAL CALL Adani Ports BUY TARGET 1750 STOP LOSS 1690 Adani Ports 1706.50 2.02%</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1327" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1237"/>
+  <autoFilter ref="A1:J1327"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
